--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -199,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="137">
+  <borders count="146">
     <border>
       <left/>
       <right/>
@@ -1665,11 +1665,117 @@
         <color rgb="000078D4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="306">
+  <cellXfs count="368">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2433,6 +2539,194 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="137" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="140" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="138" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="142" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="144" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="36" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="135" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="135" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="136" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="32" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="118" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="143" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="139" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2533,6 +2827,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2563,6 +2860,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2593,6 +2893,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2623,6 +2926,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2981,346 +3287,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="216" t="n"/>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="218" t="n"/>
+      <c r="A1" s="306" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="219" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="217" t="n"/>
-      <c r="N1" s="217" t="n"/>
-      <c r="O1" s="217" t="n"/>
-      <c r="P1" s="217" t="n"/>
-      <c r="Q1" s="217" t="n"/>
-      <c r="R1" s="217" t="n"/>
-      <c r="S1" s="217" t="n"/>
-      <c r="T1" s="217" t="n"/>
-      <c r="U1" s="217" t="n"/>
-      <c r="V1" s="217" t="n"/>
-      <c r="W1" s="217" t="n"/>
-      <c r="X1" s="217" t="n"/>
-      <c r="Y1" s="217" t="n"/>
-      <c r="Z1" s="217" t="n"/>
-      <c r="AA1" s="217" t="n"/>
-      <c r="AB1" s="217" t="n"/>
-      <c r="AC1" s="217" t="n"/>
-      <c r="AD1" s="217" t="n"/>
-      <c r="AE1" s="217" t="n"/>
-      <c r="AF1" s="217" t="n"/>
-      <c r="AG1" s="217" t="n"/>
-      <c r="AH1" s="217" t="n"/>
-      <c r="AI1" s="217" t="n"/>
-      <c r="AJ1" s="217" t="n"/>
-      <c r="AK1" s="217" t="n"/>
-      <c r="AL1" s="217" t="n"/>
-      <c r="AM1" s="217" t="n"/>
-      <c r="AN1" s="217" t="n"/>
-      <c r="AO1" s="217" t="n"/>
-      <c r="AP1" s="217" t="n"/>
-      <c r="AQ1" s="220" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="217" t="n"/>
-      <c r="AS1" s="217" t="n"/>
-      <c r="AT1" s="217" t="n"/>
-      <c r="AU1" s="217" t="n"/>
-      <c r="AV1" s="221" t="n"/>
-      <c r="AW1" s="222" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="308" t="n"/>
+      <c r="AW1" s="309" t="inlineStr">
         <is>
           <t>FRM-125</t>
         </is>
       </c>
-      <c r="AX1" s="217" t="n"/>
-      <c r="AY1" s="217" t="n"/>
-      <c r="AZ1" s="217" t="n"/>
-      <c r="BA1" s="217" t="n"/>
-      <c r="BB1" s="217" t="n"/>
-      <c r="BC1" s="217" t="n"/>
-      <c r="BD1" s="218" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="223" t="n"/>
-      <c r="B2" s="224" t="n"/>
-      <c r="C2" s="224" t="n"/>
-      <c r="D2" s="224" t="n"/>
-      <c r="E2" s="224" t="n"/>
-      <c r="F2" s="224" t="n"/>
-      <c r="G2" s="224" t="n"/>
-      <c r="H2" s="224" t="n"/>
-      <c r="I2" s="224" t="n"/>
-      <c r="J2" s="224" t="n"/>
-      <c r="K2" s="225" t="n"/>
-      <c r="L2" s="223" t="n"/>
-      <c r="M2" s="224" t="n"/>
-      <c r="N2" s="224" t="n"/>
-      <c r="O2" s="224" t="n"/>
-      <c r="P2" s="224" t="n"/>
-      <c r="Q2" s="224" t="n"/>
-      <c r="R2" s="224" t="n"/>
-      <c r="S2" s="224" t="n"/>
-      <c r="T2" s="224" t="n"/>
-      <c r="U2" s="224" t="n"/>
-      <c r="V2" s="224" t="n"/>
-      <c r="W2" s="224" t="n"/>
-      <c r="X2" s="224" t="n"/>
-      <c r="Y2" s="224" t="n"/>
-      <c r="Z2" s="224" t="n"/>
-      <c r="AA2" s="224" t="n"/>
-      <c r="AB2" s="224" t="n"/>
-      <c r="AC2" s="224" t="n"/>
-      <c r="AD2" s="224" t="n"/>
-      <c r="AE2" s="224" t="n"/>
-      <c r="AF2" s="224" t="n"/>
-      <c r="AG2" s="224" t="n"/>
-      <c r="AH2" s="224" t="n"/>
-      <c r="AI2" s="224" t="n"/>
-      <c r="AJ2" s="224" t="n"/>
-      <c r="AK2" s="224" t="n"/>
-      <c r="AL2" s="224" t="n"/>
-      <c r="AM2" s="224" t="n"/>
-      <c r="AN2" s="224" t="n"/>
-      <c r="AO2" s="224" t="n"/>
-      <c r="AP2" s="224" t="n"/>
-      <c r="AQ2" s="226" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="AQ2" s="310" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="227" t="n"/>
-      <c r="AS2" s="227" t="n"/>
-      <c r="AT2" s="227" t="n"/>
-      <c r="AU2" s="227" t="n"/>
-      <c r="AV2" s="228" t="n"/>
-      <c r="AW2" s="229" t="inlineStr">
+      <c r="AR2" s="311" t="n"/>
+      <c r="AS2" s="311" t="n"/>
+      <c r="AT2" s="311" t="n"/>
+      <c r="AU2" s="311" t="n"/>
+      <c r="AV2" s="312" t="n"/>
+      <c r="AW2" s="313" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="227" t="n"/>
-      <c r="AY2" s="227" t="n"/>
-      <c r="AZ2" s="227" t="n"/>
-      <c r="BA2" s="227" t="n"/>
-      <c r="BB2" s="227" t="n"/>
-      <c r="BC2" s="227" t="n"/>
-      <c r="BD2" s="230" t="n"/>
+      <c r="AX2" s="311" t="n"/>
+      <c r="AY2" s="311" t="n"/>
+      <c r="AZ2" s="311" t="n"/>
+      <c r="BA2" s="311" t="n"/>
+      <c r="BB2" s="311" t="n"/>
+      <c r="BC2" s="311" t="n"/>
+      <c r="BD2" s="314" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="223" t="n"/>
-      <c r="B3" s="224" t="n"/>
-      <c r="C3" s="224" t="n"/>
-      <c r="D3" s="224" t="n"/>
-      <c r="E3" s="224" t="n"/>
-      <c r="F3" s="224" t="n"/>
-      <c r="G3" s="224" t="n"/>
-      <c r="H3" s="224" t="n"/>
-      <c r="I3" s="224" t="n"/>
-      <c r="J3" s="224" t="n"/>
-      <c r="K3" s="225" t="n"/>
-      <c r="L3" s="223" t="n"/>
-      <c r="M3" s="224" t="n"/>
-      <c r="N3" s="224" t="n"/>
-      <c r="O3" s="224" t="n"/>
-      <c r="P3" s="224" t="n"/>
-      <c r="Q3" s="224" t="n"/>
-      <c r="R3" s="224" t="n"/>
-      <c r="S3" s="224" t="n"/>
-      <c r="T3" s="224" t="n"/>
-      <c r="U3" s="224" t="n"/>
-      <c r="V3" s="224" t="n"/>
-      <c r="W3" s="224" t="n"/>
-      <c r="X3" s="224" t="n"/>
-      <c r="Y3" s="224" t="n"/>
-      <c r="Z3" s="224" t="n"/>
-      <c r="AA3" s="224" t="n"/>
-      <c r="AB3" s="224" t="n"/>
-      <c r="AC3" s="224" t="n"/>
-      <c r="AD3" s="224" t="n"/>
-      <c r="AE3" s="224" t="n"/>
-      <c r="AF3" s="224" t="n"/>
-      <c r="AG3" s="224" t="n"/>
-      <c r="AH3" s="224" t="n"/>
-      <c r="AI3" s="224" t="n"/>
-      <c r="AJ3" s="224" t="n"/>
-      <c r="AK3" s="224" t="n"/>
-      <c r="AL3" s="224" t="n"/>
-      <c r="AM3" s="224" t="n"/>
-      <c r="AN3" s="224" t="n"/>
-      <c r="AO3" s="224" t="n"/>
-      <c r="AP3" s="224" t="n"/>
-      <c r="AQ3" s="226" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="AQ3" s="310" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="227" t="n"/>
-      <c r="AS3" s="227" t="n"/>
-      <c r="AT3" s="227" t="n"/>
-      <c r="AU3" s="227" t="n"/>
-      <c r="AV3" s="228" t="n"/>
-      <c r="AW3" s="229" t="inlineStr">
+      <c r="AR3" s="311" t="n"/>
+      <c r="AS3" s="311" t="n"/>
+      <c r="AT3" s="311" t="n"/>
+      <c r="AU3" s="311" t="n"/>
+      <c r="AV3" s="312" t="n"/>
+      <c r="AW3" s="313" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="227" t="n"/>
-      <c r="AY3" s="227" t="n"/>
-      <c r="AZ3" s="227" t="n"/>
-      <c r="BA3" s="227" t="n"/>
-      <c r="BB3" s="227" t="n"/>
-      <c r="BC3" s="227" t="n"/>
-      <c r="BD3" s="230" t="n"/>
+      <c r="AX3" s="311" t="n"/>
+      <c r="AY3" s="311" t="n"/>
+      <c r="AZ3" s="311" t="n"/>
+      <c r="BA3" s="311" t="n"/>
+      <c r="BB3" s="311" t="n"/>
+      <c r="BC3" s="311" t="n"/>
+      <c r="BD3" s="314" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="223" t="n"/>
-      <c r="B4" s="224" t="n"/>
-      <c r="C4" s="224" t="n"/>
-      <c r="D4" s="224" t="n"/>
-      <c r="E4" s="224" t="n"/>
-      <c r="F4" s="224" t="n"/>
-      <c r="G4" s="224" t="n"/>
-      <c r="H4" s="224" t="n"/>
-      <c r="I4" s="224" t="n"/>
-      <c r="J4" s="224" t="n"/>
-      <c r="K4" s="225" t="n"/>
+      <c r="A4" s="9" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="231" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="224" t="n"/>
-      <c r="N4" s="224" t="n"/>
-      <c r="O4" s="224" t="n"/>
-      <c r="P4" s="224" t="n"/>
-      <c r="Q4" s="224" t="n"/>
-      <c r="R4" s="224" t="n"/>
-      <c r="S4" s="224" t="n"/>
-      <c r="T4" s="224" t="n"/>
-      <c r="U4" s="224" t="n"/>
-      <c r="V4" s="224" t="n"/>
-      <c r="W4" s="224" t="n"/>
-      <c r="X4" s="224" t="n"/>
-      <c r="Y4" s="224" t="n"/>
-      <c r="Z4" s="224" t="n"/>
-      <c r="AA4" s="224" t="n"/>
-      <c r="AB4" s="224" t="n"/>
-      <c r="AC4" s="224" t="n"/>
-      <c r="AD4" s="224" t="n"/>
-      <c r="AE4" s="224" t="n"/>
-      <c r="AF4" s="224" t="n"/>
-      <c r="AG4" s="224" t="n"/>
-      <c r="AH4" s="224" t="n"/>
-      <c r="AI4" s="224" t="n"/>
-      <c r="AJ4" s="224" t="n"/>
-      <c r="AK4" s="224" t="n"/>
-      <c r="AL4" s="224" t="n"/>
-      <c r="AM4" s="224" t="n"/>
-      <c r="AN4" s="224" t="n"/>
-      <c r="AO4" s="224" t="n"/>
-      <c r="AP4" s="224" t="n"/>
-      <c r="AQ4" s="226" t="inlineStr">
+      <c r="AQ4" s="310" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="227" t="n"/>
-      <c r="AS4" s="227" t="n"/>
-      <c r="AT4" s="227" t="n"/>
-      <c r="AU4" s="227" t="n"/>
-      <c r="AV4" s="228" t="n"/>
-      <c r="AW4" s="229" t="inlineStr">
+      <c r="AR4" s="311" t="n"/>
+      <c r="AS4" s="311" t="n"/>
+      <c r="AT4" s="311" t="n"/>
+      <c r="AU4" s="311" t="n"/>
+      <c r="AV4" s="312" t="n"/>
+      <c r="AW4" s="313" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="227" t="n"/>
-      <c r="AY4" s="227" t="n"/>
-      <c r="AZ4" s="227" t="n"/>
-      <c r="BA4" s="227" t="n"/>
-      <c r="BB4" s="227" t="n"/>
-      <c r="BC4" s="227" t="n"/>
-      <c r="BD4" s="230" t="n"/>
+      <c r="AX4" s="311" t="n"/>
+      <c r="AY4" s="311" t="n"/>
+      <c r="AZ4" s="311" t="n"/>
+      <c r="BA4" s="311" t="n"/>
+      <c r="BB4" s="311" t="n"/>
+      <c r="BC4" s="311" t="n"/>
+      <c r="BD4" s="314" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="232" t="n"/>
-      <c r="B5" s="233" t="n"/>
-      <c r="C5" s="233" t="n"/>
-      <c r="D5" s="233" t="n"/>
-      <c r="E5" s="233" t="n"/>
-      <c r="F5" s="233" t="n"/>
-      <c r="G5" s="233" t="n"/>
-      <c r="H5" s="233" t="n"/>
-      <c r="I5" s="233" t="n"/>
-      <c r="J5" s="233" t="n"/>
-      <c r="K5" s="234" t="n"/>
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n"/>
       <c r="L5" s="42" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="233" t="n"/>
-      <c r="N5" s="233" t="n"/>
-      <c r="O5" s="233" t="n"/>
-      <c r="P5" s="233" t="n"/>
-      <c r="Q5" s="233" t="n"/>
-      <c r="R5" s="233" t="n"/>
-      <c r="S5" s="233" t="n"/>
-      <c r="T5" s="233" t="n"/>
-      <c r="U5" s="233" t="n"/>
-      <c r="V5" s="233" t="n"/>
-      <c r="W5" s="233" t="n"/>
-      <c r="X5" s="233" t="n"/>
-      <c r="Y5" s="233" t="n"/>
-      <c r="Z5" s="233" t="n"/>
-      <c r="AA5" s="233" t="n"/>
-      <c r="AB5" s="233" t="n"/>
-      <c r="AC5" s="233" t="n"/>
-      <c r="AD5" s="233" t="n"/>
-      <c r="AE5" s="233" t="n"/>
-      <c r="AF5" s="233" t="n"/>
-      <c r="AG5" s="233" t="n"/>
-      <c r="AH5" s="233" t="n"/>
-      <c r="AI5" s="233" t="n"/>
-      <c r="AJ5" s="233" t="n"/>
-      <c r="AK5" s="233" t="n"/>
-      <c r="AL5" s="233" t="n"/>
-      <c r="AM5" s="233" t="n"/>
-      <c r="AN5" s="233" t="n"/>
-      <c r="AO5" s="233" t="n"/>
-      <c r="AP5" s="233" t="n"/>
-      <c r="AQ5" s="235" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="13" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
+      <c r="AP5" s="13" t="n"/>
+      <c r="AQ5" s="315" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="236" t="n"/>
-      <c r="AS5" s="236" t="n"/>
-      <c r="AT5" s="236" t="n"/>
-      <c r="AU5" s="236" t="n"/>
-      <c r="AV5" s="237" t="n"/>
-      <c r="AW5" s="238" t="inlineStr">
+      <c r="AR5" s="316" t="n"/>
+      <c r="AS5" s="316" t="n"/>
+      <c r="AT5" s="316" t="n"/>
+      <c r="AU5" s="316" t="n"/>
+      <c r="AV5" s="317" t="n"/>
+      <c r="AW5" s="318" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="236" t="n"/>
-      <c r="AY5" s="236" t="n"/>
-      <c r="AZ5" s="236" t="n"/>
-      <c r="BA5" s="236" t="n"/>
-      <c r="BB5" s="236" t="n"/>
-      <c r="BC5" s="236" t="n"/>
-      <c r="BD5" s="239" t="n"/>
+      <c r="AX5" s="316" t="n"/>
+      <c r="AY5" s="316" t="n"/>
+      <c r="AZ5" s="316" t="n"/>
+      <c r="BA5" s="316" t="n"/>
+      <c r="BB5" s="316" t="n"/>
+      <c r="BC5" s="316" t="n"/>
+      <c r="BD5" s="319" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="240" t="n"/>
@@ -3381,1875 +3570,1875 @@
       <c r="BD6" s="240" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="241" t="inlineStr">
+      <c r="A7" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="242" t="n"/>
-      <c r="C7" s="242" t="n"/>
-      <c r="D7" s="242" t="n"/>
-      <c r="E7" s="242" t="n"/>
-      <c r="F7" s="242" t="n"/>
-      <c r="G7" s="242" t="n"/>
-      <c r="H7" s="242" t="n"/>
-      <c r="I7" s="242" t="n"/>
-      <c r="J7" s="242" t="n"/>
-      <c r="K7" s="242" t="n"/>
-      <c r="L7" s="242" t="n"/>
-      <c r="M7" s="242" t="n"/>
-      <c r="N7" s="242" t="n"/>
-      <c r="O7" s="242" t="n"/>
-      <c r="P7" s="242" t="n"/>
-      <c r="Q7" s="242" t="n"/>
-      <c r="R7" s="242" t="n"/>
-      <c r="S7" s="242" t="n"/>
-      <c r="T7" s="242" t="n"/>
-      <c r="U7" s="242" t="n"/>
-      <c r="V7" s="242" t="n"/>
-      <c r="W7" s="242" t="n"/>
-      <c r="X7" s="242" t="n"/>
-      <c r="Y7" s="242" t="n"/>
-      <c r="Z7" s="242" t="n"/>
-      <c r="AA7" s="242" t="n"/>
-      <c r="AB7" s="242" t="n"/>
-      <c r="AC7" s="242" t="n"/>
-      <c r="AD7" s="242" t="n"/>
-      <c r="AE7" s="242" t="n"/>
-      <c r="AF7" s="242" t="n"/>
-      <c r="AG7" s="242" t="n"/>
-      <c r="AH7" s="242" t="n"/>
-      <c r="AI7" s="242" t="n"/>
-      <c r="AJ7" s="242" t="n"/>
-      <c r="AK7" s="242" t="n"/>
-      <c r="AL7" s="242" t="n"/>
-      <c r="AM7" s="242" t="n"/>
-      <c r="AN7" s="242" t="n"/>
-      <c r="AO7" s="242" t="n"/>
-      <c r="AP7" s="242" t="n"/>
-      <c r="AQ7" s="242" t="n"/>
-      <c r="AR7" s="242" t="n"/>
-      <c r="AS7" s="242" t="n"/>
-      <c r="AT7" s="242" t="n"/>
-      <c r="AU7" s="242" t="n"/>
-      <c r="AV7" s="242" t="n"/>
-      <c r="AW7" s="242" t="n"/>
-      <c r="AX7" s="242" t="n"/>
-      <c r="AY7" s="242" t="n"/>
-      <c r="AZ7" s="242" t="n"/>
-      <c r="BA7" s="242" t="n"/>
-      <c r="BB7" s="242" t="n"/>
-      <c r="BC7" s="242" t="n"/>
-      <c r="BD7" s="243" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
+      <c r="AC7" s="6" t="n"/>
+      <c r="AD7" s="6" t="n"/>
+      <c r="AE7" s="6" t="n"/>
+      <c r="AF7" s="6" t="n"/>
+      <c r="AG7" s="6" t="n"/>
+      <c r="AH7" s="6" t="n"/>
+      <c r="AI7" s="6" t="n"/>
+      <c r="AJ7" s="6" t="n"/>
+      <c r="AK7" s="6" t="n"/>
+      <c r="AL7" s="6" t="n"/>
+      <c r="AM7" s="6" t="n"/>
+      <c r="AN7" s="6" t="n"/>
+      <c r="AO7" s="6" t="n"/>
+      <c r="AP7" s="6" t="n"/>
+      <c r="AQ7" s="6" t="n"/>
+      <c r="AR7" s="6" t="n"/>
+      <c r="AS7" s="6" t="n"/>
+      <c r="AT7" s="6" t="n"/>
+      <c r="AU7" s="6" t="n"/>
+      <c r="AV7" s="6" t="n"/>
+      <c r="AW7" s="6" t="n"/>
+      <c r="AX7" s="6" t="n"/>
+      <c r="AY7" s="6" t="n"/>
+      <c r="AZ7" s="6" t="n"/>
+      <c r="BA7" s="6" t="n"/>
+      <c r="BB7" s="6" t="n"/>
+      <c r="BC7" s="6" t="n"/>
+      <c r="BD7" s="7" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="244" t="inlineStr">
+      <c r="A8" s="321" t="inlineStr">
         <is>
           <t>CSR Register ID</t>
         </is>
       </c>
-      <c r="B8" s="245" t="n"/>
-      <c r="C8" s="245" t="n"/>
-      <c r="D8" s="245" t="n"/>
-      <c r="E8" s="245" t="n"/>
-      <c r="F8" s="245" t="n"/>
-      <c r="G8" s="245" t="n"/>
-      <c r="H8" s="245" t="n"/>
-      <c r="I8" s="245" t="n"/>
-      <c r="J8" s="246" t="n"/>
-      <c r="K8" s="247" t="n"/>
-      <c r="L8" s="248" t="n"/>
-      <c r="M8" s="248" t="n"/>
-      <c r="N8" s="248" t="n"/>
-      <c r="O8" s="248" t="n"/>
-      <c r="P8" s="248" t="n"/>
-      <c r="Q8" s="248" t="n"/>
-      <c r="R8" s="248" t="n"/>
-      <c r="S8" s="248" t="n"/>
-      <c r="T8" s="248" t="n"/>
-      <c r="U8" s="248" t="n"/>
-      <c r="V8" s="248" t="n"/>
-      <c r="W8" s="248" t="n"/>
-      <c r="X8" s="248" t="n"/>
-      <c r="Y8" s="248" t="n"/>
-      <c r="Z8" s="248" t="n"/>
-      <c r="AA8" s="248" t="n"/>
-      <c r="AB8" s="249" t="n"/>
-      <c r="AC8" s="250" t="inlineStr">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="322" t="n"/>
+      <c r="L8" s="323" t="n"/>
+      <c r="M8" s="323" t="n"/>
+      <c r="N8" s="323" t="n"/>
+      <c r="O8" s="323" t="n"/>
+      <c r="P8" s="323" t="n"/>
+      <c r="Q8" s="323" t="n"/>
+      <c r="R8" s="323" t="n"/>
+      <c r="S8" s="323" t="n"/>
+      <c r="T8" s="323" t="n"/>
+      <c r="U8" s="323" t="n"/>
+      <c r="V8" s="323" t="n"/>
+      <c r="W8" s="323" t="n"/>
+      <c r="X8" s="323" t="n"/>
+      <c r="Y8" s="323" t="n"/>
+      <c r="Z8" s="323" t="n"/>
+      <c r="AA8" s="323" t="n"/>
+      <c r="AB8" s="324" t="n"/>
+      <c r="AC8" s="325" t="inlineStr">
         <is>
           <t>Register Status</t>
         </is>
       </c>
-      <c r="AD8" s="245" t="n"/>
-      <c r="AE8" s="245" t="n"/>
-      <c r="AF8" s="245" t="n"/>
-      <c r="AG8" s="245" t="n"/>
-      <c r="AH8" s="245" t="n"/>
-      <c r="AI8" s="245" t="n"/>
-      <c r="AJ8" s="245" t="n"/>
-      <c r="AK8" s="245" t="n"/>
-      <c r="AL8" s="246" t="n"/>
-      <c r="AM8" s="247" t="n"/>
-      <c r="AN8" s="248" t="n"/>
-      <c r="AO8" s="248" t="n"/>
-      <c r="AP8" s="248" t="n"/>
-      <c r="AQ8" s="248" t="n"/>
-      <c r="AR8" s="248" t="n"/>
-      <c r="AS8" s="248" t="n"/>
-      <c r="AT8" s="248" t="n"/>
-      <c r="AU8" s="248" t="n"/>
-      <c r="AV8" s="248" t="n"/>
-      <c r="AW8" s="248" t="n"/>
-      <c r="AX8" s="248" t="n"/>
-      <c r="AY8" s="248" t="n"/>
-      <c r="AZ8" s="248" t="n"/>
-      <c r="BA8" s="248" t="n"/>
-      <c r="BB8" s="248" t="n"/>
-      <c r="BC8" s="248" t="n"/>
-      <c r="BD8" s="251" t="n"/>
+      <c r="AD8" s="31" t="n"/>
+      <c r="AE8" s="31" t="n"/>
+      <c r="AF8" s="31" t="n"/>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="31" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="31" t="n"/>
+      <c r="AL8" s="32" t="n"/>
+      <c r="AM8" s="326" t="n"/>
+      <c r="AN8" s="323" t="n"/>
+      <c r="AO8" s="323" t="n"/>
+      <c r="AP8" s="323" t="n"/>
+      <c r="AQ8" s="323" t="n"/>
+      <c r="AR8" s="323" t="n"/>
+      <c r="AS8" s="323" t="n"/>
+      <c r="AT8" s="323" t="n"/>
+      <c r="AU8" s="323" t="n"/>
+      <c r="AV8" s="323" t="n"/>
+      <c r="AW8" s="323" t="n"/>
+      <c r="AX8" s="323" t="n"/>
+      <c r="AY8" s="323" t="n"/>
+      <c r="AZ8" s="323" t="n"/>
+      <c r="BA8" s="323" t="n"/>
+      <c r="BB8" s="323" t="n"/>
+      <c r="BC8" s="323" t="n"/>
+      <c r="BD8" s="327" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="252" t="inlineStr">
+      <c r="A9" s="328" t="inlineStr">
         <is>
           <t>Customer / Scope</t>
         </is>
       </c>
-      <c r="B9" s="253" t="n"/>
-      <c r="C9" s="253" t="n"/>
-      <c r="D9" s="253" t="n"/>
-      <c r="E9" s="253" t="n"/>
-      <c r="F9" s="253" t="n"/>
-      <c r="G9" s="253" t="n"/>
-      <c r="H9" s="253" t="n"/>
-      <c r="I9" s="253" t="n"/>
-      <c r="J9" s="254" t="n"/>
-      <c r="K9" s="255" t="n"/>
-      <c r="L9" s="256" t="n"/>
-      <c r="M9" s="256" t="n"/>
-      <c r="N9" s="256" t="n"/>
-      <c r="O9" s="256" t="n"/>
-      <c r="P9" s="256" t="n"/>
-      <c r="Q9" s="256" t="n"/>
-      <c r="R9" s="256" t="n"/>
-      <c r="S9" s="256" t="n"/>
-      <c r="T9" s="256" t="n"/>
-      <c r="U9" s="256" t="n"/>
-      <c r="V9" s="256" t="n"/>
-      <c r="W9" s="256" t="n"/>
-      <c r="X9" s="256" t="n"/>
-      <c r="Y9" s="256" t="n"/>
-      <c r="Z9" s="256" t="n"/>
-      <c r="AA9" s="256" t="n"/>
-      <c r="AB9" s="257" t="n"/>
-      <c r="AC9" s="258" t="inlineStr">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="37" t="n"/>
+      <c r="K9" s="329" t="n"/>
+      <c r="L9" s="330" t="n"/>
+      <c r="M9" s="330" t="n"/>
+      <c r="N9" s="330" t="n"/>
+      <c r="O9" s="330" t="n"/>
+      <c r="P9" s="330" t="n"/>
+      <c r="Q9" s="330" t="n"/>
+      <c r="R9" s="330" t="n"/>
+      <c r="S9" s="330" t="n"/>
+      <c r="T9" s="330" t="n"/>
+      <c r="U9" s="330" t="n"/>
+      <c r="V9" s="330" t="n"/>
+      <c r="W9" s="330" t="n"/>
+      <c r="X9" s="330" t="n"/>
+      <c r="Y9" s="330" t="n"/>
+      <c r="Z9" s="330" t="n"/>
+      <c r="AA9" s="330" t="n"/>
+      <c r="AB9" s="331" t="n"/>
+      <c r="AC9" s="332" t="inlineStr">
         <is>
           <t>Process Owner</t>
         </is>
       </c>
-      <c r="AD9" s="253" t="n"/>
-      <c r="AE9" s="253" t="n"/>
-      <c r="AF9" s="253" t="n"/>
-      <c r="AG9" s="253" t="n"/>
-      <c r="AH9" s="253" t="n"/>
-      <c r="AI9" s="253" t="n"/>
-      <c r="AJ9" s="253" t="n"/>
-      <c r="AK9" s="253" t="n"/>
-      <c r="AL9" s="254" t="n"/>
-      <c r="AM9" s="255" t="n"/>
-      <c r="AN9" s="256" t="n"/>
-      <c r="AO9" s="256" t="n"/>
-      <c r="AP9" s="256" t="n"/>
-      <c r="AQ9" s="256" t="n"/>
-      <c r="AR9" s="256" t="n"/>
-      <c r="AS9" s="256" t="n"/>
-      <c r="AT9" s="256" t="n"/>
-      <c r="AU9" s="256" t="n"/>
-      <c r="AV9" s="256" t="n"/>
-      <c r="AW9" s="256" t="n"/>
-      <c r="AX9" s="256" t="n"/>
-      <c r="AY9" s="256" t="n"/>
-      <c r="AZ9" s="256" t="n"/>
-      <c r="BA9" s="256" t="n"/>
-      <c r="BB9" s="256" t="n"/>
-      <c r="BC9" s="256" t="n"/>
-      <c r="BD9" s="259" t="n"/>
+      <c r="AD9" s="36" t="n"/>
+      <c r="AE9" s="36" t="n"/>
+      <c r="AF9" s="36" t="n"/>
+      <c r="AG9" s="36" t="n"/>
+      <c r="AH9" s="36" t="n"/>
+      <c r="AI9" s="36" t="n"/>
+      <c r="AJ9" s="36" t="n"/>
+      <c r="AK9" s="36" t="n"/>
+      <c r="AL9" s="37" t="n"/>
+      <c r="AM9" s="333" t="n"/>
+      <c r="AN9" s="330" t="n"/>
+      <c r="AO9" s="330" t="n"/>
+      <c r="AP9" s="330" t="n"/>
+      <c r="AQ9" s="330" t="n"/>
+      <c r="AR9" s="330" t="n"/>
+      <c r="AS9" s="330" t="n"/>
+      <c r="AT9" s="330" t="n"/>
+      <c r="AU9" s="330" t="n"/>
+      <c r="AV9" s="330" t="n"/>
+      <c r="AW9" s="330" t="n"/>
+      <c r="AX9" s="330" t="n"/>
+      <c r="AY9" s="330" t="n"/>
+      <c r="AZ9" s="330" t="n"/>
+      <c r="BA9" s="330" t="n"/>
+      <c r="BB9" s="330" t="n"/>
+      <c r="BC9" s="330" t="n"/>
+      <c r="BD9" s="334" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="252" t="inlineStr">
+      <c r="A10" s="328" t="inlineStr">
         <is>
           <t>Review Period</t>
         </is>
       </c>
-      <c r="B10" s="253" t="n"/>
-      <c r="C10" s="253" t="n"/>
-      <c r="D10" s="253" t="n"/>
-      <c r="E10" s="253" t="n"/>
-      <c r="F10" s="253" t="n"/>
-      <c r="G10" s="253" t="n"/>
-      <c r="H10" s="253" t="n"/>
-      <c r="I10" s="253" t="n"/>
-      <c r="J10" s="254" t="n"/>
-      <c r="K10" s="255" t="n"/>
-      <c r="L10" s="256" t="n"/>
-      <c r="M10" s="256" t="n"/>
-      <c r="N10" s="256" t="n"/>
-      <c r="O10" s="256" t="n"/>
-      <c r="P10" s="256" t="n"/>
-      <c r="Q10" s="256" t="n"/>
-      <c r="R10" s="256" t="n"/>
-      <c r="S10" s="256" t="n"/>
-      <c r="T10" s="256" t="n"/>
-      <c r="U10" s="256" t="n"/>
-      <c r="V10" s="256" t="n"/>
-      <c r="W10" s="256" t="n"/>
-      <c r="X10" s="256" t="n"/>
-      <c r="Y10" s="256" t="n"/>
-      <c r="Z10" s="256" t="n"/>
-      <c r="AA10" s="256" t="n"/>
-      <c r="AB10" s="257" t="n"/>
-      <c r="AC10" s="258" t="inlineStr">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n"/>
+      <c r="D10" s="36" t="n"/>
+      <c r="E10" s="36" t="n"/>
+      <c r="F10" s="36" t="n"/>
+      <c r="G10" s="36" t="n"/>
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n"/>
+      <c r="J10" s="37" t="n"/>
+      <c r="K10" s="329" t="n"/>
+      <c r="L10" s="330" t="n"/>
+      <c r="M10" s="330" t="n"/>
+      <c r="N10" s="330" t="n"/>
+      <c r="O10" s="330" t="n"/>
+      <c r="P10" s="330" t="n"/>
+      <c r="Q10" s="330" t="n"/>
+      <c r="R10" s="330" t="n"/>
+      <c r="S10" s="330" t="n"/>
+      <c r="T10" s="330" t="n"/>
+      <c r="U10" s="330" t="n"/>
+      <c r="V10" s="330" t="n"/>
+      <c r="W10" s="330" t="n"/>
+      <c r="X10" s="330" t="n"/>
+      <c r="Y10" s="330" t="n"/>
+      <c r="Z10" s="330" t="n"/>
+      <c r="AA10" s="330" t="n"/>
+      <c r="AB10" s="331" t="n"/>
+      <c r="AC10" s="332" t="inlineStr">
         <is>
           <t>Prepared Date</t>
         </is>
       </c>
-      <c r="AD10" s="253" t="n"/>
-      <c r="AE10" s="253" t="n"/>
-      <c r="AF10" s="253" t="n"/>
-      <c r="AG10" s="253" t="n"/>
-      <c r="AH10" s="253" t="n"/>
-      <c r="AI10" s="253" t="n"/>
-      <c r="AJ10" s="253" t="n"/>
-      <c r="AK10" s="253" t="n"/>
-      <c r="AL10" s="254" t="n"/>
-      <c r="AM10" s="255" t="n"/>
-      <c r="AN10" s="256" t="n"/>
-      <c r="AO10" s="256" t="n"/>
-      <c r="AP10" s="256" t="n"/>
-      <c r="AQ10" s="256" t="n"/>
-      <c r="AR10" s="256" t="n"/>
-      <c r="AS10" s="256" t="n"/>
-      <c r="AT10" s="256" t="n"/>
-      <c r="AU10" s="256" t="n"/>
-      <c r="AV10" s="256" t="n"/>
-      <c r="AW10" s="256" t="n"/>
-      <c r="AX10" s="256" t="n"/>
-      <c r="AY10" s="256" t="n"/>
-      <c r="AZ10" s="256" t="n"/>
-      <c r="BA10" s="256" t="n"/>
-      <c r="BB10" s="256" t="n"/>
-      <c r="BC10" s="256" t="n"/>
-      <c r="BD10" s="259" t="n"/>
+      <c r="AD10" s="36" t="n"/>
+      <c r="AE10" s="36" t="n"/>
+      <c r="AF10" s="36" t="n"/>
+      <c r="AG10" s="36" t="n"/>
+      <c r="AH10" s="36" t="n"/>
+      <c r="AI10" s="36" t="n"/>
+      <c r="AJ10" s="36" t="n"/>
+      <c r="AK10" s="36" t="n"/>
+      <c r="AL10" s="37" t="n"/>
+      <c r="AM10" s="333" t="n"/>
+      <c r="AN10" s="330" t="n"/>
+      <c r="AO10" s="330" t="n"/>
+      <c r="AP10" s="330" t="n"/>
+      <c r="AQ10" s="330" t="n"/>
+      <c r="AR10" s="330" t="n"/>
+      <c r="AS10" s="330" t="n"/>
+      <c r="AT10" s="330" t="n"/>
+      <c r="AU10" s="330" t="n"/>
+      <c r="AV10" s="330" t="n"/>
+      <c r="AW10" s="330" t="n"/>
+      <c r="AX10" s="330" t="n"/>
+      <c r="AY10" s="330" t="n"/>
+      <c r="AZ10" s="330" t="n"/>
+      <c r="BA10" s="330" t="n"/>
+      <c r="BB10" s="330" t="n"/>
+      <c r="BC10" s="330" t="n"/>
+      <c r="BD10" s="334" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="260" t="inlineStr">
+      <c r="A11" s="335" t="inlineStr">
         <is>
           <t>Evidence Folder Ref</t>
         </is>
       </c>
-      <c r="B11" s="233" t="n"/>
-      <c r="C11" s="233" t="n"/>
-      <c r="D11" s="233" t="n"/>
-      <c r="E11" s="233" t="n"/>
-      <c r="F11" s="233" t="n"/>
-      <c r="G11" s="233" t="n"/>
-      <c r="H11" s="233" t="n"/>
-      <c r="I11" s="233" t="n"/>
-      <c r="J11" s="261" t="n"/>
-      <c r="K11" s="262" t="n"/>
-      <c r="L11" s="263" t="n"/>
-      <c r="M11" s="263" t="n"/>
-      <c r="N11" s="263" t="n"/>
-      <c r="O11" s="263" t="n"/>
-      <c r="P11" s="263" t="n"/>
-      <c r="Q11" s="263" t="n"/>
-      <c r="R11" s="263" t="n"/>
-      <c r="S11" s="263" t="n"/>
-      <c r="T11" s="263" t="n"/>
-      <c r="U11" s="263" t="n"/>
-      <c r="V11" s="263" t="n"/>
-      <c r="W11" s="263" t="n"/>
-      <c r="X11" s="263" t="n"/>
-      <c r="Y11" s="263" t="n"/>
-      <c r="Z11" s="263" t="n"/>
-      <c r="AA11" s="263" t="n"/>
-      <c r="AB11" s="264" t="n"/>
-      <c r="AC11" s="265" t="inlineStr">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="13" t="n"/>
+      <c r="J11" s="44" t="n"/>
+      <c r="K11" s="336" t="n"/>
+      <c r="L11" s="337" t="n"/>
+      <c r="M11" s="337" t="n"/>
+      <c r="N11" s="337" t="n"/>
+      <c r="O11" s="337" t="n"/>
+      <c r="P11" s="337" t="n"/>
+      <c r="Q11" s="337" t="n"/>
+      <c r="R11" s="337" t="n"/>
+      <c r="S11" s="337" t="n"/>
+      <c r="T11" s="337" t="n"/>
+      <c r="U11" s="337" t="n"/>
+      <c r="V11" s="337" t="n"/>
+      <c r="W11" s="337" t="n"/>
+      <c r="X11" s="337" t="n"/>
+      <c r="Y11" s="337" t="n"/>
+      <c r="Z11" s="337" t="n"/>
+      <c r="AA11" s="337" t="n"/>
+      <c r="AB11" s="338" t="n"/>
+      <c r="AC11" s="339" t="inlineStr">
         <is>
           <t>Review Owner</t>
         </is>
       </c>
-      <c r="AD11" s="233" t="n"/>
-      <c r="AE11" s="233" t="n"/>
-      <c r="AF11" s="233" t="n"/>
-      <c r="AG11" s="233" t="n"/>
-      <c r="AH11" s="233" t="n"/>
-      <c r="AI11" s="233" t="n"/>
-      <c r="AJ11" s="233" t="n"/>
-      <c r="AK11" s="233" t="n"/>
-      <c r="AL11" s="261" t="n"/>
-      <c r="AM11" s="262" t="n"/>
-      <c r="AN11" s="263" t="n"/>
-      <c r="AO11" s="263" t="n"/>
-      <c r="AP11" s="263" t="n"/>
-      <c r="AQ11" s="263" t="n"/>
-      <c r="AR11" s="263" t="n"/>
-      <c r="AS11" s="263" t="n"/>
-      <c r="AT11" s="263" t="n"/>
-      <c r="AU11" s="263" t="n"/>
-      <c r="AV11" s="263" t="n"/>
-      <c r="AW11" s="263" t="n"/>
-      <c r="AX11" s="263" t="n"/>
-      <c r="AY11" s="263" t="n"/>
-      <c r="AZ11" s="263" t="n"/>
-      <c r="BA11" s="263" t="n"/>
-      <c r="BB11" s="263" t="n"/>
-      <c r="BC11" s="263" t="n"/>
-      <c r="BD11" s="266" t="n"/>
+      <c r="AD11" s="13" t="n"/>
+      <c r="AE11" s="13" t="n"/>
+      <c r="AF11" s="13" t="n"/>
+      <c r="AG11" s="13" t="n"/>
+      <c r="AH11" s="13" t="n"/>
+      <c r="AI11" s="13" t="n"/>
+      <c r="AJ11" s="13" t="n"/>
+      <c r="AK11" s="13" t="n"/>
+      <c r="AL11" s="44" t="n"/>
+      <c r="AM11" s="340" t="n"/>
+      <c r="AN11" s="337" t="n"/>
+      <c r="AO11" s="337" t="n"/>
+      <c r="AP11" s="337" t="n"/>
+      <c r="AQ11" s="337" t="n"/>
+      <c r="AR11" s="337" t="n"/>
+      <c r="AS11" s="337" t="n"/>
+      <c r="AT11" s="337" t="n"/>
+      <c r="AU11" s="337" t="n"/>
+      <c r="AV11" s="337" t="n"/>
+      <c r="AW11" s="337" t="n"/>
+      <c r="AX11" s="337" t="n"/>
+      <c r="AY11" s="337" t="n"/>
+      <c r="AZ11" s="337" t="n"/>
+      <c r="BA11" s="337" t="n"/>
+      <c r="BB11" s="337" t="n"/>
+      <c r="BC11" s="337" t="n"/>
+      <c r="BD11" s="341" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="241" t="inlineStr">
+      <c r="A12" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. ACTIVE LOG TABLE</t>
         </is>
       </c>
-      <c r="B12" s="242" t="n"/>
-      <c r="C12" s="242" t="n"/>
-      <c r="D12" s="242" t="n"/>
-      <c r="E12" s="242" t="n"/>
-      <c r="F12" s="242" t="n"/>
-      <c r="G12" s="242" t="n"/>
-      <c r="H12" s="242" t="n"/>
-      <c r="I12" s="242" t="n"/>
-      <c r="J12" s="242" t="n"/>
-      <c r="K12" s="242" t="n"/>
-      <c r="L12" s="242" t="n"/>
-      <c r="M12" s="242" t="n"/>
-      <c r="N12" s="242" t="n"/>
-      <c r="O12" s="242" t="n"/>
-      <c r="P12" s="242" t="n"/>
-      <c r="Q12" s="242" t="n"/>
-      <c r="R12" s="242" t="n"/>
-      <c r="S12" s="242" t="n"/>
-      <c r="T12" s="242" t="n"/>
-      <c r="U12" s="242" t="n"/>
-      <c r="V12" s="242" t="n"/>
-      <c r="W12" s="242" t="n"/>
-      <c r="X12" s="242" t="n"/>
-      <c r="Y12" s="242" t="n"/>
-      <c r="Z12" s="242" t="n"/>
-      <c r="AA12" s="242" t="n"/>
-      <c r="AB12" s="242" t="n"/>
-      <c r="AC12" s="242" t="n"/>
-      <c r="AD12" s="242" t="n"/>
-      <c r="AE12" s="242" t="n"/>
-      <c r="AF12" s="242" t="n"/>
-      <c r="AG12" s="242" t="n"/>
-      <c r="AH12" s="242" t="n"/>
-      <c r="AI12" s="242" t="n"/>
-      <c r="AJ12" s="242" t="n"/>
-      <c r="AK12" s="242" t="n"/>
-      <c r="AL12" s="242" t="n"/>
-      <c r="AM12" s="242" t="n"/>
-      <c r="AN12" s="242" t="n"/>
-      <c r="AO12" s="242" t="n"/>
-      <c r="AP12" s="242" t="n"/>
-      <c r="AQ12" s="242" t="n"/>
-      <c r="AR12" s="242" t="n"/>
-      <c r="AS12" s="242" t="n"/>
-      <c r="AT12" s="242" t="n"/>
-      <c r="AU12" s="242" t="n"/>
-      <c r="AV12" s="242" t="n"/>
-      <c r="AW12" s="242" t="n"/>
-      <c r="AX12" s="242" t="n"/>
-      <c r="AY12" s="242" t="n"/>
-      <c r="AZ12" s="242" t="n"/>
-      <c r="BA12" s="242" t="n"/>
-      <c r="BB12" s="242" t="n"/>
-      <c r="BC12" s="242" t="n"/>
-      <c r="BD12" s="243" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n"/>
+      <c r="T12" s="6" t="n"/>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="n"/>
+      <c r="Y12" s="6" t="n"/>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="6" t="n"/>
+      <c r="AC12" s="6" t="n"/>
+      <c r="AD12" s="6" t="n"/>
+      <c r="AE12" s="6" t="n"/>
+      <c r="AF12" s="6" t="n"/>
+      <c r="AG12" s="6" t="n"/>
+      <c r="AH12" s="6" t="n"/>
+      <c r="AI12" s="6" t="n"/>
+      <c r="AJ12" s="6" t="n"/>
+      <c r="AK12" s="6" t="n"/>
+      <c r="AL12" s="6" t="n"/>
+      <c r="AM12" s="6" t="n"/>
+      <c r="AN12" s="6" t="n"/>
+      <c r="AO12" s="6" t="n"/>
+      <c r="AP12" s="6" t="n"/>
+      <c r="AQ12" s="6" t="n"/>
+      <c r="AR12" s="6" t="n"/>
+      <c r="AS12" s="6" t="n"/>
+      <c r="AT12" s="6" t="n"/>
+      <c r="AU12" s="6" t="n"/>
+      <c r="AV12" s="6" t="n"/>
+      <c r="AW12" s="6" t="n"/>
+      <c r="AX12" s="6" t="n"/>
+      <c r="AY12" s="6" t="n"/>
+      <c r="AZ12" s="6" t="n"/>
+      <c r="BA12" s="6" t="n"/>
+      <c r="BB12" s="6" t="n"/>
+      <c r="BC12" s="6" t="n"/>
+      <c r="BD12" s="7" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="267" t="inlineStr">
+      <c r="A13" s="48" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B13" s="246" t="n"/>
-      <c r="C13" s="268" t="inlineStr">
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="342" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="D13" s="245" t="n"/>
-      <c r="E13" s="245" t="n"/>
-      <c r="F13" s="245" t="n"/>
-      <c r="G13" s="245" t="n"/>
-      <c r="H13" s="246" t="n"/>
-      <c r="I13" s="268" t="inlineStr">
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="342" t="inlineStr">
         <is>
           <t>CSR Source</t>
         </is>
       </c>
-      <c r="J13" s="245" t="n"/>
-      <c r="K13" s="245" t="n"/>
-      <c r="L13" s="245" t="n"/>
-      <c r="M13" s="246" t="n"/>
-      <c r="N13" s="268" t="inlineStr">
+      <c r="J13" s="31" t="n"/>
+      <c r="K13" s="31" t="n"/>
+      <c r="L13" s="31" t="n"/>
+      <c r="M13" s="32" t="n"/>
+      <c r="N13" s="342" t="inlineStr">
         <is>
           <t>CSR Class</t>
         </is>
       </c>
-      <c r="O13" s="245" t="n"/>
-      <c r="P13" s="245" t="n"/>
-      <c r="Q13" s="245" t="n"/>
-      <c r="R13" s="246" t="n"/>
-      <c r="S13" s="268" t="inlineStr">
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="31" t="n"/>
+      <c r="R13" s="32" t="n"/>
+      <c r="S13" s="342" t="inlineStr">
         <is>
           <t>Requirement Summary</t>
         </is>
       </c>
-      <c r="T13" s="245" t="n"/>
-      <c r="U13" s="245" t="n"/>
-      <c r="V13" s="245" t="n"/>
-      <c r="W13" s="245" t="n"/>
-      <c r="X13" s="245" t="n"/>
-      <c r="Y13" s="246" t="n"/>
-      <c r="Z13" s="268" t="inlineStr">
+      <c r="T13" s="31" t="n"/>
+      <c r="U13" s="31" t="n"/>
+      <c r="V13" s="31" t="n"/>
+      <c r="W13" s="31" t="n"/>
+      <c r="X13" s="31" t="n"/>
+      <c r="Y13" s="32" t="n"/>
+      <c r="Z13" s="342" t="inlineStr">
         <is>
           <t>Affected Process</t>
         </is>
       </c>
-      <c r="AA13" s="245" t="n"/>
-      <c r="AB13" s="245" t="n"/>
-      <c r="AC13" s="245" t="n"/>
-      <c r="AD13" s="245" t="n"/>
-      <c r="AE13" s="245" t="n"/>
-      <c r="AF13" s="246" t="n"/>
-      <c r="AG13" s="268" t="inlineStr">
+      <c r="AA13" s="31" t="n"/>
+      <c r="AB13" s="31" t="n"/>
+      <c r="AC13" s="31" t="n"/>
+      <c r="AD13" s="31" t="n"/>
+      <c r="AE13" s="31" t="n"/>
+      <c r="AF13" s="32" t="n"/>
+      <c r="AG13" s="342" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AH13" s="245" t="n"/>
-      <c r="AI13" s="245" t="n"/>
-      <c r="AJ13" s="246" t="n"/>
-      <c r="AK13" s="268" t="inlineStr">
+      <c r="AH13" s="31" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="32" t="n"/>
+      <c r="AK13" s="342" t="inlineStr">
         <is>
           <t>Risk Level</t>
         </is>
       </c>
-      <c r="AL13" s="245" t="n"/>
-      <c r="AM13" s="245" t="n"/>
-      <c r="AN13" s="246" t="n"/>
-      <c r="AO13" s="268" t="inlineStr">
+      <c r="AL13" s="31" t="n"/>
+      <c r="AM13" s="31" t="n"/>
+      <c r="AN13" s="32" t="n"/>
+      <c r="AO13" s="342" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AP13" s="245" t="n"/>
-      <c r="AQ13" s="245" t="n"/>
-      <c r="AR13" s="246" t="n"/>
-      <c r="AS13" s="268" t="inlineStr">
+      <c r="AP13" s="31" t="n"/>
+      <c r="AQ13" s="31" t="n"/>
+      <c r="AR13" s="32" t="n"/>
+      <c r="AS13" s="342" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AT13" s="245" t="n"/>
-      <c r="AU13" s="245" t="n"/>
-      <c r="AV13" s="246" t="n"/>
-      <c r="AW13" s="268" t="inlineStr">
+      <c r="AT13" s="31" t="n"/>
+      <c r="AU13" s="31" t="n"/>
+      <c r="AV13" s="32" t="n"/>
+      <c r="AW13" s="342" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="AX13" s="245" t="n"/>
-      <c r="AY13" s="245" t="n"/>
-      <c r="AZ13" s="246" t="n"/>
-      <c r="BA13" s="268" t="inlineStr">
+      <c r="AX13" s="31" t="n"/>
+      <c r="AY13" s="31" t="n"/>
+      <c r="AZ13" s="32" t="n"/>
+      <c r="BA13" s="343" t="inlineStr">
         <is>
           <t>Closure Date</t>
         </is>
       </c>
-      <c r="BB13" s="245" t="n"/>
-      <c r="BC13" s="245" t="n"/>
-      <c r="BD13" s="269" t="n"/>
+      <c r="BB13" s="31" t="n"/>
+      <c r="BC13" s="31" t="n"/>
+      <c r="BD13" s="34" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="270">
+      <c r="A14" s="344">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B14" s="246" t="n"/>
-      <c r="C14" s="247" t="n"/>
-      <c r="D14" s="248" t="n"/>
-      <c r="E14" s="248" t="n"/>
-      <c r="F14" s="248" t="n"/>
-      <c r="G14" s="248" t="n"/>
-      <c r="H14" s="249" t="n"/>
-      <c r="I14" s="247" t="n"/>
-      <c r="J14" s="248" t="n"/>
-      <c r="K14" s="248" t="n"/>
-      <c r="L14" s="248" t="n"/>
-      <c r="M14" s="249" t="n"/>
-      <c r="N14" s="247" t="n"/>
-      <c r="O14" s="248" t="n"/>
-      <c r="P14" s="248" t="n"/>
-      <c r="Q14" s="248" t="n"/>
-      <c r="R14" s="249" t="n"/>
-      <c r="S14" s="247" t="n"/>
-      <c r="T14" s="248" t="n"/>
-      <c r="U14" s="248" t="n"/>
-      <c r="V14" s="248" t="n"/>
-      <c r="W14" s="248" t="n"/>
-      <c r="X14" s="248" t="n"/>
-      <c r="Y14" s="249" t="n"/>
-      <c r="Z14" s="247" t="n"/>
-      <c r="AA14" s="248" t="n"/>
-      <c r="AB14" s="248" t="n"/>
-      <c r="AC14" s="248" t="n"/>
-      <c r="AD14" s="248" t="n"/>
-      <c r="AE14" s="248" t="n"/>
-      <c r="AF14" s="249" t="n"/>
-      <c r="AG14" s="247" t="n"/>
-      <c r="AH14" s="248" t="n"/>
-      <c r="AI14" s="248" t="n"/>
-      <c r="AJ14" s="249" t="n"/>
-      <c r="AK14" s="247" t="n"/>
-      <c r="AL14" s="248" t="n"/>
-      <c r="AM14" s="248" t="n"/>
-      <c r="AN14" s="249" t="n"/>
-      <c r="AO14" s="247" t="n"/>
-      <c r="AP14" s="248" t="n"/>
-      <c r="AQ14" s="248" t="n"/>
-      <c r="AR14" s="249" t="n"/>
-      <c r="AS14" s="247" t="n"/>
-      <c r="AT14" s="248" t="n"/>
-      <c r="AU14" s="248" t="n"/>
-      <c r="AV14" s="249" t="n"/>
-      <c r="AW14" s="247" t="n"/>
-      <c r="AX14" s="248" t="n"/>
-      <c r="AY14" s="248" t="n"/>
-      <c r="AZ14" s="249" t="n"/>
-      <c r="BA14" s="247" t="n"/>
-      <c r="BB14" s="248" t="n"/>
-      <c r="BC14" s="248" t="n"/>
-      <c r="BD14" s="251" t="n"/>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="322" t="n"/>
+      <c r="D14" s="323" t="n"/>
+      <c r="E14" s="323" t="n"/>
+      <c r="F14" s="323" t="n"/>
+      <c r="G14" s="323" t="n"/>
+      <c r="H14" s="324" t="n"/>
+      <c r="I14" s="322" t="n"/>
+      <c r="J14" s="323" t="n"/>
+      <c r="K14" s="323" t="n"/>
+      <c r="L14" s="323" t="n"/>
+      <c r="M14" s="324" t="n"/>
+      <c r="N14" s="322" t="n"/>
+      <c r="O14" s="323" t="n"/>
+      <c r="P14" s="323" t="n"/>
+      <c r="Q14" s="323" t="n"/>
+      <c r="R14" s="324" t="n"/>
+      <c r="S14" s="322" t="n"/>
+      <c r="T14" s="323" t="n"/>
+      <c r="U14" s="323" t="n"/>
+      <c r="V14" s="323" t="n"/>
+      <c r="W14" s="323" t="n"/>
+      <c r="X14" s="323" t="n"/>
+      <c r="Y14" s="324" t="n"/>
+      <c r="Z14" s="322" t="n"/>
+      <c r="AA14" s="323" t="n"/>
+      <c r="AB14" s="323" t="n"/>
+      <c r="AC14" s="323" t="n"/>
+      <c r="AD14" s="323" t="n"/>
+      <c r="AE14" s="323" t="n"/>
+      <c r="AF14" s="324" t="n"/>
+      <c r="AG14" s="322" t="n"/>
+      <c r="AH14" s="323" t="n"/>
+      <c r="AI14" s="323" t="n"/>
+      <c r="AJ14" s="324" t="n"/>
+      <c r="AK14" s="322" t="n"/>
+      <c r="AL14" s="323" t="n"/>
+      <c r="AM14" s="323" t="n"/>
+      <c r="AN14" s="324" t="n"/>
+      <c r="AO14" s="322" t="n"/>
+      <c r="AP14" s="323" t="n"/>
+      <c r="AQ14" s="323" t="n"/>
+      <c r="AR14" s="324" t="n"/>
+      <c r="AS14" s="322" t="n"/>
+      <c r="AT14" s="323" t="n"/>
+      <c r="AU14" s="323" t="n"/>
+      <c r="AV14" s="324" t="n"/>
+      <c r="AW14" s="322" t="n"/>
+      <c r="AX14" s="323" t="n"/>
+      <c r="AY14" s="323" t="n"/>
+      <c r="AZ14" s="324" t="n"/>
+      <c r="BA14" s="326" t="n"/>
+      <c r="BB14" s="323" t="n"/>
+      <c r="BC14" s="323" t="n"/>
+      <c r="BD14" s="327" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="271">
+      <c r="A15" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B15" s="254" t="n"/>
-      <c r="C15" s="272" t="n"/>
-      <c r="D15" s="256" t="n"/>
-      <c r="E15" s="256" t="n"/>
-      <c r="F15" s="256" t="n"/>
-      <c r="G15" s="256" t="n"/>
-      <c r="H15" s="257" t="n"/>
-      <c r="I15" s="272" t="n"/>
-      <c r="J15" s="256" t="n"/>
-      <c r="K15" s="256" t="n"/>
-      <c r="L15" s="256" t="n"/>
-      <c r="M15" s="257" t="n"/>
-      <c r="N15" s="272" t="n"/>
-      <c r="O15" s="256" t="n"/>
-      <c r="P15" s="256" t="n"/>
-      <c r="Q15" s="256" t="n"/>
-      <c r="R15" s="257" t="n"/>
-      <c r="S15" s="272" t="n"/>
-      <c r="T15" s="256" t="n"/>
-      <c r="U15" s="256" t="n"/>
-      <c r="V15" s="256" t="n"/>
-      <c r="W15" s="256" t="n"/>
-      <c r="X15" s="256" t="n"/>
-      <c r="Y15" s="257" t="n"/>
-      <c r="Z15" s="272" t="n"/>
-      <c r="AA15" s="256" t="n"/>
-      <c r="AB15" s="256" t="n"/>
-      <c r="AC15" s="256" t="n"/>
-      <c r="AD15" s="256" t="n"/>
-      <c r="AE15" s="256" t="n"/>
-      <c r="AF15" s="257" t="n"/>
-      <c r="AG15" s="272" t="n"/>
-      <c r="AH15" s="256" t="n"/>
-      <c r="AI15" s="256" t="n"/>
-      <c r="AJ15" s="257" t="n"/>
-      <c r="AK15" s="272" t="n"/>
-      <c r="AL15" s="256" t="n"/>
-      <c r="AM15" s="256" t="n"/>
-      <c r="AN15" s="257" t="n"/>
-      <c r="AO15" s="272" t="n"/>
-      <c r="AP15" s="256" t="n"/>
-      <c r="AQ15" s="256" t="n"/>
-      <c r="AR15" s="257" t="n"/>
-      <c r="AS15" s="272" t="n"/>
-      <c r="AT15" s="256" t="n"/>
-      <c r="AU15" s="256" t="n"/>
-      <c r="AV15" s="257" t="n"/>
-      <c r="AW15" s="272" t="n"/>
-      <c r="AX15" s="256" t="n"/>
-      <c r="AY15" s="256" t="n"/>
-      <c r="AZ15" s="257" t="n"/>
-      <c r="BA15" s="272" t="n"/>
-      <c r="BB15" s="256" t="n"/>
-      <c r="BC15" s="256" t="n"/>
-      <c r="BD15" s="259" t="n"/>
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="346" t="n"/>
+      <c r="D15" s="330" t="n"/>
+      <c r="E15" s="330" t="n"/>
+      <c r="F15" s="330" t="n"/>
+      <c r="G15" s="330" t="n"/>
+      <c r="H15" s="331" t="n"/>
+      <c r="I15" s="346" t="n"/>
+      <c r="J15" s="330" t="n"/>
+      <c r="K15" s="330" t="n"/>
+      <c r="L15" s="330" t="n"/>
+      <c r="M15" s="331" t="n"/>
+      <c r="N15" s="346" t="n"/>
+      <c r="O15" s="330" t="n"/>
+      <c r="P15" s="330" t="n"/>
+      <c r="Q15" s="330" t="n"/>
+      <c r="R15" s="331" t="n"/>
+      <c r="S15" s="346" t="n"/>
+      <c r="T15" s="330" t="n"/>
+      <c r="U15" s="330" t="n"/>
+      <c r="V15" s="330" t="n"/>
+      <c r="W15" s="330" t="n"/>
+      <c r="X15" s="330" t="n"/>
+      <c r="Y15" s="331" t="n"/>
+      <c r="Z15" s="346" t="n"/>
+      <c r="AA15" s="330" t="n"/>
+      <c r="AB15" s="330" t="n"/>
+      <c r="AC15" s="330" t="n"/>
+      <c r="AD15" s="330" t="n"/>
+      <c r="AE15" s="330" t="n"/>
+      <c r="AF15" s="331" t="n"/>
+      <c r="AG15" s="346" t="n"/>
+      <c r="AH15" s="330" t="n"/>
+      <c r="AI15" s="330" t="n"/>
+      <c r="AJ15" s="331" t="n"/>
+      <c r="AK15" s="346" t="n"/>
+      <c r="AL15" s="330" t="n"/>
+      <c r="AM15" s="330" t="n"/>
+      <c r="AN15" s="331" t="n"/>
+      <c r="AO15" s="346" t="n"/>
+      <c r="AP15" s="330" t="n"/>
+      <c r="AQ15" s="330" t="n"/>
+      <c r="AR15" s="331" t="n"/>
+      <c r="AS15" s="346" t="n"/>
+      <c r="AT15" s="330" t="n"/>
+      <c r="AU15" s="330" t="n"/>
+      <c r="AV15" s="331" t="n"/>
+      <c r="AW15" s="346" t="n"/>
+      <c r="AX15" s="330" t="n"/>
+      <c r="AY15" s="330" t="n"/>
+      <c r="AZ15" s="331" t="n"/>
+      <c r="BA15" s="347" t="n"/>
+      <c r="BB15" s="330" t="n"/>
+      <c r="BC15" s="330" t="n"/>
+      <c r="BD15" s="334" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="271">
+      <c r="A16" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B16" s="254" t="n"/>
-      <c r="C16" s="255" t="n"/>
-      <c r="D16" s="256" t="n"/>
-      <c r="E16" s="256" t="n"/>
-      <c r="F16" s="256" t="n"/>
-      <c r="G16" s="256" t="n"/>
-      <c r="H16" s="257" t="n"/>
-      <c r="I16" s="255" t="n"/>
-      <c r="J16" s="256" t="n"/>
-      <c r="K16" s="256" t="n"/>
-      <c r="L16" s="256" t="n"/>
-      <c r="M16" s="257" t="n"/>
-      <c r="N16" s="255" t="n"/>
-      <c r="O16" s="256" t="n"/>
-      <c r="P16" s="256" t="n"/>
-      <c r="Q16" s="256" t="n"/>
-      <c r="R16" s="257" t="n"/>
-      <c r="S16" s="255" t="n"/>
-      <c r="T16" s="256" t="n"/>
-      <c r="U16" s="256" t="n"/>
-      <c r="V16" s="256" t="n"/>
-      <c r="W16" s="256" t="n"/>
-      <c r="X16" s="256" t="n"/>
-      <c r="Y16" s="257" t="n"/>
-      <c r="Z16" s="255" t="n"/>
-      <c r="AA16" s="256" t="n"/>
-      <c r="AB16" s="256" t="n"/>
-      <c r="AC16" s="256" t="n"/>
-      <c r="AD16" s="256" t="n"/>
-      <c r="AE16" s="256" t="n"/>
-      <c r="AF16" s="257" t="n"/>
-      <c r="AG16" s="255" t="n"/>
-      <c r="AH16" s="256" t="n"/>
-      <c r="AI16" s="256" t="n"/>
-      <c r="AJ16" s="257" t="n"/>
-      <c r="AK16" s="255" t="n"/>
-      <c r="AL16" s="256" t="n"/>
-      <c r="AM16" s="256" t="n"/>
-      <c r="AN16" s="257" t="n"/>
-      <c r="AO16" s="255" t="n"/>
-      <c r="AP16" s="256" t="n"/>
-      <c r="AQ16" s="256" t="n"/>
-      <c r="AR16" s="257" t="n"/>
-      <c r="AS16" s="255" t="n"/>
-      <c r="AT16" s="256" t="n"/>
-      <c r="AU16" s="256" t="n"/>
-      <c r="AV16" s="257" t="n"/>
-      <c r="AW16" s="255" t="n"/>
-      <c r="AX16" s="256" t="n"/>
-      <c r="AY16" s="256" t="n"/>
-      <c r="AZ16" s="257" t="n"/>
-      <c r="BA16" s="255" t="n"/>
-      <c r="BB16" s="256" t="n"/>
-      <c r="BC16" s="256" t="n"/>
-      <c r="BD16" s="259" t="n"/>
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="329" t="n"/>
+      <c r="D16" s="330" t="n"/>
+      <c r="E16" s="330" t="n"/>
+      <c r="F16" s="330" t="n"/>
+      <c r="G16" s="330" t="n"/>
+      <c r="H16" s="331" t="n"/>
+      <c r="I16" s="329" t="n"/>
+      <c r="J16" s="330" t="n"/>
+      <c r="K16" s="330" t="n"/>
+      <c r="L16" s="330" t="n"/>
+      <c r="M16" s="331" t="n"/>
+      <c r="N16" s="329" t="n"/>
+      <c r="O16" s="330" t="n"/>
+      <c r="P16" s="330" t="n"/>
+      <c r="Q16" s="330" t="n"/>
+      <c r="R16" s="331" t="n"/>
+      <c r="S16" s="329" t="n"/>
+      <c r="T16" s="330" t="n"/>
+      <c r="U16" s="330" t="n"/>
+      <c r="V16" s="330" t="n"/>
+      <c r="W16" s="330" t="n"/>
+      <c r="X16" s="330" t="n"/>
+      <c r="Y16" s="331" t="n"/>
+      <c r="Z16" s="329" t="n"/>
+      <c r="AA16" s="330" t="n"/>
+      <c r="AB16" s="330" t="n"/>
+      <c r="AC16" s="330" t="n"/>
+      <c r="AD16" s="330" t="n"/>
+      <c r="AE16" s="330" t="n"/>
+      <c r="AF16" s="331" t="n"/>
+      <c r="AG16" s="329" t="n"/>
+      <c r="AH16" s="330" t="n"/>
+      <c r="AI16" s="330" t="n"/>
+      <c r="AJ16" s="331" t="n"/>
+      <c r="AK16" s="329" t="n"/>
+      <c r="AL16" s="330" t="n"/>
+      <c r="AM16" s="330" t="n"/>
+      <c r="AN16" s="331" t="n"/>
+      <c r="AO16" s="329" t="n"/>
+      <c r="AP16" s="330" t="n"/>
+      <c r="AQ16" s="330" t="n"/>
+      <c r="AR16" s="331" t="n"/>
+      <c r="AS16" s="329" t="n"/>
+      <c r="AT16" s="330" t="n"/>
+      <c r="AU16" s="330" t="n"/>
+      <c r="AV16" s="331" t="n"/>
+      <c r="AW16" s="329" t="n"/>
+      <c r="AX16" s="330" t="n"/>
+      <c r="AY16" s="330" t="n"/>
+      <c r="AZ16" s="331" t="n"/>
+      <c r="BA16" s="333" t="n"/>
+      <c r="BB16" s="330" t="n"/>
+      <c r="BC16" s="330" t="n"/>
+      <c r="BD16" s="334" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="271">
+      <c r="A17" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B17" s="254" t="n"/>
-      <c r="C17" s="272" t="n"/>
-      <c r="D17" s="256" t="n"/>
-      <c r="E17" s="256" t="n"/>
-      <c r="F17" s="256" t="n"/>
-      <c r="G17" s="256" t="n"/>
-      <c r="H17" s="257" t="n"/>
-      <c r="I17" s="272" t="n"/>
-      <c r="J17" s="256" t="n"/>
-      <c r="K17" s="256" t="n"/>
-      <c r="L17" s="256" t="n"/>
-      <c r="M17" s="257" t="n"/>
-      <c r="N17" s="272" t="n"/>
-      <c r="O17" s="256" t="n"/>
-      <c r="P17" s="256" t="n"/>
-      <c r="Q17" s="256" t="n"/>
-      <c r="R17" s="257" t="n"/>
-      <c r="S17" s="272" t="n"/>
-      <c r="T17" s="256" t="n"/>
-      <c r="U17" s="256" t="n"/>
-      <c r="V17" s="256" t="n"/>
-      <c r="W17" s="256" t="n"/>
-      <c r="X17" s="256" t="n"/>
-      <c r="Y17" s="257" t="n"/>
-      <c r="Z17" s="272" t="n"/>
-      <c r="AA17" s="256" t="n"/>
-      <c r="AB17" s="256" t="n"/>
-      <c r="AC17" s="256" t="n"/>
-      <c r="AD17" s="256" t="n"/>
-      <c r="AE17" s="256" t="n"/>
-      <c r="AF17" s="257" t="n"/>
-      <c r="AG17" s="272" t="n"/>
-      <c r="AH17" s="256" t="n"/>
-      <c r="AI17" s="256" t="n"/>
-      <c r="AJ17" s="257" t="n"/>
-      <c r="AK17" s="272" t="n"/>
-      <c r="AL17" s="256" t="n"/>
-      <c r="AM17" s="256" t="n"/>
-      <c r="AN17" s="257" t="n"/>
-      <c r="AO17" s="272" t="n"/>
-      <c r="AP17" s="256" t="n"/>
-      <c r="AQ17" s="256" t="n"/>
-      <c r="AR17" s="257" t="n"/>
-      <c r="AS17" s="272" t="n"/>
-      <c r="AT17" s="256" t="n"/>
-      <c r="AU17" s="256" t="n"/>
-      <c r="AV17" s="257" t="n"/>
-      <c r="AW17" s="272" t="n"/>
-      <c r="AX17" s="256" t="n"/>
-      <c r="AY17" s="256" t="n"/>
-      <c r="AZ17" s="257" t="n"/>
-      <c r="BA17" s="272" t="n"/>
-      <c r="BB17" s="256" t="n"/>
-      <c r="BC17" s="256" t="n"/>
-      <c r="BD17" s="259" t="n"/>
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="346" t="n"/>
+      <c r="D17" s="330" t="n"/>
+      <c r="E17" s="330" t="n"/>
+      <c r="F17" s="330" t="n"/>
+      <c r="G17" s="330" t="n"/>
+      <c r="H17" s="331" t="n"/>
+      <c r="I17" s="346" t="n"/>
+      <c r="J17" s="330" t="n"/>
+      <c r="K17" s="330" t="n"/>
+      <c r="L17" s="330" t="n"/>
+      <c r="M17" s="331" t="n"/>
+      <c r="N17" s="346" t="n"/>
+      <c r="O17" s="330" t="n"/>
+      <c r="P17" s="330" t="n"/>
+      <c r="Q17" s="330" t="n"/>
+      <c r="R17" s="331" t="n"/>
+      <c r="S17" s="346" t="n"/>
+      <c r="T17" s="330" t="n"/>
+      <c r="U17" s="330" t="n"/>
+      <c r="V17" s="330" t="n"/>
+      <c r="W17" s="330" t="n"/>
+      <c r="X17" s="330" t="n"/>
+      <c r="Y17" s="331" t="n"/>
+      <c r="Z17" s="346" t="n"/>
+      <c r="AA17" s="330" t="n"/>
+      <c r="AB17" s="330" t="n"/>
+      <c r="AC17" s="330" t="n"/>
+      <c r="AD17" s="330" t="n"/>
+      <c r="AE17" s="330" t="n"/>
+      <c r="AF17" s="331" t="n"/>
+      <c r="AG17" s="346" t="n"/>
+      <c r="AH17" s="330" t="n"/>
+      <c r="AI17" s="330" t="n"/>
+      <c r="AJ17" s="331" t="n"/>
+      <c r="AK17" s="346" t="n"/>
+      <c r="AL17" s="330" t="n"/>
+      <c r="AM17" s="330" t="n"/>
+      <c r="AN17" s="331" t="n"/>
+      <c r="AO17" s="346" t="n"/>
+      <c r="AP17" s="330" t="n"/>
+      <c r="AQ17" s="330" t="n"/>
+      <c r="AR17" s="331" t="n"/>
+      <c r="AS17" s="346" t="n"/>
+      <c r="AT17" s="330" t="n"/>
+      <c r="AU17" s="330" t="n"/>
+      <c r="AV17" s="331" t="n"/>
+      <c r="AW17" s="346" t="n"/>
+      <c r="AX17" s="330" t="n"/>
+      <c r="AY17" s="330" t="n"/>
+      <c r="AZ17" s="331" t="n"/>
+      <c r="BA17" s="347" t="n"/>
+      <c r="BB17" s="330" t="n"/>
+      <c r="BC17" s="330" t="n"/>
+      <c r="BD17" s="334" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="271">
+      <c r="A18" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B18" s="254" t="n"/>
-      <c r="C18" s="255" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="257" t="n"/>
-      <c r="I18" s="255" t="n"/>
-      <c r="J18" s="256" t="n"/>
-      <c r="K18" s="256" t="n"/>
-      <c r="L18" s="256" t="n"/>
-      <c r="M18" s="257" t="n"/>
-      <c r="N18" s="255" t="n"/>
-      <c r="O18" s="256" t="n"/>
-      <c r="P18" s="256" t="n"/>
-      <c r="Q18" s="256" t="n"/>
-      <c r="R18" s="257" t="n"/>
-      <c r="S18" s="255" t="n"/>
-      <c r="T18" s="256" t="n"/>
-      <c r="U18" s="256" t="n"/>
-      <c r="V18" s="256" t="n"/>
-      <c r="W18" s="256" t="n"/>
-      <c r="X18" s="256" t="n"/>
-      <c r="Y18" s="257" t="n"/>
-      <c r="Z18" s="255" t="n"/>
-      <c r="AA18" s="256" t="n"/>
-      <c r="AB18" s="256" t="n"/>
-      <c r="AC18" s="256" t="n"/>
-      <c r="AD18" s="256" t="n"/>
-      <c r="AE18" s="256" t="n"/>
-      <c r="AF18" s="257" t="n"/>
-      <c r="AG18" s="255" t="n"/>
-      <c r="AH18" s="256" t="n"/>
-      <c r="AI18" s="256" t="n"/>
-      <c r="AJ18" s="257" t="n"/>
-      <c r="AK18" s="255" t="n"/>
-      <c r="AL18" s="256" t="n"/>
-      <c r="AM18" s="256" t="n"/>
-      <c r="AN18" s="257" t="n"/>
-      <c r="AO18" s="255" t="n"/>
-      <c r="AP18" s="256" t="n"/>
-      <c r="AQ18" s="256" t="n"/>
-      <c r="AR18" s="257" t="n"/>
-      <c r="AS18" s="255" t="n"/>
-      <c r="AT18" s="256" t="n"/>
-      <c r="AU18" s="256" t="n"/>
-      <c r="AV18" s="257" t="n"/>
-      <c r="AW18" s="255" t="n"/>
-      <c r="AX18" s="256" t="n"/>
-      <c r="AY18" s="256" t="n"/>
-      <c r="AZ18" s="257" t="n"/>
-      <c r="BA18" s="255" t="n"/>
-      <c r="BB18" s="256" t="n"/>
-      <c r="BC18" s="256" t="n"/>
-      <c r="BD18" s="259" t="n"/>
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="329" t="n"/>
+      <c r="D18" s="330" t="n"/>
+      <c r="E18" s="330" t="n"/>
+      <c r="F18" s="330" t="n"/>
+      <c r="G18" s="330" t="n"/>
+      <c r="H18" s="331" t="n"/>
+      <c r="I18" s="329" t="n"/>
+      <c r="J18" s="330" t="n"/>
+      <c r="K18" s="330" t="n"/>
+      <c r="L18" s="330" t="n"/>
+      <c r="M18" s="331" t="n"/>
+      <c r="N18" s="329" t="n"/>
+      <c r="O18" s="330" t="n"/>
+      <c r="P18" s="330" t="n"/>
+      <c r="Q18" s="330" t="n"/>
+      <c r="R18" s="331" t="n"/>
+      <c r="S18" s="329" t="n"/>
+      <c r="T18" s="330" t="n"/>
+      <c r="U18" s="330" t="n"/>
+      <c r="V18" s="330" t="n"/>
+      <c r="W18" s="330" t="n"/>
+      <c r="X18" s="330" t="n"/>
+      <c r="Y18" s="331" t="n"/>
+      <c r="Z18" s="329" t="n"/>
+      <c r="AA18" s="330" t="n"/>
+      <c r="AB18" s="330" t="n"/>
+      <c r="AC18" s="330" t="n"/>
+      <c r="AD18" s="330" t="n"/>
+      <c r="AE18" s="330" t="n"/>
+      <c r="AF18" s="331" t="n"/>
+      <c r="AG18" s="329" t="n"/>
+      <c r="AH18" s="330" t="n"/>
+      <c r="AI18" s="330" t="n"/>
+      <c r="AJ18" s="331" t="n"/>
+      <c r="AK18" s="329" t="n"/>
+      <c r="AL18" s="330" t="n"/>
+      <c r="AM18" s="330" t="n"/>
+      <c r="AN18" s="331" t="n"/>
+      <c r="AO18" s="329" t="n"/>
+      <c r="AP18" s="330" t="n"/>
+      <c r="AQ18" s="330" t="n"/>
+      <c r="AR18" s="331" t="n"/>
+      <c r="AS18" s="329" t="n"/>
+      <c r="AT18" s="330" t="n"/>
+      <c r="AU18" s="330" t="n"/>
+      <c r="AV18" s="331" t="n"/>
+      <c r="AW18" s="329" t="n"/>
+      <c r="AX18" s="330" t="n"/>
+      <c r="AY18" s="330" t="n"/>
+      <c r="AZ18" s="331" t="n"/>
+      <c r="BA18" s="333" t="n"/>
+      <c r="BB18" s="330" t="n"/>
+      <c r="BC18" s="330" t="n"/>
+      <c r="BD18" s="334" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="271">
+      <c r="A19" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B19" s="254" t="n"/>
-      <c r="C19" s="272" t="n"/>
-      <c r="D19" s="256" t="n"/>
-      <c r="E19" s="256" t="n"/>
-      <c r="F19" s="256" t="n"/>
-      <c r="G19" s="256" t="n"/>
-      <c r="H19" s="257" t="n"/>
-      <c r="I19" s="272" t="n"/>
-      <c r="J19" s="256" t="n"/>
-      <c r="K19" s="256" t="n"/>
-      <c r="L19" s="256" t="n"/>
-      <c r="M19" s="257" t="n"/>
-      <c r="N19" s="272" t="n"/>
-      <c r="O19" s="256" t="n"/>
-      <c r="P19" s="256" t="n"/>
-      <c r="Q19" s="256" t="n"/>
-      <c r="R19" s="257" t="n"/>
-      <c r="S19" s="272" t="n"/>
-      <c r="T19" s="256" t="n"/>
-      <c r="U19" s="256" t="n"/>
-      <c r="V19" s="256" t="n"/>
-      <c r="W19" s="256" t="n"/>
-      <c r="X19" s="256" t="n"/>
-      <c r="Y19" s="257" t="n"/>
-      <c r="Z19" s="272" t="n"/>
-      <c r="AA19" s="256" t="n"/>
-      <c r="AB19" s="256" t="n"/>
-      <c r="AC19" s="256" t="n"/>
-      <c r="AD19" s="256" t="n"/>
-      <c r="AE19" s="256" t="n"/>
-      <c r="AF19" s="257" t="n"/>
-      <c r="AG19" s="272" t="n"/>
-      <c r="AH19" s="256" t="n"/>
-      <c r="AI19" s="256" t="n"/>
-      <c r="AJ19" s="257" t="n"/>
-      <c r="AK19" s="272" t="n"/>
-      <c r="AL19" s="256" t="n"/>
-      <c r="AM19" s="256" t="n"/>
-      <c r="AN19" s="257" t="n"/>
-      <c r="AO19" s="272" t="n"/>
-      <c r="AP19" s="256" t="n"/>
-      <c r="AQ19" s="256" t="n"/>
-      <c r="AR19" s="257" t="n"/>
-      <c r="AS19" s="272" t="n"/>
-      <c r="AT19" s="256" t="n"/>
-      <c r="AU19" s="256" t="n"/>
-      <c r="AV19" s="257" t="n"/>
-      <c r="AW19" s="272" t="n"/>
-      <c r="AX19" s="256" t="n"/>
-      <c r="AY19" s="256" t="n"/>
-      <c r="AZ19" s="257" t="n"/>
-      <c r="BA19" s="272" t="n"/>
-      <c r="BB19" s="256" t="n"/>
-      <c r="BC19" s="256" t="n"/>
-      <c r="BD19" s="259" t="n"/>
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="346" t="n"/>
+      <c r="D19" s="330" t="n"/>
+      <c r="E19" s="330" t="n"/>
+      <c r="F19" s="330" t="n"/>
+      <c r="G19" s="330" t="n"/>
+      <c r="H19" s="331" t="n"/>
+      <c r="I19" s="346" t="n"/>
+      <c r="J19" s="330" t="n"/>
+      <c r="K19" s="330" t="n"/>
+      <c r="L19" s="330" t="n"/>
+      <c r="M19" s="331" t="n"/>
+      <c r="N19" s="346" t="n"/>
+      <c r="O19" s="330" t="n"/>
+      <c r="P19" s="330" t="n"/>
+      <c r="Q19" s="330" t="n"/>
+      <c r="R19" s="331" t="n"/>
+      <c r="S19" s="346" t="n"/>
+      <c r="T19" s="330" t="n"/>
+      <c r="U19" s="330" t="n"/>
+      <c r="V19" s="330" t="n"/>
+      <c r="W19" s="330" t="n"/>
+      <c r="X19" s="330" t="n"/>
+      <c r="Y19" s="331" t="n"/>
+      <c r="Z19" s="346" t="n"/>
+      <c r="AA19" s="330" t="n"/>
+      <c r="AB19" s="330" t="n"/>
+      <c r="AC19" s="330" t="n"/>
+      <c r="AD19" s="330" t="n"/>
+      <c r="AE19" s="330" t="n"/>
+      <c r="AF19" s="331" t="n"/>
+      <c r="AG19" s="346" t="n"/>
+      <c r="AH19" s="330" t="n"/>
+      <c r="AI19" s="330" t="n"/>
+      <c r="AJ19" s="331" t="n"/>
+      <c r="AK19" s="346" t="n"/>
+      <c r="AL19" s="330" t="n"/>
+      <c r="AM19" s="330" t="n"/>
+      <c r="AN19" s="331" t="n"/>
+      <c r="AO19" s="346" t="n"/>
+      <c r="AP19" s="330" t="n"/>
+      <c r="AQ19" s="330" t="n"/>
+      <c r="AR19" s="331" t="n"/>
+      <c r="AS19" s="346" t="n"/>
+      <c r="AT19" s="330" t="n"/>
+      <c r="AU19" s="330" t="n"/>
+      <c r="AV19" s="331" t="n"/>
+      <c r="AW19" s="346" t="n"/>
+      <c r="AX19" s="330" t="n"/>
+      <c r="AY19" s="330" t="n"/>
+      <c r="AZ19" s="331" t="n"/>
+      <c r="BA19" s="347" t="n"/>
+      <c r="BB19" s="330" t="n"/>
+      <c r="BC19" s="330" t="n"/>
+      <c r="BD19" s="334" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="271">
+      <c r="A20" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B20" s="254" t="n"/>
-      <c r="C20" s="255" t="n"/>
-      <c r="D20" s="256" t="n"/>
-      <c r="E20" s="256" t="n"/>
-      <c r="F20" s="256" t="n"/>
-      <c r="G20" s="256" t="n"/>
-      <c r="H20" s="257" t="n"/>
-      <c r="I20" s="255" t="n"/>
-      <c r="J20" s="256" t="n"/>
-      <c r="K20" s="256" t="n"/>
-      <c r="L20" s="256" t="n"/>
-      <c r="M20" s="257" t="n"/>
-      <c r="N20" s="255" t="n"/>
-      <c r="O20" s="256" t="n"/>
-      <c r="P20" s="256" t="n"/>
-      <c r="Q20" s="256" t="n"/>
-      <c r="R20" s="257" t="n"/>
-      <c r="S20" s="255" t="n"/>
-      <c r="T20" s="256" t="n"/>
-      <c r="U20" s="256" t="n"/>
-      <c r="V20" s="256" t="n"/>
-      <c r="W20" s="256" t="n"/>
-      <c r="X20" s="256" t="n"/>
-      <c r="Y20" s="257" t="n"/>
-      <c r="Z20" s="255" t="n"/>
-      <c r="AA20" s="256" t="n"/>
-      <c r="AB20" s="256" t="n"/>
-      <c r="AC20" s="256" t="n"/>
-      <c r="AD20" s="256" t="n"/>
-      <c r="AE20" s="256" t="n"/>
-      <c r="AF20" s="257" t="n"/>
-      <c r="AG20" s="255" t="n"/>
-      <c r="AH20" s="256" t="n"/>
-      <c r="AI20" s="256" t="n"/>
-      <c r="AJ20" s="257" t="n"/>
-      <c r="AK20" s="255" t="n"/>
-      <c r="AL20" s="256" t="n"/>
-      <c r="AM20" s="256" t="n"/>
-      <c r="AN20" s="257" t="n"/>
-      <c r="AO20" s="255" t="n"/>
-      <c r="AP20" s="256" t="n"/>
-      <c r="AQ20" s="256" t="n"/>
-      <c r="AR20" s="257" t="n"/>
-      <c r="AS20" s="255" t="n"/>
-      <c r="AT20" s="256" t="n"/>
-      <c r="AU20" s="256" t="n"/>
-      <c r="AV20" s="257" t="n"/>
-      <c r="AW20" s="255" t="n"/>
-      <c r="AX20" s="256" t="n"/>
-      <c r="AY20" s="256" t="n"/>
-      <c r="AZ20" s="257" t="n"/>
-      <c r="BA20" s="255" t="n"/>
-      <c r="BB20" s="256" t="n"/>
-      <c r="BC20" s="256" t="n"/>
-      <c r="BD20" s="259" t="n"/>
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="329" t="n"/>
+      <c r="D20" s="330" t="n"/>
+      <c r="E20" s="330" t="n"/>
+      <c r="F20" s="330" t="n"/>
+      <c r="G20" s="330" t="n"/>
+      <c r="H20" s="331" t="n"/>
+      <c r="I20" s="329" t="n"/>
+      <c r="J20" s="330" t="n"/>
+      <c r="K20" s="330" t="n"/>
+      <c r="L20" s="330" t="n"/>
+      <c r="M20" s="331" t="n"/>
+      <c r="N20" s="329" t="n"/>
+      <c r="O20" s="330" t="n"/>
+      <c r="P20" s="330" t="n"/>
+      <c r="Q20" s="330" t="n"/>
+      <c r="R20" s="331" t="n"/>
+      <c r="S20" s="329" t="n"/>
+      <c r="T20" s="330" t="n"/>
+      <c r="U20" s="330" t="n"/>
+      <c r="V20" s="330" t="n"/>
+      <c r="W20" s="330" t="n"/>
+      <c r="X20" s="330" t="n"/>
+      <c r="Y20" s="331" t="n"/>
+      <c r="Z20" s="329" t="n"/>
+      <c r="AA20" s="330" t="n"/>
+      <c r="AB20" s="330" t="n"/>
+      <c r="AC20" s="330" t="n"/>
+      <c r="AD20" s="330" t="n"/>
+      <c r="AE20" s="330" t="n"/>
+      <c r="AF20" s="331" t="n"/>
+      <c r="AG20" s="329" t="n"/>
+      <c r="AH20" s="330" t="n"/>
+      <c r="AI20" s="330" t="n"/>
+      <c r="AJ20" s="331" t="n"/>
+      <c r="AK20" s="329" t="n"/>
+      <c r="AL20" s="330" t="n"/>
+      <c r="AM20" s="330" t="n"/>
+      <c r="AN20" s="331" t="n"/>
+      <c r="AO20" s="329" t="n"/>
+      <c r="AP20" s="330" t="n"/>
+      <c r="AQ20" s="330" t="n"/>
+      <c r="AR20" s="331" t="n"/>
+      <c r="AS20" s="329" t="n"/>
+      <c r="AT20" s="330" t="n"/>
+      <c r="AU20" s="330" t="n"/>
+      <c r="AV20" s="331" t="n"/>
+      <c r="AW20" s="329" t="n"/>
+      <c r="AX20" s="330" t="n"/>
+      <c r="AY20" s="330" t="n"/>
+      <c r="AZ20" s="331" t="n"/>
+      <c r="BA20" s="333" t="n"/>
+      <c r="BB20" s="330" t="n"/>
+      <c r="BC20" s="330" t="n"/>
+      <c r="BD20" s="334" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="271">
+      <c r="A21" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B21" s="254" t="n"/>
-      <c r="C21" s="272" t="n"/>
-      <c r="D21" s="256" t="n"/>
-      <c r="E21" s="256" t="n"/>
-      <c r="F21" s="256" t="n"/>
-      <c r="G21" s="256" t="n"/>
-      <c r="H21" s="257" t="n"/>
-      <c r="I21" s="272" t="n"/>
-      <c r="J21" s="256" t="n"/>
-      <c r="K21" s="256" t="n"/>
-      <c r="L21" s="256" t="n"/>
-      <c r="M21" s="257" t="n"/>
-      <c r="N21" s="272" t="n"/>
-      <c r="O21" s="256" t="n"/>
-      <c r="P21" s="256" t="n"/>
-      <c r="Q21" s="256" t="n"/>
-      <c r="R21" s="257" t="n"/>
-      <c r="S21" s="272" t="n"/>
-      <c r="T21" s="256" t="n"/>
-      <c r="U21" s="256" t="n"/>
-      <c r="V21" s="256" t="n"/>
-      <c r="W21" s="256" t="n"/>
-      <c r="X21" s="256" t="n"/>
-      <c r="Y21" s="257" t="n"/>
-      <c r="Z21" s="272" t="n"/>
-      <c r="AA21" s="256" t="n"/>
-      <c r="AB21" s="256" t="n"/>
-      <c r="AC21" s="256" t="n"/>
-      <c r="AD21" s="256" t="n"/>
-      <c r="AE21" s="256" t="n"/>
-      <c r="AF21" s="257" t="n"/>
-      <c r="AG21" s="272" t="n"/>
-      <c r="AH21" s="256" t="n"/>
-      <c r="AI21" s="256" t="n"/>
-      <c r="AJ21" s="257" t="n"/>
-      <c r="AK21" s="272" t="n"/>
-      <c r="AL21" s="256" t="n"/>
-      <c r="AM21" s="256" t="n"/>
-      <c r="AN21" s="257" t="n"/>
-      <c r="AO21" s="272" t="n"/>
-      <c r="AP21" s="256" t="n"/>
-      <c r="AQ21" s="256" t="n"/>
-      <c r="AR21" s="257" t="n"/>
-      <c r="AS21" s="272" t="n"/>
-      <c r="AT21" s="256" t="n"/>
-      <c r="AU21" s="256" t="n"/>
-      <c r="AV21" s="257" t="n"/>
-      <c r="AW21" s="272" t="n"/>
-      <c r="AX21" s="256" t="n"/>
-      <c r="AY21" s="256" t="n"/>
-      <c r="AZ21" s="257" t="n"/>
-      <c r="BA21" s="272" t="n"/>
-      <c r="BB21" s="256" t="n"/>
-      <c r="BC21" s="256" t="n"/>
-      <c r="BD21" s="259" t="n"/>
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="346" t="n"/>
+      <c r="D21" s="330" t="n"/>
+      <c r="E21" s="330" t="n"/>
+      <c r="F21" s="330" t="n"/>
+      <c r="G21" s="330" t="n"/>
+      <c r="H21" s="331" t="n"/>
+      <c r="I21" s="346" t="n"/>
+      <c r="J21" s="330" t="n"/>
+      <c r="K21" s="330" t="n"/>
+      <c r="L21" s="330" t="n"/>
+      <c r="M21" s="331" t="n"/>
+      <c r="N21" s="346" t="n"/>
+      <c r="O21" s="330" t="n"/>
+      <c r="P21" s="330" t="n"/>
+      <c r="Q21" s="330" t="n"/>
+      <c r="R21" s="331" t="n"/>
+      <c r="S21" s="346" t="n"/>
+      <c r="T21" s="330" t="n"/>
+      <c r="U21" s="330" t="n"/>
+      <c r="V21" s="330" t="n"/>
+      <c r="W21" s="330" t="n"/>
+      <c r="X21" s="330" t="n"/>
+      <c r="Y21" s="331" t="n"/>
+      <c r="Z21" s="346" t="n"/>
+      <c r="AA21" s="330" t="n"/>
+      <c r="AB21" s="330" t="n"/>
+      <c r="AC21" s="330" t="n"/>
+      <c r="AD21" s="330" t="n"/>
+      <c r="AE21" s="330" t="n"/>
+      <c r="AF21" s="331" t="n"/>
+      <c r="AG21" s="346" t="n"/>
+      <c r="AH21" s="330" t="n"/>
+      <c r="AI21" s="330" t="n"/>
+      <c r="AJ21" s="331" t="n"/>
+      <c r="AK21" s="346" t="n"/>
+      <c r="AL21" s="330" t="n"/>
+      <c r="AM21" s="330" t="n"/>
+      <c r="AN21" s="331" t="n"/>
+      <c r="AO21" s="346" t="n"/>
+      <c r="AP21" s="330" t="n"/>
+      <c r="AQ21" s="330" t="n"/>
+      <c r="AR21" s="331" t="n"/>
+      <c r="AS21" s="346" t="n"/>
+      <c r="AT21" s="330" t="n"/>
+      <c r="AU21" s="330" t="n"/>
+      <c r="AV21" s="331" t="n"/>
+      <c r="AW21" s="346" t="n"/>
+      <c r="AX21" s="330" t="n"/>
+      <c r="AY21" s="330" t="n"/>
+      <c r="AZ21" s="331" t="n"/>
+      <c r="BA21" s="347" t="n"/>
+      <c r="BB21" s="330" t="n"/>
+      <c r="BC21" s="330" t="n"/>
+      <c r="BD21" s="334" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="271">
+      <c r="A22" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B22" s="254" t="n"/>
-      <c r="C22" s="255" t="n"/>
-      <c r="D22" s="256" t="n"/>
-      <c r="E22" s="256" t="n"/>
-      <c r="F22" s="256" t="n"/>
-      <c r="G22" s="256" t="n"/>
-      <c r="H22" s="257" t="n"/>
-      <c r="I22" s="255" t="n"/>
-      <c r="J22" s="256" t="n"/>
-      <c r="K22" s="256" t="n"/>
-      <c r="L22" s="256" t="n"/>
-      <c r="M22" s="257" t="n"/>
-      <c r="N22" s="255" t="n"/>
-      <c r="O22" s="256" t="n"/>
-      <c r="P22" s="256" t="n"/>
-      <c r="Q22" s="256" t="n"/>
-      <c r="R22" s="257" t="n"/>
-      <c r="S22" s="255" t="n"/>
-      <c r="T22" s="256" t="n"/>
-      <c r="U22" s="256" t="n"/>
-      <c r="V22" s="256" t="n"/>
-      <c r="W22" s="256" t="n"/>
-      <c r="X22" s="256" t="n"/>
-      <c r="Y22" s="257" t="n"/>
-      <c r="Z22" s="255" t="n"/>
-      <c r="AA22" s="256" t="n"/>
-      <c r="AB22" s="256" t="n"/>
-      <c r="AC22" s="256" t="n"/>
-      <c r="AD22" s="256" t="n"/>
-      <c r="AE22" s="256" t="n"/>
-      <c r="AF22" s="257" t="n"/>
-      <c r="AG22" s="255" t="n"/>
-      <c r="AH22" s="256" t="n"/>
-      <c r="AI22" s="256" t="n"/>
-      <c r="AJ22" s="257" t="n"/>
-      <c r="AK22" s="255" t="n"/>
-      <c r="AL22" s="256" t="n"/>
-      <c r="AM22" s="256" t="n"/>
-      <c r="AN22" s="257" t="n"/>
-      <c r="AO22" s="255" t="n"/>
-      <c r="AP22" s="256" t="n"/>
-      <c r="AQ22" s="256" t="n"/>
-      <c r="AR22" s="257" t="n"/>
-      <c r="AS22" s="255" t="n"/>
-      <c r="AT22" s="256" t="n"/>
-      <c r="AU22" s="256" t="n"/>
-      <c r="AV22" s="257" t="n"/>
-      <c r="AW22" s="255" t="n"/>
-      <c r="AX22" s="256" t="n"/>
-      <c r="AY22" s="256" t="n"/>
-      <c r="AZ22" s="257" t="n"/>
-      <c r="BA22" s="255" t="n"/>
-      <c r="BB22" s="256" t="n"/>
-      <c r="BC22" s="256" t="n"/>
-      <c r="BD22" s="259" t="n"/>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="329" t="n"/>
+      <c r="D22" s="330" t="n"/>
+      <c r="E22" s="330" t="n"/>
+      <c r="F22" s="330" t="n"/>
+      <c r="G22" s="330" t="n"/>
+      <c r="H22" s="331" t="n"/>
+      <c r="I22" s="329" t="n"/>
+      <c r="J22" s="330" t="n"/>
+      <c r="K22" s="330" t="n"/>
+      <c r="L22" s="330" t="n"/>
+      <c r="M22" s="331" t="n"/>
+      <c r="N22" s="329" t="n"/>
+      <c r="O22" s="330" t="n"/>
+      <c r="P22" s="330" t="n"/>
+      <c r="Q22" s="330" t="n"/>
+      <c r="R22" s="331" t="n"/>
+      <c r="S22" s="329" t="n"/>
+      <c r="T22" s="330" t="n"/>
+      <c r="U22" s="330" t="n"/>
+      <c r="V22" s="330" t="n"/>
+      <c r="W22" s="330" t="n"/>
+      <c r="X22" s="330" t="n"/>
+      <c r="Y22" s="331" t="n"/>
+      <c r="Z22" s="329" t="n"/>
+      <c r="AA22" s="330" t="n"/>
+      <c r="AB22" s="330" t="n"/>
+      <c r="AC22" s="330" t="n"/>
+      <c r="AD22" s="330" t="n"/>
+      <c r="AE22" s="330" t="n"/>
+      <c r="AF22" s="331" t="n"/>
+      <c r="AG22" s="329" t="n"/>
+      <c r="AH22" s="330" t="n"/>
+      <c r="AI22" s="330" t="n"/>
+      <c r="AJ22" s="331" t="n"/>
+      <c r="AK22" s="329" t="n"/>
+      <c r="AL22" s="330" t="n"/>
+      <c r="AM22" s="330" t="n"/>
+      <c r="AN22" s="331" t="n"/>
+      <c r="AO22" s="329" t="n"/>
+      <c r="AP22" s="330" t="n"/>
+      <c r="AQ22" s="330" t="n"/>
+      <c r="AR22" s="331" t="n"/>
+      <c r="AS22" s="329" t="n"/>
+      <c r="AT22" s="330" t="n"/>
+      <c r="AU22" s="330" t="n"/>
+      <c r="AV22" s="331" t="n"/>
+      <c r="AW22" s="329" t="n"/>
+      <c r="AX22" s="330" t="n"/>
+      <c r="AY22" s="330" t="n"/>
+      <c r="AZ22" s="331" t="n"/>
+      <c r="BA22" s="333" t="n"/>
+      <c r="BB22" s="330" t="n"/>
+      <c r="BC22" s="330" t="n"/>
+      <c r="BD22" s="334" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="271">
+      <c r="A23" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B23" s="254" t="n"/>
-      <c r="C23" s="272" t="n"/>
-      <c r="D23" s="256" t="n"/>
-      <c r="E23" s="256" t="n"/>
-      <c r="F23" s="256" t="n"/>
-      <c r="G23" s="256" t="n"/>
-      <c r="H23" s="257" t="n"/>
-      <c r="I23" s="272" t="n"/>
-      <c r="J23" s="256" t="n"/>
-      <c r="K23" s="256" t="n"/>
-      <c r="L23" s="256" t="n"/>
-      <c r="M23" s="257" t="n"/>
-      <c r="N23" s="272" t="n"/>
-      <c r="O23" s="256" t="n"/>
-      <c r="P23" s="256" t="n"/>
-      <c r="Q23" s="256" t="n"/>
-      <c r="R23" s="257" t="n"/>
-      <c r="S23" s="272" t="n"/>
-      <c r="T23" s="256" t="n"/>
-      <c r="U23" s="256" t="n"/>
-      <c r="V23" s="256" t="n"/>
-      <c r="W23" s="256" t="n"/>
-      <c r="X23" s="256" t="n"/>
-      <c r="Y23" s="257" t="n"/>
-      <c r="Z23" s="272" t="n"/>
-      <c r="AA23" s="256" t="n"/>
-      <c r="AB23" s="256" t="n"/>
-      <c r="AC23" s="256" t="n"/>
-      <c r="AD23" s="256" t="n"/>
-      <c r="AE23" s="256" t="n"/>
-      <c r="AF23" s="257" t="n"/>
-      <c r="AG23" s="272" t="n"/>
-      <c r="AH23" s="256" t="n"/>
-      <c r="AI23" s="256" t="n"/>
-      <c r="AJ23" s="257" t="n"/>
-      <c r="AK23" s="272" t="n"/>
-      <c r="AL23" s="256" t="n"/>
-      <c r="AM23" s="256" t="n"/>
-      <c r="AN23" s="257" t="n"/>
-      <c r="AO23" s="272" t="n"/>
-      <c r="AP23" s="256" t="n"/>
-      <c r="AQ23" s="256" t="n"/>
-      <c r="AR23" s="257" t="n"/>
-      <c r="AS23" s="272" t="n"/>
-      <c r="AT23" s="256" t="n"/>
-      <c r="AU23" s="256" t="n"/>
-      <c r="AV23" s="257" t="n"/>
-      <c r="AW23" s="272" t="n"/>
-      <c r="AX23" s="256" t="n"/>
-      <c r="AY23" s="256" t="n"/>
-      <c r="AZ23" s="257" t="n"/>
-      <c r="BA23" s="272" t="n"/>
-      <c r="BB23" s="256" t="n"/>
-      <c r="BC23" s="256" t="n"/>
-      <c r="BD23" s="259" t="n"/>
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="346" t="n"/>
+      <c r="D23" s="330" t="n"/>
+      <c r="E23" s="330" t="n"/>
+      <c r="F23" s="330" t="n"/>
+      <c r="G23" s="330" t="n"/>
+      <c r="H23" s="331" t="n"/>
+      <c r="I23" s="346" t="n"/>
+      <c r="J23" s="330" t="n"/>
+      <c r="K23" s="330" t="n"/>
+      <c r="L23" s="330" t="n"/>
+      <c r="M23" s="331" t="n"/>
+      <c r="N23" s="346" t="n"/>
+      <c r="O23" s="330" t="n"/>
+      <c r="P23" s="330" t="n"/>
+      <c r="Q23" s="330" t="n"/>
+      <c r="R23" s="331" t="n"/>
+      <c r="S23" s="346" t="n"/>
+      <c r="T23" s="330" t="n"/>
+      <c r="U23" s="330" t="n"/>
+      <c r="V23" s="330" t="n"/>
+      <c r="W23" s="330" t="n"/>
+      <c r="X23" s="330" t="n"/>
+      <c r="Y23" s="331" t="n"/>
+      <c r="Z23" s="346" t="n"/>
+      <c r="AA23" s="330" t="n"/>
+      <c r="AB23" s="330" t="n"/>
+      <c r="AC23" s="330" t="n"/>
+      <c r="AD23" s="330" t="n"/>
+      <c r="AE23" s="330" t="n"/>
+      <c r="AF23" s="331" t="n"/>
+      <c r="AG23" s="346" t="n"/>
+      <c r="AH23" s="330" t="n"/>
+      <c r="AI23" s="330" t="n"/>
+      <c r="AJ23" s="331" t="n"/>
+      <c r="AK23" s="346" t="n"/>
+      <c r="AL23" s="330" t="n"/>
+      <c r="AM23" s="330" t="n"/>
+      <c r="AN23" s="331" t="n"/>
+      <c r="AO23" s="346" t="n"/>
+      <c r="AP23" s="330" t="n"/>
+      <c r="AQ23" s="330" t="n"/>
+      <c r="AR23" s="331" t="n"/>
+      <c r="AS23" s="346" t="n"/>
+      <c r="AT23" s="330" t="n"/>
+      <c r="AU23" s="330" t="n"/>
+      <c r="AV23" s="331" t="n"/>
+      <c r="AW23" s="346" t="n"/>
+      <c r="AX23" s="330" t="n"/>
+      <c r="AY23" s="330" t="n"/>
+      <c r="AZ23" s="331" t="n"/>
+      <c r="BA23" s="347" t="n"/>
+      <c r="BB23" s="330" t="n"/>
+      <c r="BC23" s="330" t="n"/>
+      <c r="BD23" s="334" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="271">
+      <c r="A24" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B24" s="254" t="n"/>
-      <c r="C24" s="255" t="n"/>
-      <c r="D24" s="256" t="n"/>
-      <c r="E24" s="256" t="n"/>
-      <c r="F24" s="256" t="n"/>
-      <c r="G24" s="256" t="n"/>
-      <c r="H24" s="257" t="n"/>
-      <c r="I24" s="255" t="n"/>
-      <c r="J24" s="256" t="n"/>
-      <c r="K24" s="256" t="n"/>
-      <c r="L24" s="256" t="n"/>
-      <c r="M24" s="257" t="n"/>
-      <c r="N24" s="255" t="n"/>
-      <c r="O24" s="256" t="n"/>
-      <c r="P24" s="256" t="n"/>
-      <c r="Q24" s="256" t="n"/>
-      <c r="R24" s="257" t="n"/>
-      <c r="S24" s="255" t="n"/>
-      <c r="T24" s="256" t="n"/>
-      <c r="U24" s="256" t="n"/>
-      <c r="V24" s="256" t="n"/>
-      <c r="W24" s="256" t="n"/>
-      <c r="X24" s="256" t="n"/>
-      <c r="Y24" s="257" t="n"/>
-      <c r="Z24" s="255" t="n"/>
-      <c r="AA24" s="256" t="n"/>
-      <c r="AB24" s="256" t="n"/>
-      <c r="AC24" s="256" t="n"/>
-      <c r="AD24" s="256" t="n"/>
-      <c r="AE24" s="256" t="n"/>
-      <c r="AF24" s="257" t="n"/>
-      <c r="AG24" s="255" t="n"/>
-      <c r="AH24" s="256" t="n"/>
-      <c r="AI24" s="256" t="n"/>
-      <c r="AJ24" s="257" t="n"/>
-      <c r="AK24" s="255" t="n"/>
-      <c r="AL24" s="256" t="n"/>
-      <c r="AM24" s="256" t="n"/>
-      <c r="AN24" s="257" t="n"/>
-      <c r="AO24" s="255" t="n"/>
-      <c r="AP24" s="256" t="n"/>
-      <c r="AQ24" s="256" t="n"/>
-      <c r="AR24" s="257" t="n"/>
-      <c r="AS24" s="255" t="n"/>
-      <c r="AT24" s="256" t="n"/>
-      <c r="AU24" s="256" t="n"/>
-      <c r="AV24" s="257" t="n"/>
-      <c r="AW24" s="255" t="n"/>
-      <c r="AX24" s="256" t="n"/>
-      <c r="AY24" s="256" t="n"/>
-      <c r="AZ24" s="257" t="n"/>
-      <c r="BA24" s="255" t="n"/>
-      <c r="BB24" s="256" t="n"/>
-      <c r="BC24" s="256" t="n"/>
-      <c r="BD24" s="259" t="n"/>
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="329" t="n"/>
+      <c r="D24" s="330" t="n"/>
+      <c r="E24" s="330" t="n"/>
+      <c r="F24" s="330" t="n"/>
+      <c r="G24" s="330" t="n"/>
+      <c r="H24" s="331" t="n"/>
+      <c r="I24" s="329" t="n"/>
+      <c r="J24" s="330" t="n"/>
+      <c r="K24" s="330" t="n"/>
+      <c r="L24" s="330" t="n"/>
+      <c r="M24" s="331" t="n"/>
+      <c r="N24" s="329" t="n"/>
+      <c r="O24" s="330" t="n"/>
+      <c r="P24" s="330" t="n"/>
+      <c r="Q24" s="330" t="n"/>
+      <c r="R24" s="331" t="n"/>
+      <c r="S24" s="329" t="n"/>
+      <c r="T24" s="330" t="n"/>
+      <c r="U24" s="330" t="n"/>
+      <c r="V24" s="330" t="n"/>
+      <c r="W24" s="330" t="n"/>
+      <c r="X24" s="330" t="n"/>
+      <c r="Y24" s="331" t="n"/>
+      <c r="Z24" s="329" t="n"/>
+      <c r="AA24" s="330" t="n"/>
+      <c r="AB24" s="330" t="n"/>
+      <c r="AC24" s="330" t="n"/>
+      <c r="AD24" s="330" t="n"/>
+      <c r="AE24" s="330" t="n"/>
+      <c r="AF24" s="331" t="n"/>
+      <c r="AG24" s="329" t="n"/>
+      <c r="AH24" s="330" t="n"/>
+      <c r="AI24" s="330" t="n"/>
+      <c r="AJ24" s="331" t="n"/>
+      <c r="AK24" s="329" t="n"/>
+      <c r="AL24" s="330" t="n"/>
+      <c r="AM24" s="330" t="n"/>
+      <c r="AN24" s="331" t="n"/>
+      <c r="AO24" s="329" t="n"/>
+      <c r="AP24" s="330" t="n"/>
+      <c r="AQ24" s="330" t="n"/>
+      <c r="AR24" s="331" t="n"/>
+      <c r="AS24" s="329" t="n"/>
+      <c r="AT24" s="330" t="n"/>
+      <c r="AU24" s="330" t="n"/>
+      <c r="AV24" s="331" t="n"/>
+      <c r="AW24" s="329" t="n"/>
+      <c r="AX24" s="330" t="n"/>
+      <c r="AY24" s="330" t="n"/>
+      <c r="AZ24" s="331" t="n"/>
+      <c r="BA24" s="333" t="n"/>
+      <c r="BB24" s="330" t="n"/>
+      <c r="BC24" s="330" t="n"/>
+      <c r="BD24" s="334" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="271">
+      <c r="A25" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B25" s="254" t="n"/>
-      <c r="C25" s="272" t="n"/>
-      <c r="D25" s="256" t="n"/>
-      <c r="E25" s="256" t="n"/>
-      <c r="F25" s="256" t="n"/>
-      <c r="G25" s="256" t="n"/>
-      <c r="H25" s="257" t="n"/>
-      <c r="I25" s="272" t="n"/>
-      <c r="J25" s="256" t="n"/>
-      <c r="K25" s="256" t="n"/>
-      <c r="L25" s="256" t="n"/>
-      <c r="M25" s="257" t="n"/>
-      <c r="N25" s="272" t="n"/>
-      <c r="O25" s="256" t="n"/>
-      <c r="P25" s="256" t="n"/>
-      <c r="Q25" s="256" t="n"/>
-      <c r="R25" s="257" t="n"/>
-      <c r="S25" s="272" t="n"/>
-      <c r="T25" s="256" t="n"/>
-      <c r="U25" s="256" t="n"/>
-      <c r="V25" s="256" t="n"/>
-      <c r="W25" s="256" t="n"/>
-      <c r="X25" s="256" t="n"/>
-      <c r="Y25" s="257" t="n"/>
-      <c r="Z25" s="272" t="n"/>
-      <c r="AA25" s="256" t="n"/>
-      <c r="AB25" s="256" t="n"/>
-      <c r="AC25" s="256" t="n"/>
-      <c r="AD25" s="256" t="n"/>
-      <c r="AE25" s="256" t="n"/>
-      <c r="AF25" s="257" t="n"/>
-      <c r="AG25" s="272" t="n"/>
-      <c r="AH25" s="256" t="n"/>
-      <c r="AI25" s="256" t="n"/>
-      <c r="AJ25" s="257" t="n"/>
-      <c r="AK25" s="272" t="n"/>
-      <c r="AL25" s="256" t="n"/>
-      <c r="AM25" s="256" t="n"/>
-      <c r="AN25" s="257" t="n"/>
-      <c r="AO25" s="272" t="n"/>
-      <c r="AP25" s="256" t="n"/>
-      <c r="AQ25" s="256" t="n"/>
-      <c r="AR25" s="257" t="n"/>
-      <c r="AS25" s="272" t="n"/>
-      <c r="AT25" s="256" t="n"/>
-      <c r="AU25" s="256" t="n"/>
-      <c r="AV25" s="257" t="n"/>
-      <c r="AW25" s="272" t="n"/>
-      <c r="AX25" s="256" t="n"/>
-      <c r="AY25" s="256" t="n"/>
-      <c r="AZ25" s="257" t="n"/>
-      <c r="BA25" s="272" t="n"/>
-      <c r="BB25" s="256" t="n"/>
-      <c r="BC25" s="256" t="n"/>
-      <c r="BD25" s="259" t="n"/>
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="346" t="n"/>
+      <c r="D25" s="330" t="n"/>
+      <c r="E25" s="330" t="n"/>
+      <c r="F25" s="330" t="n"/>
+      <c r="G25" s="330" t="n"/>
+      <c r="H25" s="331" t="n"/>
+      <c r="I25" s="346" t="n"/>
+      <c r="J25" s="330" t="n"/>
+      <c r="K25" s="330" t="n"/>
+      <c r="L25" s="330" t="n"/>
+      <c r="M25" s="331" t="n"/>
+      <c r="N25" s="346" t="n"/>
+      <c r="O25" s="330" t="n"/>
+      <c r="P25" s="330" t="n"/>
+      <c r="Q25" s="330" t="n"/>
+      <c r="R25" s="331" t="n"/>
+      <c r="S25" s="346" t="n"/>
+      <c r="T25" s="330" t="n"/>
+      <c r="U25" s="330" t="n"/>
+      <c r="V25" s="330" t="n"/>
+      <c r="W25" s="330" t="n"/>
+      <c r="X25" s="330" t="n"/>
+      <c r="Y25" s="331" t="n"/>
+      <c r="Z25" s="346" t="n"/>
+      <c r="AA25" s="330" t="n"/>
+      <c r="AB25" s="330" t="n"/>
+      <c r="AC25" s="330" t="n"/>
+      <c r="AD25" s="330" t="n"/>
+      <c r="AE25" s="330" t="n"/>
+      <c r="AF25" s="331" t="n"/>
+      <c r="AG25" s="346" t="n"/>
+      <c r="AH25" s="330" t="n"/>
+      <c r="AI25" s="330" t="n"/>
+      <c r="AJ25" s="331" t="n"/>
+      <c r="AK25" s="346" t="n"/>
+      <c r="AL25" s="330" t="n"/>
+      <c r="AM25" s="330" t="n"/>
+      <c r="AN25" s="331" t="n"/>
+      <c r="AO25" s="346" t="n"/>
+      <c r="AP25" s="330" t="n"/>
+      <c r="AQ25" s="330" t="n"/>
+      <c r="AR25" s="331" t="n"/>
+      <c r="AS25" s="346" t="n"/>
+      <c r="AT25" s="330" t="n"/>
+      <c r="AU25" s="330" t="n"/>
+      <c r="AV25" s="331" t="n"/>
+      <c r="AW25" s="346" t="n"/>
+      <c r="AX25" s="330" t="n"/>
+      <c r="AY25" s="330" t="n"/>
+      <c r="AZ25" s="331" t="n"/>
+      <c r="BA25" s="347" t="n"/>
+      <c r="BB25" s="330" t="n"/>
+      <c r="BC25" s="330" t="n"/>
+      <c r="BD25" s="334" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="271">
+      <c r="A26" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B26" s="254" t="n"/>
-      <c r="C26" s="255" t="n"/>
-      <c r="D26" s="256" t="n"/>
-      <c r="E26" s="256" t="n"/>
-      <c r="F26" s="256" t="n"/>
-      <c r="G26" s="256" t="n"/>
-      <c r="H26" s="257" t="n"/>
-      <c r="I26" s="255" t="n"/>
-      <c r="J26" s="256" t="n"/>
-      <c r="K26" s="256" t="n"/>
-      <c r="L26" s="256" t="n"/>
-      <c r="M26" s="257" t="n"/>
-      <c r="N26" s="255" t="n"/>
-      <c r="O26" s="256" t="n"/>
-      <c r="P26" s="256" t="n"/>
-      <c r="Q26" s="256" t="n"/>
-      <c r="R26" s="257" t="n"/>
-      <c r="S26" s="255" t="n"/>
-      <c r="T26" s="256" t="n"/>
-      <c r="U26" s="256" t="n"/>
-      <c r="V26" s="256" t="n"/>
-      <c r="W26" s="256" t="n"/>
-      <c r="X26" s="256" t="n"/>
-      <c r="Y26" s="257" t="n"/>
-      <c r="Z26" s="255" t="n"/>
-      <c r="AA26" s="256" t="n"/>
-      <c r="AB26" s="256" t="n"/>
-      <c r="AC26" s="256" t="n"/>
-      <c r="AD26" s="256" t="n"/>
-      <c r="AE26" s="256" t="n"/>
-      <c r="AF26" s="257" t="n"/>
-      <c r="AG26" s="255" t="n"/>
-      <c r="AH26" s="256" t="n"/>
-      <c r="AI26" s="256" t="n"/>
-      <c r="AJ26" s="257" t="n"/>
-      <c r="AK26" s="255" t="n"/>
-      <c r="AL26" s="256" t="n"/>
-      <c r="AM26" s="256" t="n"/>
-      <c r="AN26" s="257" t="n"/>
-      <c r="AO26" s="255" t="n"/>
-      <c r="AP26" s="256" t="n"/>
-      <c r="AQ26" s="256" t="n"/>
-      <c r="AR26" s="257" t="n"/>
-      <c r="AS26" s="255" t="n"/>
-      <c r="AT26" s="256" t="n"/>
-      <c r="AU26" s="256" t="n"/>
-      <c r="AV26" s="257" t="n"/>
-      <c r="AW26" s="255" t="n"/>
-      <c r="AX26" s="256" t="n"/>
-      <c r="AY26" s="256" t="n"/>
-      <c r="AZ26" s="257" t="n"/>
-      <c r="BA26" s="255" t="n"/>
-      <c r="BB26" s="256" t="n"/>
-      <c r="BC26" s="256" t="n"/>
-      <c r="BD26" s="259" t="n"/>
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="329" t="n"/>
+      <c r="D26" s="330" t="n"/>
+      <c r="E26" s="330" t="n"/>
+      <c r="F26" s="330" t="n"/>
+      <c r="G26" s="330" t="n"/>
+      <c r="H26" s="331" t="n"/>
+      <c r="I26" s="329" t="n"/>
+      <c r="J26" s="330" t="n"/>
+      <c r="K26" s="330" t="n"/>
+      <c r="L26" s="330" t="n"/>
+      <c r="M26" s="331" t="n"/>
+      <c r="N26" s="329" t="n"/>
+      <c r="O26" s="330" t="n"/>
+      <c r="P26" s="330" t="n"/>
+      <c r="Q26" s="330" t="n"/>
+      <c r="R26" s="331" t="n"/>
+      <c r="S26" s="329" t="n"/>
+      <c r="T26" s="330" t="n"/>
+      <c r="U26" s="330" t="n"/>
+      <c r="V26" s="330" t="n"/>
+      <c r="W26" s="330" t="n"/>
+      <c r="X26" s="330" t="n"/>
+      <c r="Y26" s="331" t="n"/>
+      <c r="Z26" s="329" t="n"/>
+      <c r="AA26" s="330" t="n"/>
+      <c r="AB26" s="330" t="n"/>
+      <c r="AC26" s="330" t="n"/>
+      <c r="AD26" s="330" t="n"/>
+      <c r="AE26" s="330" t="n"/>
+      <c r="AF26" s="331" t="n"/>
+      <c r="AG26" s="329" t="n"/>
+      <c r="AH26" s="330" t="n"/>
+      <c r="AI26" s="330" t="n"/>
+      <c r="AJ26" s="331" t="n"/>
+      <c r="AK26" s="329" t="n"/>
+      <c r="AL26" s="330" t="n"/>
+      <c r="AM26" s="330" t="n"/>
+      <c r="AN26" s="331" t="n"/>
+      <c r="AO26" s="329" t="n"/>
+      <c r="AP26" s="330" t="n"/>
+      <c r="AQ26" s="330" t="n"/>
+      <c r="AR26" s="331" t="n"/>
+      <c r="AS26" s="329" t="n"/>
+      <c r="AT26" s="330" t="n"/>
+      <c r="AU26" s="330" t="n"/>
+      <c r="AV26" s="331" t="n"/>
+      <c r="AW26" s="329" t="n"/>
+      <c r="AX26" s="330" t="n"/>
+      <c r="AY26" s="330" t="n"/>
+      <c r="AZ26" s="331" t="n"/>
+      <c r="BA26" s="333" t="n"/>
+      <c r="BB26" s="330" t="n"/>
+      <c r="BC26" s="330" t="n"/>
+      <c r="BD26" s="334" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="271">
+      <c r="A27" s="345">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B27" s="254" t="n"/>
-      <c r="C27" s="272" t="n"/>
-      <c r="D27" s="256" t="n"/>
-      <c r="E27" s="256" t="n"/>
-      <c r="F27" s="256" t="n"/>
-      <c r="G27" s="256" t="n"/>
-      <c r="H27" s="257" t="n"/>
-      <c r="I27" s="272" t="n"/>
-      <c r="J27" s="256" t="n"/>
-      <c r="K27" s="256" t="n"/>
-      <c r="L27" s="256" t="n"/>
-      <c r="M27" s="257" t="n"/>
-      <c r="N27" s="272" t="n"/>
-      <c r="O27" s="256" t="n"/>
-      <c r="P27" s="256" t="n"/>
-      <c r="Q27" s="256" t="n"/>
-      <c r="R27" s="257" t="n"/>
-      <c r="S27" s="272" t="n"/>
-      <c r="T27" s="256" t="n"/>
-      <c r="U27" s="256" t="n"/>
-      <c r="V27" s="256" t="n"/>
-      <c r="W27" s="256" t="n"/>
-      <c r="X27" s="256" t="n"/>
-      <c r="Y27" s="257" t="n"/>
-      <c r="Z27" s="272" t="n"/>
-      <c r="AA27" s="256" t="n"/>
-      <c r="AB27" s="256" t="n"/>
-      <c r="AC27" s="256" t="n"/>
-      <c r="AD27" s="256" t="n"/>
-      <c r="AE27" s="256" t="n"/>
-      <c r="AF27" s="257" t="n"/>
-      <c r="AG27" s="272" t="n"/>
-      <c r="AH27" s="256" t="n"/>
-      <c r="AI27" s="256" t="n"/>
-      <c r="AJ27" s="257" t="n"/>
-      <c r="AK27" s="272" t="n"/>
-      <c r="AL27" s="256" t="n"/>
-      <c r="AM27" s="256" t="n"/>
-      <c r="AN27" s="257" t="n"/>
-      <c r="AO27" s="272" t="n"/>
-      <c r="AP27" s="256" t="n"/>
-      <c r="AQ27" s="256" t="n"/>
-      <c r="AR27" s="257" t="n"/>
-      <c r="AS27" s="272" t="n"/>
-      <c r="AT27" s="256" t="n"/>
-      <c r="AU27" s="256" t="n"/>
-      <c r="AV27" s="257" t="n"/>
-      <c r="AW27" s="272" t="n"/>
-      <c r="AX27" s="256" t="n"/>
-      <c r="AY27" s="256" t="n"/>
-      <c r="AZ27" s="257" t="n"/>
-      <c r="BA27" s="272" t="n"/>
-      <c r="BB27" s="256" t="n"/>
-      <c r="BC27" s="256" t="n"/>
-      <c r="BD27" s="259" t="n"/>
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="346" t="n"/>
+      <c r="D27" s="330" t="n"/>
+      <c r="E27" s="330" t="n"/>
+      <c r="F27" s="330" t="n"/>
+      <c r="G27" s="330" t="n"/>
+      <c r="H27" s="331" t="n"/>
+      <c r="I27" s="346" t="n"/>
+      <c r="J27" s="330" t="n"/>
+      <c r="K27" s="330" t="n"/>
+      <c r="L27" s="330" t="n"/>
+      <c r="M27" s="331" t="n"/>
+      <c r="N27" s="346" t="n"/>
+      <c r="O27" s="330" t="n"/>
+      <c r="P27" s="330" t="n"/>
+      <c r="Q27" s="330" t="n"/>
+      <c r="R27" s="331" t="n"/>
+      <c r="S27" s="346" t="n"/>
+      <c r="T27" s="330" t="n"/>
+      <c r="U27" s="330" t="n"/>
+      <c r="V27" s="330" t="n"/>
+      <c r="W27" s="330" t="n"/>
+      <c r="X27" s="330" t="n"/>
+      <c r="Y27" s="331" t="n"/>
+      <c r="Z27" s="346" t="n"/>
+      <c r="AA27" s="330" t="n"/>
+      <c r="AB27" s="330" t="n"/>
+      <c r="AC27" s="330" t="n"/>
+      <c r="AD27" s="330" t="n"/>
+      <c r="AE27" s="330" t="n"/>
+      <c r="AF27" s="331" t="n"/>
+      <c r="AG27" s="346" t="n"/>
+      <c r="AH27" s="330" t="n"/>
+      <c r="AI27" s="330" t="n"/>
+      <c r="AJ27" s="331" t="n"/>
+      <c r="AK27" s="346" t="n"/>
+      <c r="AL27" s="330" t="n"/>
+      <c r="AM27" s="330" t="n"/>
+      <c r="AN27" s="331" t="n"/>
+      <c r="AO27" s="346" t="n"/>
+      <c r="AP27" s="330" t="n"/>
+      <c r="AQ27" s="330" t="n"/>
+      <c r="AR27" s="331" t="n"/>
+      <c r="AS27" s="346" t="n"/>
+      <c r="AT27" s="330" t="n"/>
+      <c r="AU27" s="330" t="n"/>
+      <c r="AV27" s="331" t="n"/>
+      <c r="AW27" s="346" t="n"/>
+      <c r="AX27" s="330" t="n"/>
+      <c r="AY27" s="330" t="n"/>
+      <c r="AZ27" s="331" t="n"/>
+      <c r="BA27" s="347" t="n"/>
+      <c r="BB27" s="330" t="n"/>
+      <c r="BC27" s="330" t="n"/>
+      <c r="BD27" s="334" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="273">
+      <c r="A28" s="348">
         <f>ROW()-ROW($A$14)+1</f>
         <v/>
       </c>
-      <c r="B28" s="261" t="n"/>
-      <c r="C28" s="262" t="n"/>
-      <c r="D28" s="263" t="n"/>
-      <c r="E28" s="263" t="n"/>
-      <c r="F28" s="263" t="n"/>
-      <c r="G28" s="263" t="n"/>
-      <c r="H28" s="264" t="n"/>
-      <c r="I28" s="262" t="n"/>
-      <c r="J28" s="263" t="n"/>
-      <c r="K28" s="263" t="n"/>
-      <c r="L28" s="263" t="n"/>
-      <c r="M28" s="264" t="n"/>
-      <c r="N28" s="262" t="n"/>
-      <c r="O28" s="263" t="n"/>
-      <c r="P28" s="263" t="n"/>
-      <c r="Q28" s="263" t="n"/>
-      <c r="R28" s="264" t="n"/>
-      <c r="S28" s="262" t="n"/>
-      <c r="T28" s="263" t="n"/>
-      <c r="U28" s="263" t="n"/>
-      <c r="V28" s="263" t="n"/>
-      <c r="W28" s="263" t="n"/>
-      <c r="X28" s="263" t="n"/>
-      <c r="Y28" s="264" t="n"/>
-      <c r="Z28" s="262" t="n"/>
-      <c r="AA28" s="263" t="n"/>
-      <c r="AB28" s="263" t="n"/>
-      <c r="AC28" s="263" t="n"/>
-      <c r="AD28" s="263" t="n"/>
-      <c r="AE28" s="263" t="n"/>
-      <c r="AF28" s="264" t="n"/>
-      <c r="AG28" s="262" t="n"/>
-      <c r="AH28" s="263" t="n"/>
-      <c r="AI28" s="263" t="n"/>
-      <c r="AJ28" s="264" t="n"/>
-      <c r="AK28" s="262" t="n"/>
-      <c r="AL28" s="263" t="n"/>
-      <c r="AM28" s="263" t="n"/>
-      <c r="AN28" s="264" t="n"/>
-      <c r="AO28" s="262" t="n"/>
-      <c r="AP28" s="263" t="n"/>
-      <c r="AQ28" s="263" t="n"/>
-      <c r="AR28" s="264" t="n"/>
-      <c r="AS28" s="262" t="n"/>
-      <c r="AT28" s="263" t="n"/>
-      <c r="AU28" s="263" t="n"/>
-      <c r="AV28" s="264" t="n"/>
-      <c r="AW28" s="262" t="n"/>
-      <c r="AX28" s="263" t="n"/>
-      <c r="AY28" s="263" t="n"/>
-      <c r="AZ28" s="264" t="n"/>
-      <c r="BA28" s="262" t="n"/>
-      <c r="BB28" s="263" t="n"/>
-      <c r="BC28" s="263" t="n"/>
-      <c r="BD28" s="266" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="336" t="n"/>
+      <c r="D28" s="337" t="n"/>
+      <c r="E28" s="337" t="n"/>
+      <c r="F28" s="337" t="n"/>
+      <c r="G28" s="337" t="n"/>
+      <c r="H28" s="338" t="n"/>
+      <c r="I28" s="336" t="n"/>
+      <c r="J28" s="337" t="n"/>
+      <c r="K28" s="337" t="n"/>
+      <c r="L28" s="337" t="n"/>
+      <c r="M28" s="338" t="n"/>
+      <c r="N28" s="336" t="n"/>
+      <c r="O28" s="337" t="n"/>
+      <c r="P28" s="337" t="n"/>
+      <c r="Q28" s="337" t="n"/>
+      <c r="R28" s="338" t="n"/>
+      <c r="S28" s="336" t="n"/>
+      <c r="T28" s="337" t="n"/>
+      <c r="U28" s="337" t="n"/>
+      <c r="V28" s="337" t="n"/>
+      <c r="W28" s="337" t="n"/>
+      <c r="X28" s="337" t="n"/>
+      <c r="Y28" s="338" t="n"/>
+      <c r="Z28" s="336" t="n"/>
+      <c r="AA28" s="337" t="n"/>
+      <c r="AB28" s="337" t="n"/>
+      <c r="AC28" s="337" t="n"/>
+      <c r="AD28" s="337" t="n"/>
+      <c r="AE28" s="337" t="n"/>
+      <c r="AF28" s="338" t="n"/>
+      <c r="AG28" s="336" t="n"/>
+      <c r="AH28" s="337" t="n"/>
+      <c r="AI28" s="337" t="n"/>
+      <c r="AJ28" s="338" t="n"/>
+      <c r="AK28" s="336" t="n"/>
+      <c r="AL28" s="337" t="n"/>
+      <c r="AM28" s="337" t="n"/>
+      <c r="AN28" s="338" t="n"/>
+      <c r="AO28" s="336" t="n"/>
+      <c r="AP28" s="337" t="n"/>
+      <c r="AQ28" s="337" t="n"/>
+      <c r="AR28" s="338" t="n"/>
+      <c r="AS28" s="336" t="n"/>
+      <c r="AT28" s="337" t="n"/>
+      <c r="AU28" s="337" t="n"/>
+      <c r="AV28" s="338" t="n"/>
+      <c r="AW28" s="336" t="n"/>
+      <c r="AX28" s="337" t="n"/>
+      <c r="AY28" s="337" t="n"/>
+      <c r="AZ28" s="338" t="n"/>
+      <c r="BA28" s="340" t="n"/>
+      <c r="BB28" s="337" t="n"/>
+      <c r="BC28" s="337" t="n"/>
+      <c r="BD28" s="341" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="241" t="inlineStr">
+      <c r="A29" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. PERIODIC REVIEW / CLOSURE</t>
         </is>
       </c>
-      <c r="B29" s="242" t="n"/>
-      <c r="C29" s="242" t="n"/>
-      <c r="D29" s="242" t="n"/>
-      <c r="E29" s="242" t="n"/>
-      <c r="F29" s="242" t="n"/>
-      <c r="G29" s="242" t="n"/>
-      <c r="H29" s="242" t="n"/>
-      <c r="I29" s="242" t="n"/>
-      <c r="J29" s="242" t="n"/>
-      <c r="K29" s="242" t="n"/>
-      <c r="L29" s="242" t="n"/>
-      <c r="M29" s="242" t="n"/>
-      <c r="N29" s="242" t="n"/>
-      <c r="O29" s="242" t="n"/>
-      <c r="P29" s="242" t="n"/>
-      <c r="Q29" s="242" t="n"/>
-      <c r="R29" s="242" t="n"/>
-      <c r="S29" s="242" t="n"/>
-      <c r="T29" s="242" t="n"/>
-      <c r="U29" s="242" t="n"/>
-      <c r="V29" s="242" t="n"/>
-      <c r="W29" s="242" t="n"/>
-      <c r="X29" s="242" t="n"/>
-      <c r="Y29" s="242" t="n"/>
-      <c r="Z29" s="242" t="n"/>
-      <c r="AA29" s="242" t="n"/>
-      <c r="AB29" s="242" t="n"/>
-      <c r="AC29" s="242" t="n"/>
-      <c r="AD29" s="242" t="n"/>
-      <c r="AE29" s="242" t="n"/>
-      <c r="AF29" s="242" t="n"/>
-      <c r="AG29" s="242" t="n"/>
-      <c r="AH29" s="242" t="n"/>
-      <c r="AI29" s="242" t="n"/>
-      <c r="AJ29" s="242" t="n"/>
-      <c r="AK29" s="242" t="n"/>
-      <c r="AL29" s="242" t="n"/>
-      <c r="AM29" s="242" t="n"/>
-      <c r="AN29" s="242" t="n"/>
-      <c r="AO29" s="242" t="n"/>
-      <c r="AP29" s="242" t="n"/>
-      <c r="AQ29" s="242" t="n"/>
-      <c r="AR29" s="242" t="n"/>
-      <c r="AS29" s="242" t="n"/>
-      <c r="AT29" s="242" t="n"/>
-      <c r="AU29" s="242" t="n"/>
-      <c r="AV29" s="242" t="n"/>
-      <c r="AW29" s="242" t="n"/>
-      <c r="AX29" s="242" t="n"/>
-      <c r="AY29" s="242" t="n"/>
-      <c r="AZ29" s="242" t="n"/>
-      <c r="BA29" s="242" t="n"/>
-      <c r="BB29" s="242" t="n"/>
-      <c r="BC29" s="242" t="n"/>
-      <c r="BD29" s="243" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="6" t="n"/>
+      <c r="K29" s="6" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="6" t="n"/>
+      <c r="T29" s="6" t="n"/>
+      <c r="U29" s="6" t="n"/>
+      <c r="V29" s="6" t="n"/>
+      <c r="W29" s="6" t="n"/>
+      <c r="X29" s="6" t="n"/>
+      <c r="Y29" s="6" t="n"/>
+      <c r="Z29" s="6" t="n"/>
+      <c r="AA29" s="6" t="n"/>
+      <c r="AB29" s="6" t="n"/>
+      <c r="AC29" s="6" t="n"/>
+      <c r="AD29" s="6" t="n"/>
+      <c r="AE29" s="6" t="n"/>
+      <c r="AF29" s="6" t="n"/>
+      <c r="AG29" s="6" t="n"/>
+      <c r="AH29" s="6" t="n"/>
+      <c r="AI29" s="6" t="n"/>
+      <c r="AJ29" s="6" t="n"/>
+      <c r="AK29" s="6" t="n"/>
+      <c r="AL29" s="6" t="n"/>
+      <c r="AM29" s="6" t="n"/>
+      <c r="AN29" s="6" t="n"/>
+      <c r="AO29" s="6" t="n"/>
+      <c r="AP29" s="6" t="n"/>
+      <c r="AQ29" s="6" t="n"/>
+      <c r="AR29" s="6" t="n"/>
+      <c r="AS29" s="6" t="n"/>
+      <c r="AT29" s="6" t="n"/>
+      <c r="AU29" s="6" t="n"/>
+      <c r="AV29" s="6" t="n"/>
+      <c r="AW29" s="6" t="n"/>
+      <c r="AX29" s="6" t="n"/>
+      <c r="AY29" s="6" t="n"/>
+      <c r="AZ29" s="6" t="n"/>
+      <c r="BA29" s="6" t="n"/>
+      <c r="BB29" s="6" t="n"/>
+      <c r="BC29" s="6" t="n"/>
+      <c r="BD29" s="7" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="244" t="inlineStr">
+      <c r="A30" s="321" t="inlineStr">
         <is>
           <t>Review Date</t>
         </is>
       </c>
-      <c r="B30" s="245" t="n"/>
-      <c r="C30" s="245" t="n"/>
-      <c r="D30" s="245" t="n"/>
-      <c r="E30" s="245" t="n"/>
-      <c r="F30" s="245" t="n"/>
-      <c r="G30" s="245" t="n"/>
-      <c r="H30" s="245" t="n"/>
-      <c r="I30" s="245" t="n"/>
-      <c r="J30" s="246" t="n"/>
-      <c r="K30" s="247" t="n"/>
-      <c r="L30" s="248" t="n"/>
-      <c r="M30" s="248" t="n"/>
-      <c r="N30" s="248" t="n"/>
-      <c r="O30" s="248" t="n"/>
-      <c r="P30" s="248" t="n"/>
-      <c r="Q30" s="248" t="n"/>
-      <c r="R30" s="248" t="n"/>
-      <c r="S30" s="248" t="n"/>
-      <c r="T30" s="248" t="n"/>
-      <c r="U30" s="248" t="n"/>
-      <c r="V30" s="248" t="n"/>
-      <c r="W30" s="248" t="n"/>
-      <c r="X30" s="248" t="n"/>
-      <c r="Y30" s="248" t="n"/>
-      <c r="Z30" s="248" t="n"/>
-      <c r="AA30" s="248" t="n"/>
-      <c r="AB30" s="249" t="n"/>
-      <c r="AC30" s="250" t="inlineStr">
+      <c r="B30" s="31" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="32" t="n"/>
+      <c r="K30" s="322" t="n"/>
+      <c r="L30" s="323" t="n"/>
+      <c r="M30" s="323" t="n"/>
+      <c r="N30" s="323" t="n"/>
+      <c r="O30" s="323" t="n"/>
+      <c r="P30" s="323" t="n"/>
+      <c r="Q30" s="323" t="n"/>
+      <c r="R30" s="323" t="n"/>
+      <c r="S30" s="323" t="n"/>
+      <c r="T30" s="323" t="n"/>
+      <c r="U30" s="323" t="n"/>
+      <c r="V30" s="323" t="n"/>
+      <c r="W30" s="323" t="n"/>
+      <c r="X30" s="323" t="n"/>
+      <c r="Y30" s="323" t="n"/>
+      <c r="Z30" s="323" t="n"/>
+      <c r="AA30" s="323" t="n"/>
+      <c r="AB30" s="324" t="n"/>
+      <c r="AC30" s="325" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="AD30" s="245" t="n"/>
-      <c r="AE30" s="245" t="n"/>
-      <c r="AF30" s="245" t="n"/>
-      <c r="AG30" s="245" t="n"/>
-      <c r="AH30" s="245" t="n"/>
-      <c r="AI30" s="245" t="n"/>
-      <c r="AJ30" s="245" t="n"/>
-      <c r="AK30" s="245" t="n"/>
-      <c r="AL30" s="246" t="n"/>
-      <c r="AM30" s="247" t="n"/>
-      <c r="AN30" s="248" t="n"/>
-      <c r="AO30" s="248" t="n"/>
-      <c r="AP30" s="248" t="n"/>
-      <c r="AQ30" s="248" t="n"/>
-      <c r="AR30" s="248" t="n"/>
-      <c r="AS30" s="248" t="n"/>
-      <c r="AT30" s="248" t="n"/>
-      <c r="AU30" s="248" t="n"/>
-      <c r="AV30" s="248" t="n"/>
-      <c r="AW30" s="248" t="n"/>
-      <c r="AX30" s="248" t="n"/>
-      <c r="AY30" s="248" t="n"/>
-      <c r="AZ30" s="248" t="n"/>
-      <c r="BA30" s="248" t="n"/>
-      <c r="BB30" s="248" t="n"/>
-      <c r="BC30" s="248" t="n"/>
-      <c r="BD30" s="251" t="n"/>
+      <c r="AD30" s="31" t="n"/>
+      <c r="AE30" s="31" t="n"/>
+      <c r="AF30" s="31" t="n"/>
+      <c r="AG30" s="31" t="n"/>
+      <c r="AH30" s="31" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="31" t="n"/>
+      <c r="AL30" s="32" t="n"/>
+      <c r="AM30" s="326" t="n"/>
+      <c r="AN30" s="323" t="n"/>
+      <c r="AO30" s="323" t="n"/>
+      <c r="AP30" s="323" t="n"/>
+      <c r="AQ30" s="323" t="n"/>
+      <c r="AR30" s="323" t="n"/>
+      <c r="AS30" s="323" t="n"/>
+      <c r="AT30" s="323" t="n"/>
+      <c r="AU30" s="323" t="n"/>
+      <c r="AV30" s="323" t="n"/>
+      <c r="AW30" s="323" t="n"/>
+      <c r="AX30" s="323" t="n"/>
+      <c r="AY30" s="323" t="n"/>
+      <c r="AZ30" s="323" t="n"/>
+      <c r="BA30" s="323" t="n"/>
+      <c r="BB30" s="323" t="n"/>
+      <c r="BC30" s="323" t="n"/>
+      <c r="BD30" s="327" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="252" t="inlineStr">
+      <c r="A31" s="328" t="inlineStr">
         <is>
           <t>Escalated CSR Items</t>
         </is>
       </c>
-      <c r="B31" s="253" t="n"/>
-      <c r="C31" s="253" t="n"/>
-      <c r="D31" s="253" t="n"/>
-      <c r="E31" s="253" t="n"/>
-      <c r="F31" s="253" t="n"/>
-      <c r="G31" s="253" t="n"/>
-      <c r="H31" s="253" t="n"/>
-      <c r="I31" s="253" t="n"/>
-      <c r="J31" s="254" t="n"/>
-      <c r="K31" s="255" t="n"/>
-      <c r="L31" s="256" t="n"/>
-      <c r="M31" s="256" t="n"/>
-      <c r="N31" s="256" t="n"/>
-      <c r="O31" s="256" t="n"/>
-      <c r="P31" s="256" t="n"/>
-      <c r="Q31" s="256" t="n"/>
-      <c r="R31" s="256" t="n"/>
-      <c r="S31" s="256" t="n"/>
-      <c r="T31" s="256" t="n"/>
-      <c r="U31" s="256" t="n"/>
-      <c r="V31" s="256" t="n"/>
-      <c r="W31" s="256" t="n"/>
-      <c r="X31" s="256" t="n"/>
-      <c r="Y31" s="256" t="n"/>
-      <c r="Z31" s="256" t="n"/>
-      <c r="AA31" s="256" t="n"/>
-      <c r="AB31" s="257" t="n"/>
-      <c r="AC31" s="258" t="inlineStr">
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n"/>
+      <c r="H31" s="36" t="n"/>
+      <c r="I31" s="36" t="n"/>
+      <c r="J31" s="37" t="n"/>
+      <c r="K31" s="329" t="n"/>
+      <c r="L31" s="330" t="n"/>
+      <c r="M31" s="330" t="n"/>
+      <c r="N31" s="330" t="n"/>
+      <c r="O31" s="330" t="n"/>
+      <c r="P31" s="330" t="n"/>
+      <c r="Q31" s="330" t="n"/>
+      <c r="R31" s="330" t="n"/>
+      <c r="S31" s="330" t="n"/>
+      <c r="T31" s="330" t="n"/>
+      <c r="U31" s="330" t="n"/>
+      <c r="V31" s="330" t="n"/>
+      <c r="W31" s="330" t="n"/>
+      <c r="X31" s="330" t="n"/>
+      <c r="Y31" s="330" t="n"/>
+      <c r="Z31" s="330" t="n"/>
+      <c r="AA31" s="330" t="n"/>
+      <c r="AB31" s="331" t="n"/>
+      <c r="AC31" s="332" t="inlineStr">
         <is>
           <t>Final Status</t>
         </is>
       </c>
-      <c r="AD31" s="253" t="n"/>
-      <c r="AE31" s="253" t="n"/>
-      <c r="AF31" s="253" t="n"/>
-      <c r="AG31" s="253" t="n"/>
-      <c r="AH31" s="253" t="n"/>
-      <c r="AI31" s="253" t="n"/>
-      <c r="AJ31" s="253" t="n"/>
-      <c r="AK31" s="253" t="n"/>
-      <c r="AL31" s="254" t="n"/>
-      <c r="AM31" s="255" t="n"/>
-      <c r="AN31" s="256" t="n"/>
-      <c r="AO31" s="256" t="n"/>
-      <c r="AP31" s="256" t="n"/>
-      <c r="AQ31" s="256" t="n"/>
-      <c r="AR31" s="256" t="n"/>
-      <c r="AS31" s="256" t="n"/>
-      <c r="AT31" s="256" t="n"/>
-      <c r="AU31" s="256" t="n"/>
-      <c r="AV31" s="256" t="n"/>
-      <c r="AW31" s="256" t="n"/>
-      <c r="AX31" s="256" t="n"/>
-      <c r="AY31" s="256" t="n"/>
-      <c r="AZ31" s="256" t="n"/>
-      <c r="BA31" s="256" t="n"/>
-      <c r="BB31" s="256" t="n"/>
-      <c r="BC31" s="256" t="n"/>
-      <c r="BD31" s="259" t="n"/>
+      <c r="AD31" s="36" t="n"/>
+      <c r="AE31" s="36" t="n"/>
+      <c r="AF31" s="36" t="n"/>
+      <c r="AG31" s="36" t="n"/>
+      <c r="AH31" s="36" t="n"/>
+      <c r="AI31" s="36" t="n"/>
+      <c r="AJ31" s="36" t="n"/>
+      <c r="AK31" s="36" t="n"/>
+      <c r="AL31" s="37" t="n"/>
+      <c r="AM31" s="333" t="n"/>
+      <c r="AN31" s="330" t="n"/>
+      <c r="AO31" s="330" t="n"/>
+      <c r="AP31" s="330" t="n"/>
+      <c r="AQ31" s="330" t="n"/>
+      <c r="AR31" s="330" t="n"/>
+      <c r="AS31" s="330" t="n"/>
+      <c r="AT31" s="330" t="n"/>
+      <c r="AU31" s="330" t="n"/>
+      <c r="AV31" s="330" t="n"/>
+      <c r="AW31" s="330" t="n"/>
+      <c r="AX31" s="330" t="n"/>
+      <c r="AY31" s="330" t="n"/>
+      <c r="AZ31" s="330" t="n"/>
+      <c r="BA31" s="330" t="n"/>
+      <c r="BB31" s="330" t="n"/>
+      <c r="BC31" s="330" t="n"/>
+      <c r="BD31" s="334" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="260" t="inlineStr">
+      <c r="A32" s="335" t="inlineStr">
         <is>
           <t>Retention / Archive Ref</t>
         </is>
       </c>
-      <c r="B32" s="233" t="n"/>
-      <c r="C32" s="233" t="n"/>
-      <c r="D32" s="233" t="n"/>
-      <c r="E32" s="233" t="n"/>
-      <c r="F32" s="233" t="n"/>
-      <c r="G32" s="233" t="n"/>
-      <c r="H32" s="233" t="n"/>
-      <c r="I32" s="233" t="n"/>
-      <c r="J32" s="261" t="n"/>
-      <c r="K32" s="262" t="n"/>
-      <c r="L32" s="263" t="n"/>
-      <c r="M32" s="263" t="n"/>
-      <c r="N32" s="263" t="n"/>
-      <c r="O32" s="263" t="n"/>
-      <c r="P32" s="263" t="n"/>
-      <c r="Q32" s="263" t="n"/>
-      <c r="R32" s="263" t="n"/>
-      <c r="S32" s="263" t="n"/>
-      <c r="T32" s="263" t="n"/>
-      <c r="U32" s="263" t="n"/>
-      <c r="V32" s="263" t="n"/>
-      <c r="W32" s="263" t="n"/>
-      <c r="X32" s="263" t="n"/>
-      <c r="Y32" s="263" t="n"/>
-      <c r="Z32" s="263" t="n"/>
-      <c r="AA32" s="263" t="n"/>
-      <c r="AB32" s="264" t="n"/>
-      <c r="AC32" s="265" t="inlineStr">
+      <c r="B32" s="13" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="13" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="13" t="n"/>
+      <c r="G32" s="13" t="n"/>
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="13" t="n"/>
+      <c r="J32" s="44" t="n"/>
+      <c r="K32" s="336" t="n"/>
+      <c r="L32" s="337" t="n"/>
+      <c r="M32" s="337" t="n"/>
+      <c r="N32" s="337" t="n"/>
+      <c r="O32" s="337" t="n"/>
+      <c r="P32" s="337" t="n"/>
+      <c r="Q32" s="337" t="n"/>
+      <c r="R32" s="337" t="n"/>
+      <c r="S32" s="337" t="n"/>
+      <c r="T32" s="337" t="n"/>
+      <c r="U32" s="337" t="n"/>
+      <c r="V32" s="337" t="n"/>
+      <c r="W32" s="337" t="n"/>
+      <c r="X32" s="337" t="n"/>
+      <c r="Y32" s="337" t="n"/>
+      <c r="Z32" s="337" t="n"/>
+      <c r="AA32" s="337" t="n"/>
+      <c r="AB32" s="338" t="n"/>
+      <c r="AC32" s="339" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="AD32" s="233" t="n"/>
-      <c r="AE32" s="233" t="n"/>
-      <c r="AF32" s="233" t="n"/>
-      <c r="AG32" s="233" t="n"/>
-      <c r="AH32" s="233" t="n"/>
-      <c r="AI32" s="233" t="n"/>
-      <c r="AJ32" s="233" t="n"/>
-      <c r="AK32" s="233" t="n"/>
-      <c r="AL32" s="261" t="n"/>
-      <c r="AM32" s="262" t="n"/>
-      <c r="AN32" s="263" t="n"/>
-      <c r="AO32" s="263" t="n"/>
-      <c r="AP32" s="263" t="n"/>
-      <c r="AQ32" s="263" t="n"/>
-      <c r="AR32" s="263" t="n"/>
-      <c r="AS32" s="263" t="n"/>
-      <c r="AT32" s="263" t="n"/>
-      <c r="AU32" s="263" t="n"/>
-      <c r="AV32" s="263" t="n"/>
-      <c r="AW32" s="263" t="n"/>
-      <c r="AX32" s="263" t="n"/>
-      <c r="AY32" s="263" t="n"/>
-      <c r="AZ32" s="263" t="n"/>
-      <c r="BA32" s="263" t="n"/>
-      <c r="BB32" s="263" t="n"/>
-      <c r="BC32" s="263" t="n"/>
-      <c r="BD32" s="266" t="n"/>
+      <c r="AD32" s="13" t="n"/>
+      <c r="AE32" s="13" t="n"/>
+      <c r="AF32" s="13" t="n"/>
+      <c r="AG32" s="13" t="n"/>
+      <c r="AH32" s="13" t="n"/>
+      <c r="AI32" s="13" t="n"/>
+      <c r="AJ32" s="13" t="n"/>
+      <c r="AK32" s="13" t="n"/>
+      <c r="AL32" s="44" t="n"/>
+      <c r="AM32" s="340" t="n"/>
+      <c r="AN32" s="337" t="n"/>
+      <c r="AO32" s="337" t="n"/>
+      <c r="AP32" s="337" t="n"/>
+      <c r="AQ32" s="337" t="n"/>
+      <c r="AR32" s="337" t="n"/>
+      <c r="AS32" s="337" t="n"/>
+      <c r="AT32" s="337" t="n"/>
+      <c r="AU32" s="337" t="n"/>
+      <c r="AV32" s="337" t="n"/>
+      <c r="AW32" s="337" t="n"/>
+      <c r="AX32" s="337" t="n"/>
+      <c r="AY32" s="337" t="n"/>
+      <c r="AZ32" s="337" t="n"/>
+      <c r="BA32" s="337" t="n"/>
+      <c r="BB32" s="337" t="n"/>
+      <c r="BC32" s="337" t="n"/>
+      <c r="BD32" s="341" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="241" t="inlineStr">
+      <c r="A33" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. PERIODIC REVIEW SIGN-OFF</t>
         </is>
       </c>
-      <c r="B33" s="242" t="n"/>
-      <c r="C33" s="242" t="n"/>
-      <c r="D33" s="242" t="n"/>
-      <c r="E33" s="242" t="n"/>
-      <c r="F33" s="242" t="n"/>
-      <c r="G33" s="242" t="n"/>
-      <c r="H33" s="242" t="n"/>
-      <c r="I33" s="242" t="n"/>
-      <c r="J33" s="242" t="n"/>
-      <c r="K33" s="242" t="n"/>
-      <c r="L33" s="242" t="n"/>
-      <c r="M33" s="242" t="n"/>
-      <c r="N33" s="242" t="n"/>
-      <c r="O33" s="242" t="n"/>
-      <c r="P33" s="242" t="n"/>
-      <c r="Q33" s="242" t="n"/>
-      <c r="R33" s="242" t="n"/>
-      <c r="S33" s="242" t="n"/>
-      <c r="T33" s="242" t="n"/>
-      <c r="U33" s="242" t="n"/>
-      <c r="V33" s="242" t="n"/>
-      <c r="W33" s="242" t="n"/>
-      <c r="X33" s="242" t="n"/>
-      <c r="Y33" s="242" t="n"/>
-      <c r="Z33" s="242" t="n"/>
-      <c r="AA33" s="242" t="n"/>
-      <c r="AB33" s="242" t="n"/>
-      <c r="AC33" s="242" t="n"/>
-      <c r="AD33" s="242" t="n"/>
-      <c r="AE33" s="242" t="n"/>
-      <c r="AF33" s="242" t="n"/>
-      <c r="AG33" s="242" t="n"/>
-      <c r="AH33" s="242" t="n"/>
-      <c r="AI33" s="242" t="n"/>
-      <c r="AJ33" s="242" t="n"/>
-      <c r="AK33" s="242" t="n"/>
-      <c r="AL33" s="242" t="n"/>
-      <c r="AM33" s="242" t="n"/>
-      <c r="AN33" s="242" t="n"/>
-      <c r="AO33" s="242" t="n"/>
-      <c r="AP33" s="242" t="n"/>
-      <c r="AQ33" s="242" t="n"/>
-      <c r="AR33" s="242" t="n"/>
-      <c r="AS33" s="242" t="n"/>
-      <c r="AT33" s="242" t="n"/>
-      <c r="AU33" s="242" t="n"/>
-      <c r="AV33" s="242" t="n"/>
-      <c r="AW33" s="242" t="n"/>
-      <c r="AX33" s="242" t="n"/>
-      <c r="AY33" s="242" t="n"/>
-      <c r="AZ33" s="242" t="n"/>
-      <c r="BA33" s="242" t="n"/>
-      <c r="BB33" s="242" t="n"/>
-      <c r="BC33" s="242" t="n"/>
-      <c r="BD33" s="243" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="6" t="n"/>
+      <c r="I33" s="6" t="n"/>
+      <c r="J33" s="6" t="n"/>
+      <c r="K33" s="6" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="6" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="6" t="n"/>
+      <c r="T33" s="6" t="n"/>
+      <c r="U33" s="6" t="n"/>
+      <c r="V33" s="6" t="n"/>
+      <c r="W33" s="6" t="n"/>
+      <c r="X33" s="6" t="n"/>
+      <c r="Y33" s="6" t="n"/>
+      <c r="Z33" s="6" t="n"/>
+      <c r="AA33" s="6" t="n"/>
+      <c r="AB33" s="6" t="n"/>
+      <c r="AC33" s="6" t="n"/>
+      <c r="AD33" s="6" t="n"/>
+      <c r="AE33" s="6" t="n"/>
+      <c r="AF33" s="6" t="n"/>
+      <c r="AG33" s="6" t="n"/>
+      <c r="AH33" s="6" t="n"/>
+      <c r="AI33" s="6" t="n"/>
+      <c r="AJ33" s="6" t="n"/>
+      <c r="AK33" s="6" t="n"/>
+      <c r="AL33" s="6" t="n"/>
+      <c r="AM33" s="6" t="n"/>
+      <c r="AN33" s="6" t="n"/>
+      <c r="AO33" s="6" t="n"/>
+      <c r="AP33" s="6" t="n"/>
+      <c r="AQ33" s="6" t="n"/>
+      <c r="AR33" s="6" t="n"/>
+      <c r="AS33" s="6" t="n"/>
+      <c r="AT33" s="6" t="n"/>
+      <c r="AU33" s="6" t="n"/>
+      <c r="AV33" s="6" t="n"/>
+      <c r="AW33" s="6" t="n"/>
+      <c r="AX33" s="6" t="n"/>
+      <c r="AY33" s="6" t="n"/>
+      <c r="AZ33" s="6" t="n"/>
+      <c r="BA33" s="6" t="n"/>
+      <c r="BB33" s="6" t="n"/>
+      <c r="BC33" s="6" t="n"/>
+      <c r="BD33" s="7" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="270" t="inlineStr">
+      <c r="A34" s="344" t="inlineStr">
         <is>
           <t>Reviewed By</t>
         </is>
       </c>
-      <c r="B34" s="245" t="n"/>
-      <c r="C34" s="245" t="n"/>
-      <c r="D34" s="245" t="n"/>
-      <c r="E34" s="245" t="n"/>
-      <c r="F34" s="245" t="n"/>
-      <c r="G34" s="245" t="n"/>
-      <c r="H34" s="245" t="n"/>
-      <c r="I34" s="245" t="n"/>
-      <c r="J34" s="245" t="n"/>
-      <c r="K34" s="245" t="n"/>
-      <c r="L34" s="245" t="n"/>
-      <c r="M34" s="245" t="n"/>
-      <c r="N34" s="245" t="n"/>
-      <c r="O34" s="245" t="n"/>
-      <c r="P34" s="245" t="n"/>
-      <c r="Q34" s="245" t="n"/>
-      <c r="R34" s="246" t="n"/>
-      <c r="S34" s="274" t="inlineStr">
+      <c r="B34" s="31" t="n"/>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n"/>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n"/>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="31" t="n"/>
+      <c r="Q34" s="31" t="n"/>
+      <c r="R34" s="32" t="n"/>
+      <c r="S34" s="349" t="inlineStr">
         <is>
           <t>Process Owner</t>
         </is>
       </c>
-      <c r="T34" s="245" t="n"/>
-      <c r="U34" s="245" t="n"/>
-      <c r="V34" s="245" t="n"/>
-      <c r="W34" s="245" t="n"/>
-      <c r="X34" s="245" t="n"/>
-      <c r="Y34" s="245" t="n"/>
-      <c r="Z34" s="245" t="n"/>
-      <c r="AA34" s="245" t="n"/>
-      <c r="AB34" s="245" t="n"/>
-      <c r="AC34" s="245" t="n"/>
-      <c r="AD34" s="245" t="n"/>
-      <c r="AE34" s="245" t="n"/>
-      <c r="AF34" s="245" t="n"/>
-      <c r="AG34" s="245" t="n"/>
-      <c r="AH34" s="245" t="n"/>
-      <c r="AI34" s="245" t="n"/>
-      <c r="AJ34" s="245" t="n"/>
-      <c r="AK34" s="246" t="n"/>
-      <c r="AL34" s="274" t="inlineStr">
+      <c r="T34" s="31" t="n"/>
+      <c r="U34" s="31" t="n"/>
+      <c r="V34" s="31" t="n"/>
+      <c r="W34" s="31" t="n"/>
+      <c r="X34" s="31" t="n"/>
+      <c r="Y34" s="31" t="n"/>
+      <c r="Z34" s="31" t="n"/>
+      <c r="AA34" s="31" t="n"/>
+      <c r="AB34" s="31" t="n"/>
+      <c r="AC34" s="31" t="n"/>
+      <c r="AD34" s="31" t="n"/>
+      <c r="AE34" s="31" t="n"/>
+      <c r="AF34" s="31" t="n"/>
+      <c r="AG34" s="31" t="n"/>
+      <c r="AH34" s="31" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="32" t="n"/>
+      <c r="AL34" s="350" t="inlineStr">
         <is>
           <t>Approved By</t>
         </is>
       </c>
-      <c r="AM34" s="245" t="n"/>
-      <c r="AN34" s="245" t="n"/>
-      <c r="AO34" s="245" t="n"/>
-      <c r="AP34" s="245" t="n"/>
-      <c r="AQ34" s="245" t="n"/>
-      <c r="AR34" s="245" t="n"/>
-      <c r="AS34" s="245" t="n"/>
-      <c r="AT34" s="245" t="n"/>
-      <c r="AU34" s="245" t="n"/>
-      <c r="AV34" s="245" t="n"/>
-      <c r="AW34" s="245" t="n"/>
-      <c r="AX34" s="245" t="n"/>
-      <c r="AY34" s="245" t="n"/>
-      <c r="AZ34" s="245" t="n"/>
-      <c r="BA34" s="245" t="n"/>
-      <c r="BB34" s="245" t="n"/>
-      <c r="BC34" s="245" t="n"/>
-      <c r="BD34" s="269" t="n"/>
+      <c r="AM34" s="31" t="n"/>
+      <c r="AN34" s="31" t="n"/>
+      <c r="AO34" s="31" t="n"/>
+      <c r="AP34" s="31" t="n"/>
+      <c r="AQ34" s="31" t="n"/>
+      <c r="AR34" s="31" t="n"/>
+      <c r="AS34" s="31" t="n"/>
+      <c r="AT34" s="31" t="n"/>
+      <c r="AU34" s="31" t="n"/>
+      <c r="AV34" s="31" t="n"/>
+      <c r="AW34" s="31" t="n"/>
+      <c r="AX34" s="31" t="n"/>
+      <c r="AY34" s="31" t="n"/>
+      <c r="AZ34" s="31" t="n"/>
+      <c r="BA34" s="31" t="n"/>
+      <c r="BB34" s="31" t="n"/>
+      <c r="BC34" s="31" t="n"/>
+      <c r="BD34" s="34" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="275" t="inlineStr">
+      <c r="A35" s="351" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B35" s="263" t="n"/>
-      <c r="C35" s="263" t="n"/>
-      <c r="D35" s="263" t="n"/>
-      <c r="E35" s="263" t="n"/>
-      <c r="F35" s="263" t="n"/>
-      <c r="G35" s="263" t="n"/>
-      <c r="H35" s="263" t="n"/>
-      <c r="I35" s="263" t="n"/>
-      <c r="J35" s="263" t="n"/>
-      <c r="K35" s="263" t="n"/>
-      <c r="L35" s="263" t="n"/>
-      <c r="M35" s="263" t="n"/>
-      <c r="N35" s="263" t="n"/>
-      <c r="O35" s="263" t="n"/>
-      <c r="P35" s="263" t="n"/>
-      <c r="Q35" s="263" t="n"/>
-      <c r="R35" s="264" t="n"/>
-      <c r="S35" s="276" t="inlineStr">
+      <c r="B35" s="337" t="n"/>
+      <c r="C35" s="337" t="n"/>
+      <c r="D35" s="337" t="n"/>
+      <c r="E35" s="337" t="n"/>
+      <c r="F35" s="337" t="n"/>
+      <c r="G35" s="337" t="n"/>
+      <c r="H35" s="337" t="n"/>
+      <c r="I35" s="337" t="n"/>
+      <c r="J35" s="337" t="n"/>
+      <c r="K35" s="337" t="n"/>
+      <c r="L35" s="337" t="n"/>
+      <c r="M35" s="337" t="n"/>
+      <c r="N35" s="337" t="n"/>
+      <c r="O35" s="337" t="n"/>
+      <c r="P35" s="337" t="n"/>
+      <c r="Q35" s="337" t="n"/>
+      <c r="R35" s="338" t="n"/>
+      <c r="S35" s="352" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T35" s="263" t="n"/>
-      <c r="U35" s="263" t="n"/>
-      <c r="V35" s="263" t="n"/>
-      <c r="W35" s="263" t="n"/>
-      <c r="X35" s="263" t="n"/>
-      <c r="Y35" s="263" t="n"/>
-      <c r="Z35" s="263" t="n"/>
-      <c r="AA35" s="263" t="n"/>
-      <c r="AB35" s="263" t="n"/>
-      <c r="AC35" s="263" t="n"/>
-      <c r="AD35" s="263" t="n"/>
-      <c r="AE35" s="263" t="n"/>
-      <c r="AF35" s="263" t="n"/>
-      <c r="AG35" s="263" t="n"/>
-      <c r="AH35" s="263" t="n"/>
-      <c r="AI35" s="263" t="n"/>
-      <c r="AJ35" s="263" t="n"/>
-      <c r="AK35" s="264" t="n"/>
-      <c r="AL35" s="276" t="inlineStr">
+      <c r="T35" s="337" t="n"/>
+      <c r="U35" s="337" t="n"/>
+      <c r="V35" s="337" t="n"/>
+      <c r="W35" s="337" t="n"/>
+      <c r="X35" s="337" t="n"/>
+      <c r="Y35" s="337" t="n"/>
+      <c r="Z35" s="337" t="n"/>
+      <c r="AA35" s="337" t="n"/>
+      <c r="AB35" s="337" t="n"/>
+      <c r="AC35" s="337" t="n"/>
+      <c r="AD35" s="337" t="n"/>
+      <c r="AE35" s="337" t="n"/>
+      <c r="AF35" s="337" t="n"/>
+      <c r="AG35" s="337" t="n"/>
+      <c r="AH35" s="337" t="n"/>
+      <c r="AI35" s="337" t="n"/>
+      <c r="AJ35" s="337" t="n"/>
+      <c r="AK35" s="338" t="n"/>
+      <c r="AL35" s="353" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AM35" s="263" t="n"/>
-      <c r="AN35" s="263" t="n"/>
-      <c r="AO35" s="263" t="n"/>
-      <c r="AP35" s="263" t="n"/>
-      <c r="AQ35" s="263" t="n"/>
-      <c r="AR35" s="263" t="n"/>
-      <c r="AS35" s="263" t="n"/>
-      <c r="AT35" s="263" t="n"/>
-      <c r="AU35" s="263" t="n"/>
-      <c r="AV35" s="263" t="n"/>
-      <c r="AW35" s="263" t="n"/>
-      <c r="AX35" s="263" t="n"/>
-      <c r="AY35" s="263" t="n"/>
-      <c r="AZ35" s="263" t="n"/>
-      <c r="BA35" s="263" t="n"/>
-      <c r="BB35" s="263" t="n"/>
-      <c r="BC35" s="263" t="n"/>
-      <c r="BD35" s="266" t="n"/>
+      <c r="AM35" s="337" t="n"/>
+      <c r="AN35" s="337" t="n"/>
+      <c r="AO35" s="337" t="n"/>
+      <c r="AP35" s="337" t="n"/>
+      <c r="AQ35" s="337" t="n"/>
+      <c r="AR35" s="337" t="n"/>
+      <c r="AS35" s="337" t="n"/>
+      <c r="AT35" s="337" t="n"/>
+      <c r="AU35" s="337" t="n"/>
+      <c r="AV35" s="337" t="n"/>
+      <c r="AW35" s="337" t="n"/>
+      <c r="AX35" s="337" t="n"/>
+      <c r="AY35" s="337" t="n"/>
+      <c r="AZ35" s="337" t="n"/>
+      <c r="BA35" s="337" t="n"/>
+      <c r="BB35" s="337" t="n"/>
+      <c r="BC35" s="337" t="n"/>
+      <c r="BD35" s="341" t="n"/>
     </row>
     <row r="36" ht="3" customHeight="1">
       <c r="A36" s="277" t="n"/>
@@ -5310,66 +5499,66 @@
       <c r="BD36" s="277" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="241" t="inlineStr">
+      <c r="A37" s="320" t="inlineStr">
         <is>
           <t>NOTICE: Keep one row per customer-specific requirement. Record the source, class, affected process, owner, risk level, due date and current status; do not dilute customer language into vague summaries.</t>
         </is>
       </c>
-      <c r="B37" s="242" t="n"/>
-      <c r="C37" s="242" t="n"/>
-      <c r="D37" s="242" t="n"/>
-      <c r="E37" s="242" t="n"/>
-      <c r="F37" s="242" t="n"/>
-      <c r="G37" s="242" t="n"/>
-      <c r="H37" s="242" t="n"/>
-      <c r="I37" s="242" t="n"/>
-      <c r="J37" s="242" t="n"/>
-      <c r="K37" s="242" t="n"/>
-      <c r="L37" s="242" t="n"/>
-      <c r="M37" s="242" t="n"/>
-      <c r="N37" s="242" t="n"/>
-      <c r="O37" s="242" t="n"/>
-      <c r="P37" s="242" t="n"/>
-      <c r="Q37" s="242" t="n"/>
-      <c r="R37" s="242" t="n"/>
-      <c r="S37" s="242" t="n"/>
-      <c r="T37" s="242" t="n"/>
-      <c r="U37" s="242" t="n"/>
-      <c r="V37" s="242" t="n"/>
-      <c r="W37" s="242" t="n"/>
-      <c r="X37" s="242" t="n"/>
-      <c r="Y37" s="242" t="n"/>
-      <c r="Z37" s="242" t="n"/>
-      <c r="AA37" s="242" t="n"/>
-      <c r="AB37" s="242" t="n"/>
-      <c r="AC37" s="242" t="n"/>
-      <c r="AD37" s="242" t="n"/>
-      <c r="AE37" s="242" t="n"/>
-      <c r="AF37" s="242" t="n"/>
-      <c r="AG37" s="242" t="n"/>
-      <c r="AH37" s="242" t="n"/>
-      <c r="AI37" s="242" t="n"/>
-      <c r="AJ37" s="242" t="n"/>
-      <c r="AK37" s="242" t="n"/>
-      <c r="AL37" s="242" t="n"/>
-      <c r="AM37" s="242" t="n"/>
-      <c r="AN37" s="242" t="n"/>
-      <c r="AO37" s="242" t="n"/>
-      <c r="AP37" s="242" t="n"/>
-      <c r="AQ37" s="242" t="n"/>
-      <c r="AR37" s="242" t="n"/>
-      <c r="AS37" s="242" t="n"/>
-      <c r="AT37" s="242" t="n"/>
-      <c r="AU37" s="242" t="n"/>
-      <c r="AV37" s="242" t="n"/>
-      <c r="AW37" s="242" t="n"/>
-      <c r="AX37" s="242" t="n"/>
-      <c r="AY37" s="242" t="n"/>
-      <c r="AZ37" s="242" t="n"/>
-      <c r="BA37" s="242" t="n"/>
-      <c r="BB37" s="242" t="n"/>
-      <c r="BC37" s="242" t="n"/>
-      <c r="BD37" s="243" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="6" t="n"/>
+      <c r="I37" s="6" t="n"/>
+      <c r="J37" s="6" t="n"/>
+      <c r="K37" s="6" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="6" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="6" t="n"/>
+      <c r="T37" s="6" t="n"/>
+      <c r="U37" s="6" t="n"/>
+      <c r="V37" s="6" t="n"/>
+      <c r="W37" s="6" t="n"/>
+      <c r="X37" s="6" t="n"/>
+      <c r="Y37" s="6" t="n"/>
+      <c r="Z37" s="6" t="n"/>
+      <c r="AA37" s="6" t="n"/>
+      <c r="AB37" s="6" t="n"/>
+      <c r="AC37" s="6" t="n"/>
+      <c r="AD37" s="6" t="n"/>
+      <c r="AE37" s="6" t="n"/>
+      <c r="AF37" s="6" t="n"/>
+      <c r="AG37" s="6" t="n"/>
+      <c r="AH37" s="6" t="n"/>
+      <c r="AI37" s="6" t="n"/>
+      <c r="AJ37" s="6" t="n"/>
+      <c r="AK37" s="6" t="n"/>
+      <c r="AL37" s="6" t="n"/>
+      <c r="AM37" s="6" t="n"/>
+      <c r="AN37" s="6" t="n"/>
+      <c r="AO37" s="6" t="n"/>
+      <c r="AP37" s="6" t="n"/>
+      <c r="AQ37" s="6" t="n"/>
+      <c r="AR37" s="6" t="n"/>
+      <c r="AS37" s="6" t="n"/>
+      <c r="AT37" s="6" t="n"/>
+      <c r="AU37" s="6" t="n"/>
+      <c r="AV37" s="6" t="n"/>
+      <c r="AW37" s="6" t="n"/>
+      <c r="AX37" s="6" t="n"/>
+      <c r="AY37" s="6" t="n"/>
+      <c r="AZ37" s="6" t="n"/>
+      <c r="BA37" s="6" t="n"/>
+      <c r="BB37" s="6" t="n"/>
+      <c r="BC37" s="6" t="n"/>
+      <c r="BD37" s="7" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -6009,346 +6198,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="216" t="n"/>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="218" t="n"/>
+      <c r="A1" s="306" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="219" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — CSR CLASSIFICATION REFERENCE</t>
         </is>
       </c>
-      <c r="M1" s="217" t="n"/>
-      <c r="N1" s="217" t="n"/>
-      <c r="O1" s="217" t="n"/>
-      <c r="P1" s="217" t="n"/>
-      <c r="Q1" s="217" t="n"/>
-      <c r="R1" s="217" t="n"/>
-      <c r="S1" s="217" t="n"/>
-      <c r="T1" s="217" t="n"/>
-      <c r="U1" s="217" t="n"/>
-      <c r="V1" s="217" t="n"/>
-      <c r="W1" s="217" t="n"/>
-      <c r="X1" s="217" t="n"/>
-      <c r="Y1" s="217" t="n"/>
-      <c r="Z1" s="217" t="n"/>
-      <c r="AA1" s="217" t="n"/>
-      <c r="AB1" s="217" t="n"/>
-      <c r="AC1" s="217" t="n"/>
-      <c r="AD1" s="217" t="n"/>
-      <c r="AE1" s="217" t="n"/>
-      <c r="AF1" s="217" t="n"/>
-      <c r="AG1" s="217" t="n"/>
-      <c r="AH1" s="217" t="n"/>
-      <c r="AI1" s="217" t="n"/>
-      <c r="AJ1" s="217" t="n"/>
-      <c r="AK1" s="217" t="n"/>
-      <c r="AL1" s="217" t="n"/>
-      <c r="AM1" s="217" t="n"/>
-      <c r="AN1" s="217" t="n"/>
-      <c r="AO1" s="217" t="n"/>
-      <c r="AP1" s="217" t="n"/>
-      <c r="AQ1" s="220" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="217" t="n"/>
-      <c r="AS1" s="217" t="n"/>
-      <c r="AT1" s="217" t="n"/>
-      <c r="AU1" s="217" t="n"/>
-      <c r="AV1" s="221" t="n"/>
-      <c r="AW1" s="222" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="308" t="n"/>
+      <c r="AW1" s="309" t="inlineStr">
         <is>
           <t>FRM-125</t>
         </is>
       </c>
-      <c r="AX1" s="217" t="n"/>
-      <c r="AY1" s="217" t="n"/>
-      <c r="AZ1" s="217" t="n"/>
-      <c r="BA1" s="217" t="n"/>
-      <c r="BB1" s="217" t="n"/>
-      <c r="BC1" s="217" t="n"/>
-      <c r="BD1" s="218" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="223" t="n"/>
-      <c r="B2" s="224" t="n"/>
-      <c r="C2" s="224" t="n"/>
-      <c r="D2" s="224" t="n"/>
-      <c r="E2" s="224" t="n"/>
-      <c r="F2" s="224" t="n"/>
-      <c r="G2" s="224" t="n"/>
-      <c r="H2" s="224" t="n"/>
-      <c r="I2" s="224" t="n"/>
-      <c r="J2" s="224" t="n"/>
-      <c r="K2" s="225" t="n"/>
-      <c r="L2" s="223" t="n"/>
-      <c r="M2" s="224" t="n"/>
-      <c r="N2" s="224" t="n"/>
-      <c r="O2" s="224" t="n"/>
-      <c r="P2" s="224" t="n"/>
-      <c r="Q2" s="224" t="n"/>
-      <c r="R2" s="224" t="n"/>
-      <c r="S2" s="224" t="n"/>
-      <c r="T2" s="224" t="n"/>
-      <c r="U2" s="224" t="n"/>
-      <c r="V2" s="224" t="n"/>
-      <c r="W2" s="224" t="n"/>
-      <c r="X2" s="224" t="n"/>
-      <c r="Y2" s="224" t="n"/>
-      <c r="Z2" s="224" t="n"/>
-      <c r="AA2" s="224" t="n"/>
-      <c r="AB2" s="224" t="n"/>
-      <c r="AC2" s="224" t="n"/>
-      <c r="AD2" s="224" t="n"/>
-      <c r="AE2" s="224" t="n"/>
-      <c r="AF2" s="224" t="n"/>
-      <c r="AG2" s="224" t="n"/>
-      <c r="AH2" s="224" t="n"/>
-      <c r="AI2" s="224" t="n"/>
-      <c r="AJ2" s="224" t="n"/>
-      <c r="AK2" s="224" t="n"/>
-      <c r="AL2" s="224" t="n"/>
-      <c r="AM2" s="224" t="n"/>
-      <c r="AN2" s="224" t="n"/>
-      <c r="AO2" s="224" t="n"/>
-      <c r="AP2" s="224" t="n"/>
-      <c r="AQ2" s="226" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="AQ2" s="310" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="227" t="n"/>
-      <c r="AS2" s="227" t="n"/>
-      <c r="AT2" s="227" t="n"/>
-      <c r="AU2" s="227" t="n"/>
-      <c r="AV2" s="228" t="n"/>
-      <c r="AW2" s="229" t="inlineStr">
+      <c r="AR2" s="311" t="n"/>
+      <c r="AS2" s="311" t="n"/>
+      <c r="AT2" s="311" t="n"/>
+      <c r="AU2" s="311" t="n"/>
+      <c r="AV2" s="312" t="n"/>
+      <c r="AW2" s="313" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="227" t="n"/>
-      <c r="AY2" s="227" t="n"/>
-      <c r="AZ2" s="227" t="n"/>
-      <c r="BA2" s="227" t="n"/>
-      <c r="BB2" s="227" t="n"/>
-      <c r="BC2" s="227" t="n"/>
-      <c r="BD2" s="230" t="n"/>
+      <c r="AX2" s="311" t="n"/>
+      <c r="AY2" s="311" t="n"/>
+      <c r="AZ2" s="311" t="n"/>
+      <c r="BA2" s="311" t="n"/>
+      <c r="BB2" s="311" t="n"/>
+      <c r="BC2" s="311" t="n"/>
+      <c r="BD2" s="314" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="223" t="n"/>
-      <c r="B3" s="224" t="n"/>
-      <c r="C3" s="224" t="n"/>
-      <c r="D3" s="224" t="n"/>
-      <c r="E3" s="224" t="n"/>
-      <c r="F3" s="224" t="n"/>
-      <c r="G3" s="224" t="n"/>
-      <c r="H3" s="224" t="n"/>
-      <c r="I3" s="224" t="n"/>
-      <c r="J3" s="224" t="n"/>
-      <c r="K3" s="225" t="n"/>
-      <c r="L3" s="223" t="n"/>
-      <c r="M3" s="224" t="n"/>
-      <c r="N3" s="224" t="n"/>
-      <c r="O3" s="224" t="n"/>
-      <c r="P3" s="224" t="n"/>
-      <c r="Q3" s="224" t="n"/>
-      <c r="R3" s="224" t="n"/>
-      <c r="S3" s="224" t="n"/>
-      <c r="T3" s="224" t="n"/>
-      <c r="U3" s="224" t="n"/>
-      <c r="V3" s="224" t="n"/>
-      <c r="W3" s="224" t="n"/>
-      <c r="X3" s="224" t="n"/>
-      <c r="Y3" s="224" t="n"/>
-      <c r="Z3" s="224" t="n"/>
-      <c r="AA3" s="224" t="n"/>
-      <c r="AB3" s="224" t="n"/>
-      <c r="AC3" s="224" t="n"/>
-      <c r="AD3" s="224" t="n"/>
-      <c r="AE3" s="224" t="n"/>
-      <c r="AF3" s="224" t="n"/>
-      <c r="AG3" s="224" t="n"/>
-      <c r="AH3" s="224" t="n"/>
-      <c r="AI3" s="224" t="n"/>
-      <c r="AJ3" s="224" t="n"/>
-      <c r="AK3" s="224" t="n"/>
-      <c r="AL3" s="224" t="n"/>
-      <c r="AM3" s="224" t="n"/>
-      <c r="AN3" s="224" t="n"/>
-      <c r="AO3" s="224" t="n"/>
-      <c r="AP3" s="224" t="n"/>
-      <c r="AQ3" s="226" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="AQ3" s="310" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="227" t="n"/>
-      <c r="AS3" s="227" t="n"/>
-      <c r="AT3" s="227" t="n"/>
-      <c r="AU3" s="227" t="n"/>
-      <c r="AV3" s="228" t="n"/>
-      <c r="AW3" s="229" t="inlineStr">
+      <c r="AR3" s="311" t="n"/>
+      <c r="AS3" s="311" t="n"/>
+      <c r="AT3" s="311" t="n"/>
+      <c r="AU3" s="311" t="n"/>
+      <c r="AV3" s="312" t="n"/>
+      <c r="AW3" s="313" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="227" t="n"/>
-      <c r="AY3" s="227" t="n"/>
-      <c r="AZ3" s="227" t="n"/>
-      <c r="BA3" s="227" t="n"/>
-      <c r="BB3" s="227" t="n"/>
-      <c r="BC3" s="227" t="n"/>
-      <c r="BD3" s="230" t="n"/>
+      <c r="AX3" s="311" t="n"/>
+      <c r="AY3" s="311" t="n"/>
+      <c r="AZ3" s="311" t="n"/>
+      <c r="BA3" s="311" t="n"/>
+      <c r="BB3" s="311" t="n"/>
+      <c r="BC3" s="311" t="n"/>
+      <c r="BD3" s="314" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="223" t="n"/>
-      <c r="B4" s="224" t="n"/>
-      <c r="C4" s="224" t="n"/>
-      <c r="D4" s="224" t="n"/>
-      <c r="E4" s="224" t="n"/>
-      <c r="F4" s="224" t="n"/>
-      <c r="G4" s="224" t="n"/>
-      <c r="H4" s="224" t="n"/>
-      <c r="I4" s="224" t="n"/>
-      <c r="J4" s="224" t="n"/>
-      <c r="K4" s="225" t="n"/>
+      <c r="A4" s="9" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="231" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="224" t="n"/>
-      <c r="N4" s="224" t="n"/>
-      <c r="O4" s="224" t="n"/>
-      <c r="P4" s="224" t="n"/>
-      <c r="Q4" s="224" t="n"/>
-      <c r="R4" s="224" t="n"/>
-      <c r="S4" s="224" t="n"/>
-      <c r="T4" s="224" t="n"/>
-      <c r="U4" s="224" t="n"/>
-      <c r="V4" s="224" t="n"/>
-      <c r="W4" s="224" t="n"/>
-      <c r="X4" s="224" t="n"/>
-      <c r="Y4" s="224" t="n"/>
-      <c r="Z4" s="224" t="n"/>
-      <c r="AA4" s="224" t="n"/>
-      <c r="AB4" s="224" t="n"/>
-      <c r="AC4" s="224" t="n"/>
-      <c r="AD4" s="224" t="n"/>
-      <c r="AE4" s="224" t="n"/>
-      <c r="AF4" s="224" t="n"/>
-      <c r="AG4" s="224" t="n"/>
-      <c r="AH4" s="224" t="n"/>
-      <c r="AI4" s="224" t="n"/>
-      <c r="AJ4" s="224" t="n"/>
-      <c r="AK4" s="224" t="n"/>
-      <c r="AL4" s="224" t="n"/>
-      <c r="AM4" s="224" t="n"/>
-      <c r="AN4" s="224" t="n"/>
-      <c r="AO4" s="224" t="n"/>
-      <c r="AP4" s="224" t="n"/>
-      <c r="AQ4" s="226" t="inlineStr">
+      <c r="AQ4" s="310" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="227" t="n"/>
-      <c r="AS4" s="227" t="n"/>
-      <c r="AT4" s="227" t="n"/>
-      <c r="AU4" s="227" t="n"/>
-      <c r="AV4" s="228" t="n"/>
-      <c r="AW4" s="229" t="inlineStr">
+      <c r="AR4" s="311" t="n"/>
+      <c r="AS4" s="311" t="n"/>
+      <c r="AT4" s="311" t="n"/>
+      <c r="AU4" s="311" t="n"/>
+      <c r="AV4" s="312" t="n"/>
+      <c r="AW4" s="313" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="227" t="n"/>
-      <c r="AY4" s="227" t="n"/>
-      <c r="AZ4" s="227" t="n"/>
-      <c r="BA4" s="227" t="n"/>
-      <c r="BB4" s="227" t="n"/>
-      <c r="BC4" s="227" t="n"/>
-      <c r="BD4" s="230" t="n"/>
+      <c r="AX4" s="311" t="n"/>
+      <c r="AY4" s="311" t="n"/>
+      <c r="AZ4" s="311" t="n"/>
+      <c r="BA4" s="311" t="n"/>
+      <c r="BB4" s="311" t="n"/>
+      <c r="BC4" s="311" t="n"/>
+      <c r="BD4" s="314" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="232" t="n"/>
-      <c r="B5" s="233" t="n"/>
-      <c r="C5" s="233" t="n"/>
-      <c r="D5" s="233" t="n"/>
-      <c r="E5" s="233" t="n"/>
-      <c r="F5" s="233" t="n"/>
-      <c r="G5" s="233" t="n"/>
-      <c r="H5" s="233" t="n"/>
-      <c r="I5" s="233" t="n"/>
-      <c r="J5" s="233" t="n"/>
-      <c r="K5" s="234" t="n"/>
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n"/>
       <c r="L5" s="42" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="233" t="n"/>
-      <c r="N5" s="233" t="n"/>
-      <c r="O5" s="233" t="n"/>
-      <c r="P5" s="233" t="n"/>
-      <c r="Q5" s="233" t="n"/>
-      <c r="R5" s="233" t="n"/>
-      <c r="S5" s="233" t="n"/>
-      <c r="T5" s="233" t="n"/>
-      <c r="U5" s="233" t="n"/>
-      <c r="V5" s="233" t="n"/>
-      <c r="W5" s="233" t="n"/>
-      <c r="X5" s="233" t="n"/>
-      <c r="Y5" s="233" t="n"/>
-      <c r="Z5" s="233" t="n"/>
-      <c r="AA5" s="233" t="n"/>
-      <c r="AB5" s="233" t="n"/>
-      <c r="AC5" s="233" t="n"/>
-      <c r="AD5" s="233" t="n"/>
-      <c r="AE5" s="233" t="n"/>
-      <c r="AF5" s="233" t="n"/>
-      <c r="AG5" s="233" t="n"/>
-      <c r="AH5" s="233" t="n"/>
-      <c r="AI5" s="233" t="n"/>
-      <c r="AJ5" s="233" t="n"/>
-      <c r="AK5" s="233" t="n"/>
-      <c r="AL5" s="233" t="n"/>
-      <c r="AM5" s="233" t="n"/>
-      <c r="AN5" s="233" t="n"/>
-      <c r="AO5" s="233" t="n"/>
-      <c r="AP5" s="233" t="n"/>
-      <c r="AQ5" s="235" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="13" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
+      <c r="AP5" s="13" t="n"/>
+      <c r="AQ5" s="315" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="236" t="n"/>
-      <c r="AS5" s="236" t="n"/>
-      <c r="AT5" s="236" t="n"/>
-      <c r="AU5" s="236" t="n"/>
-      <c r="AV5" s="237" t="n"/>
-      <c r="AW5" s="238" t="inlineStr">
+      <c r="AR5" s="316" t="n"/>
+      <c r="AS5" s="316" t="n"/>
+      <c r="AT5" s="316" t="n"/>
+      <c r="AU5" s="316" t="n"/>
+      <c r="AV5" s="317" t="n"/>
+      <c r="AW5" s="318" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="236" t="n"/>
-      <c r="AY5" s="236" t="n"/>
-      <c r="AZ5" s="236" t="n"/>
-      <c r="BA5" s="236" t="n"/>
-      <c r="BB5" s="236" t="n"/>
-      <c r="BC5" s="236" t="n"/>
-      <c r="BD5" s="239" t="n"/>
+      <c r="AX5" s="316" t="n"/>
+      <c r="AY5" s="316" t="n"/>
+      <c r="AZ5" s="316" t="n"/>
+      <c r="BA5" s="316" t="n"/>
+      <c r="BB5" s="316" t="n"/>
+      <c r="BC5" s="316" t="n"/>
+      <c r="BD5" s="319" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="240" t="n"/>
@@ -6409,868 +6481,868 @@
       <c r="BD6" s="240" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="241" t="inlineStr">
+      <c r="A7" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="242" t="n"/>
-      <c r="C7" s="242" t="n"/>
-      <c r="D7" s="242" t="n"/>
-      <c r="E7" s="242" t="n"/>
-      <c r="F7" s="242" t="n"/>
-      <c r="G7" s="242" t="n"/>
-      <c r="H7" s="242" t="n"/>
-      <c r="I7" s="242" t="n"/>
-      <c r="J7" s="242" t="n"/>
-      <c r="K7" s="242" t="n"/>
-      <c r="L7" s="242" t="n"/>
-      <c r="M7" s="242" t="n"/>
-      <c r="N7" s="242" t="n"/>
-      <c r="O7" s="242" t="n"/>
-      <c r="P7" s="242" t="n"/>
-      <c r="Q7" s="242" t="n"/>
-      <c r="R7" s="242" t="n"/>
-      <c r="S7" s="242" t="n"/>
-      <c r="T7" s="242" t="n"/>
-      <c r="U7" s="242" t="n"/>
-      <c r="V7" s="242" t="n"/>
-      <c r="W7" s="242" t="n"/>
-      <c r="X7" s="242" t="n"/>
-      <c r="Y7" s="242" t="n"/>
-      <c r="Z7" s="242" t="n"/>
-      <c r="AA7" s="242" t="n"/>
-      <c r="AB7" s="242" t="n"/>
-      <c r="AC7" s="242" t="n"/>
-      <c r="AD7" s="242" t="n"/>
-      <c r="AE7" s="242" t="n"/>
-      <c r="AF7" s="242" t="n"/>
-      <c r="AG7" s="242" t="n"/>
-      <c r="AH7" s="242" t="n"/>
-      <c r="AI7" s="242" t="n"/>
-      <c r="AJ7" s="242" t="n"/>
-      <c r="AK7" s="242" t="n"/>
-      <c r="AL7" s="242" t="n"/>
-      <c r="AM7" s="242" t="n"/>
-      <c r="AN7" s="242" t="n"/>
-      <c r="AO7" s="242" t="n"/>
-      <c r="AP7" s="242" t="n"/>
-      <c r="AQ7" s="242" t="n"/>
-      <c r="AR7" s="242" t="n"/>
-      <c r="AS7" s="242" t="n"/>
-      <c r="AT7" s="242" t="n"/>
-      <c r="AU7" s="242" t="n"/>
-      <c r="AV7" s="242" t="n"/>
-      <c r="AW7" s="242" t="n"/>
-      <c r="AX7" s="242" t="n"/>
-      <c r="AY7" s="242" t="n"/>
-      <c r="AZ7" s="242" t="n"/>
-      <c r="BA7" s="242" t="n"/>
-      <c r="BB7" s="242" t="n"/>
-      <c r="BC7" s="242" t="n"/>
-      <c r="BD7" s="243" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
+      <c r="AC7" s="6" t="n"/>
+      <c r="AD7" s="6" t="n"/>
+      <c r="AE7" s="6" t="n"/>
+      <c r="AF7" s="6" t="n"/>
+      <c r="AG7" s="6" t="n"/>
+      <c r="AH7" s="6" t="n"/>
+      <c r="AI7" s="6" t="n"/>
+      <c r="AJ7" s="6" t="n"/>
+      <c r="AK7" s="6" t="n"/>
+      <c r="AL7" s="6" t="n"/>
+      <c r="AM7" s="6" t="n"/>
+      <c r="AN7" s="6" t="n"/>
+      <c r="AO7" s="6" t="n"/>
+      <c r="AP7" s="6" t="n"/>
+      <c r="AQ7" s="6" t="n"/>
+      <c r="AR7" s="6" t="n"/>
+      <c r="AS7" s="6" t="n"/>
+      <c r="AT7" s="6" t="n"/>
+      <c r="AU7" s="6" t="n"/>
+      <c r="AV7" s="6" t="n"/>
+      <c r="AW7" s="6" t="n"/>
+      <c r="AX7" s="6" t="n"/>
+      <c r="AY7" s="6" t="n"/>
+      <c r="AZ7" s="6" t="n"/>
+      <c r="BA7" s="6" t="n"/>
+      <c r="BB7" s="6" t="n"/>
+      <c r="BC7" s="6" t="n"/>
+      <c r="BD7" s="7" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="244" t="inlineStr">
+      <c r="A8" s="321" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="245" t="n"/>
-      <c r="C8" s="245" t="n"/>
-      <c r="D8" s="245" t="n"/>
-      <c r="E8" s="245" t="n"/>
-      <c r="F8" s="245" t="n"/>
-      <c r="G8" s="245" t="n"/>
-      <c r="H8" s="245" t="n"/>
-      <c r="I8" s="245" t="n"/>
-      <c r="J8" s="246" t="n"/>
-      <c r="K8" s="278" t="inlineStr">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="354" t="inlineStr">
         <is>
           <t>SOP-101 / SOP-102; ANNEX-QMS-001 / 002 / 011 / 024</t>
         </is>
       </c>
-      <c r="L8" s="245" t="n"/>
-      <c r="M8" s="245" t="n"/>
-      <c r="N8" s="245" t="n"/>
-      <c r="O8" s="245" t="n"/>
-      <c r="P8" s="245" t="n"/>
-      <c r="Q8" s="245" t="n"/>
-      <c r="R8" s="245" t="n"/>
-      <c r="S8" s="245" t="n"/>
-      <c r="T8" s="245" t="n"/>
-      <c r="U8" s="245" t="n"/>
-      <c r="V8" s="245" t="n"/>
-      <c r="W8" s="245" t="n"/>
-      <c r="X8" s="245" t="n"/>
-      <c r="Y8" s="245" t="n"/>
-      <c r="Z8" s="245" t="n"/>
-      <c r="AA8" s="245" t="n"/>
-      <c r="AB8" s="245" t="n"/>
-      <c r="AC8" s="245" t="n"/>
-      <c r="AD8" s="245" t="n"/>
-      <c r="AE8" s="245" t="n"/>
-      <c r="AF8" s="245" t="n"/>
-      <c r="AG8" s="245" t="n"/>
-      <c r="AH8" s="245" t="n"/>
-      <c r="AI8" s="245" t="n"/>
-      <c r="AJ8" s="245" t="n"/>
-      <c r="AK8" s="245" t="n"/>
-      <c r="AL8" s="245" t="n"/>
-      <c r="AM8" s="245" t="n"/>
-      <c r="AN8" s="245" t="n"/>
-      <c r="AO8" s="245" t="n"/>
-      <c r="AP8" s="245" t="n"/>
-      <c r="AQ8" s="245" t="n"/>
-      <c r="AR8" s="245" t="n"/>
-      <c r="AS8" s="245" t="n"/>
-      <c r="AT8" s="245" t="n"/>
-      <c r="AU8" s="245" t="n"/>
-      <c r="AV8" s="245" t="n"/>
-      <c r="AW8" s="245" t="n"/>
-      <c r="AX8" s="245" t="n"/>
-      <c r="AY8" s="245" t="n"/>
-      <c r="AZ8" s="245" t="n"/>
-      <c r="BA8" s="245" t="n"/>
-      <c r="BB8" s="245" t="n"/>
-      <c r="BC8" s="245" t="n"/>
-      <c r="BD8" s="269" t="n"/>
+      <c r="L8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="31" t="n"/>
+      <c r="O8" s="31" t="n"/>
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="31" t="n"/>
+      <c r="R8" s="31" t="n"/>
+      <c r="S8" s="31" t="n"/>
+      <c r="T8" s="31" t="n"/>
+      <c r="U8" s="31" t="n"/>
+      <c r="V8" s="31" t="n"/>
+      <c r="W8" s="31" t="n"/>
+      <c r="X8" s="31" t="n"/>
+      <c r="Y8" s="31" t="n"/>
+      <c r="Z8" s="31" t="n"/>
+      <c r="AA8" s="31" t="n"/>
+      <c r="AB8" s="31" t="n"/>
+      <c r="AC8" s="31" t="n"/>
+      <c r="AD8" s="31" t="n"/>
+      <c r="AE8" s="31" t="n"/>
+      <c r="AF8" s="31" t="n"/>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="31" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="31" t="n"/>
+      <c r="AL8" s="31" t="n"/>
+      <c r="AM8" s="31" t="n"/>
+      <c r="AN8" s="31" t="n"/>
+      <c r="AO8" s="31" t="n"/>
+      <c r="AP8" s="31" t="n"/>
+      <c r="AQ8" s="31" t="n"/>
+      <c r="AR8" s="31" t="n"/>
+      <c r="AS8" s="31" t="n"/>
+      <c r="AT8" s="31" t="n"/>
+      <c r="AU8" s="31" t="n"/>
+      <c r="AV8" s="31" t="n"/>
+      <c r="AW8" s="31" t="n"/>
+      <c r="AX8" s="31" t="n"/>
+      <c r="AY8" s="31" t="n"/>
+      <c r="AZ8" s="31" t="n"/>
+      <c r="BA8" s="31" t="n"/>
+      <c r="BB8" s="31" t="n"/>
+      <c r="BC8" s="31" t="n"/>
+      <c r="BD8" s="34" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="252" t="inlineStr">
+      <c r="A9" s="328" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="253" t="n"/>
-      <c r="C9" s="253" t="n"/>
-      <c r="D9" s="253" t="n"/>
-      <c r="E9" s="253" t="n"/>
-      <c r="F9" s="253" t="n"/>
-      <c r="G9" s="253" t="n"/>
-      <c r="H9" s="253" t="n"/>
-      <c r="I9" s="253" t="n"/>
-      <c r="J9" s="254" t="n"/>
-      <c r="K9" s="279" t="inlineStr">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="37" t="n"/>
+      <c r="K9" s="38" t="inlineStr">
         <is>
           <t>Excel Table — rolling CSR register (freeze / filter required)</t>
         </is>
       </c>
-      <c r="L9" s="253" t="n"/>
-      <c r="M9" s="253" t="n"/>
-      <c r="N9" s="253" t="n"/>
-      <c r="O9" s="253" t="n"/>
-      <c r="P9" s="253" t="n"/>
-      <c r="Q9" s="253" t="n"/>
-      <c r="R9" s="253" t="n"/>
-      <c r="S9" s="253" t="n"/>
-      <c r="T9" s="253" t="n"/>
-      <c r="U9" s="253" t="n"/>
-      <c r="V9" s="253" t="n"/>
-      <c r="W9" s="253" t="n"/>
-      <c r="X9" s="253" t="n"/>
-      <c r="Y9" s="253" t="n"/>
-      <c r="Z9" s="253" t="n"/>
-      <c r="AA9" s="253" t="n"/>
-      <c r="AB9" s="253" t="n"/>
-      <c r="AC9" s="253" t="n"/>
-      <c r="AD9" s="253" t="n"/>
-      <c r="AE9" s="253" t="n"/>
-      <c r="AF9" s="253" t="n"/>
-      <c r="AG9" s="253" t="n"/>
-      <c r="AH9" s="253" t="n"/>
-      <c r="AI9" s="253" t="n"/>
-      <c r="AJ9" s="253" t="n"/>
-      <c r="AK9" s="253" t="n"/>
-      <c r="AL9" s="253" t="n"/>
-      <c r="AM9" s="253" t="n"/>
-      <c r="AN9" s="253" t="n"/>
-      <c r="AO9" s="253" t="n"/>
-      <c r="AP9" s="253" t="n"/>
-      <c r="AQ9" s="253" t="n"/>
-      <c r="AR9" s="253" t="n"/>
-      <c r="AS9" s="253" t="n"/>
-      <c r="AT9" s="253" t="n"/>
-      <c r="AU9" s="253" t="n"/>
-      <c r="AV9" s="253" t="n"/>
-      <c r="AW9" s="253" t="n"/>
-      <c r="AX9" s="253" t="n"/>
-      <c r="AY9" s="253" t="n"/>
-      <c r="AZ9" s="253" t="n"/>
-      <c r="BA9" s="253" t="n"/>
-      <c r="BB9" s="253" t="n"/>
-      <c r="BC9" s="253" t="n"/>
-      <c r="BD9" s="280" t="n"/>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="36" t="n"/>
+      <c r="N9" s="36" t="n"/>
+      <c r="O9" s="36" t="n"/>
+      <c r="P9" s="36" t="n"/>
+      <c r="Q9" s="36" t="n"/>
+      <c r="R9" s="36" t="n"/>
+      <c r="S9" s="36" t="n"/>
+      <c r="T9" s="36" t="n"/>
+      <c r="U9" s="36" t="n"/>
+      <c r="V9" s="36" t="n"/>
+      <c r="W9" s="36" t="n"/>
+      <c r="X9" s="36" t="n"/>
+      <c r="Y9" s="36" t="n"/>
+      <c r="Z9" s="36" t="n"/>
+      <c r="AA9" s="36" t="n"/>
+      <c r="AB9" s="36" t="n"/>
+      <c r="AC9" s="36" t="n"/>
+      <c r="AD9" s="36" t="n"/>
+      <c r="AE9" s="36" t="n"/>
+      <c r="AF9" s="36" t="n"/>
+      <c r="AG9" s="36" t="n"/>
+      <c r="AH9" s="36" t="n"/>
+      <c r="AI9" s="36" t="n"/>
+      <c r="AJ9" s="36" t="n"/>
+      <c r="AK9" s="36" t="n"/>
+      <c r="AL9" s="36" t="n"/>
+      <c r="AM9" s="36" t="n"/>
+      <c r="AN9" s="36" t="n"/>
+      <c r="AO9" s="36" t="n"/>
+      <c r="AP9" s="36" t="n"/>
+      <c r="AQ9" s="36" t="n"/>
+      <c r="AR9" s="36" t="n"/>
+      <c r="AS9" s="36" t="n"/>
+      <c r="AT9" s="36" t="n"/>
+      <c r="AU9" s="36" t="n"/>
+      <c r="AV9" s="36" t="n"/>
+      <c r="AW9" s="36" t="n"/>
+      <c r="AX9" s="36" t="n"/>
+      <c r="AY9" s="36" t="n"/>
+      <c r="AZ9" s="36" t="n"/>
+      <c r="BA9" s="36" t="n"/>
+      <c r="BB9" s="36" t="n"/>
+      <c r="BC9" s="36" t="n"/>
+      <c r="BD9" s="39" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="260" t="inlineStr">
+      <c r="A10" s="335" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="233" t="n"/>
-      <c r="C10" s="233" t="n"/>
-      <c r="D10" s="233" t="n"/>
-      <c r="E10" s="233" t="n"/>
-      <c r="F10" s="233" t="n"/>
-      <c r="G10" s="233" t="n"/>
-      <c r="H10" s="233" t="n"/>
-      <c r="I10" s="233" t="n"/>
-      <c r="J10" s="261" t="n"/>
-      <c r="K10" s="281" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="44" t="n"/>
+      <c r="K10" s="45" t="inlineStr">
         <is>
           <t>Customer CSR register bridges Pack C governance to Pack A contract / engineering controls and Pack B quality / packaging / cleanliness obligations.</t>
         </is>
       </c>
-      <c r="L10" s="233" t="n"/>
-      <c r="M10" s="233" t="n"/>
-      <c r="N10" s="233" t="n"/>
-      <c r="O10" s="233" t="n"/>
-      <c r="P10" s="233" t="n"/>
-      <c r="Q10" s="233" t="n"/>
-      <c r="R10" s="233" t="n"/>
-      <c r="S10" s="233" t="n"/>
-      <c r="T10" s="233" t="n"/>
-      <c r="U10" s="233" t="n"/>
-      <c r="V10" s="233" t="n"/>
-      <c r="W10" s="233" t="n"/>
-      <c r="X10" s="233" t="n"/>
-      <c r="Y10" s="233" t="n"/>
-      <c r="Z10" s="233" t="n"/>
-      <c r="AA10" s="233" t="n"/>
-      <c r="AB10" s="233" t="n"/>
-      <c r="AC10" s="233" t="n"/>
-      <c r="AD10" s="233" t="n"/>
-      <c r="AE10" s="233" t="n"/>
-      <c r="AF10" s="233" t="n"/>
-      <c r="AG10" s="233" t="n"/>
-      <c r="AH10" s="233" t="n"/>
-      <c r="AI10" s="233" t="n"/>
-      <c r="AJ10" s="233" t="n"/>
-      <c r="AK10" s="233" t="n"/>
-      <c r="AL10" s="233" t="n"/>
-      <c r="AM10" s="233" t="n"/>
-      <c r="AN10" s="233" t="n"/>
-      <c r="AO10" s="233" t="n"/>
-      <c r="AP10" s="233" t="n"/>
-      <c r="AQ10" s="233" t="n"/>
-      <c r="AR10" s="233" t="n"/>
-      <c r="AS10" s="233" t="n"/>
-      <c r="AT10" s="233" t="n"/>
-      <c r="AU10" s="233" t="n"/>
-      <c r="AV10" s="233" t="n"/>
-      <c r="AW10" s="233" t="n"/>
-      <c r="AX10" s="233" t="n"/>
-      <c r="AY10" s="233" t="n"/>
-      <c r="AZ10" s="233" t="n"/>
-      <c r="BA10" s="233" t="n"/>
-      <c r="BB10" s="233" t="n"/>
-      <c r="BC10" s="233" t="n"/>
-      <c r="BD10" s="234" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="13" t="n"/>
+      <c r="AD10" s="13" t="n"/>
+      <c r="AE10" s="13" t="n"/>
+      <c r="AF10" s="13" t="n"/>
+      <c r="AG10" s="13" t="n"/>
+      <c r="AH10" s="13" t="n"/>
+      <c r="AI10" s="13" t="n"/>
+      <c r="AJ10" s="13" t="n"/>
+      <c r="AK10" s="13" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="13" t="n"/>
+      <c r="AN10" s="13" t="n"/>
+      <c r="AO10" s="13" t="n"/>
+      <c r="AP10" s="13" t="n"/>
+      <c r="AQ10" s="13" t="n"/>
+      <c r="AR10" s="13" t="n"/>
+      <c r="AS10" s="13" t="n"/>
+      <c r="AT10" s="13" t="n"/>
+      <c r="AU10" s="13" t="n"/>
+      <c r="AV10" s="13" t="n"/>
+      <c r="AW10" s="13" t="n"/>
+      <c r="AX10" s="13" t="n"/>
+      <c r="AY10" s="13" t="n"/>
+      <c r="AZ10" s="13" t="n"/>
+      <c r="BA10" s="13" t="n"/>
+      <c r="BB10" s="13" t="n"/>
+      <c r="BC10" s="13" t="n"/>
+      <c r="BD10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="241" t="inlineStr">
+      <c r="A11" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  CSR FLAG REFERENCE</t>
         </is>
       </c>
-      <c r="B11" s="242" t="n"/>
-      <c r="C11" s="242" t="n"/>
-      <c r="D11" s="242" t="n"/>
-      <c r="E11" s="242" t="n"/>
-      <c r="F11" s="242" t="n"/>
-      <c r="G11" s="242" t="n"/>
-      <c r="H11" s="242" t="n"/>
-      <c r="I11" s="242" t="n"/>
-      <c r="J11" s="242" t="n"/>
-      <c r="K11" s="242" t="n"/>
-      <c r="L11" s="242" t="n"/>
-      <c r="M11" s="242" t="n"/>
-      <c r="N11" s="242" t="n"/>
-      <c r="O11" s="242" t="n"/>
-      <c r="P11" s="242" t="n"/>
-      <c r="Q11" s="242" t="n"/>
-      <c r="R11" s="242" t="n"/>
-      <c r="S11" s="242" t="n"/>
-      <c r="T11" s="242" t="n"/>
-      <c r="U11" s="242" t="n"/>
-      <c r="V11" s="242" t="n"/>
-      <c r="W11" s="242" t="n"/>
-      <c r="X11" s="242" t="n"/>
-      <c r="Y11" s="242" t="n"/>
-      <c r="Z11" s="242" t="n"/>
-      <c r="AA11" s="242" t="n"/>
-      <c r="AB11" s="242" t="n"/>
-      <c r="AC11" s="242" t="n"/>
-      <c r="AD11" s="242" t="n"/>
-      <c r="AE11" s="242" t="n"/>
-      <c r="AF11" s="242" t="n"/>
-      <c r="AG11" s="242" t="n"/>
-      <c r="AH11" s="242" t="n"/>
-      <c r="AI11" s="242" t="n"/>
-      <c r="AJ11" s="242" t="n"/>
-      <c r="AK11" s="242" t="n"/>
-      <c r="AL11" s="242" t="n"/>
-      <c r="AM11" s="242" t="n"/>
-      <c r="AN11" s="242" t="n"/>
-      <c r="AO11" s="242" t="n"/>
-      <c r="AP11" s="242" t="n"/>
-      <c r="AQ11" s="242" t="n"/>
-      <c r="AR11" s="242" t="n"/>
-      <c r="AS11" s="242" t="n"/>
-      <c r="AT11" s="242" t="n"/>
-      <c r="AU11" s="242" t="n"/>
-      <c r="AV11" s="242" t="n"/>
-      <c r="AW11" s="242" t="n"/>
-      <c r="AX11" s="242" t="n"/>
-      <c r="AY11" s="242" t="n"/>
-      <c r="AZ11" s="242" t="n"/>
-      <c r="BA11" s="242" t="n"/>
-      <c r="BB11" s="242" t="n"/>
-      <c r="BC11" s="242" t="n"/>
-      <c r="BD11" s="243" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
+      <c r="AB11" s="6" t="n"/>
+      <c r="AC11" s="6" t="n"/>
+      <c r="AD11" s="6" t="n"/>
+      <c r="AE11" s="6" t="n"/>
+      <c r="AF11" s="6" t="n"/>
+      <c r="AG11" s="6" t="n"/>
+      <c r="AH11" s="6" t="n"/>
+      <c r="AI11" s="6" t="n"/>
+      <c r="AJ11" s="6" t="n"/>
+      <c r="AK11" s="6" t="n"/>
+      <c r="AL11" s="6" t="n"/>
+      <c r="AM11" s="6" t="n"/>
+      <c r="AN11" s="6" t="n"/>
+      <c r="AO11" s="6" t="n"/>
+      <c r="AP11" s="6" t="n"/>
+      <c r="AQ11" s="6" t="n"/>
+      <c r="AR11" s="6" t="n"/>
+      <c r="AS11" s="6" t="n"/>
+      <c r="AT11" s="6" t="n"/>
+      <c r="AU11" s="6" t="n"/>
+      <c r="AV11" s="6" t="n"/>
+      <c r="AW11" s="6" t="n"/>
+      <c r="AX11" s="6" t="n"/>
+      <c r="AY11" s="6" t="n"/>
+      <c r="AZ11" s="6" t="n"/>
+      <c r="BA11" s="6" t="n"/>
+      <c r="BB11" s="6" t="n"/>
+      <c r="BC11" s="6" t="n"/>
+      <c r="BD11" s="7" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="267" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Flag</t>
         </is>
       </c>
-      <c r="B12" s="245" t="n"/>
-      <c r="C12" s="245" t="n"/>
-      <c r="D12" s="245" t="n"/>
-      <c r="E12" s="245" t="n"/>
-      <c r="F12" s="245" t="n"/>
-      <c r="G12" s="245" t="n"/>
-      <c r="H12" s="245" t="n"/>
-      <c r="I12" s="245" t="n"/>
-      <c r="J12" s="245" t="n"/>
-      <c r="K12" s="245" t="n"/>
-      <c r="L12" s="246" t="n"/>
-      <c r="M12" s="268" t="inlineStr">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="31" t="n"/>
+      <c r="G12" s="31" t="n"/>
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="32" t="n"/>
+      <c r="M12" s="342" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
-      <c r="N12" s="245" t="n"/>
-      <c r="O12" s="245" t="n"/>
-      <c r="P12" s="245" t="n"/>
-      <c r="Q12" s="245" t="n"/>
-      <c r="R12" s="245" t="n"/>
-      <c r="S12" s="245" t="n"/>
-      <c r="T12" s="245" t="n"/>
-      <c r="U12" s="245" t="n"/>
-      <c r="V12" s="245" t="n"/>
-      <c r="W12" s="245" t="n"/>
-      <c r="X12" s="246" t="n"/>
-      <c r="Y12" s="268" t="inlineStr">
+      <c r="N12" s="31" t="n"/>
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="31" t="n"/>
+      <c r="Q12" s="31" t="n"/>
+      <c r="R12" s="31" t="n"/>
+      <c r="S12" s="31" t="n"/>
+      <c r="T12" s="31" t="n"/>
+      <c r="U12" s="31" t="n"/>
+      <c r="V12" s="31" t="n"/>
+      <c r="W12" s="31" t="n"/>
+      <c r="X12" s="32" t="n"/>
+      <c r="Y12" s="342" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="Z12" s="245" t="n"/>
-      <c r="AA12" s="245" t="n"/>
-      <c r="AB12" s="245" t="n"/>
-      <c r="AC12" s="245" t="n"/>
-      <c r="AD12" s="245" t="n"/>
-      <c r="AE12" s="245" t="n"/>
-      <c r="AF12" s="245" t="n"/>
-      <c r="AG12" s="245" t="n"/>
-      <c r="AH12" s="245" t="n"/>
-      <c r="AI12" s="246" t="n"/>
-      <c r="AJ12" s="268" t="inlineStr">
+      <c r="Z12" s="31" t="n"/>
+      <c r="AA12" s="31" t="n"/>
+      <c r="AB12" s="31" t="n"/>
+      <c r="AC12" s="31" t="n"/>
+      <c r="AD12" s="31" t="n"/>
+      <c r="AE12" s="31" t="n"/>
+      <c r="AF12" s="31" t="n"/>
+      <c r="AG12" s="31" t="n"/>
+      <c r="AH12" s="31" t="n"/>
+      <c r="AI12" s="32" t="n"/>
+      <c r="AJ12" s="342" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AK12" s="245" t="n"/>
-      <c r="AL12" s="245" t="n"/>
-      <c r="AM12" s="245" t="n"/>
-      <c r="AN12" s="245" t="n"/>
-      <c r="AO12" s="245" t="n"/>
-      <c r="AP12" s="245" t="n"/>
-      <c r="AQ12" s="245" t="n"/>
-      <c r="AR12" s="245" t="n"/>
-      <c r="AS12" s="246" t="n"/>
-      <c r="AT12" s="268" t="inlineStr">
+      <c r="AK12" s="31" t="n"/>
+      <c r="AL12" s="31" t="n"/>
+      <c r="AM12" s="31" t="n"/>
+      <c r="AN12" s="31" t="n"/>
+      <c r="AO12" s="31" t="n"/>
+      <c r="AP12" s="31" t="n"/>
+      <c r="AQ12" s="31" t="n"/>
+      <c r="AR12" s="31" t="n"/>
+      <c r="AS12" s="32" t="n"/>
+      <c r="AT12" s="343" t="inlineStr">
         <is>
           <t>Response</t>
         </is>
       </c>
-      <c r="AU12" s="245" t="n"/>
-      <c r="AV12" s="245" t="n"/>
-      <c r="AW12" s="245" t="n"/>
-      <c r="AX12" s="245" t="n"/>
-      <c r="AY12" s="245" t="n"/>
-      <c r="AZ12" s="245" t="n"/>
-      <c r="BA12" s="245" t="n"/>
-      <c r="BB12" s="245" t="n"/>
-      <c r="BC12" s="245" t="n"/>
-      <c r="BD12" s="269" t="n"/>
+      <c r="AU12" s="31" t="n"/>
+      <c r="AV12" s="31" t="n"/>
+      <c r="AW12" s="31" t="n"/>
+      <c r="AX12" s="31" t="n"/>
+      <c r="AY12" s="31" t="n"/>
+      <c r="AZ12" s="31" t="n"/>
+      <c r="BA12" s="31" t="n"/>
+      <c r="BB12" s="31" t="n"/>
+      <c r="BC12" s="31" t="n"/>
+      <c r="BD12" s="34" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="282" t="n"/>
-      <c r="B13" s="248" t="n"/>
-      <c r="C13" s="248" t="n"/>
-      <c r="D13" s="248" t="n"/>
-      <c r="E13" s="248" t="n"/>
-      <c r="F13" s="248" t="n"/>
-      <c r="G13" s="248" t="n"/>
-      <c r="H13" s="248" t="n"/>
-      <c r="I13" s="248" t="n"/>
-      <c r="J13" s="248" t="n"/>
-      <c r="K13" s="248" t="n"/>
-      <c r="L13" s="249" t="n"/>
-      <c r="M13" s="247" t="n"/>
-      <c r="N13" s="248" t="n"/>
-      <c r="O13" s="248" t="n"/>
-      <c r="P13" s="248" t="n"/>
-      <c r="Q13" s="248" t="n"/>
-      <c r="R13" s="248" t="n"/>
-      <c r="S13" s="248" t="n"/>
-      <c r="T13" s="248" t="n"/>
-      <c r="U13" s="248" t="n"/>
-      <c r="V13" s="248" t="n"/>
-      <c r="W13" s="248" t="n"/>
-      <c r="X13" s="249" t="n"/>
-      <c r="Y13" s="247" t="n"/>
-      <c r="Z13" s="248" t="n"/>
-      <c r="AA13" s="248" t="n"/>
-      <c r="AB13" s="248" t="n"/>
-      <c r="AC13" s="248" t="n"/>
-      <c r="AD13" s="248" t="n"/>
-      <c r="AE13" s="248" t="n"/>
-      <c r="AF13" s="248" t="n"/>
-      <c r="AG13" s="248" t="n"/>
-      <c r="AH13" s="248" t="n"/>
-      <c r="AI13" s="249" t="n"/>
-      <c r="AJ13" s="247" t="n"/>
-      <c r="AK13" s="248" t="n"/>
-      <c r="AL13" s="248" t="n"/>
-      <c r="AM13" s="248" t="n"/>
-      <c r="AN13" s="248" t="n"/>
-      <c r="AO13" s="248" t="n"/>
-      <c r="AP13" s="248" t="n"/>
-      <c r="AQ13" s="248" t="n"/>
-      <c r="AR13" s="248" t="n"/>
-      <c r="AS13" s="249" t="n"/>
-      <c r="AT13" s="247" t="n"/>
-      <c r="AU13" s="248" t="n"/>
-      <c r="AV13" s="248" t="n"/>
-      <c r="AW13" s="248" t="n"/>
-      <c r="AX13" s="248" t="n"/>
-      <c r="AY13" s="248" t="n"/>
-      <c r="AZ13" s="248" t="n"/>
-      <c r="BA13" s="248" t="n"/>
-      <c r="BB13" s="248" t="n"/>
-      <c r="BC13" s="248" t="n"/>
-      <c r="BD13" s="251" t="n"/>
+      <c r="A13" s="355" t="n"/>
+      <c r="B13" s="323" t="n"/>
+      <c r="C13" s="323" t="n"/>
+      <c r="D13" s="323" t="n"/>
+      <c r="E13" s="323" t="n"/>
+      <c r="F13" s="323" t="n"/>
+      <c r="G13" s="323" t="n"/>
+      <c r="H13" s="323" t="n"/>
+      <c r="I13" s="323" t="n"/>
+      <c r="J13" s="323" t="n"/>
+      <c r="K13" s="323" t="n"/>
+      <c r="L13" s="324" t="n"/>
+      <c r="M13" s="322" t="n"/>
+      <c r="N13" s="323" t="n"/>
+      <c r="O13" s="323" t="n"/>
+      <c r="P13" s="323" t="n"/>
+      <c r="Q13" s="323" t="n"/>
+      <c r="R13" s="323" t="n"/>
+      <c r="S13" s="323" t="n"/>
+      <c r="T13" s="323" t="n"/>
+      <c r="U13" s="323" t="n"/>
+      <c r="V13" s="323" t="n"/>
+      <c r="W13" s="323" t="n"/>
+      <c r="X13" s="324" t="n"/>
+      <c r="Y13" s="322" t="n"/>
+      <c r="Z13" s="323" t="n"/>
+      <c r="AA13" s="323" t="n"/>
+      <c r="AB13" s="323" t="n"/>
+      <c r="AC13" s="323" t="n"/>
+      <c r="AD13" s="323" t="n"/>
+      <c r="AE13" s="323" t="n"/>
+      <c r="AF13" s="323" t="n"/>
+      <c r="AG13" s="323" t="n"/>
+      <c r="AH13" s="323" t="n"/>
+      <c r="AI13" s="324" t="n"/>
+      <c r="AJ13" s="322" t="n"/>
+      <c r="AK13" s="323" t="n"/>
+      <c r="AL13" s="323" t="n"/>
+      <c r="AM13" s="323" t="n"/>
+      <c r="AN13" s="323" t="n"/>
+      <c r="AO13" s="323" t="n"/>
+      <c r="AP13" s="323" t="n"/>
+      <c r="AQ13" s="323" t="n"/>
+      <c r="AR13" s="323" t="n"/>
+      <c r="AS13" s="324" t="n"/>
+      <c r="AT13" s="326" t="n"/>
+      <c r="AU13" s="323" t="n"/>
+      <c r="AV13" s="323" t="n"/>
+      <c r="AW13" s="323" t="n"/>
+      <c r="AX13" s="323" t="n"/>
+      <c r="AY13" s="323" t="n"/>
+      <c r="AZ13" s="323" t="n"/>
+      <c r="BA13" s="323" t="n"/>
+      <c r="BB13" s="323" t="n"/>
+      <c r="BC13" s="323" t="n"/>
+      <c r="BD13" s="327" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="283" t="n"/>
-      <c r="B14" s="256" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="256" t="n"/>
-      <c r="G14" s="256" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
-      <c r="J14" s="256" t="n"/>
-      <c r="K14" s="256" t="n"/>
-      <c r="L14" s="257" t="n"/>
-      <c r="M14" s="272" t="n"/>
-      <c r="N14" s="256" t="n"/>
-      <c r="O14" s="256" t="n"/>
-      <c r="P14" s="256" t="n"/>
-      <c r="Q14" s="256" t="n"/>
-      <c r="R14" s="256" t="n"/>
-      <c r="S14" s="256" t="n"/>
-      <c r="T14" s="256" t="n"/>
-      <c r="U14" s="256" t="n"/>
-      <c r="V14" s="256" t="n"/>
-      <c r="W14" s="256" t="n"/>
-      <c r="X14" s="257" t="n"/>
-      <c r="Y14" s="272" t="n"/>
-      <c r="Z14" s="256" t="n"/>
-      <c r="AA14" s="256" t="n"/>
-      <c r="AB14" s="256" t="n"/>
-      <c r="AC14" s="256" t="n"/>
-      <c r="AD14" s="256" t="n"/>
-      <c r="AE14" s="256" t="n"/>
-      <c r="AF14" s="256" t="n"/>
-      <c r="AG14" s="256" t="n"/>
-      <c r="AH14" s="256" t="n"/>
-      <c r="AI14" s="257" t="n"/>
-      <c r="AJ14" s="272" t="n"/>
-      <c r="AK14" s="256" t="n"/>
-      <c r="AL14" s="256" t="n"/>
-      <c r="AM14" s="256" t="n"/>
-      <c r="AN14" s="256" t="n"/>
-      <c r="AO14" s="256" t="n"/>
-      <c r="AP14" s="256" t="n"/>
-      <c r="AQ14" s="256" t="n"/>
-      <c r="AR14" s="256" t="n"/>
-      <c r="AS14" s="257" t="n"/>
-      <c r="AT14" s="272" t="n"/>
-      <c r="AU14" s="256" t="n"/>
-      <c r="AV14" s="256" t="n"/>
-      <c r="AW14" s="256" t="n"/>
-      <c r="AX14" s="256" t="n"/>
-      <c r="AY14" s="256" t="n"/>
-      <c r="AZ14" s="256" t="n"/>
-      <c r="BA14" s="256" t="n"/>
-      <c r="BB14" s="256" t="n"/>
-      <c r="BC14" s="256" t="n"/>
-      <c r="BD14" s="259" t="n"/>
+      <c r="A14" s="356" t="n"/>
+      <c r="B14" s="330" t="n"/>
+      <c r="C14" s="330" t="n"/>
+      <c r="D14" s="330" t="n"/>
+      <c r="E14" s="330" t="n"/>
+      <c r="F14" s="330" t="n"/>
+      <c r="G14" s="330" t="n"/>
+      <c r="H14" s="330" t="n"/>
+      <c r="I14" s="330" t="n"/>
+      <c r="J14" s="330" t="n"/>
+      <c r="K14" s="330" t="n"/>
+      <c r="L14" s="331" t="n"/>
+      <c r="M14" s="346" t="n"/>
+      <c r="N14" s="330" t="n"/>
+      <c r="O14" s="330" t="n"/>
+      <c r="P14" s="330" t="n"/>
+      <c r="Q14" s="330" t="n"/>
+      <c r="R14" s="330" t="n"/>
+      <c r="S14" s="330" t="n"/>
+      <c r="T14" s="330" t="n"/>
+      <c r="U14" s="330" t="n"/>
+      <c r="V14" s="330" t="n"/>
+      <c r="W14" s="330" t="n"/>
+      <c r="X14" s="331" t="n"/>
+      <c r="Y14" s="346" t="n"/>
+      <c r="Z14" s="330" t="n"/>
+      <c r="AA14" s="330" t="n"/>
+      <c r="AB14" s="330" t="n"/>
+      <c r="AC14" s="330" t="n"/>
+      <c r="AD14" s="330" t="n"/>
+      <c r="AE14" s="330" t="n"/>
+      <c r="AF14" s="330" t="n"/>
+      <c r="AG14" s="330" t="n"/>
+      <c r="AH14" s="330" t="n"/>
+      <c r="AI14" s="331" t="n"/>
+      <c r="AJ14" s="346" t="n"/>
+      <c r="AK14" s="330" t="n"/>
+      <c r="AL14" s="330" t="n"/>
+      <c r="AM14" s="330" t="n"/>
+      <c r="AN14" s="330" t="n"/>
+      <c r="AO14" s="330" t="n"/>
+      <c r="AP14" s="330" t="n"/>
+      <c r="AQ14" s="330" t="n"/>
+      <c r="AR14" s="330" t="n"/>
+      <c r="AS14" s="331" t="n"/>
+      <c r="AT14" s="347" t="n"/>
+      <c r="AU14" s="330" t="n"/>
+      <c r="AV14" s="330" t="n"/>
+      <c r="AW14" s="330" t="n"/>
+      <c r="AX14" s="330" t="n"/>
+      <c r="AY14" s="330" t="n"/>
+      <c r="AZ14" s="330" t="n"/>
+      <c r="BA14" s="330" t="n"/>
+      <c r="BB14" s="330" t="n"/>
+      <c r="BC14" s="330" t="n"/>
+      <c r="BD14" s="334" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="284" t="n"/>
-      <c r="B15" s="256" t="n"/>
-      <c r="C15" s="256" t="n"/>
-      <c r="D15" s="256" t="n"/>
-      <c r="E15" s="256" t="n"/>
-      <c r="F15" s="256" t="n"/>
-      <c r="G15" s="256" t="n"/>
-      <c r="H15" s="256" t="n"/>
-      <c r="I15" s="256" t="n"/>
-      <c r="J15" s="256" t="n"/>
-      <c r="K15" s="256" t="n"/>
-      <c r="L15" s="257" t="n"/>
-      <c r="M15" s="255" t="n"/>
-      <c r="N15" s="256" t="n"/>
-      <c r="O15" s="256" t="n"/>
-      <c r="P15" s="256" t="n"/>
-      <c r="Q15" s="256" t="n"/>
-      <c r="R15" s="256" t="n"/>
-      <c r="S15" s="256" t="n"/>
-      <c r="T15" s="256" t="n"/>
-      <c r="U15" s="256" t="n"/>
-      <c r="V15" s="256" t="n"/>
-      <c r="W15" s="256" t="n"/>
-      <c r="X15" s="257" t="n"/>
-      <c r="Y15" s="255" t="n"/>
-      <c r="Z15" s="256" t="n"/>
-      <c r="AA15" s="256" t="n"/>
-      <c r="AB15" s="256" t="n"/>
-      <c r="AC15" s="256" t="n"/>
-      <c r="AD15" s="256" t="n"/>
-      <c r="AE15" s="256" t="n"/>
-      <c r="AF15" s="256" t="n"/>
-      <c r="AG15" s="256" t="n"/>
-      <c r="AH15" s="256" t="n"/>
-      <c r="AI15" s="257" t="n"/>
-      <c r="AJ15" s="255" t="n"/>
-      <c r="AK15" s="256" t="n"/>
-      <c r="AL15" s="256" t="n"/>
-      <c r="AM15" s="256" t="n"/>
-      <c r="AN15" s="256" t="n"/>
-      <c r="AO15" s="256" t="n"/>
-      <c r="AP15" s="256" t="n"/>
-      <c r="AQ15" s="256" t="n"/>
-      <c r="AR15" s="256" t="n"/>
-      <c r="AS15" s="257" t="n"/>
-      <c r="AT15" s="255" t="n"/>
-      <c r="AU15" s="256" t="n"/>
-      <c r="AV15" s="256" t="n"/>
-      <c r="AW15" s="256" t="n"/>
-      <c r="AX15" s="256" t="n"/>
-      <c r="AY15" s="256" t="n"/>
-      <c r="AZ15" s="256" t="n"/>
-      <c r="BA15" s="256" t="n"/>
-      <c r="BB15" s="256" t="n"/>
-      <c r="BC15" s="256" t="n"/>
-      <c r="BD15" s="259" t="n"/>
+      <c r="A15" s="357" t="n"/>
+      <c r="B15" s="330" t="n"/>
+      <c r="C15" s="330" t="n"/>
+      <c r="D15" s="330" t="n"/>
+      <c r="E15" s="330" t="n"/>
+      <c r="F15" s="330" t="n"/>
+      <c r="G15" s="330" t="n"/>
+      <c r="H15" s="330" t="n"/>
+      <c r="I15" s="330" t="n"/>
+      <c r="J15" s="330" t="n"/>
+      <c r="K15" s="330" t="n"/>
+      <c r="L15" s="331" t="n"/>
+      <c r="M15" s="329" t="n"/>
+      <c r="N15" s="330" t="n"/>
+      <c r="O15" s="330" t="n"/>
+      <c r="P15" s="330" t="n"/>
+      <c r="Q15" s="330" t="n"/>
+      <c r="R15" s="330" t="n"/>
+      <c r="S15" s="330" t="n"/>
+      <c r="T15" s="330" t="n"/>
+      <c r="U15" s="330" t="n"/>
+      <c r="V15" s="330" t="n"/>
+      <c r="W15" s="330" t="n"/>
+      <c r="X15" s="331" t="n"/>
+      <c r="Y15" s="329" t="n"/>
+      <c r="Z15" s="330" t="n"/>
+      <c r="AA15" s="330" t="n"/>
+      <c r="AB15" s="330" t="n"/>
+      <c r="AC15" s="330" t="n"/>
+      <c r="AD15" s="330" t="n"/>
+      <c r="AE15" s="330" t="n"/>
+      <c r="AF15" s="330" t="n"/>
+      <c r="AG15" s="330" t="n"/>
+      <c r="AH15" s="330" t="n"/>
+      <c r="AI15" s="331" t="n"/>
+      <c r="AJ15" s="329" t="n"/>
+      <c r="AK15" s="330" t="n"/>
+      <c r="AL15" s="330" t="n"/>
+      <c r="AM15" s="330" t="n"/>
+      <c r="AN15" s="330" t="n"/>
+      <c r="AO15" s="330" t="n"/>
+      <c r="AP15" s="330" t="n"/>
+      <c r="AQ15" s="330" t="n"/>
+      <c r="AR15" s="330" t="n"/>
+      <c r="AS15" s="331" t="n"/>
+      <c r="AT15" s="333" t="n"/>
+      <c r="AU15" s="330" t="n"/>
+      <c r="AV15" s="330" t="n"/>
+      <c r="AW15" s="330" t="n"/>
+      <c r="AX15" s="330" t="n"/>
+      <c r="AY15" s="330" t="n"/>
+      <c r="AZ15" s="330" t="n"/>
+      <c r="BA15" s="330" t="n"/>
+      <c r="BB15" s="330" t="n"/>
+      <c r="BC15" s="330" t="n"/>
+      <c r="BD15" s="334" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="283" t="n"/>
-      <c r="B16" s="256" t="n"/>
-      <c r="C16" s="256" t="n"/>
-      <c r="D16" s="256" t="n"/>
-      <c r="E16" s="256" t="n"/>
-      <c r="F16" s="256" t="n"/>
-      <c r="G16" s="256" t="n"/>
-      <c r="H16" s="256" t="n"/>
-      <c r="I16" s="256" t="n"/>
-      <c r="J16" s="256" t="n"/>
-      <c r="K16" s="256" t="n"/>
-      <c r="L16" s="257" t="n"/>
-      <c r="M16" s="272" t="n"/>
-      <c r="N16" s="256" t="n"/>
-      <c r="O16" s="256" t="n"/>
-      <c r="P16" s="256" t="n"/>
-      <c r="Q16" s="256" t="n"/>
-      <c r="R16" s="256" t="n"/>
-      <c r="S16" s="256" t="n"/>
-      <c r="T16" s="256" t="n"/>
-      <c r="U16" s="256" t="n"/>
-      <c r="V16" s="256" t="n"/>
-      <c r="W16" s="256" t="n"/>
-      <c r="X16" s="257" t="n"/>
-      <c r="Y16" s="272" t="n"/>
-      <c r="Z16" s="256" t="n"/>
-      <c r="AA16" s="256" t="n"/>
-      <c r="AB16" s="256" t="n"/>
-      <c r="AC16" s="256" t="n"/>
-      <c r="AD16" s="256" t="n"/>
-      <c r="AE16" s="256" t="n"/>
-      <c r="AF16" s="256" t="n"/>
-      <c r="AG16" s="256" t="n"/>
-      <c r="AH16" s="256" t="n"/>
-      <c r="AI16" s="257" t="n"/>
-      <c r="AJ16" s="272" t="n"/>
-      <c r="AK16" s="256" t="n"/>
-      <c r="AL16" s="256" t="n"/>
-      <c r="AM16" s="256" t="n"/>
-      <c r="AN16" s="256" t="n"/>
-      <c r="AO16" s="256" t="n"/>
-      <c r="AP16" s="256" t="n"/>
-      <c r="AQ16" s="256" t="n"/>
-      <c r="AR16" s="256" t="n"/>
-      <c r="AS16" s="257" t="n"/>
-      <c r="AT16" s="272" t="n"/>
-      <c r="AU16" s="256" t="n"/>
-      <c r="AV16" s="256" t="n"/>
-      <c r="AW16" s="256" t="n"/>
-      <c r="AX16" s="256" t="n"/>
-      <c r="AY16" s="256" t="n"/>
-      <c r="AZ16" s="256" t="n"/>
-      <c r="BA16" s="256" t="n"/>
-      <c r="BB16" s="256" t="n"/>
-      <c r="BC16" s="256" t="n"/>
-      <c r="BD16" s="259" t="n"/>
+      <c r="A16" s="356" t="n"/>
+      <c r="B16" s="330" t="n"/>
+      <c r="C16" s="330" t="n"/>
+      <c r="D16" s="330" t="n"/>
+      <c r="E16" s="330" t="n"/>
+      <c r="F16" s="330" t="n"/>
+      <c r="G16" s="330" t="n"/>
+      <c r="H16" s="330" t="n"/>
+      <c r="I16" s="330" t="n"/>
+      <c r="J16" s="330" t="n"/>
+      <c r="K16" s="330" t="n"/>
+      <c r="L16" s="331" t="n"/>
+      <c r="M16" s="346" t="n"/>
+      <c r="N16" s="330" t="n"/>
+      <c r="O16" s="330" t="n"/>
+      <c r="P16" s="330" t="n"/>
+      <c r="Q16" s="330" t="n"/>
+      <c r="R16" s="330" t="n"/>
+      <c r="S16" s="330" t="n"/>
+      <c r="T16" s="330" t="n"/>
+      <c r="U16" s="330" t="n"/>
+      <c r="V16" s="330" t="n"/>
+      <c r="W16" s="330" t="n"/>
+      <c r="X16" s="331" t="n"/>
+      <c r="Y16" s="346" t="n"/>
+      <c r="Z16" s="330" t="n"/>
+      <c r="AA16" s="330" t="n"/>
+      <c r="AB16" s="330" t="n"/>
+      <c r="AC16" s="330" t="n"/>
+      <c r="AD16" s="330" t="n"/>
+      <c r="AE16" s="330" t="n"/>
+      <c r="AF16" s="330" t="n"/>
+      <c r="AG16" s="330" t="n"/>
+      <c r="AH16" s="330" t="n"/>
+      <c r="AI16" s="331" t="n"/>
+      <c r="AJ16" s="346" t="n"/>
+      <c r="AK16" s="330" t="n"/>
+      <c r="AL16" s="330" t="n"/>
+      <c r="AM16" s="330" t="n"/>
+      <c r="AN16" s="330" t="n"/>
+      <c r="AO16" s="330" t="n"/>
+      <c r="AP16" s="330" t="n"/>
+      <c r="AQ16" s="330" t="n"/>
+      <c r="AR16" s="330" t="n"/>
+      <c r="AS16" s="331" t="n"/>
+      <c r="AT16" s="347" t="n"/>
+      <c r="AU16" s="330" t="n"/>
+      <c r="AV16" s="330" t="n"/>
+      <c r="AW16" s="330" t="n"/>
+      <c r="AX16" s="330" t="n"/>
+      <c r="AY16" s="330" t="n"/>
+      <c r="AZ16" s="330" t="n"/>
+      <c r="BA16" s="330" t="n"/>
+      <c r="BB16" s="330" t="n"/>
+      <c r="BC16" s="330" t="n"/>
+      <c r="BD16" s="334" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="284" t="n"/>
-      <c r="B17" s="256" t="n"/>
-      <c r="C17" s="256" t="n"/>
-      <c r="D17" s="256" t="n"/>
-      <c r="E17" s="256" t="n"/>
-      <c r="F17" s="256" t="n"/>
-      <c r="G17" s="256" t="n"/>
-      <c r="H17" s="256" t="n"/>
-      <c r="I17" s="256" t="n"/>
-      <c r="J17" s="256" t="n"/>
-      <c r="K17" s="256" t="n"/>
-      <c r="L17" s="257" t="n"/>
-      <c r="M17" s="255" t="n"/>
-      <c r="N17" s="256" t="n"/>
-      <c r="O17" s="256" t="n"/>
-      <c r="P17" s="256" t="n"/>
-      <c r="Q17" s="256" t="n"/>
-      <c r="R17" s="256" t="n"/>
-      <c r="S17" s="256" t="n"/>
-      <c r="T17" s="256" t="n"/>
-      <c r="U17" s="256" t="n"/>
-      <c r="V17" s="256" t="n"/>
-      <c r="W17" s="256" t="n"/>
-      <c r="X17" s="257" t="n"/>
-      <c r="Y17" s="255" t="n"/>
-      <c r="Z17" s="256" t="n"/>
-      <c r="AA17" s="256" t="n"/>
-      <c r="AB17" s="256" t="n"/>
-      <c r="AC17" s="256" t="n"/>
-      <c r="AD17" s="256" t="n"/>
-      <c r="AE17" s="256" t="n"/>
-      <c r="AF17" s="256" t="n"/>
-      <c r="AG17" s="256" t="n"/>
-      <c r="AH17" s="256" t="n"/>
-      <c r="AI17" s="257" t="n"/>
-      <c r="AJ17" s="255" t="n"/>
-      <c r="AK17" s="256" t="n"/>
-      <c r="AL17" s="256" t="n"/>
-      <c r="AM17" s="256" t="n"/>
-      <c r="AN17" s="256" t="n"/>
-      <c r="AO17" s="256" t="n"/>
-      <c r="AP17" s="256" t="n"/>
-      <c r="AQ17" s="256" t="n"/>
-      <c r="AR17" s="256" t="n"/>
-      <c r="AS17" s="257" t="n"/>
-      <c r="AT17" s="255" t="n"/>
-      <c r="AU17" s="256" t="n"/>
-      <c r="AV17" s="256" t="n"/>
-      <c r="AW17" s="256" t="n"/>
-      <c r="AX17" s="256" t="n"/>
-      <c r="AY17" s="256" t="n"/>
-      <c r="AZ17" s="256" t="n"/>
-      <c r="BA17" s="256" t="n"/>
-      <c r="BB17" s="256" t="n"/>
-      <c r="BC17" s="256" t="n"/>
-      <c r="BD17" s="259" t="n"/>
+      <c r="A17" s="357" t="n"/>
+      <c r="B17" s="330" t="n"/>
+      <c r="C17" s="330" t="n"/>
+      <c r="D17" s="330" t="n"/>
+      <c r="E17" s="330" t="n"/>
+      <c r="F17" s="330" t="n"/>
+      <c r="G17" s="330" t="n"/>
+      <c r="H17" s="330" t="n"/>
+      <c r="I17" s="330" t="n"/>
+      <c r="J17" s="330" t="n"/>
+      <c r="K17" s="330" t="n"/>
+      <c r="L17" s="331" t="n"/>
+      <c r="M17" s="329" t="n"/>
+      <c r="N17" s="330" t="n"/>
+      <c r="O17" s="330" t="n"/>
+      <c r="P17" s="330" t="n"/>
+      <c r="Q17" s="330" t="n"/>
+      <c r="R17" s="330" t="n"/>
+      <c r="S17" s="330" t="n"/>
+      <c r="T17" s="330" t="n"/>
+      <c r="U17" s="330" t="n"/>
+      <c r="V17" s="330" t="n"/>
+      <c r="W17" s="330" t="n"/>
+      <c r="X17" s="331" t="n"/>
+      <c r="Y17" s="329" t="n"/>
+      <c r="Z17" s="330" t="n"/>
+      <c r="AA17" s="330" t="n"/>
+      <c r="AB17" s="330" t="n"/>
+      <c r="AC17" s="330" t="n"/>
+      <c r="AD17" s="330" t="n"/>
+      <c r="AE17" s="330" t="n"/>
+      <c r="AF17" s="330" t="n"/>
+      <c r="AG17" s="330" t="n"/>
+      <c r="AH17" s="330" t="n"/>
+      <c r="AI17" s="331" t="n"/>
+      <c r="AJ17" s="329" t="n"/>
+      <c r="AK17" s="330" t="n"/>
+      <c r="AL17" s="330" t="n"/>
+      <c r="AM17" s="330" t="n"/>
+      <c r="AN17" s="330" t="n"/>
+      <c r="AO17" s="330" t="n"/>
+      <c r="AP17" s="330" t="n"/>
+      <c r="AQ17" s="330" t="n"/>
+      <c r="AR17" s="330" t="n"/>
+      <c r="AS17" s="331" t="n"/>
+      <c r="AT17" s="333" t="n"/>
+      <c r="AU17" s="330" t="n"/>
+      <c r="AV17" s="330" t="n"/>
+      <c r="AW17" s="330" t="n"/>
+      <c r="AX17" s="330" t="n"/>
+      <c r="AY17" s="330" t="n"/>
+      <c r="AZ17" s="330" t="n"/>
+      <c r="BA17" s="330" t="n"/>
+      <c r="BB17" s="330" t="n"/>
+      <c r="BC17" s="330" t="n"/>
+      <c r="BD17" s="334" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="283" t="n"/>
-      <c r="B18" s="256" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="256" t="n"/>
-      <c r="G18" s="256" t="n"/>
-      <c r="H18" s="256" t="n"/>
-      <c r="I18" s="256" t="n"/>
-      <c r="J18" s="256" t="n"/>
-      <c r="K18" s="256" t="n"/>
-      <c r="L18" s="257" t="n"/>
-      <c r="M18" s="272" t="n"/>
-      <c r="N18" s="256" t="n"/>
-      <c r="O18" s="256" t="n"/>
-      <c r="P18" s="256" t="n"/>
-      <c r="Q18" s="256" t="n"/>
-      <c r="R18" s="256" t="n"/>
-      <c r="S18" s="256" t="n"/>
-      <c r="T18" s="256" t="n"/>
-      <c r="U18" s="256" t="n"/>
-      <c r="V18" s="256" t="n"/>
-      <c r="W18" s="256" t="n"/>
-      <c r="X18" s="257" t="n"/>
-      <c r="Y18" s="272" t="n"/>
-      <c r="Z18" s="256" t="n"/>
-      <c r="AA18" s="256" t="n"/>
-      <c r="AB18" s="256" t="n"/>
-      <c r="AC18" s="256" t="n"/>
-      <c r="AD18" s="256" t="n"/>
-      <c r="AE18" s="256" t="n"/>
-      <c r="AF18" s="256" t="n"/>
-      <c r="AG18" s="256" t="n"/>
-      <c r="AH18" s="256" t="n"/>
-      <c r="AI18" s="257" t="n"/>
-      <c r="AJ18" s="272" t="n"/>
-      <c r="AK18" s="256" t="n"/>
-      <c r="AL18" s="256" t="n"/>
-      <c r="AM18" s="256" t="n"/>
-      <c r="AN18" s="256" t="n"/>
-      <c r="AO18" s="256" t="n"/>
-      <c r="AP18" s="256" t="n"/>
-      <c r="AQ18" s="256" t="n"/>
-      <c r="AR18" s="256" t="n"/>
-      <c r="AS18" s="257" t="n"/>
-      <c r="AT18" s="272" t="n"/>
-      <c r="AU18" s="256" t="n"/>
-      <c r="AV18" s="256" t="n"/>
-      <c r="AW18" s="256" t="n"/>
-      <c r="AX18" s="256" t="n"/>
-      <c r="AY18" s="256" t="n"/>
-      <c r="AZ18" s="256" t="n"/>
-      <c r="BA18" s="256" t="n"/>
-      <c r="BB18" s="256" t="n"/>
-      <c r="BC18" s="256" t="n"/>
-      <c r="BD18" s="259" t="n"/>
+      <c r="A18" s="356" t="n"/>
+      <c r="B18" s="330" t="n"/>
+      <c r="C18" s="330" t="n"/>
+      <c r="D18" s="330" t="n"/>
+      <c r="E18" s="330" t="n"/>
+      <c r="F18" s="330" t="n"/>
+      <c r="G18" s="330" t="n"/>
+      <c r="H18" s="330" t="n"/>
+      <c r="I18" s="330" t="n"/>
+      <c r="J18" s="330" t="n"/>
+      <c r="K18" s="330" t="n"/>
+      <c r="L18" s="331" t="n"/>
+      <c r="M18" s="346" t="n"/>
+      <c r="N18" s="330" t="n"/>
+      <c r="O18" s="330" t="n"/>
+      <c r="P18" s="330" t="n"/>
+      <c r="Q18" s="330" t="n"/>
+      <c r="R18" s="330" t="n"/>
+      <c r="S18" s="330" t="n"/>
+      <c r="T18" s="330" t="n"/>
+      <c r="U18" s="330" t="n"/>
+      <c r="V18" s="330" t="n"/>
+      <c r="W18" s="330" t="n"/>
+      <c r="X18" s="331" t="n"/>
+      <c r="Y18" s="346" t="n"/>
+      <c r="Z18" s="330" t="n"/>
+      <c r="AA18" s="330" t="n"/>
+      <c r="AB18" s="330" t="n"/>
+      <c r="AC18" s="330" t="n"/>
+      <c r="AD18" s="330" t="n"/>
+      <c r="AE18" s="330" t="n"/>
+      <c r="AF18" s="330" t="n"/>
+      <c r="AG18" s="330" t="n"/>
+      <c r="AH18" s="330" t="n"/>
+      <c r="AI18" s="331" t="n"/>
+      <c r="AJ18" s="346" t="n"/>
+      <c r="AK18" s="330" t="n"/>
+      <c r="AL18" s="330" t="n"/>
+      <c r="AM18" s="330" t="n"/>
+      <c r="AN18" s="330" t="n"/>
+      <c r="AO18" s="330" t="n"/>
+      <c r="AP18" s="330" t="n"/>
+      <c r="AQ18" s="330" t="n"/>
+      <c r="AR18" s="330" t="n"/>
+      <c r="AS18" s="331" t="n"/>
+      <c r="AT18" s="347" t="n"/>
+      <c r="AU18" s="330" t="n"/>
+      <c r="AV18" s="330" t="n"/>
+      <c r="AW18" s="330" t="n"/>
+      <c r="AX18" s="330" t="n"/>
+      <c r="AY18" s="330" t="n"/>
+      <c r="AZ18" s="330" t="n"/>
+      <c r="BA18" s="330" t="n"/>
+      <c r="BB18" s="330" t="n"/>
+      <c r="BC18" s="330" t="n"/>
+      <c r="BD18" s="334" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="284" t="n"/>
-      <c r="B19" s="256" t="n"/>
-      <c r="C19" s="256" t="n"/>
-      <c r="D19" s="256" t="n"/>
-      <c r="E19" s="256" t="n"/>
-      <c r="F19" s="256" t="n"/>
-      <c r="G19" s="256" t="n"/>
-      <c r="H19" s="256" t="n"/>
-      <c r="I19" s="256" t="n"/>
-      <c r="J19" s="256" t="n"/>
-      <c r="K19" s="256" t="n"/>
-      <c r="L19" s="257" t="n"/>
-      <c r="M19" s="255" t="n"/>
-      <c r="N19" s="256" t="n"/>
-      <c r="O19" s="256" t="n"/>
-      <c r="P19" s="256" t="n"/>
-      <c r="Q19" s="256" t="n"/>
-      <c r="R19" s="256" t="n"/>
-      <c r="S19" s="256" t="n"/>
-      <c r="T19" s="256" t="n"/>
-      <c r="U19" s="256" t="n"/>
-      <c r="V19" s="256" t="n"/>
-      <c r="W19" s="256" t="n"/>
-      <c r="X19" s="257" t="n"/>
-      <c r="Y19" s="255" t="n"/>
-      <c r="Z19" s="256" t="n"/>
-      <c r="AA19" s="256" t="n"/>
-      <c r="AB19" s="256" t="n"/>
-      <c r="AC19" s="256" t="n"/>
-      <c r="AD19" s="256" t="n"/>
-      <c r="AE19" s="256" t="n"/>
-      <c r="AF19" s="256" t="n"/>
-      <c r="AG19" s="256" t="n"/>
-      <c r="AH19" s="256" t="n"/>
-      <c r="AI19" s="257" t="n"/>
-      <c r="AJ19" s="255" t="n"/>
-      <c r="AK19" s="256" t="n"/>
-      <c r="AL19" s="256" t="n"/>
-      <c r="AM19" s="256" t="n"/>
-      <c r="AN19" s="256" t="n"/>
-      <c r="AO19" s="256" t="n"/>
-      <c r="AP19" s="256" t="n"/>
-      <c r="AQ19" s="256" t="n"/>
-      <c r="AR19" s="256" t="n"/>
-      <c r="AS19" s="257" t="n"/>
-      <c r="AT19" s="255" t="n"/>
-      <c r="AU19" s="256" t="n"/>
-      <c r="AV19" s="256" t="n"/>
-      <c r="AW19" s="256" t="n"/>
-      <c r="AX19" s="256" t="n"/>
-      <c r="AY19" s="256" t="n"/>
-      <c r="AZ19" s="256" t="n"/>
-      <c r="BA19" s="256" t="n"/>
-      <c r="BB19" s="256" t="n"/>
-      <c r="BC19" s="256" t="n"/>
-      <c r="BD19" s="259" t="n"/>
+      <c r="A19" s="357" t="n"/>
+      <c r="B19" s="330" t="n"/>
+      <c r="C19" s="330" t="n"/>
+      <c r="D19" s="330" t="n"/>
+      <c r="E19" s="330" t="n"/>
+      <c r="F19" s="330" t="n"/>
+      <c r="G19" s="330" t="n"/>
+      <c r="H19" s="330" t="n"/>
+      <c r="I19" s="330" t="n"/>
+      <c r="J19" s="330" t="n"/>
+      <c r="K19" s="330" t="n"/>
+      <c r="L19" s="331" t="n"/>
+      <c r="M19" s="329" t="n"/>
+      <c r="N19" s="330" t="n"/>
+      <c r="O19" s="330" t="n"/>
+      <c r="P19" s="330" t="n"/>
+      <c r="Q19" s="330" t="n"/>
+      <c r="R19" s="330" t="n"/>
+      <c r="S19" s="330" t="n"/>
+      <c r="T19" s="330" t="n"/>
+      <c r="U19" s="330" t="n"/>
+      <c r="V19" s="330" t="n"/>
+      <c r="W19" s="330" t="n"/>
+      <c r="X19" s="331" t="n"/>
+      <c r="Y19" s="329" t="n"/>
+      <c r="Z19" s="330" t="n"/>
+      <c r="AA19" s="330" t="n"/>
+      <c r="AB19" s="330" t="n"/>
+      <c r="AC19" s="330" t="n"/>
+      <c r="AD19" s="330" t="n"/>
+      <c r="AE19" s="330" t="n"/>
+      <c r="AF19" s="330" t="n"/>
+      <c r="AG19" s="330" t="n"/>
+      <c r="AH19" s="330" t="n"/>
+      <c r="AI19" s="331" t="n"/>
+      <c r="AJ19" s="329" t="n"/>
+      <c r="AK19" s="330" t="n"/>
+      <c r="AL19" s="330" t="n"/>
+      <c r="AM19" s="330" t="n"/>
+      <c r="AN19" s="330" t="n"/>
+      <c r="AO19" s="330" t="n"/>
+      <c r="AP19" s="330" t="n"/>
+      <c r="AQ19" s="330" t="n"/>
+      <c r="AR19" s="330" t="n"/>
+      <c r="AS19" s="331" t="n"/>
+      <c r="AT19" s="333" t="n"/>
+      <c r="AU19" s="330" t="n"/>
+      <c r="AV19" s="330" t="n"/>
+      <c r="AW19" s="330" t="n"/>
+      <c r="AX19" s="330" t="n"/>
+      <c r="AY19" s="330" t="n"/>
+      <c r="AZ19" s="330" t="n"/>
+      <c r="BA19" s="330" t="n"/>
+      <c r="BB19" s="330" t="n"/>
+      <c r="BC19" s="330" t="n"/>
+      <c r="BD19" s="334" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="285" t="n"/>
-      <c r="B20" s="263" t="n"/>
-      <c r="C20" s="263" t="n"/>
-      <c r="D20" s="263" t="n"/>
-      <c r="E20" s="263" t="n"/>
-      <c r="F20" s="263" t="n"/>
-      <c r="G20" s="263" t="n"/>
-      <c r="H20" s="263" t="n"/>
-      <c r="I20" s="263" t="n"/>
-      <c r="J20" s="263" t="n"/>
-      <c r="K20" s="263" t="n"/>
-      <c r="L20" s="264" t="n"/>
-      <c r="M20" s="286" t="n"/>
-      <c r="N20" s="263" t="n"/>
-      <c r="O20" s="263" t="n"/>
-      <c r="P20" s="263" t="n"/>
-      <c r="Q20" s="263" t="n"/>
-      <c r="R20" s="263" t="n"/>
-      <c r="S20" s="263" t="n"/>
-      <c r="T20" s="263" t="n"/>
-      <c r="U20" s="263" t="n"/>
-      <c r="V20" s="263" t="n"/>
-      <c r="W20" s="263" t="n"/>
-      <c r="X20" s="264" t="n"/>
-      <c r="Y20" s="286" t="n"/>
-      <c r="Z20" s="263" t="n"/>
-      <c r="AA20" s="263" t="n"/>
-      <c r="AB20" s="263" t="n"/>
-      <c r="AC20" s="263" t="n"/>
-      <c r="AD20" s="263" t="n"/>
-      <c r="AE20" s="263" t="n"/>
-      <c r="AF20" s="263" t="n"/>
-      <c r="AG20" s="263" t="n"/>
-      <c r="AH20" s="263" t="n"/>
-      <c r="AI20" s="264" t="n"/>
-      <c r="AJ20" s="286" t="n"/>
-      <c r="AK20" s="263" t="n"/>
-      <c r="AL20" s="263" t="n"/>
-      <c r="AM20" s="263" t="n"/>
-      <c r="AN20" s="263" t="n"/>
-      <c r="AO20" s="263" t="n"/>
-      <c r="AP20" s="263" t="n"/>
-      <c r="AQ20" s="263" t="n"/>
-      <c r="AR20" s="263" t="n"/>
-      <c r="AS20" s="264" t="n"/>
-      <c r="AT20" s="286" t="n"/>
-      <c r="AU20" s="263" t="n"/>
-      <c r="AV20" s="263" t="n"/>
-      <c r="AW20" s="263" t="n"/>
-      <c r="AX20" s="263" t="n"/>
-      <c r="AY20" s="263" t="n"/>
-      <c r="AZ20" s="263" t="n"/>
-      <c r="BA20" s="263" t="n"/>
-      <c r="BB20" s="263" t="n"/>
-      <c r="BC20" s="263" t="n"/>
-      <c r="BD20" s="266" t="n"/>
+      <c r="A20" s="358" t="n"/>
+      <c r="B20" s="337" t="n"/>
+      <c r="C20" s="337" t="n"/>
+      <c r="D20" s="337" t="n"/>
+      <c r="E20" s="337" t="n"/>
+      <c r="F20" s="337" t="n"/>
+      <c r="G20" s="337" t="n"/>
+      <c r="H20" s="337" t="n"/>
+      <c r="I20" s="337" t="n"/>
+      <c r="J20" s="337" t="n"/>
+      <c r="K20" s="337" t="n"/>
+      <c r="L20" s="338" t="n"/>
+      <c r="M20" s="359" t="n"/>
+      <c r="N20" s="337" t="n"/>
+      <c r="O20" s="337" t="n"/>
+      <c r="P20" s="337" t="n"/>
+      <c r="Q20" s="337" t="n"/>
+      <c r="R20" s="337" t="n"/>
+      <c r="S20" s="337" t="n"/>
+      <c r="T20" s="337" t="n"/>
+      <c r="U20" s="337" t="n"/>
+      <c r="V20" s="337" t="n"/>
+      <c r="W20" s="337" t="n"/>
+      <c r="X20" s="338" t="n"/>
+      <c r="Y20" s="359" t="n"/>
+      <c r="Z20" s="337" t="n"/>
+      <c r="AA20" s="337" t="n"/>
+      <c r="AB20" s="337" t="n"/>
+      <c r="AC20" s="337" t="n"/>
+      <c r="AD20" s="337" t="n"/>
+      <c r="AE20" s="337" t="n"/>
+      <c r="AF20" s="337" t="n"/>
+      <c r="AG20" s="337" t="n"/>
+      <c r="AH20" s="337" t="n"/>
+      <c r="AI20" s="338" t="n"/>
+      <c r="AJ20" s="359" t="n"/>
+      <c r="AK20" s="337" t="n"/>
+      <c r="AL20" s="337" t="n"/>
+      <c r="AM20" s="337" t="n"/>
+      <c r="AN20" s="337" t="n"/>
+      <c r="AO20" s="337" t="n"/>
+      <c r="AP20" s="337" t="n"/>
+      <c r="AQ20" s="337" t="n"/>
+      <c r="AR20" s="337" t="n"/>
+      <c r="AS20" s="338" t="n"/>
+      <c r="AT20" s="360" t="n"/>
+      <c r="AU20" s="337" t="n"/>
+      <c r="AV20" s="337" t="n"/>
+      <c r="AW20" s="337" t="n"/>
+      <c r="AX20" s="337" t="n"/>
+      <c r="AY20" s="337" t="n"/>
+      <c r="AZ20" s="337" t="n"/>
+      <c r="BA20" s="337" t="n"/>
+      <c r="BB20" s="337" t="n"/>
+      <c r="BC20" s="337" t="n"/>
+      <c r="BD20" s="341" t="n"/>
     </row>
     <row r="21" ht="3" customHeight="1">
       <c r="A21" s="277" t="n"/>
@@ -7331,66 +7403,66 @@
       <c r="BD21" s="277" t="n"/>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="241" t="inlineStr">
+      <c r="A22" s="320" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="242" t="n"/>
-      <c r="C22" s="242" t="n"/>
-      <c r="D22" s="242" t="n"/>
-      <c r="E22" s="242" t="n"/>
-      <c r="F22" s="242" t="n"/>
-      <c r="G22" s="242" t="n"/>
-      <c r="H22" s="242" t="n"/>
-      <c r="I22" s="242" t="n"/>
-      <c r="J22" s="242" t="n"/>
-      <c r="K22" s="242" t="n"/>
-      <c r="L22" s="242" t="n"/>
-      <c r="M22" s="242" t="n"/>
-      <c r="N22" s="242" t="n"/>
-      <c r="O22" s="242" t="n"/>
-      <c r="P22" s="242" t="n"/>
-      <c r="Q22" s="242" t="n"/>
-      <c r="R22" s="242" t="n"/>
-      <c r="S22" s="242" t="n"/>
-      <c r="T22" s="242" t="n"/>
-      <c r="U22" s="242" t="n"/>
-      <c r="V22" s="242" t="n"/>
-      <c r="W22" s="242" t="n"/>
-      <c r="X22" s="242" t="n"/>
-      <c r="Y22" s="242" t="n"/>
-      <c r="Z22" s="242" t="n"/>
-      <c r="AA22" s="242" t="n"/>
-      <c r="AB22" s="242" t="n"/>
-      <c r="AC22" s="242" t="n"/>
-      <c r="AD22" s="242" t="n"/>
-      <c r="AE22" s="242" t="n"/>
-      <c r="AF22" s="242" t="n"/>
-      <c r="AG22" s="242" t="n"/>
-      <c r="AH22" s="242" t="n"/>
-      <c r="AI22" s="242" t="n"/>
-      <c r="AJ22" s="242" t="n"/>
-      <c r="AK22" s="242" t="n"/>
-      <c r="AL22" s="242" t="n"/>
-      <c r="AM22" s="242" t="n"/>
-      <c r="AN22" s="242" t="n"/>
-      <c r="AO22" s="242" t="n"/>
-      <c r="AP22" s="242" t="n"/>
-      <c r="AQ22" s="242" t="n"/>
-      <c r="AR22" s="242" t="n"/>
-      <c r="AS22" s="242" t="n"/>
-      <c r="AT22" s="242" t="n"/>
-      <c r="AU22" s="242" t="n"/>
-      <c r="AV22" s="242" t="n"/>
-      <c r="AW22" s="242" t="n"/>
-      <c r="AX22" s="242" t="n"/>
-      <c r="AY22" s="242" t="n"/>
-      <c r="AZ22" s="242" t="n"/>
-      <c r="BA22" s="242" t="n"/>
-      <c r="BB22" s="242" t="n"/>
-      <c r="BC22" s="242" t="n"/>
-      <c r="BD22" s="243" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
+      <c r="AB22" s="6" t="n"/>
+      <c r="AC22" s="6" t="n"/>
+      <c r="AD22" s="6" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="6" t="n"/>
+      <c r="AG22" s="6" t="n"/>
+      <c r="AH22" s="6" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="6" t="n"/>
+      <c r="AK22" s="6" t="n"/>
+      <c r="AL22" s="6" t="n"/>
+      <c r="AM22" s="6" t="n"/>
+      <c r="AN22" s="6" t="n"/>
+      <c r="AO22" s="6" t="n"/>
+      <c r="AP22" s="6" t="n"/>
+      <c r="AQ22" s="6" t="n"/>
+      <c r="AR22" s="6" t="n"/>
+      <c r="AS22" s="6" t="n"/>
+      <c r="AT22" s="6" t="n"/>
+      <c r="AU22" s="6" t="n"/>
+      <c r="AV22" s="6" t="n"/>
+      <c r="AW22" s="6" t="n"/>
+      <c r="AX22" s="6" t="n"/>
+      <c r="AY22" s="6" t="n"/>
+      <c r="AZ22" s="6" t="n"/>
+      <c r="BA22" s="6" t="n"/>
+      <c r="BB22" s="6" t="n"/>
+      <c r="BC22" s="6" t="n"/>
+      <c r="BD22" s="7" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -7723,346 +7795,229 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="216" t="n"/>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="218" t="n"/>
+      <c r="A1" s="306" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="219" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — EVIDENCE REFERENCE REGISTER</t>
         </is>
       </c>
-      <c r="M1" s="217" t="n"/>
-      <c r="N1" s="217" t="n"/>
-      <c r="O1" s="217" t="n"/>
-      <c r="P1" s="217" t="n"/>
-      <c r="Q1" s="217" t="n"/>
-      <c r="R1" s="217" t="n"/>
-      <c r="S1" s="217" t="n"/>
-      <c r="T1" s="217" t="n"/>
-      <c r="U1" s="217" t="n"/>
-      <c r="V1" s="217" t="n"/>
-      <c r="W1" s="217" t="n"/>
-      <c r="X1" s="217" t="n"/>
-      <c r="Y1" s="217" t="n"/>
-      <c r="Z1" s="217" t="n"/>
-      <c r="AA1" s="217" t="n"/>
-      <c r="AB1" s="217" t="n"/>
-      <c r="AC1" s="217" t="n"/>
-      <c r="AD1" s="217" t="n"/>
-      <c r="AE1" s="217" t="n"/>
-      <c r="AF1" s="217" t="n"/>
-      <c r="AG1" s="217" t="n"/>
-      <c r="AH1" s="217" t="n"/>
-      <c r="AI1" s="217" t="n"/>
-      <c r="AJ1" s="217" t="n"/>
-      <c r="AK1" s="217" t="n"/>
-      <c r="AL1" s="217" t="n"/>
-      <c r="AM1" s="217" t="n"/>
-      <c r="AN1" s="217" t="n"/>
-      <c r="AO1" s="217" t="n"/>
-      <c r="AP1" s="217" t="n"/>
-      <c r="AQ1" s="220" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="217" t="n"/>
-      <c r="AS1" s="217" t="n"/>
-      <c r="AT1" s="217" t="n"/>
-      <c r="AU1" s="217" t="n"/>
-      <c r="AV1" s="221" t="n"/>
-      <c r="AW1" s="222" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="308" t="n"/>
+      <c r="AW1" s="309" t="inlineStr">
         <is>
           <t>FRM-125</t>
         </is>
       </c>
-      <c r="AX1" s="217" t="n"/>
-      <c r="AY1" s="217" t="n"/>
-      <c r="AZ1" s="217" t="n"/>
-      <c r="BA1" s="217" t="n"/>
-      <c r="BB1" s="217" t="n"/>
-      <c r="BC1" s="217" t="n"/>
-      <c r="BD1" s="218" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="223" t="n"/>
-      <c r="B2" s="224" t="n"/>
-      <c r="C2" s="224" t="n"/>
-      <c r="D2" s="224" t="n"/>
-      <c r="E2" s="224" t="n"/>
-      <c r="F2" s="224" t="n"/>
-      <c r="G2" s="224" t="n"/>
-      <c r="H2" s="224" t="n"/>
-      <c r="I2" s="224" t="n"/>
-      <c r="J2" s="224" t="n"/>
-      <c r="K2" s="225" t="n"/>
-      <c r="L2" s="223" t="n"/>
-      <c r="M2" s="224" t="n"/>
-      <c r="N2" s="224" t="n"/>
-      <c r="O2" s="224" t="n"/>
-      <c r="P2" s="224" t="n"/>
-      <c r="Q2" s="224" t="n"/>
-      <c r="R2" s="224" t="n"/>
-      <c r="S2" s="224" t="n"/>
-      <c r="T2" s="224" t="n"/>
-      <c r="U2" s="224" t="n"/>
-      <c r="V2" s="224" t="n"/>
-      <c r="W2" s="224" t="n"/>
-      <c r="X2" s="224" t="n"/>
-      <c r="Y2" s="224" t="n"/>
-      <c r="Z2" s="224" t="n"/>
-      <c r="AA2" s="224" t="n"/>
-      <c r="AB2" s="224" t="n"/>
-      <c r="AC2" s="224" t="n"/>
-      <c r="AD2" s="224" t="n"/>
-      <c r="AE2" s="224" t="n"/>
-      <c r="AF2" s="224" t="n"/>
-      <c r="AG2" s="224" t="n"/>
-      <c r="AH2" s="224" t="n"/>
-      <c r="AI2" s="224" t="n"/>
-      <c r="AJ2" s="224" t="n"/>
-      <c r="AK2" s="224" t="n"/>
-      <c r="AL2" s="224" t="n"/>
-      <c r="AM2" s="224" t="n"/>
-      <c r="AN2" s="224" t="n"/>
-      <c r="AO2" s="224" t="n"/>
-      <c r="AP2" s="224" t="n"/>
-      <c r="AQ2" s="226" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="AQ2" s="310" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="227" t="n"/>
-      <c r="AS2" s="227" t="n"/>
-      <c r="AT2" s="227" t="n"/>
-      <c r="AU2" s="227" t="n"/>
-      <c r="AV2" s="228" t="n"/>
-      <c r="AW2" s="229" t="inlineStr">
+      <c r="AR2" s="311" t="n"/>
+      <c r="AS2" s="311" t="n"/>
+      <c r="AT2" s="311" t="n"/>
+      <c r="AU2" s="311" t="n"/>
+      <c r="AV2" s="312" t="n"/>
+      <c r="AW2" s="313" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="227" t="n"/>
-      <c r="AY2" s="227" t="n"/>
-      <c r="AZ2" s="227" t="n"/>
-      <c r="BA2" s="227" t="n"/>
-      <c r="BB2" s="227" t="n"/>
-      <c r="BC2" s="227" t="n"/>
-      <c r="BD2" s="230" t="n"/>
+      <c r="AX2" s="311" t="n"/>
+      <c r="AY2" s="311" t="n"/>
+      <c r="AZ2" s="311" t="n"/>
+      <c r="BA2" s="311" t="n"/>
+      <c r="BB2" s="311" t="n"/>
+      <c r="BC2" s="311" t="n"/>
+      <c r="BD2" s="314" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="223" t="n"/>
-      <c r="B3" s="224" t="n"/>
-      <c r="C3" s="224" t="n"/>
-      <c r="D3" s="224" t="n"/>
-      <c r="E3" s="224" t="n"/>
-      <c r="F3" s="224" t="n"/>
-      <c r="G3" s="224" t="n"/>
-      <c r="H3" s="224" t="n"/>
-      <c r="I3" s="224" t="n"/>
-      <c r="J3" s="224" t="n"/>
-      <c r="K3" s="225" t="n"/>
-      <c r="L3" s="223" t="n"/>
-      <c r="M3" s="224" t="n"/>
-      <c r="N3" s="224" t="n"/>
-      <c r="O3" s="224" t="n"/>
-      <c r="P3" s="224" t="n"/>
-      <c r="Q3" s="224" t="n"/>
-      <c r="R3" s="224" t="n"/>
-      <c r="S3" s="224" t="n"/>
-      <c r="T3" s="224" t="n"/>
-      <c r="U3" s="224" t="n"/>
-      <c r="V3" s="224" t="n"/>
-      <c r="W3" s="224" t="n"/>
-      <c r="X3" s="224" t="n"/>
-      <c r="Y3" s="224" t="n"/>
-      <c r="Z3" s="224" t="n"/>
-      <c r="AA3" s="224" t="n"/>
-      <c r="AB3" s="224" t="n"/>
-      <c r="AC3" s="224" t="n"/>
-      <c r="AD3" s="224" t="n"/>
-      <c r="AE3" s="224" t="n"/>
-      <c r="AF3" s="224" t="n"/>
-      <c r="AG3" s="224" t="n"/>
-      <c r="AH3" s="224" t="n"/>
-      <c r="AI3" s="224" t="n"/>
-      <c r="AJ3" s="224" t="n"/>
-      <c r="AK3" s="224" t="n"/>
-      <c r="AL3" s="224" t="n"/>
-      <c r="AM3" s="224" t="n"/>
-      <c r="AN3" s="224" t="n"/>
-      <c r="AO3" s="224" t="n"/>
-      <c r="AP3" s="224" t="n"/>
-      <c r="AQ3" s="226" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="AQ3" s="310" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="227" t="n"/>
-      <c r="AS3" s="227" t="n"/>
-      <c r="AT3" s="227" t="n"/>
-      <c r="AU3" s="227" t="n"/>
-      <c r="AV3" s="228" t="n"/>
-      <c r="AW3" s="229" t="inlineStr">
+      <c r="AR3" s="311" t="n"/>
+      <c r="AS3" s="311" t="n"/>
+      <c r="AT3" s="311" t="n"/>
+      <c r="AU3" s="311" t="n"/>
+      <c r="AV3" s="312" t="n"/>
+      <c r="AW3" s="313" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="227" t="n"/>
-      <c r="AY3" s="227" t="n"/>
-      <c r="AZ3" s="227" t="n"/>
-      <c r="BA3" s="227" t="n"/>
-      <c r="BB3" s="227" t="n"/>
-      <c r="BC3" s="227" t="n"/>
-      <c r="BD3" s="230" t="n"/>
+      <c r="AX3" s="311" t="n"/>
+      <c r="AY3" s="311" t="n"/>
+      <c r="AZ3" s="311" t="n"/>
+      <c r="BA3" s="311" t="n"/>
+      <c r="BB3" s="311" t="n"/>
+      <c r="BC3" s="311" t="n"/>
+      <c r="BD3" s="314" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="223" t="n"/>
-      <c r="B4" s="224" t="n"/>
-      <c r="C4" s="224" t="n"/>
-      <c r="D4" s="224" t="n"/>
-      <c r="E4" s="224" t="n"/>
-      <c r="F4" s="224" t="n"/>
-      <c r="G4" s="224" t="n"/>
-      <c r="H4" s="224" t="n"/>
-      <c r="I4" s="224" t="n"/>
-      <c r="J4" s="224" t="n"/>
-      <c r="K4" s="225" t="n"/>
+      <c r="A4" s="9" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="231" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="224" t="n"/>
-      <c r="N4" s="224" t="n"/>
-      <c r="O4" s="224" t="n"/>
-      <c r="P4" s="224" t="n"/>
-      <c r="Q4" s="224" t="n"/>
-      <c r="R4" s="224" t="n"/>
-      <c r="S4" s="224" t="n"/>
-      <c r="T4" s="224" t="n"/>
-      <c r="U4" s="224" t="n"/>
-      <c r="V4" s="224" t="n"/>
-      <c r="W4" s="224" t="n"/>
-      <c r="X4" s="224" t="n"/>
-      <c r="Y4" s="224" t="n"/>
-      <c r="Z4" s="224" t="n"/>
-      <c r="AA4" s="224" t="n"/>
-      <c r="AB4" s="224" t="n"/>
-      <c r="AC4" s="224" t="n"/>
-      <c r="AD4" s="224" t="n"/>
-      <c r="AE4" s="224" t="n"/>
-      <c r="AF4" s="224" t="n"/>
-      <c r="AG4" s="224" t="n"/>
-      <c r="AH4" s="224" t="n"/>
-      <c r="AI4" s="224" t="n"/>
-      <c r="AJ4" s="224" t="n"/>
-      <c r="AK4" s="224" t="n"/>
-      <c r="AL4" s="224" t="n"/>
-      <c r="AM4" s="224" t="n"/>
-      <c r="AN4" s="224" t="n"/>
-      <c r="AO4" s="224" t="n"/>
-      <c r="AP4" s="224" t="n"/>
-      <c r="AQ4" s="226" t="inlineStr">
+      <c r="AQ4" s="310" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="227" t="n"/>
-      <c r="AS4" s="227" t="n"/>
-      <c r="AT4" s="227" t="n"/>
-      <c r="AU4" s="227" t="n"/>
-      <c r="AV4" s="228" t="n"/>
-      <c r="AW4" s="229" t="inlineStr">
+      <c r="AR4" s="311" t="n"/>
+      <c r="AS4" s="311" t="n"/>
+      <c r="AT4" s="311" t="n"/>
+      <c r="AU4" s="311" t="n"/>
+      <c r="AV4" s="312" t="n"/>
+      <c r="AW4" s="313" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="227" t="n"/>
-      <c r="AY4" s="227" t="n"/>
-      <c r="AZ4" s="227" t="n"/>
-      <c r="BA4" s="227" t="n"/>
-      <c r="BB4" s="227" t="n"/>
-      <c r="BC4" s="227" t="n"/>
-      <c r="BD4" s="230" t="n"/>
+      <c r="AX4" s="311" t="n"/>
+      <c r="AY4" s="311" t="n"/>
+      <c r="AZ4" s="311" t="n"/>
+      <c r="BA4" s="311" t="n"/>
+      <c r="BB4" s="311" t="n"/>
+      <c r="BC4" s="311" t="n"/>
+      <c r="BD4" s="314" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="232" t="n"/>
-      <c r="B5" s="233" t="n"/>
-      <c r="C5" s="233" t="n"/>
-      <c r="D5" s="233" t="n"/>
-      <c r="E5" s="233" t="n"/>
-      <c r="F5" s="233" t="n"/>
-      <c r="G5" s="233" t="n"/>
-      <c r="H5" s="233" t="n"/>
-      <c r="I5" s="233" t="n"/>
-      <c r="J5" s="233" t="n"/>
-      <c r="K5" s="234" t="n"/>
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n"/>
       <c r="L5" s="42" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="233" t="n"/>
-      <c r="N5" s="233" t="n"/>
-      <c r="O5" s="233" t="n"/>
-      <c r="P5" s="233" t="n"/>
-      <c r="Q5" s="233" t="n"/>
-      <c r="R5" s="233" t="n"/>
-      <c r="S5" s="233" t="n"/>
-      <c r="T5" s="233" t="n"/>
-      <c r="U5" s="233" t="n"/>
-      <c r="V5" s="233" t="n"/>
-      <c r="W5" s="233" t="n"/>
-      <c r="X5" s="233" t="n"/>
-      <c r="Y5" s="233" t="n"/>
-      <c r="Z5" s="233" t="n"/>
-      <c r="AA5" s="233" t="n"/>
-      <c r="AB5" s="233" t="n"/>
-      <c r="AC5" s="233" t="n"/>
-      <c r="AD5" s="233" t="n"/>
-      <c r="AE5" s="233" t="n"/>
-      <c r="AF5" s="233" t="n"/>
-      <c r="AG5" s="233" t="n"/>
-      <c r="AH5" s="233" t="n"/>
-      <c r="AI5" s="233" t="n"/>
-      <c r="AJ5" s="233" t="n"/>
-      <c r="AK5" s="233" t="n"/>
-      <c r="AL5" s="233" t="n"/>
-      <c r="AM5" s="233" t="n"/>
-      <c r="AN5" s="233" t="n"/>
-      <c r="AO5" s="233" t="n"/>
-      <c r="AP5" s="233" t="n"/>
-      <c r="AQ5" s="235" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="13" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
+      <c r="AP5" s="13" t="n"/>
+      <c r="AQ5" s="315" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="236" t="n"/>
-      <c r="AS5" s="236" t="n"/>
-      <c r="AT5" s="236" t="n"/>
-      <c r="AU5" s="236" t="n"/>
-      <c r="AV5" s="237" t="n"/>
-      <c r="AW5" s="238" t="inlineStr">
+      <c r="AR5" s="316" t="n"/>
+      <c r="AS5" s="316" t="n"/>
+      <c r="AT5" s="316" t="n"/>
+      <c r="AU5" s="316" t="n"/>
+      <c r="AV5" s="317" t="n"/>
+      <c r="AW5" s="318" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="236" t="n"/>
-      <c r="AY5" s="236" t="n"/>
-      <c r="AZ5" s="236" t="n"/>
-      <c r="BA5" s="236" t="n"/>
-      <c r="BB5" s="236" t="n"/>
-      <c r="BC5" s="236" t="n"/>
-      <c r="BD5" s="239" t="n"/>
+      <c r="AX5" s="316" t="n"/>
+      <c r="AY5" s="316" t="n"/>
+      <c r="AZ5" s="316" t="n"/>
+      <c r="BA5" s="316" t="n"/>
+      <c r="BB5" s="316" t="n"/>
+      <c r="BC5" s="316" t="n"/>
+      <c r="BD5" s="319" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="240" t="n"/>
@@ -8123,822 +8078,822 @@
       <c r="BD6" s="240" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="241" t="inlineStr">
+      <c r="A7" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
         </is>
       </c>
-      <c r="B7" s="242" t="n"/>
-      <c r="C7" s="242" t="n"/>
-      <c r="D7" s="242" t="n"/>
-      <c r="E7" s="242" t="n"/>
-      <c r="F7" s="242" t="n"/>
-      <c r="G7" s="242" t="n"/>
-      <c r="H7" s="242" t="n"/>
-      <c r="I7" s="242" t="n"/>
-      <c r="J7" s="242" t="n"/>
-      <c r="K7" s="242" t="n"/>
-      <c r="L7" s="242" t="n"/>
-      <c r="M7" s="242" t="n"/>
-      <c r="N7" s="242" t="n"/>
-      <c r="O7" s="242" t="n"/>
-      <c r="P7" s="242" t="n"/>
-      <c r="Q7" s="242" t="n"/>
-      <c r="R7" s="242" t="n"/>
-      <c r="S7" s="242" t="n"/>
-      <c r="T7" s="242" t="n"/>
-      <c r="U7" s="242" t="n"/>
-      <c r="V7" s="242" t="n"/>
-      <c r="W7" s="242" t="n"/>
-      <c r="X7" s="242" t="n"/>
-      <c r="Y7" s="242" t="n"/>
-      <c r="Z7" s="242" t="n"/>
-      <c r="AA7" s="242" t="n"/>
-      <c r="AB7" s="242" t="n"/>
-      <c r="AC7" s="242" t="n"/>
-      <c r="AD7" s="242" t="n"/>
-      <c r="AE7" s="242" t="n"/>
-      <c r="AF7" s="242" t="n"/>
-      <c r="AG7" s="242" t="n"/>
-      <c r="AH7" s="242" t="n"/>
-      <c r="AI7" s="242" t="n"/>
-      <c r="AJ7" s="242" t="n"/>
-      <c r="AK7" s="242" t="n"/>
-      <c r="AL7" s="242" t="n"/>
-      <c r="AM7" s="242" t="n"/>
-      <c r="AN7" s="242" t="n"/>
-      <c r="AO7" s="242" t="n"/>
-      <c r="AP7" s="242" t="n"/>
-      <c r="AQ7" s="242" t="n"/>
-      <c r="AR7" s="242" t="n"/>
-      <c r="AS7" s="242" t="n"/>
-      <c r="AT7" s="242" t="n"/>
-      <c r="AU7" s="242" t="n"/>
-      <c r="AV7" s="242" t="n"/>
-      <c r="AW7" s="242" t="n"/>
-      <c r="AX7" s="242" t="n"/>
-      <c r="AY7" s="242" t="n"/>
-      <c r="AZ7" s="242" t="n"/>
-      <c r="BA7" s="242" t="n"/>
-      <c r="BB7" s="242" t="n"/>
-      <c r="BC7" s="242" t="n"/>
-      <c r="BD7" s="243" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
+      <c r="AC7" s="6" t="n"/>
+      <c r="AD7" s="6" t="n"/>
+      <c r="AE7" s="6" t="n"/>
+      <c r="AF7" s="6" t="n"/>
+      <c r="AG7" s="6" t="n"/>
+      <c r="AH7" s="6" t="n"/>
+      <c r="AI7" s="6" t="n"/>
+      <c r="AJ7" s="6" t="n"/>
+      <c r="AK7" s="6" t="n"/>
+      <c r="AL7" s="6" t="n"/>
+      <c r="AM7" s="6" t="n"/>
+      <c r="AN7" s="6" t="n"/>
+      <c r="AO7" s="6" t="n"/>
+      <c r="AP7" s="6" t="n"/>
+      <c r="AQ7" s="6" t="n"/>
+      <c r="AR7" s="6" t="n"/>
+      <c r="AS7" s="6" t="n"/>
+      <c r="AT7" s="6" t="n"/>
+      <c r="AU7" s="6" t="n"/>
+      <c r="AV7" s="6" t="n"/>
+      <c r="AW7" s="6" t="n"/>
+      <c r="AX7" s="6" t="n"/>
+      <c r="AY7" s="6" t="n"/>
+      <c r="AZ7" s="6" t="n"/>
+      <c r="BA7" s="6" t="n"/>
+      <c r="BB7" s="6" t="n"/>
+      <c r="BC7" s="6" t="n"/>
+      <c r="BD7" s="7" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="244" t="inlineStr">
+      <c r="A8" s="321" t="inlineStr">
         <is>
           <t>Source Links</t>
         </is>
       </c>
-      <c r="B8" s="245" t="n"/>
-      <c r="C8" s="245" t="n"/>
-      <c r="D8" s="245" t="n"/>
-      <c r="E8" s="245" t="n"/>
-      <c r="F8" s="245" t="n"/>
-      <c r="G8" s="245" t="n"/>
-      <c r="H8" s="245" t="n"/>
-      <c r="I8" s="245" t="n"/>
-      <c r="J8" s="246" t="n"/>
-      <c r="K8" s="278" t="inlineStr">
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="31" t="n"/>
+      <c r="D8" s="31" t="n"/>
+      <c r="E8" s="31" t="n"/>
+      <c r="F8" s="31" t="n"/>
+      <c r="G8" s="31" t="n"/>
+      <c r="H8" s="31" t="n"/>
+      <c r="I8" s="31" t="n"/>
+      <c r="J8" s="32" t="n"/>
+      <c r="K8" s="354" t="inlineStr">
         <is>
           <t>SOP-101 / SOP-102; ANNEX-QMS-001 / 002 / 011 / 024</t>
         </is>
       </c>
-      <c r="L8" s="245" t="n"/>
-      <c r="M8" s="245" t="n"/>
-      <c r="N8" s="245" t="n"/>
-      <c r="O8" s="245" t="n"/>
-      <c r="P8" s="245" t="n"/>
-      <c r="Q8" s="245" t="n"/>
-      <c r="R8" s="245" t="n"/>
-      <c r="S8" s="245" t="n"/>
-      <c r="T8" s="245" t="n"/>
-      <c r="U8" s="245" t="n"/>
-      <c r="V8" s="245" t="n"/>
-      <c r="W8" s="245" t="n"/>
-      <c r="X8" s="245" t="n"/>
-      <c r="Y8" s="245" t="n"/>
-      <c r="Z8" s="245" t="n"/>
-      <c r="AA8" s="245" t="n"/>
-      <c r="AB8" s="245" t="n"/>
-      <c r="AC8" s="245" t="n"/>
-      <c r="AD8" s="245" t="n"/>
-      <c r="AE8" s="245" t="n"/>
-      <c r="AF8" s="245" t="n"/>
-      <c r="AG8" s="245" t="n"/>
-      <c r="AH8" s="245" t="n"/>
-      <c r="AI8" s="245" t="n"/>
-      <c r="AJ8" s="245" t="n"/>
-      <c r="AK8" s="245" t="n"/>
-      <c r="AL8" s="245" t="n"/>
-      <c r="AM8" s="245" t="n"/>
-      <c r="AN8" s="245" t="n"/>
-      <c r="AO8" s="245" t="n"/>
-      <c r="AP8" s="245" t="n"/>
-      <c r="AQ8" s="245" t="n"/>
-      <c r="AR8" s="245" t="n"/>
-      <c r="AS8" s="245" t="n"/>
-      <c r="AT8" s="245" t="n"/>
-      <c r="AU8" s="245" t="n"/>
-      <c r="AV8" s="245" t="n"/>
-      <c r="AW8" s="245" t="n"/>
-      <c r="AX8" s="245" t="n"/>
-      <c r="AY8" s="245" t="n"/>
-      <c r="AZ8" s="245" t="n"/>
-      <c r="BA8" s="245" t="n"/>
-      <c r="BB8" s="245" t="n"/>
-      <c r="BC8" s="245" t="n"/>
-      <c r="BD8" s="269" t="n"/>
+      <c r="L8" s="31" t="n"/>
+      <c r="M8" s="31" t="n"/>
+      <c r="N8" s="31" t="n"/>
+      <c r="O8" s="31" t="n"/>
+      <c r="P8" s="31" t="n"/>
+      <c r="Q8" s="31" t="n"/>
+      <c r="R8" s="31" t="n"/>
+      <c r="S8" s="31" t="n"/>
+      <c r="T8" s="31" t="n"/>
+      <c r="U8" s="31" t="n"/>
+      <c r="V8" s="31" t="n"/>
+      <c r="W8" s="31" t="n"/>
+      <c r="X8" s="31" t="n"/>
+      <c r="Y8" s="31" t="n"/>
+      <c r="Z8" s="31" t="n"/>
+      <c r="AA8" s="31" t="n"/>
+      <c r="AB8" s="31" t="n"/>
+      <c r="AC8" s="31" t="n"/>
+      <c r="AD8" s="31" t="n"/>
+      <c r="AE8" s="31" t="n"/>
+      <c r="AF8" s="31" t="n"/>
+      <c r="AG8" s="31" t="n"/>
+      <c r="AH8" s="31" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="31" t="n"/>
+      <c r="AL8" s="31" t="n"/>
+      <c r="AM8" s="31" t="n"/>
+      <c r="AN8" s="31" t="n"/>
+      <c r="AO8" s="31" t="n"/>
+      <c r="AP8" s="31" t="n"/>
+      <c r="AQ8" s="31" t="n"/>
+      <c r="AR8" s="31" t="n"/>
+      <c r="AS8" s="31" t="n"/>
+      <c r="AT8" s="31" t="n"/>
+      <c r="AU8" s="31" t="n"/>
+      <c r="AV8" s="31" t="n"/>
+      <c r="AW8" s="31" t="n"/>
+      <c r="AX8" s="31" t="n"/>
+      <c r="AY8" s="31" t="n"/>
+      <c r="AZ8" s="31" t="n"/>
+      <c r="BA8" s="31" t="n"/>
+      <c r="BB8" s="31" t="n"/>
+      <c r="BC8" s="31" t="n"/>
+      <c r="BD8" s="34" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="252" t="inlineStr">
+      <c r="A9" s="328" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B9" s="253" t="n"/>
-      <c r="C9" s="253" t="n"/>
-      <c r="D9" s="253" t="n"/>
-      <c r="E9" s="253" t="n"/>
-      <c r="F9" s="253" t="n"/>
-      <c r="G9" s="253" t="n"/>
-      <c r="H9" s="253" t="n"/>
-      <c r="I9" s="253" t="n"/>
-      <c r="J9" s="254" t="n"/>
-      <c r="K9" s="279" t="inlineStr">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n"/>
+      <c r="D9" s="36" t="n"/>
+      <c r="E9" s="36" t="n"/>
+      <c r="F9" s="36" t="n"/>
+      <c r="G9" s="36" t="n"/>
+      <c r="H9" s="36" t="n"/>
+      <c r="I9" s="36" t="n"/>
+      <c r="J9" s="37" t="n"/>
+      <c r="K9" s="38" t="inlineStr">
         <is>
           <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
         </is>
       </c>
-      <c r="L9" s="253" t="n"/>
-      <c r="M9" s="253" t="n"/>
-      <c r="N9" s="253" t="n"/>
-      <c r="O9" s="253" t="n"/>
-      <c r="P9" s="253" t="n"/>
-      <c r="Q9" s="253" t="n"/>
-      <c r="R9" s="253" t="n"/>
-      <c r="S9" s="253" t="n"/>
-      <c r="T9" s="253" t="n"/>
-      <c r="U9" s="253" t="n"/>
-      <c r="V9" s="253" t="n"/>
-      <c r="W9" s="253" t="n"/>
-      <c r="X9" s="253" t="n"/>
-      <c r="Y9" s="253" t="n"/>
-      <c r="Z9" s="253" t="n"/>
-      <c r="AA9" s="253" t="n"/>
-      <c r="AB9" s="253" t="n"/>
-      <c r="AC9" s="253" t="n"/>
-      <c r="AD9" s="253" t="n"/>
-      <c r="AE9" s="253" t="n"/>
-      <c r="AF9" s="253" t="n"/>
-      <c r="AG9" s="253" t="n"/>
-      <c r="AH9" s="253" t="n"/>
-      <c r="AI9" s="253" t="n"/>
-      <c r="AJ9" s="253" t="n"/>
-      <c r="AK9" s="253" t="n"/>
-      <c r="AL9" s="253" t="n"/>
-      <c r="AM9" s="253" t="n"/>
-      <c r="AN9" s="253" t="n"/>
-      <c r="AO9" s="253" t="n"/>
-      <c r="AP9" s="253" t="n"/>
-      <c r="AQ9" s="253" t="n"/>
-      <c r="AR9" s="253" t="n"/>
-      <c r="AS9" s="253" t="n"/>
-      <c r="AT9" s="253" t="n"/>
-      <c r="AU9" s="253" t="n"/>
-      <c r="AV9" s="253" t="n"/>
-      <c r="AW9" s="253" t="n"/>
-      <c r="AX9" s="253" t="n"/>
-      <c r="AY9" s="253" t="n"/>
-      <c r="AZ9" s="253" t="n"/>
-      <c r="BA9" s="253" t="n"/>
-      <c r="BB9" s="253" t="n"/>
-      <c r="BC9" s="253" t="n"/>
-      <c r="BD9" s="280" t="n"/>
+      <c r="L9" s="36" t="n"/>
+      <c r="M9" s="36" t="n"/>
+      <c r="N9" s="36" t="n"/>
+      <c r="O9" s="36" t="n"/>
+      <c r="P9" s="36" t="n"/>
+      <c r="Q9" s="36" t="n"/>
+      <c r="R9" s="36" t="n"/>
+      <c r="S9" s="36" t="n"/>
+      <c r="T9" s="36" t="n"/>
+      <c r="U9" s="36" t="n"/>
+      <c r="V9" s="36" t="n"/>
+      <c r="W9" s="36" t="n"/>
+      <c r="X9" s="36" t="n"/>
+      <c r="Y9" s="36" t="n"/>
+      <c r="Z9" s="36" t="n"/>
+      <c r="AA9" s="36" t="n"/>
+      <c r="AB9" s="36" t="n"/>
+      <c r="AC9" s="36" t="n"/>
+      <c r="AD9" s="36" t="n"/>
+      <c r="AE9" s="36" t="n"/>
+      <c r="AF9" s="36" t="n"/>
+      <c r="AG9" s="36" t="n"/>
+      <c r="AH9" s="36" t="n"/>
+      <c r="AI9" s="36" t="n"/>
+      <c r="AJ9" s="36" t="n"/>
+      <c r="AK9" s="36" t="n"/>
+      <c r="AL9" s="36" t="n"/>
+      <c r="AM9" s="36" t="n"/>
+      <c r="AN9" s="36" t="n"/>
+      <c r="AO9" s="36" t="n"/>
+      <c r="AP9" s="36" t="n"/>
+      <c r="AQ9" s="36" t="n"/>
+      <c r="AR9" s="36" t="n"/>
+      <c r="AS9" s="36" t="n"/>
+      <c r="AT9" s="36" t="n"/>
+      <c r="AU9" s="36" t="n"/>
+      <c r="AV9" s="36" t="n"/>
+      <c r="AW9" s="36" t="n"/>
+      <c r="AX9" s="36" t="n"/>
+      <c r="AY9" s="36" t="n"/>
+      <c r="AZ9" s="36" t="n"/>
+      <c r="BA9" s="36" t="n"/>
+      <c r="BB9" s="36" t="n"/>
+      <c r="BC9" s="36" t="n"/>
+      <c r="BD9" s="39" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="260" t="inlineStr">
+      <c r="A10" s="335" t="inlineStr">
         <is>
           <t>Boundary / SoR</t>
         </is>
       </c>
-      <c r="B10" s="233" t="n"/>
-      <c r="C10" s="233" t="n"/>
-      <c r="D10" s="233" t="n"/>
-      <c r="E10" s="233" t="n"/>
-      <c r="F10" s="233" t="n"/>
-      <c r="G10" s="233" t="n"/>
-      <c r="H10" s="233" t="n"/>
-      <c r="I10" s="233" t="n"/>
-      <c r="J10" s="261" t="n"/>
-      <c r="K10" s="281" t="inlineStr">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="13" t="n"/>
+      <c r="J10" s="44" t="n"/>
+      <c r="K10" s="45" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="L10" s="233" t="n"/>
-      <c r="M10" s="233" t="n"/>
-      <c r="N10" s="233" t="n"/>
-      <c r="O10" s="233" t="n"/>
-      <c r="P10" s="233" t="n"/>
-      <c r="Q10" s="233" t="n"/>
-      <c r="R10" s="233" t="n"/>
-      <c r="S10" s="233" t="n"/>
-      <c r="T10" s="233" t="n"/>
-      <c r="U10" s="233" t="n"/>
-      <c r="V10" s="233" t="n"/>
-      <c r="W10" s="233" t="n"/>
-      <c r="X10" s="233" t="n"/>
-      <c r="Y10" s="233" t="n"/>
-      <c r="Z10" s="233" t="n"/>
-      <c r="AA10" s="233" t="n"/>
-      <c r="AB10" s="233" t="n"/>
-      <c r="AC10" s="233" t="n"/>
-      <c r="AD10" s="233" t="n"/>
-      <c r="AE10" s="233" t="n"/>
-      <c r="AF10" s="233" t="n"/>
-      <c r="AG10" s="233" t="n"/>
-      <c r="AH10" s="233" t="n"/>
-      <c r="AI10" s="233" t="n"/>
-      <c r="AJ10" s="233" t="n"/>
-      <c r="AK10" s="233" t="n"/>
-      <c r="AL10" s="233" t="n"/>
-      <c r="AM10" s="233" t="n"/>
-      <c r="AN10" s="233" t="n"/>
-      <c r="AO10" s="233" t="n"/>
-      <c r="AP10" s="233" t="n"/>
-      <c r="AQ10" s="233" t="n"/>
-      <c r="AR10" s="233" t="n"/>
-      <c r="AS10" s="233" t="n"/>
-      <c r="AT10" s="233" t="n"/>
-      <c r="AU10" s="233" t="n"/>
-      <c r="AV10" s="233" t="n"/>
-      <c r="AW10" s="233" t="n"/>
-      <c r="AX10" s="233" t="n"/>
-      <c r="AY10" s="233" t="n"/>
-      <c r="AZ10" s="233" t="n"/>
-      <c r="BA10" s="233" t="n"/>
-      <c r="BB10" s="233" t="n"/>
-      <c r="BC10" s="233" t="n"/>
-      <c r="BD10" s="234" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
+      <c r="P10" s="13" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
+      <c r="U10" s="13" t="n"/>
+      <c r="V10" s="13" t="n"/>
+      <c r="W10" s="13" t="n"/>
+      <c r="X10" s="13" t="n"/>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="13" t="n"/>
+      <c r="AC10" s="13" t="n"/>
+      <c r="AD10" s="13" t="n"/>
+      <c r="AE10" s="13" t="n"/>
+      <c r="AF10" s="13" t="n"/>
+      <c r="AG10" s="13" t="n"/>
+      <c r="AH10" s="13" t="n"/>
+      <c r="AI10" s="13" t="n"/>
+      <c r="AJ10" s="13" t="n"/>
+      <c r="AK10" s="13" t="n"/>
+      <c r="AL10" s="13" t="n"/>
+      <c r="AM10" s="13" t="n"/>
+      <c r="AN10" s="13" t="n"/>
+      <c r="AO10" s="13" t="n"/>
+      <c r="AP10" s="13" t="n"/>
+      <c r="AQ10" s="13" t="n"/>
+      <c r="AR10" s="13" t="n"/>
+      <c r="AS10" s="13" t="n"/>
+      <c r="AT10" s="13" t="n"/>
+      <c r="AU10" s="13" t="n"/>
+      <c r="AV10" s="13" t="n"/>
+      <c r="AW10" s="13" t="n"/>
+      <c r="AX10" s="13" t="n"/>
+      <c r="AY10" s="13" t="n"/>
+      <c r="AZ10" s="13" t="n"/>
+      <c r="BA10" s="13" t="n"/>
+      <c r="BB10" s="13" t="n"/>
+      <c r="BC10" s="13" t="n"/>
+      <c r="BD10" s="14" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="241" t="inlineStr">
+      <c r="A11" s="320" t="inlineStr">
         <is>
           <t xml:space="preserve">  SUPPORT TABLE</t>
         </is>
       </c>
-      <c r="B11" s="242" t="n"/>
-      <c r="C11" s="242" t="n"/>
-      <c r="D11" s="242" t="n"/>
-      <c r="E11" s="242" t="n"/>
-      <c r="F11" s="242" t="n"/>
-      <c r="G11" s="242" t="n"/>
-      <c r="H11" s="242" t="n"/>
-      <c r="I11" s="242" t="n"/>
-      <c r="J11" s="242" t="n"/>
-      <c r="K11" s="242" t="n"/>
-      <c r="L11" s="242" t="n"/>
-      <c r="M11" s="242" t="n"/>
-      <c r="N11" s="242" t="n"/>
-      <c r="O11" s="242" t="n"/>
-      <c r="P11" s="242" t="n"/>
-      <c r="Q11" s="242" t="n"/>
-      <c r="R11" s="242" t="n"/>
-      <c r="S11" s="242" t="n"/>
-      <c r="T11" s="242" t="n"/>
-      <c r="U11" s="242" t="n"/>
-      <c r="V11" s="242" t="n"/>
-      <c r="W11" s="242" t="n"/>
-      <c r="X11" s="242" t="n"/>
-      <c r="Y11" s="242" t="n"/>
-      <c r="Z11" s="242" t="n"/>
-      <c r="AA11" s="242" t="n"/>
-      <c r="AB11" s="242" t="n"/>
-      <c r="AC11" s="242" t="n"/>
-      <c r="AD11" s="242" t="n"/>
-      <c r="AE11" s="242" t="n"/>
-      <c r="AF11" s="242" t="n"/>
-      <c r="AG11" s="242" t="n"/>
-      <c r="AH11" s="242" t="n"/>
-      <c r="AI11" s="242" t="n"/>
-      <c r="AJ11" s="242" t="n"/>
-      <c r="AK11" s="242" t="n"/>
-      <c r="AL11" s="242" t="n"/>
-      <c r="AM11" s="242" t="n"/>
-      <c r="AN11" s="242" t="n"/>
-      <c r="AO11" s="242" t="n"/>
-      <c r="AP11" s="242" t="n"/>
-      <c r="AQ11" s="242" t="n"/>
-      <c r="AR11" s="242" t="n"/>
-      <c r="AS11" s="242" t="n"/>
-      <c r="AT11" s="242" t="n"/>
-      <c r="AU11" s="242" t="n"/>
-      <c r="AV11" s="242" t="n"/>
-      <c r="AW11" s="242" t="n"/>
-      <c r="AX11" s="242" t="n"/>
-      <c r="AY11" s="242" t="n"/>
-      <c r="AZ11" s="242" t="n"/>
-      <c r="BA11" s="242" t="n"/>
-      <c r="BB11" s="242" t="n"/>
-      <c r="BC11" s="242" t="n"/>
-      <c r="BD11" s="243" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="6" t="n"/>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="n"/>
+      <c r="T11" s="6" t="n"/>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="6" t="n"/>
+      <c r="W11" s="6" t="n"/>
+      <c r="X11" s="6" t="n"/>
+      <c r="Y11" s="6" t="n"/>
+      <c r="Z11" s="6" t="n"/>
+      <c r="AA11" s="6" t="n"/>
+      <c r="AB11" s="6" t="n"/>
+      <c r="AC11" s="6" t="n"/>
+      <c r="AD11" s="6" t="n"/>
+      <c r="AE11" s="6" t="n"/>
+      <c r="AF11" s="6" t="n"/>
+      <c r="AG11" s="6" t="n"/>
+      <c r="AH11" s="6" t="n"/>
+      <c r="AI11" s="6" t="n"/>
+      <c r="AJ11" s="6" t="n"/>
+      <c r="AK11" s="6" t="n"/>
+      <c r="AL11" s="6" t="n"/>
+      <c r="AM11" s="6" t="n"/>
+      <c r="AN11" s="6" t="n"/>
+      <c r="AO11" s="6" t="n"/>
+      <c r="AP11" s="6" t="n"/>
+      <c r="AQ11" s="6" t="n"/>
+      <c r="AR11" s="6" t="n"/>
+      <c r="AS11" s="6" t="n"/>
+      <c r="AT11" s="6" t="n"/>
+      <c r="AU11" s="6" t="n"/>
+      <c r="AV11" s="6" t="n"/>
+      <c r="AW11" s="6" t="n"/>
+      <c r="AX11" s="6" t="n"/>
+      <c r="AY11" s="6" t="n"/>
+      <c r="AZ11" s="6" t="n"/>
+      <c r="BA11" s="6" t="n"/>
+      <c r="BB11" s="6" t="n"/>
+      <c r="BC11" s="6" t="n"/>
+      <c r="BD11" s="7" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="267" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Evidence ID</t>
         </is>
       </c>
-      <c r="B12" s="245" t="n"/>
-      <c r="C12" s="245" t="n"/>
-      <c r="D12" s="245" t="n"/>
-      <c r="E12" s="245" t="n"/>
-      <c r="F12" s="246" t="n"/>
-      <c r="G12" s="268" t="inlineStr">
+      <c r="B12" s="31" t="n"/>
+      <c r="C12" s="31" t="n"/>
+      <c r="D12" s="31" t="n"/>
+      <c r="E12" s="31" t="n"/>
+      <c r="F12" s="32" t="n"/>
+      <c r="G12" s="342" t="inlineStr">
         <is>
           <t>Related Record</t>
         </is>
       </c>
-      <c r="H12" s="245" t="n"/>
-      <c r="I12" s="245" t="n"/>
-      <c r="J12" s="245" t="n"/>
-      <c r="K12" s="245" t="n"/>
-      <c r="L12" s="245" t="n"/>
-      <c r="M12" s="246" t="n"/>
-      <c r="N12" s="268" t="inlineStr">
+      <c r="H12" s="31" t="n"/>
+      <c r="I12" s="31" t="n"/>
+      <c r="J12" s="31" t="n"/>
+      <c r="K12" s="31" t="n"/>
+      <c r="L12" s="31" t="n"/>
+      <c r="M12" s="32" t="n"/>
+      <c r="N12" s="342" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="O12" s="245" t="n"/>
-      <c r="P12" s="245" t="n"/>
-      <c r="Q12" s="245" t="n"/>
-      <c r="R12" s="245" t="n"/>
-      <c r="S12" s="245" t="n"/>
-      <c r="T12" s="245" t="n"/>
-      <c r="U12" s="245" t="n"/>
-      <c r="V12" s="245" t="n"/>
-      <c r="W12" s="246" t="n"/>
-      <c r="X12" s="268" t="inlineStr">
+      <c r="O12" s="31" t="n"/>
+      <c r="P12" s="31" t="n"/>
+      <c r="Q12" s="31" t="n"/>
+      <c r="R12" s="31" t="n"/>
+      <c r="S12" s="31" t="n"/>
+      <c r="T12" s="31" t="n"/>
+      <c r="U12" s="31" t="n"/>
+      <c r="V12" s="31" t="n"/>
+      <c r="W12" s="32" t="n"/>
+      <c r="X12" s="342" t="inlineStr">
         <is>
           <t>Source System</t>
         </is>
       </c>
-      <c r="Y12" s="245" t="n"/>
-      <c r="Z12" s="245" t="n"/>
-      <c r="AA12" s="245" t="n"/>
-      <c r="AB12" s="245" t="n"/>
-      <c r="AC12" s="245" t="n"/>
-      <c r="AD12" s="246" t="n"/>
-      <c r="AE12" s="268" t="inlineStr">
+      <c r="Y12" s="31" t="n"/>
+      <c r="Z12" s="31" t="n"/>
+      <c r="AA12" s="31" t="n"/>
+      <c r="AB12" s="31" t="n"/>
+      <c r="AC12" s="31" t="n"/>
+      <c r="AD12" s="32" t="n"/>
+      <c r="AE12" s="342" t="inlineStr">
         <is>
           <t>Reference Path or Link</t>
         </is>
       </c>
-      <c r="AF12" s="245" t="n"/>
-      <c r="AG12" s="245" t="n"/>
-      <c r="AH12" s="245" t="n"/>
-      <c r="AI12" s="245" t="n"/>
-      <c r="AJ12" s="245" t="n"/>
-      <c r="AK12" s="245" t="n"/>
-      <c r="AL12" s="246" t="n"/>
-      <c r="AM12" s="268" t="inlineStr">
+      <c r="AF12" s="31" t="n"/>
+      <c r="AG12" s="31" t="n"/>
+      <c r="AH12" s="31" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="31" t="n"/>
+      <c r="AL12" s="32" t="n"/>
+      <c r="AM12" s="342" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AN12" s="245" t="n"/>
-      <c r="AO12" s="245" t="n"/>
-      <c r="AP12" s="245" t="n"/>
-      <c r="AQ12" s="245" t="n"/>
-      <c r="AR12" s="246" t="n"/>
-      <c r="AS12" s="268" t="inlineStr">
+      <c r="AN12" s="31" t="n"/>
+      <c r="AO12" s="31" t="n"/>
+      <c r="AP12" s="31" t="n"/>
+      <c r="AQ12" s="31" t="n"/>
+      <c r="AR12" s="32" t="n"/>
+      <c r="AS12" s="342" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="AT12" s="245" t="n"/>
-      <c r="AU12" s="245" t="n"/>
-      <c r="AV12" s="245" t="n"/>
-      <c r="AW12" s="246" t="n"/>
-      <c r="AX12" s="268" t="inlineStr">
+      <c r="AT12" s="31" t="n"/>
+      <c r="AU12" s="31" t="n"/>
+      <c r="AV12" s="31" t="n"/>
+      <c r="AW12" s="32" t="n"/>
+      <c r="AX12" s="343" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="AY12" s="245" t="n"/>
-      <c r="AZ12" s="245" t="n"/>
-      <c r="BA12" s="245" t="n"/>
-      <c r="BB12" s="245" t="n"/>
-      <c r="BC12" s="245" t="n"/>
-      <c r="BD12" s="269" t="n"/>
+      <c r="AY12" s="31" t="n"/>
+      <c r="AZ12" s="31" t="n"/>
+      <c r="BA12" s="31" t="n"/>
+      <c r="BB12" s="31" t="n"/>
+      <c r="BC12" s="31" t="n"/>
+      <c r="BD12" s="34" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="282" t="n"/>
-      <c r="B13" s="248" t="n"/>
-      <c r="C13" s="248" t="n"/>
-      <c r="D13" s="248" t="n"/>
-      <c r="E13" s="248" t="n"/>
-      <c r="F13" s="249" t="n"/>
-      <c r="G13" s="247" t="n"/>
-      <c r="H13" s="248" t="n"/>
-      <c r="I13" s="248" t="n"/>
-      <c r="J13" s="248" t="n"/>
-      <c r="K13" s="248" t="n"/>
-      <c r="L13" s="248" t="n"/>
-      <c r="M13" s="249" t="n"/>
-      <c r="N13" s="247" t="n"/>
-      <c r="O13" s="248" t="n"/>
-      <c r="P13" s="248" t="n"/>
-      <c r="Q13" s="248" t="n"/>
-      <c r="R13" s="248" t="n"/>
-      <c r="S13" s="248" t="n"/>
-      <c r="T13" s="248" t="n"/>
-      <c r="U13" s="248" t="n"/>
-      <c r="V13" s="248" t="n"/>
-      <c r="W13" s="249" t="n"/>
-      <c r="X13" s="247" t="n"/>
-      <c r="Y13" s="248" t="n"/>
-      <c r="Z13" s="248" t="n"/>
-      <c r="AA13" s="248" t="n"/>
-      <c r="AB13" s="248" t="n"/>
-      <c r="AC13" s="248" t="n"/>
-      <c r="AD13" s="249" t="n"/>
-      <c r="AE13" s="247" t="n"/>
-      <c r="AF13" s="248" t="n"/>
-      <c r="AG13" s="248" t="n"/>
-      <c r="AH13" s="248" t="n"/>
-      <c r="AI13" s="248" t="n"/>
-      <c r="AJ13" s="248" t="n"/>
-      <c r="AK13" s="248" t="n"/>
-      <c r="AL13" s="249" t="n"/>
-      <c r="AM13" s="247" t="n"/>
-      <c r="AN13" s="248" t="n"/>
-      <c r="AO13" s="248" t="n"/>
-      <c r="AP13" s="248" t="n"/>
-      <c r="AQ13" s="248" t="n"/>
-      <c r="AR13" s="249" t="n"/>
-      <c r="AS13" s="247" t="n"/>
-      <c r="AT13" s="248" t="n"/>
-      <c r="AU13" s="248" t="n"/>
-      <c r="AV13" s="248" t="n"/>
-      <c r="AW13" s="249" t="n"/>
-      <c r="AX13" s="247" t="n"/>
-      <c r="AY13" s="248" t="n"/>
-      <c r="AZ13" s="248" t="n"/>
-      <c r="BA13" s="248" t="n"/>
-      <c r="BB13" s="248" t="n"/>
-      <c r="BC13" s="248" t="n"/>
-      <c r="BD13" s="251" t="n"/>
+      <c r="A13" s="355" t="n"/>
+      <c r="B13" s="323" t="n"/>
+      <c r="C13" s="323" t="n"/>
+      <c r="D13" s="323" t="n"/>
+      <c r="E13" s="323" t="n"/>
+      <c r="F13" s="324" t="n"/>
+      <c r="G13" s="322" t="n"/>
+      <c r="H13" s="323" t="n"/>
+      <c r="I13" s="323" t="n"/>
+      <c r="J13" s="323" t="n"/>
+      <c r="K13" s="323" t="n"/>
+      <c r="L13" s="323" t="n"/>
+      <c r="M13" s="324" t="n"/>
+      <c r="N13" s="322" t="n"/>
+      <c r="O13" s="323" t="n"/>
+      <c r="P13" s="323" t="n"/>
+      <c r="Q13" s="323" t="n"/>
+      <c r="R13" s="323" t="n"/>
+      <c r="S13" s="323" t="n"/>
+      <c r="T13" s="323" t="n"/>
+      <c r="U13" s="323" t="n"/>
+      <c r="V13" s="323" t="n"/>
+      <c r="W13" s="324" t="n"/>
+      <c r="X13" s="322" t="n"/>
+      <c r="Y13" s="323" t="n"/>
+      <c r="Z13" s="323" t="n"/>
+      <c r="AA13" s="323" t="n"/>
+      <c r="AB13" s="323" t="n"/>
+      <c r="AC13" s="323" t="n"/>
+      <c r="AD13" s="324" t="n"/>
+      <c r="AE13" s="322" t="n"/>
+      <c r="AF13" s="323" t="n"/>
+      <c r="AG13" s="323" t="n"/>
+      <c r="AH13" s="323" t="n"/>
+      <c r="AI13" s="323" t="n"/>
+      <c r="AJ13" s="323" t="n"/>
+      <c r="AK13" s="323" t="n"/>
+      <c r="AL13" s="324" t="n"/>
+      <c r="AM13" s="322" t="n"/>
+      <c r="AN13" s="323" t="n"/>
+      <c r="AO13" s="323" t="n"/>
+      <c r="AP13" s="323" t="n"/>
+      <c r="AQ13" s="323" t="n"/>
+      <c r="AR13" s="324" t="n"/>
+      <c r="AS13" s="322" t="n"/>
+      <c r="AT13" s="323" t="n"/>
+      <c r="AU13" s="323" t="n"/>
+      <c r="AV13" s="323" t="n"/>
+      <c r="AW13" s="324" t="n"/>
+      <c r="AX13" s="326" t="n"/>
+      <c r="AY13" s="323" t="n"/>
+      <c r="AZ13" s="323" t="n"/>
+      <c r="BA13" s="323" t="n"/>
+      <c r="BB13" s="323" t="n"/>
+      <c r="BC13" s="323" t="n"/>
+      <c r="BD13" s="327" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="283" t="n"/>
-      <c r="B14" s="256" t="n"/>
-      <c r="C14" s="256" t="n"/>
-      <c r="D14" s="256" t="n"/>
-      <c r="E14" s="256" t="n"/>
-      <c r="F14" s="257" t="n"/>
-      <c r="G14" s="272" t="n"/>
-      <c r="H14" s="256" t="n"/>
-      <c r="I14" s="256" t="n"/>
-      <c r="J14" s="256" t="n"/>
-      <c r="K14" s="256" t="n"/>
-      <c r="L14" s="256" t="n"/>
-      <c r="M14" s="257" t="n"/>
-      <c r="N14" s="272" t="n"/>
-      <c r="O14" s="256" t="n"/>
-      <c r="P14" s="256" t="n"/>
-      <c r="Q14" s="256" t="n"/>
-      <c r="R14" s="256" t="n"/>
-      <c r="S14" s="256" t="n"/>
-      <c r="T14" s="256" t="n"/>
-      <c r="U14" s="256" t="n"/>
-      <c r="V14" s="256" t="n"/>
-      <c r="W14" s="257" t="n"/>
-      <c r="X14" s="272" t="n"/>
-      <c r="Y14" s="256" t="n"/>
-      <c r="Z14" s="256" t="n"/>
-      <c r="AA14" s="256" t="n"/>
-      <c r="AB14" s="256" t="n"/>
-      <c r="AC14" s="256" t="n"/>
-      <c r="AD14" s="257" t="n"/>
-      <c r="AE14" s="272" t="n"/>
-      <c r="AF14" s="256" t="n"/>
-      <c r="AG14" s="256" t="n"/>
-      <c r="AH14" s="256" t="n"/>
-      <c r="AI14" s="256" t="n"/>
-      <c r="AJ14" s="256" t="n"/>
-      <c r="AK14" s="256" t="n"/>
-      <c r="AL14" s="257" t="n"/>
-      <c r="AM14" s="272" t="n"/>
-      <c r="AN14" s="256" t="n"/>
-      <c r="AO14" s="256" t="n"/>
-      <c r="AP14" s="256" t="n"/>
-      <c r="AQ14" s="256" t="n"/>
-      <c r="AR14" s="257" t="n"/>
-      <c r="AS14" s="272" t="n"/>
-      <c r="AT14" s="256" t="n"/>
-      <c r="AU14" s="256" t="n"/>
-      <c r="AV14" s="256" t="n"/>
-      <c r="AW14" s="257" t="n"/>
-      <c r="AX14" s="272" t="n"/>
-      <c r="AY14" s="256" t="n"/>
-      <c r="AZ14" s="256" t="n"/>
-      <c r="BA14" s="256" t="n"/>
-      <c r="BB14" s="256" t="n"/>
-      <c r="BC14" s="256" t="n"/>
-      <c r="BD14" s="259" t="n"/>
+      <c r="A14" s="356" t="n"/>
+      <c r="B14" s="330" t="n"/>
+      <c r="C14" s="330" t="n"/>
+      <c r="D14" s="330" t="n"/>
+      <c r="E14" s="330" t="n"/>
+      <c r="F14" s="331" t="n"/>
+      <c r="G14" s="346" t="n"/>
+      <c r="H14" s="330" t="n"/>
+      <c r="I14" s="330" t="n"/>
+      <c r="J14" s="330" t="n"/>
+      <c r="K14" s="330" t="n"/>
+      <c r="L14" s="330" t="n"/>
+      <c r="M14" s="331" t="n"/>
+      <c r="N14" s="346" t="n"/>
+      <c r="O14" s="330" t="n"/>
+      <c r="P14" s="330" t="n"/>
+      <c r="Q14" s="330" t="n"/>
+      <c r="R14" s="330" t="n"/>
+      <c r="S14" s="330" t="n"/>
+      <c r="T14" s="330" t="n"/>
+      <c r="U14" s="330" t="n"/>
+      <c r="V14" s="330" t="n"/>
+      <c r="W14" s="331" t="n"/>
+      <c r="X14" s="346" t="n"/>
+      <c r="Y14" s="330" t="n"/>
+      <c r="Z14" s="330" t="n"/>
+      <c r="AA14" s="330" t="n"/>
+      <c r="AB14" s="330" t="n"/>
+      <c r="AC14" s="330" t="n"/>
+      <c r="AD14" s="331" t="n"/>
+      <c r="AE14" s="346" t="n"/>
+      <c r="AF14" s="330" t="n"/>
+      <c r="AG14" s="330" t="n"/>
+      <c r="AH14" s="330" t="n"/>
+      <c r="AI14" s="330" t="n"/>
+      <c r="AJ14" s="330" t="n"/>
+      <c r="AK14" s="330" t="n"/>
+      <c r="AL14" s="331" t="n"/>
+      <c r="AM14" s="346" t="n"/>
+      <c r="AN14" s="330" t="n"/>
+      <c r="AO14" s="330" t="n"/>
+      <c r="AP14" s="330" t="n"/>
+      <c r="AQ14" s="330" t="n"/>
+      <c r="AR14" s="331" t="n"/>
+      <c r="AS14" s="346" t="n"/>
+      <c r="AT14" s="330" t="n"/>
+      <c r="AU14" s="330" t="n"/>
+      <c r="AV14" s="330" t="n"/>
+      <c r="AW14" s="331" t="n"/>
+      <c r="AX14" s="347" t="n"/>
+      <c r="AY14" s="330" t="n"/>
+      <c r="AZ14" s="330" t="n"/>
+      <c r="BA14" s="330" t="n"/>
+      <c r="BB14" s="330" t="n"/>
+      <c r="BC14" s="330" t="n"/>
+      <c r="BD14" s="334" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="284" t="n"/>
-      <c r="B15" s="256" t="n"/>
-      <c r="C15" s="256" t="n"/>
-      <c r="D15" s="256" t="n"/>
-      <c r="E15" s="256" t="n"/>
-      <c r="F15" s="257" t="n"/>
-      <c r="G15" s="255" t="n"/>
-      <c r="H15" s="256" t="n"/>
-      <c r="I15" s="256" t="n"/>
-      <c r="J15" s="256" t="n"/>
-      <c r="K15" s="256" t="n"/>
-      <c r="L15" s="256" t="n"/>
-      <c r="M15" s="257" t="n"/>
-      <c r="N15" s="255" t="n"/>
-      <c r="O15" s="256" t="n"/>
-      <c r="P15" s="256" t="n"/>
-      <c r="Q15" s="256" t="n"/>
-      <c r="R15" s="256" t="n"/>
-      <c r="S15" s="256" t="n"/>
-      <c r="T15" s="256" t="n"/>
-      <c r="U15" s="256" t="n"/>
-      <c r="V15" s="256" t="n"/>
-      <c r="W15" s="257" t="n"/>
-      <c r="X15" s="255" t="n"/>
-      <c r="Y15" s="256" t="n"/>
-      <c r="Z15" s="256" t="n"/>
-      <c r="AA15" s="256" t="n"/>
-      <c r="AB15" s="256" t="n"/>
-      <c r="AC15" s="256" t="n"/>
-      <c r="AD15" s="257" t="n"/>
-      <c r="AE15" s="255" t="n"/>
-      <c r="AF15" s="256" t="n"/>
-      <c r="AG15" s="256" t="n"/>
-      <c r="AH15" s="256" t="n"/>
-      <c r="AI15" s="256" t="n"/>
-      <c r="AJ15" s="256" t="n"/>
-      <c r="AK15" s="256" t="n"/>
-      <c r="AL15" s="257" t="n"/>
-      <c r="AM15" s="255" t="n"/>
-      <c r="AN15" s="256" t="n"/>
-      <c r="AO15" s="256" t="n"/>
-      <c r="AP15" s="256" t="n"/>
-      <c r="AQ15" s="256" t="n"/>
-      <c r="AR15" s="257" t="n"/>
-      <c r="AS15" s="255" t="n"/>
-      <c r="AT15" s="256" t="n"/>
-      <c r="AU15" s="256" t="n"/>
-      <c r="AV15" s="256" t="n"/>
-      <c r="AW15" s="257" t="n"/>
-      <c r="AX15" s="255" t="n"/>
-      <c r="AY15" s="256" t="n"/>
-      <c r="AZ15" s="256" t="n"/>
-      <c r="BA15" s="256" t="n"/>
-      <c r="BB15" s="256" t="n"/>
-      <c r="BC15" s="256" t="n"/>
-      <c r="BD15" s="259" t="n"/>
+      <c r="A15" s="357" t="n"/>
+      <c r="B15" s="330" t="n"/>
+      <c r="C15" s="330" t="n"/>
+      <c r="D15" s="330" t="n"/>
+      <c r="E15" s="330" t="n"/>
+      <c r="F15" s="331" t="n"/>
+      <c r="G15" s="329" t="n"/>
+      <c r="H15" s="330" t="n"/>
+      <c r="I15" s="330" t="n"/>
+      <c r="J15" s="330" t="n"/>
+      <c r="K15" s="330" t="n"/>
+      <c r="L15" s="330" t="n"/>
+      <c r="M15" s="331" t="n"/>
+      <c r="N15" s="329" t="n"/>
+      <c r="O15" s="330" t="n"/>
+      <c r="P15" s="330" t="n"/>
+      <c r="Q15" s="330" t="n"/>
+      <c r="R15" s="330" t="n"/>
+      <c r="S15" s="330" t="n"/>
+      <c r="T15" s="330" t="n"/>
+      <c r="U15" s="330" t="n"/>
+      <c r="V15" s="330" t="n"/>
+      <c r="W15" s="331" t="n"/>
+      <c r="X15" s="329" t="n"/>
+      <c r="Y15" s="330" t="n"/>
+      <c r="Z15" s="330" t="n"/>
+      <c r="AA15" s="330" t="n"/>
+      <c r="AB15" s="330" t="n"/>
+      <c r="AC15" s="330" t="n"/>
+      <c r="AD15" s="331" t="n"/>
+      <c r="AE15" s="329" t="n"/>
+      <c r="AF15" s="330" t="n"/>
+      <c r="AG15" s="330" t="n"/>
+      <c r="AH15" s="330" t="n"/>
+      <c r="AI15" s="330" t="n"/>
+      <c r="AJ15" s="330" t="n"/>
+      <c r="AK15" s="330" t="n"/>
+      <c r="AL15" s="331" t="n"/>
+      <c r="AM15" s="329" t="n"/>
+      <c r="AN15" s="330" t="n"/>
+      <c r="AO15" s="330" t="n"/>
+      <c r="AP15" s="330" t="n"/>
+      <c r="AQ15" s="330" t="n"/>
+      <c r="AR15" s="331" t="n"/>
+      <c r="AS15" s="329" t="n"/>
+      <c r="AT15" s="330" t="n"/>
+      <c r="AU15" s="330" t="n"/>
+      <c r="AV15" s="330" t="n"/>
+      <c r="AW15" s="331" t="n"/>
+      <c r="AX15" s="333" t="n"/>
+      <c r="AY15" s="330" t="n"/>
+      <c r="AZ15" s="330" t="n"/>
+      <c r="BA15" s="330" t="n"/>
+      <c r="BB15" s="330" t="n"/>
+      <c r="BC15" s="330" t="n"/>
+      <c r="BD15" s="334" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="283" t="n"/>
-      <c r="B16" s="256" t="n"/>
-      <c r="C16" s="256" t="n"/>
-      <c r="D16" s="256" t="n"/>
-      <c r="E16" s="256" t="n"/>
-      <c r="F16" s="257" t="n"/>
-      <c r="G16" s="272" t="n"/>
-      <c r="H16" s="256" t="n"/>
-      <c r="I16" s="256" t="n"/>
-      <c r="J16" s="256" t="n"/>
-      <c r="K16" s="256" t="n"/>
-      <c r="L16" s="256" t="n"/>
-      <c r="M16" s="257" t="n"/>
-      <c r="N16" s="272" t="n"/>
-      <c r="O16" s="256" t="n"/>
-      <c r="P16" s="256" t="n"/>
-      <c r="Q16" s="256" t="n"/>
-      <c r="R16" s="256" t="n"/>
-      <c r="S16" s="256" t="n"/>
-      <c r="T16" s="256" t="n"/>
-      <c r="U16" s="256" t="n"/>
-      <c r="V16" s="256" t="n"/>
-      <c r="W16" s="257" t="n"/>
-      <c r="X16" s="272" t="n"/>
-      <c r="Y16" s="256" t="n"/>
-      <c r="Z16" s="256" t="n"/>
-      <c r="AA16" s="256" t="n"/>
-      <c r="AB16" s="256" t="n"/>
-      <c r="AC16" s="256" t="n"/>
-      <c r="AD16" s="257" t="n"/>
-      <c r="AE16" s="272" t="n"/>
-      <c r="AF16" s="256" t="n"/>
-      <c r="AG16" s="256" t="n"/>
-      <c r="AH16" s="256" t="n"/>
-      <c r="AI16" s="256" t="n"/>
-      <c r="AJ16" s="256" t="n"/>
-      <c r="AK16" s="256" t="n"/>
-      <c r="AL16" s="257" t="n"/>
-      <c r="AM16" s="272" t="n"/>
-      <c r="AN16" s="256" t="n"/>
-      <c r="AO16" s="256" t="n"/>
-      <c r="AP16" s="256" t="n"/>
-      <c r="AQ16" s="256" t="n"/>
-      <c r="AR16" s="257" t="n"/>
-      <c r="AS16" s="272" t="n"/>
-      <c r="AT16" s="256" t="n"/>
-      <c r="AU16" s="256" t="n"/>
-      <c r="AV16" s="256" t="n"/>
-      <c r="AW16" s="257" t="n"/>
-      <c r="AX16" s="272" t="n"/>
-      <c r="AY16" s="256" t="n"/>
-      <c r="AZ16" s="256" t="n"/>
-      <c r="BA16" s="256" t="n"/>
-      <c r="BB16" s="256" t="n"/>
-      <c r="BC16" s="256" t="n"/>
-      <c r="BD16" s="259" t="n"/>
+      <c r="A16" s="356" t="n"/>
+      <c r="B16" s="330" t="n"/>
+      <c r="C16" s="330" t="n"/>
+      <c r="D16" s="330" t="n"/>
+      <c r="E16" s="330" t="n"/>
+      <c r="F16" s="331" t="n"/>
+      <c r="G16" s="346" t="n"/>
+      <c r="H16" s="330" t="n"/>
+      <c r="I16" s="330" t="n"/>
+      <c r="J16" s="330" t="n"/>
+      <c r="K16" s="330" t="n"/>
+      <c r="L16" s="330" t="n"/>
+      <c r="M16" s="331" t="n"/>
+      <c r="N16" s="346" t="n"/>
+      <c r="O16" s="330" t="n"/>
+      <c r="P16" s="330" t="n"/>
+      <c r="Q16" s="330" t="n"/>
+      <c r="R16" s="330" t="n"/>
+      <c r="S16" s="330" t="n"/>
+      <c r="T16" s="330" t="n"/>
+      <c r="U16" s="330" t="n"/>
+      <c r="V16" s="330" t="n"/>
+      <c r="W16" s="331" t="n"/>
+      <c r="X16" s="346" t="n"/>
+      <c r="Y16" s="330" t="n"/>
+      <c r="Z16" s="330" t="n"/>
+      <c r="AA16" s="330" t="n"/>
+      <c r="AB16" s="330" t="n"/>
+      <c r="AC16" s="330" t="n"/>
+      <c r="AD16" s="331" t="n"/>
+      <c r="AE16" s="346" t="n"/>
+      <c r="AF16" s="330" t="n"/>
+      <c r="AG16" s="330" t="n"/>
+      <c r="AH16" s="330" t="n"/>
+      <c r="AI16" s="330" t="n"/>
+      <c r="AJ16" s="330" t="n"/>
+      <c r="AK16" s="330" t="n"/>
+      <c r="AL16" s="331" t="n"/>
+      <c r="AM16" s="346" t="n"/>
+      <c r="AN16" s="330" t="n"/>
+      <c r="AO16" s="330" t="n"/>
+      <c r="AP16" s="330" t="n"/>
+      <c r="AQ16" s="330" t="n"/>
+      <c r="AR16" s="331" t="n"/>
+      <c r="AS16" s="346" t="n"/>
+      <c r="AT16" s="330" t="n"/>
+      <c r="AU16" s="330" t="n"/>
+      <c r="AV16" s="330" t="n"/>
+      <c r="AW16" s="331" t="n"/>
+      <c r="AX16" s="347" t="n"/>
+      <c r="AY16" s="330" t="n"/>
+      <c r="AZ16" s="330" t="n"/>
+      <c r="BA16" s="330" t="n"/>
+      <c r="BB16" s="330" t="n"/>
+      <c r="BC16" s="330" t="n"/>
+      <c r="BD16" s="334" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="284" t="n"/>
-      <c r="B17" s="256" t="n"/>
-      <c r="C17" s="256" t="n"/>
-      <c r="D17" s="256" t="n"/>
-      <c r="E17" s="256" t="n"/>
-      <c r="F17" s="257" t="n"/>
-      <c r="G17" s="255" t="n"/>
-      <c r="H17" s="256" t="n"/>
-      <c r="I17" s="256" t="n"/>
-      <c r="J17" s="256" t="n"/>
-      <c r="K17" s="256" t="n"/>
-      <c r="L17" s="256" t="n"/>
-      <c r="M17" s="257" t="n"/>
-      <c r="N17" s="255" t="n"/>
-      <c r="O17" s="256" t="n"/>
-      <c r="P17" s="256" t="n"/>
-      <c r="Q17" s="256" t="n"/>
-      <c r="R17" s="256" t="n"/>
-      <c r="S17" s="256" t="n"/>
-      <c r="T17" s="256" t="n"/>
-      <c r="U17" s="256" t="n"/>
-      <c r="V17" s="256" t="n"/>
-      <c r="W17" s="257" t="n"/>
-      <c r="X17" s="255" t="n"/>
-      <c r="Y17" s="256" t="n"/>
-      <c r="Z17" s="256" t="n"/>
-      <c r="AA17" s="256" t="n"/>
-      <c r="AB17" s="256" t="n"/>
-      <c r="AC17" s="256" t="n"/>
-      <c r="AD17" s="257" t="n"/>
-      <c r="AE17" s="255" t="n"/>
-      <c r="AF17" s="256" t="n"/>
-      <c r="AG17" s="256" t="n"/>
-      <c r="AH17" s="256" t="n"/>
-      <c r="AI17" s="256" t="n"/>
-      <c r="AJ17" s="256" t="n"/>
-      <c r="AK17" s="256" t="n"/>
-      <c r="AL17" s="257" t="n"/>
-      <c r="AM17" s="255" t="n"/>
-      <c r="AN17" s="256" t="n"/>
-      <c r="AO17" s="256" t="n"/>
-      <c r="AP17" s="256" t="n"/>
-      <c r="AQ17" s="256" t="n"/>
-      <c r="AR17" s="257" t="n"/>
-      <c r="AS17" s="255" t="n"/>
-      <c r="AT17" s="256" t="n"/>
-      <c r="AU17" s="256" t="n"/>
-      <c r="AV17" s="256" t="n"/>
-      <c r="AW17" s="257" t="n"/>
-      <c r="AX17" s="255" t="n"/>
-      <c r="AY17" s="256" t="n"/>
-      <c r="AZ17" s="256" t="n"/>
-      <c r="BA17" s="256" t="n"/>
-      <c r="BB17" s="256" t="n"/>
-      <c r="BC17" s="256" t="n"/>
-      <c r="BD17" s="259" t="n"/>
+      <c r="A17" s="357" t="n"/>
+      <c r="B17" s="330" t="n"/>
+      <c r="C17" s="330" t="n"/>
+      <c r="D17" s="330" t="n"/>
+      <c r="E17" s="330" t="n"/>
+      <c r="F17" s="331" t="n"/>
+      <c r="G17" s="329" t="n"/>
+      <c r="H17" s="330" t="n"/>
+      <c r="I17" s="330" t="n"/>
+      <c r="J17" s="330" t="n"/>
+      <c r="K17" s="330" t="n"/>
+      <c r="L17" s="330" t="n"/>
+      <c r="M17" s="331" t="n"/>
+      <c r="N17" s="329" t="n"/>
+      <c r="O17" s="330" t="n"/>
+      <c r="P17" s="330" t="n"/>
+      <c r="Q17" s="330" t="n"/>
+      <c r="R17" s="330" t="n"/>
+      <c r="S17" s="330" t="n"/>
+      <c r="T17" s="330" t="n"/>
+      <c r="U17" s="330" t="n"/>
+      <c r="V17" s="330" t="n"/>
+      <c r="W17" s="331" t="n"/>
+      <c r="X17" s="329" t="n"/>
+      <c r="Y17" s="330" t="n"/>
+      <c r="Z17" s="330" t="n"/>
+      <c r="AA17" s="330" t="n"/>
+      <c r="AB17" s="330" t="n"/>
+      <c r="AC17" s="330" t="n"/>
+      <c r="AD17" s="331" t="n"/>
+      <c r="AE17" s="329" t="n"/>
+      <c r="AF17" s="330" t="n"/>
+      <c r="AG17" s="330" t="n"/>
+      <c r="AH17" s="330" t="n"/>
+      <c r="AI17" s="330" t="n"/>
+      <c r="AJ17" s="330" t="n"/>
+      <c r="AK17" s="330" t="n"/>
+      <c r="AL17" s="331" t="n"/>
+      <c r="AM17" s="329" t="n"/>
+      <c r="AN17" s="330" t="n"/>
+      <c r="AO17" s="330" t="n"/>
+      <c r="AP17" s="330" t="n"/>
+      <c r="AQ17" s="330" t="n"/>
+      <c r="AR17" s="331" t="n"/>
+      <c r="AS17" s="329" t="n"/>
+      <c r="AT17" s="330" t="n"/>
+      <c r="AU17" s="330" t="n"/>
+      <c r="AV17" s="330" t="n"/>
+      <c r="AW17" s="331" t="n"/>
+      <c r="AX17" s="333" t="n"/>
+      <c r="AY17" s="330" t="n"/>
+      <c r="AZ17" s="330" t="n"/>
+      <c r="BA17" s="330" t="n"/>
+      <c r="BB17" s="330" t="n"/>
+      <c r="BC17" s="330" t="n"/>
+      <c r="BD17" s="334" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="283" t="n"/>
-      <c r="B18" s="256" t="n"/>
-      <c r="C18" s="256" t="n"/>
-      <c r="D18" s="256" t="n"/>
-      <c r="E18" s="256" t="n"/>
-      <c r="F18" s="257" t="n"/>
-      <c r="G18" s="272" t="n"/>
-      <c r="H18" s="256" t="n"/>
-      <c r="I18" s="256" t="n"/>
-      <c r="J18" s="256" t="n"/>
-      <c r="K18" s="256" t="n"/>
-      <c r="L18" s="256" t="n"/>
-      <c r="M18" s="257" t="n"/>
-      <c r="N18" s="272" t="n"/>
-      <c r="O18" s="256" t="n"/>
-      <c r="P18" s="256" t="n"/>
-      <c r="Q18" s="256" t="n"/>
-      <c r="R18" s="256" t="n"/>
-      <c r="S18" s="256" t="n"/>
-      <c r="T18" s="256" t="n"/>
-      <c r="U18" s="256" t="n"/>
-      <c r="V18" s="256" t="n"/>
-      <c r="W18" s="257" t="n"/>
-      <c r="X18" s="272" t="n"/>
-      <c r="Y18" s="256" t="n"/>
-      <c r="Z18" s="256" t="n"/>
-      <c r="AA18" s="256" t="n"/>
-      <c r="AB18" s="256" t="n"/>
-      <c r="AC18" s="256" t="n"/>
-      <c r="AD18" s="257" t="n"/>
-      <c r="AE18" s="272" t="n"/>
-      <c r="AF18" s="256" t="n"/>
-      <c r="AG18" s="256" t="n"/>
-      <c r="AH18" s="256" t="n"/>
-      <c r="AI18" s="256" t="n"/>
-      <c r="AJ18" s="256" t="n"/>
-      <c r="AK18" s="256" t="n"/>
-      <c r="AL18" s="257" t="n"/>
-      <c r="AM18" s="272" t="n"/>
-      <c r="AN18" s="256" t="n"/>
-      <c r="AO18" s="256" t="n"/>
-      <c r="AP18" s="256" t="n"/>
-      <c r="AQ18" s="256" t="n"/>
-      <c r="AR18" s="257" t="n"/>
-      <c r="AS18" s="272" t="n"/>
-      <c r="AT18" s="256" t="n"/>
-      <c r="AU18" s="256" t="n"/>
-      <c r="AV18" s="256" t="n"/>
-      <c r="AW18" s="257" t="n"/>
-      <c r="AX18" s="272" t="n"/>
-      <c r="AY18" s="256" t="n"/>
-      <c r="AZ18" s="256" t="n"/>
-      <c r="BA18" s="256" t="n"/>
-      <c r="BB18" s="256" t="n"/>
-      <c r="BC18" s="256" t="n"/>
-      <c r="BD18" s="259" t="n"/>
+      <c r="A18" s="356" t="n"/>
+      <c r="B18" s="330" t="n"/>
+      <c r="C18" s="330" t="n"/>
+      <c r="D18" s="330" t="n"/>
+      <c r="E18" s="330" t="n"/>
+      <c r="F18" s="331" t="n"/>
+      <c r="G18" s="346" t="n"/>
+      <c r="H18" s="330" t="n"/>
+      <c r="I18" s="330" t="n"/>
+      <c r="J18" s="330" t="n"/>
+      <c r="K18" s="330" t="n"/>
+      <c r="L18" s="330" t="n"/>
+      <c r="M18" s="331" t="n"/>
+      <c r="N18" s="346" t="n"/>
+      <c r="O18" s="330" t="n"/>
+      <c r="P18" s="330" t="n"/>
+      <c r="Q18" s="330" t="n"/>
+      <c r="R18" s="330" t="n"/>
+      <c r="S18" s="330" t="n"/>
+      <c r="T18" s="330" t="n"/>
+      <c r="U18" s="330" t="n"/>
+      <c r="V18" s="330" t="n"/>
+      <c r="W18" s="331" t="n"/>
+      <c r="X18" s="346" t="n"/>
+      <c r="Y18" s="330" t="n"/>
+      <c r="Z18" s="330" t="n"/>
+      <c r="AA18" s="330" t="n"/>
+      <c r="AB18" s="330" t="n"/>
+      <c r="AC18" s="330" t="n"/>
+      <c r="AD18" s="331" t="n"/>
+      <c r="AE18" s="346" t="n"/>
+      <c r="AF18" s="330" t="n"/>
+      <c r="AG18" s="330" t="n"/>
+      <c r="AH18" s="330" t="n"/>
+      <c r="AI18" s="330" t="n"/>
+      <c r="AJ18" s="330" t="n"/>
+      <c r="AK18" s="330" t="n"/>
+      <c r="AL18" s="331" t="n"/>
+      <c r="AM18" s="346" t="n"/>
+      <c r="AN18" s="330" t="n"/>
+      <c r="AO18" s="330" t="n"/>
+      <c r="AP18" s="330" t="n"/>
+      <c r="AQ18" s="330" t="n"/>
+      <c r="AR18" s="331" t="n"/>
+      <c r="AS18" s="346" t="n"/>
+      <c r="AT18" s="330" t="n"/>
+      <c r="AU18" s="330" t="n"/>
+      <c r="AV18" s="330" t="n"/>
+      <c r="AW18" s="331" t="n"/>
+      <c r="AX18" s="347" t="n"/>
+      <c r="AY18" s="330" t="n"/>
+      <c r="AZ18" s="330" t="n"/>
+      <c r="BA18" s="330" t="n"/>
+      <c r="BB18" s="330" t="n"/>
+      <c r="BC18" s="330" t="n"/>
+      <c r="BD18" s="334" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="287" t="n"/>
-      <c r="B19" s="263" t="n"/>
-      <c r="C19" s="263" t="n"/>
-      <c r="D19" s="263" t="n"/>
-      <c r="E19" s="263" t="n"/>
-      <c r="F19" s="264" t="n"/>
-      <c r="G19" s="262" t="n"/>
-      <c r="H19" s="263" t="n"/>
-      <c r="I19" s="263" t="n"/>
-      <c r="J19" s="263" t="n"/>
-      <c r="K19" s="263" t="n"/>
-      <c r="L19" s="263" t="n"/>
-      <c r="M19" s="264" t="n"/>
-      <c r="N19" s="262" t="n"/>
-      <c r="O19" s="263" t="n"/>
-      <c r="P19" s="263" t="n"/>
-      <c r="Q19" s="263" t="n"/>
-      <c r="R19" s="263" t="n"/>
-      <c r="S19" s="263" t="n"/>
-      <c r="T19" s="263" t="n"/>
-      <c r="U19" s="263" t="n"/>
-      <c r="V19" s="263" t="n"/>
-      <c r="W19" s="264" t="n"/>
-      <c r="X19" s="262" t="n"/>
-      <c r="Y19" s="263" t="n"/>
-      <c r="Z19" s="263" t="n"/>
-      <c r="AA19" s="263" t="n"/>
-      <c r="AB19" s="263" t="n"/>
-      <c r="AC19" s="263" t="n"/>
-      <c r="AD19" s="264" t="n"/>
-      <c r="AE19" s="262" t="n"/>
-      <c r="AF19" s="263" t="n"/>
-      <c r="AG19" s="263" t="n"/>
-      <c r="AH19" s="263" t="n"/>
-      <c r="AI19" s="263" t="n"/>
-      <c r="AJ19" s="263" t="n"/>
-      <c r="AK19" s="263" t="n"/>
-      <c r="AL19" s="264" t="n"/>
-      <c r="AM19" s="262" t="n"/>
-      <c r="AN19" s="263" t="n"/>
-      <c r="AO19" s="263" t="n"/>
-      <c r="AP19" s="263" t="n"/>
-      <c r="AQ19" s="263" t="n"/>
-      <c r="AR19" s="264" t="n"/>
-      <c r="AS19" s="262" t="n"/>
-      <c r="AT19" s="263" t="n"/>
-      <c r="AU19" s="263" t="n"/>
-      <c r="AV19" s="263" t="n"/>
-      <c r="AW19" s="264" t="n"/>
-      <c r="AX19" s="262" t="n"/>
-      <c r="AY19" s="263" t="n"/>
-      <c r="AZ19" s="263" t="n"/>
-      <c r="BA19" s="263" t="n"/>
-      <c r="BB19" s="263" t="n"/>
-      <c r="BC19" s="263" t="n"/>
-      <c r="BD19" s="266" t="n"/>
+      <c r="A19" s="361" t="n"/>
+      <c r="B19" s="337" t="n"/>
+      <c r="C19" s="337" t="n"/>
+      <c r="D19" s="337" t="n"/>
+      <c r="E19" s="337" t="n"/>
+      <c r="F19" s="338" t="n"/>
+      <c r="G19" s="336" t="n"/>
+      <c r="H19" s="337" t="n"/>
+      <c r="I19" s="337" t="n"/>
+      <c r="J19" s="337" t="n"/>
+      <c r="K19" s="337" t="n"/>
+      <c r="L19" s="337" t="n"/>
+      <c r="M19" s="338" t="n"/>
+      <c r="N19" s="336" t="n"/>
+      <c r="O19" s="337" t="n"/>
+      <c r="P19" s="337" t="n"/>
+      <c r="Q19" s="337" t="n"/>
+      <c r="R19" s="337" t="n"/>
+      <c r="S19" s="337" t="n"/>
+      <c r="T19" s="337" t="n"/>
+      <c r="U19" s="337" t="n"/>
+      <c r="V19" s="337" t="n"/>
+      <c r="W19" s="338" t="n"/>
+      <c r="X19" s="336" t="n"/>
+      <c r="Y19" s="337" t="n"/>
+      <c r="Z19" s="337" t="n"/>
+      <c r="AA19" s="337" t="n"/>
+      <c r="AB19" s="337" t="n"/>
+      <c r="AC19" s="337" t="n"/>
+      <c r="AD19" s="338" t="n"/>
+      <c r="AE19" s="336" t="n"/>
+      <c r="AF19" s="337" t="n"/>
+      <c r="AG19" s="337" t="n"/>
+      <c r="AH19" s="337" t="n"/>
+      <c r="AI19" s="337" t="n"/>
+      <c r="AJ19" s="337" t="n"/>
+      <c r="AK19" s="337" t="n"/>
+      <c r="AL19" s="338" t="n"/>
+      <c r="AM19" s="336" t="n"/>
+      <c r="AN19" s="337" t="n"/>
+      <c r="AO19" s="337" t="n"/>
+      <c r="AP19" s="337" t="n"/>
+      <c r="AQ19" s="337" t="n"/>
+      <c r="AR19" s="338" t="n"/>
+      <c r="AS19" s="336" t="n"/>
+      <c r="AT19" s="337" t="n"/>
+      <c r="AU19" s="337" t="n"/>
+      <c r="AV19" s="337" t="n"/>
+      <c r="AW19" s="338" t="n"/>
+      <c r="AX19" s="340" t="n"/>
+      <c r="AY19" s="337" t="n"/>
+      <c r="AZ19" s="337" t="n"/>
+      <c r="BA19" s="337" t="n"/>
+      <c r="BB19" s="337" t="n"/>
+      <c r="BC19" s="337" t="n"/>
+      <c r="BD19" s="341" t="n"/>
     </row>
     <row r="20" ht="3" customHeight="1">
       <c r="A20" s="277" t="n"/>
@@ -8999,66 +8954,66 @@
       <c r="BD20" s="277" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="241" t="inlineStr">
+      <c r="A21" s="320" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="242" t="n"/>
-      <c r="C21" s="242" t="n"/>
-      <c r="D21" s="242" t="n"/>
-      <c r="E21" s="242" t="n"/>
-      <c r="F21" s="242" t="n"/>
-      <c r="G21" s="242" t="n"/>
-      <c r="H21" s="242" t="n"/>
-      <c r="I21" s="242" t="n"/>
-      <c r="J21" s="242" t="n"/>
-      <c r="K21" s="242" t="n"/>
-      <c r="L21" s="242" t="n"/>
-      <c r="M21" s="242" t="n"/>
-      <c r="N21" s="242" t="n"/>
-      <c r="O21" s="242" t="n"/>
-      <c r="P21" s="242" t="n"/>
-      <c r="Q21" s="242" t="n"/>
-      <c r="R21" s="242" t="n"/>
-      <c r="S21" s="242" t="n"/>
-      <c r="T21" s="242" t="n"/>
-      <c r="U21" s="242" t="n"/>
-      <c r="V21" s="242" t="n"/>
-      <c r="W21" s="242" t="n"/>
-      <c r="X21" s="242" t="n"/>
-      <c r="Y21" s="242" t="n"/>
-      <c r="Z21" s="242" t="n"/>
-      <c r="AA21" s="242" t="n"/>
-      <c r="AB21" s="242" t="n"/>
-      <c r="AC21" s="242" t="n"/>
-      <c r="AD21" s="242" t="n"/>
-      <c r="AE21" s="242" t="n"/>
-      <c r="AF21" s="242" t="n"/>
-      <c r="AG21" s="242" t="n"/>
-      <c r="AH21" s="242" t="n"/>
-      <c r="AI21" s="242" t="n"/>
-      <c r="AJ21" s="242" t="n"/>
-      <c r="AK21" s="242" t="n"/>
-      <c r="AL21" s="242" t="n"/>
-      <c r="AM21" s="242" t="n"/>
-      <c r="AN21" s="242" t="n"/>
-      <c r="AO21" s="242" t="n"/>
-      <c r="AP21" s="242" t="n"/>
-      <c r="AQ21" s="242" t="n"/>
-      <c r="AR21" s="242" t="n"/>
-      <c r="AS21" s="242" t="n"/>
-      <c r="AT21" s="242" t="n"/>
-      <c r="AU21" s="242" t="n"/>
-      <c r="AV21" s="242" t="n"/>
-      <c r="AW21" s="242" t="n"/>
-      <c r="AX21" s="242" t="n"/>
-      <c r="AY21" s="242" t="n"/>
-      <c r="AZ21" s="242" t="n"/>
-      <c r="BA21" s="242" t="n"/>
-      <c r="BB21" s="242" t="n"/>
-      <c r="BC21" s="242" t="n"/>
-      <c r="BD21" s="243" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="6" t="n"/>
+      <c r="K21" s="6" t="n"/>
+      <c r="L21" s="6" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="6" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="n"/>
+      <c r="T21" s="6" t="n"/>
+      <c r="U21" s="6" t="n"/>
+      <c r="V21" s="6" t="n"/>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
+      <c r="AA21" s="6" t="n"/>
+      <c r="AB21" s="6" t="n"/>
+      <c r="AC21" s="6" t="n"/>
+      <c r="AD21" s="6" t="n"/>
+      <c r="AE21" s="6" t="n"/>
+      <c r="AF21" s="6" t="n"/>
+      <c r="AG21" s="6" t="n"/>
+      <c r="AH21" s="6" t="n"/>
+      <c r="AI21" s="6" t="n"/>
+      <c r="AJ21" s="6" t="n"/>
+      <c r="AK21" s="6" t="n"/>
+      <c r="AL21" s="6" t="n"/>
+      <c r="AM21" s="6" t="n"/>
+      <c r="AN21" s="6" t="n"/>
+      <c r="AO21" s="6" t="n"/>
+      <c r="AP21" s="6" t="n"/>
+      <c r="AQ21" s="6" t="n"/>
+      <c r="AR21" s="6" t="n"/>
+      <c r="AS21" s="6" t="n"/>
+      <c r="AT21" s="6" t="n"/>
+      <c r="AU21" s="6" t="n"/>
+      <c r="AV21" s="6" t="n"/>
+      <c r="AW21" s="6" t="n"/>
+      <c r="AX21" s="6" t="n"/>
+      <c r="AY21" s="6" t="n"/>
+      <c r="AZ21" s="6" t="n"/>
+      <c r="BA21" s="6" t="n"/>
+      <c r="BB21" s="6" t="n"/>
+      <c r="BC21" s="6" t="n"/>
+      <c r="BD21" s="7" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -9411,528 +9366,356 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="216" t="n"/>
-      <c r="B1" s="217" t="n"/>
-      <c r="C1" s="217" t="n"/>
-      <c r="D1" s="217" t="n"/>
-      <c r="E1" s="217" t="n"/>
-      <c r="F1" s="217" t="n"/>
-      <c r="G1" s="217" t="n"/>
-      <c r="H1" s="217" t="n"/>
-      <c r="I1" s="217" t="n"/>
-      <c r="J1" s="217" t="n"/>
-      <c r="K1" s="218" t="n"/>
+      <c r="A1" s="306" t="n"/>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="3" t="n"/>
       <c r="L1" s="288" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — CONTROLLED LOOKUP LISTS</t>
         </is>
       </c>
-      <c r="M1" s="217" t="n"/>
-      <c r="N1" s="217" t="n"/>
-      <c r="O1" s="217" t="n"/>
-      <c r="P1" s="217" t="n"/>
-      <c r="Q1" s="217" t="n"/>
-      <c r="R1" s="217" t="n"/>
-      <c r="S1" s="217" t="n"/>
-      <c r="T1" s="217" t="n"/>
-      <c r="U1" s="217" t="n"/>
-      <c r="V1" s="217" t="n"/>
-      <c r="W1" s="217" t="n"/>
-      <c r="X1" s="217" t="n"/>
-      <c r="Y1" s="217" t="n"/>
-      <c r="Z1" s="217" t="n"/>
-      <c r="AA1" s="217" t="n"/>
-      <c r="AB1" s="217" t="n"/>
-      <c r="AC1" s="217" t="n"/>
-      <c r="AD1" s="217" t="n"/>
-      <c r="AE1" s="217" t="n"/>
-      <c r="AF1" s="217" t="n"/>
-      <c r="AG1" s="217" t="n"/>
-      <c r="AH1" s="217" t="n"/>
-      <c r="AI1" s="217" t="n"/>
-      <c r="AJ1" s="217" t="n"/>
-      <c r="AK1" s="217" t="n"/>
-      <c r="AL1" s="217" t="n"/>
-      <c r="AM1" s="217" t="n"/>
-      <c r="AN1" s="217" t="n"/>
-      <c r="AO1" s="217" t="n"/>
-      <c r="AP1" s="217" t="n"/>
-      <c r="AQ1" s="289" t="inlineStr">
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
+      <c r="W1" s="2" t="n"/>
+      <c r="X1" s="2" t="n"/>
+      <c r="Y1" s="2" t="n"/>
+      <c r="Z1" s="2" t="n"/>
+      <c r="AA1" s="2" t="n"/>
+      <c r="AB1" s="2" t="n"/>
+      <c r="AC1" s="2" t="n"/>
+      <c r="AD1" s="2" t="n"/>
+      <c r="AE1" s="2" t="n"/>
+      <c r="AF1" s="2" t="n"/>
+      <c r="AG1" s="2" t="n"/>
+      <c r="AH1" s="2" t="n"/>
+      <c r="AI1" s="2" t="n"/>
+      <c r="AJ1" s="2" t="n"/>
+      <c r="AK1" s="2" t="n"/>
+      <c r="AL1" s="2" t="n"/>
+      <c r="AM1" s="2" t="n"/>
+      <c r="AN1" s="2" t="n"/>
+      <c r="AO1" s="2" t="n"/>
+      <c r="AP1" s="2" t="n"/>
+      <c r="AQ1" s="362" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AR1" s="217" t="n"/>
-      <c r="AS1" s="217" t="n"/>
-      <c r="AT1" s="217" t="n"/>
-      <c r="AU1" s="217" t="n"/>
-      <c r="AV1" s="221" t="n"/>
-      <c r="AW1" s="290" t="inlineStr">
+      <c r="AR1" s="2" t="n"/>
+      <c r="AS1" s="2" t="n"/>
+      <c r="AT1" s="2" t="n"/>
+      <c r="AU1" s="2" t="n"/>
+      <c r="AV1" s="308" t="n"/>
+      <c r="AW1" s="363" t="inlineStr">
         <is>
           <t>FRM-125</t>
         </is>
       </c>
-      <c r="AX1" s="217" t="n"/>
-      <c r="AY1" s="217" t="n"/>
-      <c r="AZ1" s="217" t="n"/>
-      <c r="BA1" s="217" t="n"/>
-      <c r="BB1" s="217" t="n"/>
-      <c r="BC1" s="217" t="n"/>
-      <c r="BD1" s="218" t="n"/>
+      <c r="AX1" s="2" t="n"/>
+      <c r="AY1" s="2" t="n"/>
+      <c r="AZ1" s="2" t="n"/>
+      <c r="BA1" s="2" t="n"/>
+      <c r="BB1" s="2" t="n"/>
+      <c r="BC1" s="2" t="n"/>
+      <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="223" t="n"/>
-      <c r="B2" s="224" t="n"/>
-      <c r="C2" s="224" t="n"/>
-      <c r="D2" s="224" t="n"/>
-      <c r="E2" s="224" t="n"/>
-      <c r="F2" s="224" t="n"/>
-      <c r="G2" s="224" t="n"/>
-      <c r="H2" s="224" t="n"/>
-      <c r="I2" s="224" t="n"/>
-      <c r="J2" s="224" t="n"/>
-      <c r="K2" s="225" t="n"/>
-      <c r="L2" s="223" t="n"/>
-      <c r="M2" s="224" t="n"/>
-      <c r="N2" s="224" t="n"/>
-      <c r="O2" s="224" t="n"/>
-      <c r="P2" s="224" t="n"/>
-      <c r="Q2" s="224" t="n"/>
-      <c r="R2" s="224" t="n"/>
-      <c r="S2" s="224" t="n"/>
-      <c r="T2" s="224" t="n"/>
-      <c r="U2" s="224" t="n"/>
-      <c r="V2" s="224" t="n"/>
-      <c r="W2" s="224" t="n"/>
-      <c r="X2" s="224" t="n"/>
-      <c r="Y2" s="224" t="n"/>
-      <c r="Z2" s="224" t="n"/>
-      <c r="AA2" s="224" t="n"/>
-      <c r="AB2" s="224" t="n"/>
-      <c r="AC2" s="224" t="n"/>
-      <c r="AD2" s="224" t="n"/>
-      <c r="AE2" s="224" t="n"/>
-      <c r="AF2" s="224" t="n"/>
-      <c r="AG2" s="224" t="n"/>
-      <c r="AH2" s="224" t="n"/>
-      <c r="AI2" s="224" t="n"/>
-      <c r="AJ2" s="224" t="n"/>
-      <c r="AK2" s="224" t="n"/>
-      <c r="AL2" s="224" t="n"/>
-      <c r="AM2" s="224" t="n"/>
-      <c r="AN2" s="224" t="n"/>
-      <c r="AO2" s="224" t="n"/>
-      <c r="AP2" s="224" t="n"/>
-      <c r="AQ2" s="291" t="inlineStr">
+      <c r="A2" s="9" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="9" t="n"/>
+      <c r="AQ2" s="364" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="227" t="n"/>
-      <c r="AS2" s="227" t="n"/>
-      <c r="AT2" s="227" t="n"/>
-      <c r="AU2" s="227" t="n"/>
-      <c r="AV2" s="228" t="n"/>
-      <c r="AW2" s="292" t="inlineStr">
+      <c r="AR2" s="311" t="n"/>
+      <c r="AS2" s="311" t="n"/>
+      <c r="AT2" s="311" t="n"/>
+      <c r="AU2" s="311" t="n"/>
+      <c r="AV2" s="312" t="n"/>
+      <c r="AW2" s="365" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="227" t="n"/>
-      <c r="AY2" s="227" t="n"/>
-      <c r="AZ2" s="227" t="n"/>
-      <c r="BA2" s="227" t="n"/>
-      <c r="BB2" s="227" t="n"/>
-      <c r="BC2" s="227" t="n"/>
-      <c r="BD2" s="230" t="n"/>
+      <c r="AX2" s="311" t="n"/>
+      <c r="AY2" s="311" t="n"/>
+      <c r="AZ2" s="311" t="n"/>
+      <c r="BA2" s="311" t="n"/>
+      <c r="BB2" s="311" t="n"/>
+      <c r="BC2" s="311" t="n"/>
+      <c r="BD2" s="314" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="223" t="n"/>
-      <c r="B3" s="224" t="n"/>
-      <c r="C3" s="224" t="n"/>
-      <c r="D3" s="224" t="n"/>
-      <c r="E3" s="224" t="n"/>
-      <c r="F3" s="224" t="n"/>
-      <c r="G3" s="224" t="n"/>
-      <c r="H3" s="224" t="n"/>
-      <c r="I3" s="224" t="n"/>
-      <c r="J3" s="224" t="n"/>
-      <c r="K3" s="225" t="n"/>
-      <c r="L3" s="223" t="n"/>
-      <c r="M3" s="224" t="n"/>
-      <c r="N3" s="224" t="n"/>
-      <c r="O3" s="224" t="n"/>
-      <c r="P3" s="224" t="n"/>
-      <c r="Q3" s="224" t="n"/>
-      <c r="R3" s="224" t="n"/>
-      <c r="S3" s="224" t="n"/>
-      <c r="T3" s="224" t="n"/>
-      <c r="U3" s="224" t="n"/>
-      <c r="V3" s="224" t="n"/>
-      <c r="W3" s="224" t="n"/>
-      <c r="X3" s="224" t="n"/>
-      <c r="Y3" s="224" t="n"/>
-      <c r="Z3" s="224" t="n"/>
-      <c r="AA3" s="224" t="n"/>
-      <c r="AB3" s="224" t="n"/>
-      <c r="AC3" s="224" t="n"/>
-      <c r="AD3" s="224" t="n"/>
-      <c r="AE3" s="224" t="n"/>
-      <c r="AF3" s="224" t="n"/>
-      <c r="AG3" s="224" t="n"/>
-      <c r="AH3" s="224" t="n"/>
-      <c r="AI3" s="224" t="n"/>
-      <c r="AJ3" s="224" t="n"/>
-      <c r="AK3" s="224" t="n"/>
-      <c r="AL3" s="224" t="n"/>
-      <c r="AM3" s="224" t="n"/>
-      <c r="AN3" s="224" t="n"/>
-      <c r="AO3" s="224" t="n"/>
-      <c r="AP3" s="224" t="n"/>
-      <c r="AQ3" s="291" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="9" t="n"/>
+      <c r="AQ3" s="364" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="227" t="n"/>
-      <c r="AS3" s="227" t="n"/>
-      <c r="AT3" s="227" t="n"/>
-      <c r="AU3" s="227" t="n"/>
-      <c r="AV3" s="228" t="n"/>
-      <c r="AW3" s="292" t="inlineStr">
+      <c r="AR3" s="311" t="n"/>
+      <c r="AS3" s="311" t="n"/>
+      <c r="AT3" s="311" t="n"/>
+      <c r="AU3" s="311" t="n"/>
+      <c r="AV3" s="312" t="n"/>
+      <c r="AW3" s="365" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="227" t="n"/>
-      <c r="AY3" s="227" t="n"/>
-      <c r="AZ3" s="227" t="n"/>
-      <c r="BA3" s="227" t="n"/>
-      <c r="BB3" s="227" t="n"/>
-      <c r="BC3" s="227" t="n"/>
-      <c r="BD3" s="230" t="n"/>
+      <c r="AX3" s="311" t="n"/>
+      <c r="AY3" s="311" t="n"/>
+      <c r="AZ3" s="311" t="n"/>
+      <c r="BA3" s="311" t="n"/>
+      <c r="BB3" s="311" t="n"/>
+      <c r="BC3" s="311" t="n"/>
+      <c r="BD3" s="314" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="223" t="n"/>
-      <c r="B4" s="224" t="n"/>
-      <c r="C4" s="224" t="n"/>
-      <c r="D4" s="224" t="n"/>
-      <c r="E4" s="224" t="n"/>
-      <c r="F4" s="224" t="n"/>
-      <c r="G4" s="224" t="n"/>
-      <c r="H4" s="224" t="n"/>
-      <c r="I4" s="224" t="n"/>
-      <c r="J4" s="224" t="n"/>
-      <c r="K4" s="225" t="n"/>
+      <c r="A4" s="9" t="n"/>
+      <c r="K4" s="10" t="n"/>
       <c r="L4" s="41" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="224" t="n"/>
-      <c r="N4" s="224" t="n"/>
-      <c r="O4" s="224" t="n"/>
-      <c r="P4" s="224" t="n"/>
-      <c r="Q4" s="224" t="n"/>
-      <c r="R4" s="224" t="n"/>
-      <c r="S4" s="224" t="n"/>
-      <c r="T4" s="224" t="n"/>
-      <c r="U4" s="224" t="n"/>
-      <c r="V4" s="224" t="n"/>
-      <c r="W4" s="224" t="n"/>
-      <c r="X4" s="224" t="n"/>
-      <c r="Y4" s="224" t="n"/>
-      <c r="Z4" s="224" t="n"/>
-      <c r="AA4" s="224" t="n"/>
-      <c r="AB4" s="224" t="n"/>
-      <c r="AC4" s="224" t="n"/>
-      <c r="AD4" s="224" t="n"/>
-      <c r="AE4" s="224" t="n"/>
-      <c r="AF4" s="224" t="n"/>
-      <c r="AG4" s="224" t="n"/>
-      <c r="AH4" s="224" t="n"/>
-      <c r="AI4" s="224" t="n"/>
-      <c r="AJ4" s="224" t="n"/>
-      <c r="AK4" s="224" t="n"/>
-      <c r="AL4" s="224" t="n"/>
-      <c r="AM4" s="224" t="n"/>
-      <c r="AN4" s="224" t="n"/>
-      <c r="AO4" s="224" t="n"/>
-      <c r="AP4" s="224" t="n"/>
-      <c r="AQ4" s="291" t="inlineStr">
+      <c r="AQ4" s="364" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="227" t="n"/>
-      <c r="AS4" s="227" t="n"/>
-      <c r="AT4" s="227" t="n"/>
-      <c r="AU4" s="227" t="n"/>
-      <c r="AV4" s="228" t="n"/>
-      <c r="AW4" s="292" t="inlineStr">
+      <c r="AR4" s="311" t="n"/>
+      <c r="AS4" s="311" t="n"/>
+      <c r="AT4" s="311" t="n"/>
+      <c r="AU4" s="311" t="n"/>
+      <c r="AV4" s="312" t="n"/>
+      <c r="AW4" s="365" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="227" t="n"/>
-      <c r="AY4" s="227" t="n"/>
-      <c r="AZ4" s="227" t="n"/>
-      <c r="BA4" s="227" t="n"/>
-      <c r="BB4" s="227" t="n"/>
-      <c r="BC4" s="227" t="n"/>
-      <c r="BD4" s="230" t="n"/>
+      <c r="AX4" s="311" t="n"/>
+      <c r="AY4" s="311" t="n"/>
+      <c r="AZ4" s="311" t="n"/>
+      <c r="BA4" s="311" t="n"/>
+      <c r="BB4" s="311" t="n"/>
+      <c r="BC4" s="311" t="n"/>
+      <c r="BD4" s="314" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="232" t="n"/>
-      <c r="B5" s="233" t="n"/>
-      <c r="C5" s="233" t="n"/>
-      <c r="D5" s="233" t="n"/>
-      <c r="E5" s="233" t="n"/>
-      <c r="F5" s="233" t="n"/>
-      <c r="G5" s="233" t="n"/>
-      <c r="H5" s="233" t="n"/>
-      <c r="I5" s="233" t="n"/>
-      <c r="J5" s="233" t="n"/>
-      <c r="K5" s="234" t="n"/>
+      <c r="A5" s="12" t="n"/>
+      <c r="B5" s="13" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
+      <c r="H5" s="13" t="n"/>
+      <c r="I5" s="13" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="14" t="n"/>
       <c r="L5" s="42" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="233" t="n"/>
-      <c r="N5" s="233" t="n"/>
-      <c r="O5" s="233" t="n"/>
-      <c r="P5" s="233" t="n"/>
-      <c r="Q5" s="233" t="n"/>
-      <c r="R5" s="233" t="n"/>
-      <c r="S5" s="233" t="n"/>
-      <c r="T5" s="233" t="n"/>
-      <c r="U5" s="233" t="n"/>
-      <c r="V5" s="233" t="n"/>
-      <c r="W5" s="233" t="n"/>
-      <c r="X5" s="233" t="n"/>
-      <c r="Y5" s="233" t="n"/>
-      <c r="Z5" s="233" t="n"/>
-      <c r="AA5" s="233" t="n"/>
-      <c r="AB5" s="233" t="n"/>
-      <c r="AC5" s="233" t="n"/>
-      <c r="AD5" s="233" t="n"/>
-      <c r="AE5" s="233" t="n"/>
-      <c r="AF5" s="233" t="n"/>
-      <c r="AG5" s="233" t="n"/>
-      <c r="AH5" s="233" t="n"/>
-      <c r="AI5" s="233" t="n"/>
-      <c r="AJ5" s="233" t="n"/>
-      <c r="AK5" s="233" t="n"/>
-      <c r="AL5" s="233" t="n"/>
-      <c r="AM5" s="233" t="n"/>
-      <c r="AN5" s="233" t="n"/>
-      <c r="AO5" s="233" t="n"/>
-      <c r="AP5" s="233" t="n"/>
-      <c r="AQ5" s="293" t="inlineStr">
+      <c r="M5" s="13" t="n"/>
+      <c r="N5" s="13" t="n"/>
+      <c r="O5" s="13" t="n"/>
+      <c r="P5" s="13" t="n"/>
+      <c r="Q5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
+      <c r="S5" s="13" t="n"/>
+      <c r="T5" s="13" t="n"/>
+      <c r="U5" s="13" t="n"/>
+      <c r="V5" s="13" t="n"/>
+      <c r="W5" s="13" t="n"/>
+      <c r="X5" s="13" t="n"/>
+      <c r="Y5" s="13" t="n"/>
+      <c r="Z5" s="13" t="n"/>
+      <c r="AA5" s="13" t="n"/>
+      <c r="AB5" s="13" t="n"/>
+      <c r="AC5" s="13" t="n"/>
+      <c r="AD5" s="13" t="n"/>
+      <c r="AE5" s="13" t="n"/>
+      <c r="AF5" s="13" t="n"/>
+      <c r="AG5" s="13" t="n"/>
+      <c r="AH5" s="13" t="n"/>
+      <c r="AI5" s="13" t="n"/>
+      <c r="AJ5" s="13" t="n"/>
+      <c r="AK5" s="13" t="n"/>
+      <c r="AL5" s="13" t="n"/>
+      <c r="AM5" s="13" t="n"/>
+      <c r="AN5" s="13" t="n"/>
+      <c r="AO5" s="13" t="n"/>
+      <c r="AP5" s="13" t="n"/>
+      <c r="AQ5" s="366" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="236" t="n"/>
-      <c r="AS5" s="236" t="n"/>
-      <c r="AT5" s="236" t="n"/>
-      <c r="AU5" s="236" t="n"/>
-      <c r="AV5" s="237" t="n"/>
-      <c r="AW5" s="294" t="inlineStr">
+      <c r="AR5" s="316" t="n"/>
+      <c r="AS5" s="316" t="n"/>
+      <c r="AT5" s="316" t="n"/>
+      <c r="AU5" s="316" t="n"/>
+      <c r="AV5" s="317" t="n"/>
+      <c r="AW5" s="367" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="236" t="n"/>
-      <c r="AY5" s="236" t="n"/>
-      <c r="AZ5" s="236" t="n"/>
-      <c r="BA5" s="236" t="n"/>
-      <c r="BB5" s="236" t="n"/>
-      <c r="BC5" s="236" t="n"/>
-      <c r="BD5" s="239" t="n"/>
+      <c r="AX5" s="316" t="n"/>
+      <c r="AY5" s="316" t="n"/>
+      <c r="AZ5" s="316" t="n"/>
+      <c r="BA5" s="316" t="n"/>
+      <c r="BB5" s="316" t="n"/>
+      <c r="BC5" s="316" t="n"/>
+      <c r="BD5" s="319" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
       <c r="A6" s="277" t="n"/>
-      <c r="B6" s="224" t="n"/>
-      <c r="C6" s="224" t="n"/>
-      <c r="D6" s="224" t="n"/>
-      <c r="E6" s="224" t="n"/>
-      <c r="F6" s="224" t="n"/>
-      <c r="G6" s="224" t="n"/>
-      <c r="H6" s="224" t="n"/>
-      <c r="I6" s="224" t="n"/>
-      <c r="J6" s="224" t="n"/>
-      <c r="K6" s="224" t="n"/>
-      <c r="L6" s="224" t="n"/>
-      <c r="M6" s="224" t="n"/>
-      <c r="N6" s="224" t="n"/>
-      <c r="O6" s="224" t="n"/>
-      <c r="P6" s="224" t="n"/>
-      <c r="Q6" s="224" t="n"/>
-      <c r="R6" s="224" t="n"/>
-      <c r="S6" s="224" t="n"/>
-      <c r="T6" s="224" t="n"/>
-      <c r="U6" s="224" t="n"/>
-      <c r="V6" s="224" t="n"/>
-      <c r="W6" s="224" t="n"/>
-      <c r="X6" s="224" t="n"/>
-      <c r="Y6" s="224" t="n"/>
-      <c r="Z6" s="224" t="n"/>
-      <c r="AA6" s="224" t="n"/>
-      <c r="AB6" s="224" t="n"/>
-      <c r="AC6" s="224" t="n"/>
-      <c r="AD6" s="224" t="n"/>
-      <c r="AE6" s="224" t="n"/>
-      <c r="AF6" s="224" t="n"/>
-      <c r="AG6" s="224" t="n"/>
-      <c r="AH6" s="224" t="n"/>
-      <c r="AI6" s="224" t="n"/>
-      <c r="AJ6" s="224" t="n"/>
-      <c r="AK6" s="224" t="n"/>
-      <c r="AL6" s="224" t="n"/>
-      <c r="AM6" s="224" t="n"/>
-      <c r="AN6" s="224" t="n"/>
-      <c r="AO6" s="224" t="n"/>
-      <c r="AP6" s="224" t="n"/>
-      <c r="AQ6" s="224" t="n"/>
-      <c r="AR6" s="224" t="n"/>
-      <c r="AS6" s="224" t="n"/>
-      <c r="AT6" s="224" t="n"/>
-      <c r="AU6" s="224" t="n"/>
-      <c r="AV6" s="224" t="n"/>
-      <c r="AW6" s="224" t="n"/>
-      <c r="AX6" s="224" t="n"/>
-      <c r="AY6" s="224" t="n"/>
-      <c r="AZ6" s="224" t="n"/>
-      <c r="BA6" s="224" t="n"/>
-      <c r="BB6" s="224" t="n"/>
-      <c r="BC6" s="224" t="n"/>
-      <c r="BD6" s="224" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="295" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
         </is>
       </c>
-      <c r="B7" s="242" t="n"/>
-      <c r="C7" s="242" t="n"/>
-      <c r="D7" s="242" t="n"/>
-      <c r="E7" s="242" t="n"/>
-      <c r="F7" s="242" t="n"/>
-      <c r="G7" s="242" t="n"/>
-      <c r="H7" s="242" t="n"/>
-      <c r="I7" s="242" t="n"/>
-      <c r="J7" s="242" t="n"/>
-      <c r="K7" s="242" t="n"/>
-      <c r="L7" s="242" t="n"/>
-      <c r="M7" s="242" t="n"/>
-      <c r="N7" s="242" t="n"/>
-      <c r="O7" s="242" t="n"/>
-      <c r="P7" s="242" t="n"/>
-      <c r="Q7" s="242" t="n"/>
-      <c r="R7" s="242" t="n"/>
-      <c r="S7" s="242" t="n"/>
-      <c r="T7" s="242" t="n"/>
-      <c r="U7" s="242" t="n"/>
-      <c r="V7" s="242" t="n"/>
-      <c r="W7" s="242" t="n"/>
-      <c r="X7" s="242" t="n"/>
-      <c r="Y7" s="242" t="n"/>
-      <c r="Z7" s="242" t="n"/>
-      <c r="AA7" s="242" t="n"/>
-      <c r="AB7" s="242" t="n"/>
-      <c r="AC7" s="242" t="n"/>
-      <c r="AD7" s="242" t="n"/>
-      <c r="AE7" s="242" t="n"/>
-      <c r="AF7" s="242" t="n"/>
-      <c r="AG7" s="242" t="n"/>
-      <c r="AH7" s="242" t="n"/>
-      <c r="AI7" s="242" t="n"/>
-      <c r="AJ7" s="242" t="n"/>
-      <c r="AK7" s="242" t="n"/>
-      <c r="AL7" s="242" t="n"/>
-      <c r="AM7" s="242" t="n"/>
-      <c r="AN7" s="242" t="n"/>
-      <c r="AO7" s="242" t="n"/>
-      <c r="AP7" s="242" t="n"/>
-      <c r="AQ7" s="242" t="n"/>
-      <c r="AR7" s="242" t="n"/>
-      <c r="AS7" s="242" t="n"/>
-      <c r="AT7" s="242" t="n"/>
-      <c r="AU7" s="242" t="n"/>
-      <c r="AV7" s="242" t="n"/>
-      <c r="AW7" s="242" t="n"/>
-      <c r="AX7" s="242" t="n"/>
-      <c r="AY7" s="242" t="n"/>
-      <c r="AZ7" s="242" t="n"/>
-      <c r="BA7" s="242" t="n"/>
-      <c r="BB7" s="242" t="n"/>
-      <c r="BC7" s="242" t="n"/>
-      <c r="BD7" s="243" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="6" t="n"/>
+      <c r="K7" s="6" t="n"/>
+      <c r="L7" s="6" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
+      <c r="W7" s="6" t="n"/>
+      <c r="X7" s="6" t="n"/>
+      <c r="Y7" s="6" t="n"/>
+      <c r="Z7" s="6" t="n"/>
+      <c r="AA7" s="6" t="n"/>
+      <c r="AB7" s="6" t="n"/>
+      <c r="AC7" s="6" t="n"/>
+      <c r="AD7" s="6" t="n"/>
+      <c r="AE7" s="6" t="n"/>
+      <c r="AF7" s="6" t="n"/>
+      <c r="AG7" s="6" t="n"/>
+      <c r="AH7" s="6" t="n"/>
+      <c r="AI7" s="6" t="n"/>
+      <c r="AJ7" s="6" t="n"/>
+      <c r="AK7" s="6" t="n"/>
+      <c r="AL7" s="6" t="n"/>
+      <c r="AM7" s="6" t="n"/>
+      <c r="AN7" s="6" t="n"/>
+      <c r="AO7" s="6" t="n"/>
+      <c r="AP7" s="6" t="n"/>
+      <c r="AQ7" s="6" t="n"/>
+      <c r="AR7" s="6" t="n"/>
+      <c r="AS7" s="6" t="n"/>
+      <c r="AT7" s="6" t="n"/>
+      <c r="AU7" s="6" t="n"/>
+      <c r="AV7" s="6" t="n"/>
+      <c r="AW7" s="6" t="n"/>
+      <c r="AX7" s="6" t="n"/>
+      <c r="AY7" s="6" t="n"/>
+      <c r="AZ7" s="6" t="n"/>
+      <c r="BA7" s="6" t="n"/>
+      <c r="BB7" s="6" t="n"/>
+      <c r="BC7" s="6" t="n"/>
+      <c r="BD7" s="7" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="296" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="242" t="n"/>
-      <c r="C8" s="242" t="n"/>
-      <c r="D8" s="242" t="n"/>
-      <c r="E8" s="242" t="n"/>
-      <c r="F8" s="242" t="n"/>
-      <c r="G8" s="242" t="n"/>
-      <c r="H8" s="242" t="n"/>
-      <c r="I8" s="242" t="n"/>
-      <c r="J8" s="242" t="n"/>
-      <c r="K8" s="242" t="n"/>
-      <c r="L8" s="242" t="n"/>
-      <c r="M8" s="242" t="n"/>
-      <c r="N8" s="242" t="n"/>
-      <c r="O8" s="242" t="n"/>
-      <c r="P8" s="242" t="n"/>
-      <c r="Q8" s="242" t="n"/>
-      <c r="R8" s="242" t="n"/>
-      <c r="S8" s="242" t="n"/>
-      <c r="T8" s="242" t="n"/>
-      <c r="U8" s="242" t="n"/>
-      <c r="V8" s="242" t="n"/>
-      <c r="W8" s="242" t="n"/>
-      <c r="X8" s="242" t="n"/>
-      <c r="Y8" s="242" t="n"/>
-      <c r="Z8" s="242" t="n"/>
-      <c r="AA8" s="242" t="n"/>
-      <c r="AB8" s="242" t="n"/>
-      <c r="AC8" s="242" t="n"/>
-      <c r="AD8" s="242" t="n"/>
-      <c r="AE8" s="242" t="n"/>
-      <c r="AF8" s="242" t="n"/>
-      <c r="AG8" s="242" t="n"/>
-      <c r="AH8" s="242" t="n"/>
-      <c r="AI8" s="242" t="n"/>
-      <c r="AJ8" s="242" t="n"/>
-      <c r="AK8" s="242" t="n"/>
-      <c r="AL8" s="242" t="n"/>
-      <c r="AM8" s="242" t="n"/>
-      <c r="AN8" s="242" t="n"/>
-      <c r="AO8" s="242" t="n"/>
-      <c r="AP8" s="242" t="n"/>
-      <c r="AQ8" s="242" t="n"/>
-      <c r="AR8" s="242" t="n"/>
-      <c r="AS8" s="242" t="n"/>
-      <c r="AT8" s="242" t="n"/>
-      <c r="AU8" s="242" t="n"/>
-      <c r="AV8" s="242" t="n"/>
-      <c r="AW8" s="242" t="n"/>
-      <c r="AX8" s="242" t="n"/>
-      <c r="AY8" s="242" t="n"/>
-      <c r="AZ8" s="242" t="n"/>
-      <c r="BA8" s="242" t="n"/>
-      <c r="BB8" s="242" t="n"/>
-      <c r="BC8" s="242" t="n"/>
-      <c r="BD8" s="243" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="6" t="n"/>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="n"/>
+      <c r="M8" s="6" t="n"/>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="n"/>
+      <c r="T8" s="6" t="n"/>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="n"/>
+      <c r="Y8" s="6" t="n"/>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="6" t="n"/>
+      <c r="AC8" s="6" t="n"/>
+      <c r="AD8" s="6" t="n"/>
+      <c r="AE8" s="6" t="n"/>
+      <c r="AF8" s="6" t="n"/>
+      <c r="AG8" s="6" t="n"/>
+      <c r="AH8" s="6" t="n"/>
+      <c r="AI8" s="6" t="n"/>
+      <c r="AJ8" s="6" t="n"/>
+      <c r="AK8" s="6" t="n"/>
+      <c r="AL8" s="6" t="n"/>
+      <c r="AM8" s="6" t="n"/>
+      <c r="AN8" s="6" t="n"/>
+      <c r="AO8" s="6" t="n"/>
+      <c r="AP8" s="6" t="n"/>
+      <c r="AQ8" s="6" t="n"/>
+      <c r="AR8" s="6" t="n"/>
+      <c r="AS8" s="6" t="n"/>
+      <c r="AT8" s="6" t="n"/>
+      <c r="AU8" s="6" t="n"/>
+      <c r="AV8" s="6" t="n"/>
+      <c r="AW8" s="6" t="n"/>
+      <c r="AX8" s="6" t="n"/>
+      <c r="AY8" s="6" t="n"/>
+      <c r="AZ8" s="6" t="n"/>
+      <c r="BA8" s="6" t="n"/>
+      <c r="BB8" s="6" t="n"/>
+      <c r="BC8" s="6" t="n"/>
+      <c r="BD8" s="7" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="267" t="inlineStr">
@@ -11305,66 +11088,66 @@
       <c r="BD21" s="305" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="296" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="242" t="n"/>
-      <c r="C22" s="242" t="n"/>
-      <c r="D22" s="242" t="n"/>
-      <c r="E22" s="242" t="n"/>
-      <c r="F22" s="242" t="n"/>
-      <c r="G22" s="242" t="n"/>
-      <c r="H22" s="242" t="n"/>
-      <c r="I22" s="242" t="n"/>
-      <c r="J22" s="242" t="n"/>
-      <c r="K22" s="242" t="n"/>
-      <c r="L22" s="242" t="n"/>
-      <c r="M22" s="242" t="n"/>
-      <c r="N22" s="242" t="n"/>
-      <c r="O22" s="242" t="n"/>
-      <c r="P22" s="242" t="n"/>
-      <c r="Q22" s="242" t="n"/>
-      <c r="R22" s="242" t="n"/>
-      <c r="S22" s="242" t="n"/>
-      <c r="T22" s="242" t="n"/>
-      <c r="U22" s="242" t="n"/>
-      <c r="V22" s="242" t="n"/>
-      <c r="W22" s="242" t="n"/>
-      <c r="X22" s="242" t="n"/>
-      <c r="Y22" s="242" t="n"/>
-      <c r="Z22" s="242" t="n"/>
-      <c r="AA22" s="242" t="n"/>
-      <c r="AB22" s="242" t="n"/>
-      <c r="AC22" s="242" t="n"/>
-      <c r="AD22" s="242" t="n"/>
-      <c r="AE22" s="242" t="n"/>
-      <c r="AF22" s="242" t="n"/>
-      <c r="AG22" s="242" t="n"/>
-      <c r="AH22" s="242" t="n"/>
-      <c r="AI22" s="242" t="n"/>
-      <c r="AJ22" s="242" t="n"/>
-      <c r="AK22" s="242" t="n"/>
-      <c r="AL22" s="242" t="n"/>
-      <c r="AM22" s="242" t="n"/>
-      <c r="AN22" s="242" t="n"/>
-      <c r="AO22" s="242" t="n"/>
-      <c r="AP22" s="242" t="n"/>
-      <c r="AQ22" s="242" t="n"/>
-      <c r="AR22" s="242" t="n"/>
-      <c r="AS22" s="242" t="n"/>
-      <c r="AT22" s="242" t="n"/>
-      <c r="AU22" s="242" t="n"/>
-      <c r="AV22" s="242" t="n"/>
-      <c r="AW22" s="242" t="n"/>
-      <c r="AX22" s="242" t="n"/>
-      <c r="AY22" s="242" t="n"/>
-      <c r="AZ22" s="242" t="n"/>
-      <c r="BA22" s="242" t="n"/>
-      <c r="BB22" s="242" t="n"/>
-      <c r="BC22" s="242" t="n"/>
-      <c r="BD22" s="243" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="6" t="n"/>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="n"/>
+      <c r="N22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="6" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="n"/>
+      <c r="T22" s="6" t="n"/>
+      <c r="U22" s="6" t="n"/>
+      <c r="V22" s="6" t="n"/>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
+      <c r="AB22" s="6" t="n"/>
+      <c r="AC22" s="6" t="n"/>
+      <c r="AD22" s="6" t="n"/>
+      <c r="AE22" s="6" t="n"/>
+      <c r="AF22" s="6" t="n"/>
+      <c r="AG22" s="6" t="n"/>
+      <c r="AH22" s="6" t="n"/>
+      <c r="AI22" s="6" t="n"/>
+      <c r="AJ22" s="6" t="n"/>
+      <c r="AK22" s="6" t="n"/>
+      <c r="AL22" s="6" t="n"/>
+      <c r="AM22" s="6" t="n"/>
+      <c r="AN22" s="6" t="n"/>
+      <c r="AO22" s="6" t="n"/>
+      <c r="AP22" s="6" t="n"/>
+      <c r="AQ22" s="6" t="n"/>
+      <c r="AR22" s="6" t="n"/>
+      <c r="AS22" s="6" t="n"/>
+      <c r="AT22" s="6" t="n"/>
+      <c r="AU22" s="6" t="n"/>
+      <c r="AV22" s="6" t="n"/>
+      <c r="AW22" s="6" t="n"/>
+      <c r="AX22" s="6" t="n"/>
+      <c r="AY22" s="6" t="n"/>
+      <c r="AZ22" s="6" t="n"/>
+      <c r="BA22" s="6" t="n"/>
+      <c r="BB22" s="6" t="n"/>
+      <c r="BC22" s="6" t="n"/>
+      <c r="BD22" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRReg" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRFlags" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRFlags" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -26,10 +26,648 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. ACTIVE LOG TABLE</t>
+  </si>
+  <si>
+    <t>  3. PERIODIC REVIEW / CLOSURE</t>
+  </si>
+  <si>
+    <t>  4. PERIODIC REVIEW SIGN-OFF</t>
+  </si>
+  <si>
+    <t>  CSR FLAG REFERENCE</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$14)+1</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCEPT</t>
+  </si>
+  <si>
+    <t>ACCEPT WITH ACTION</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>AWARE</t>
+  </si>
+  <si>
+    <t>Affected Process</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Boundary / SoR</t>
+  </si>
+  <si>
+    <t>CERTIFICATION BODY</t>
+  </si>
+  <si>
+    <t>CERT_STATUS</t>
+  </si>
+  <si>
+    <t>CLASSROOM</t>
+  </si>
+  <si>
+    <t>CLIMATE_SCENARIO</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COACHING</t>
+  </si>
+  <si>
+    <t>COMBINED</t>
+  </si>
+  <si>
+    <t>COMMUNITY</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACTUAL</t>
+  </si>
+  <si>
+    <t>COPY_ACTION</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR Class</t>
+  </si>
+  <si>
+    <t>CSR Register ID</t>
+  </si>
+  <si>
+    <t>CSR Source</t>
+  </si>
+  <si>
+    <t>CSR_CLASS</t>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>CUSTOMER CSR REGISTER</t>
+  </si>
+  <si>
+    <t>CUSTOMER CSR REGISTER — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>CUSTOMER CSR REGISTER — CSR CLASSIFICATION REFERENCE</t>
+  </si>
+  <si>
+    <t>CUSTOMER CSR REGISTER — EVIDENCE REFERENCE REGISTER</t>
+  </si>
+  <si>
+    <t>Closure Date</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Customer / Scope</t>
+  </si>
+  <si>
+    <t>Customer CSR register bridges Pack C governance to Pack A contract / engineering controls and Pack B quality / packaging / cleanliness obligations.</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DESTROY</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT_PRIORITY</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ENVIRONMENT</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>EXPIRING</t>
+  </si>
+  <si>
+    <t>EXTERNAL COURSE</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Escalated CSR Items</t>
+  </si>
+  <si>
+    <t>Evidence Folder Ref</t>
+  </si>
+  <si>
+    <t>Evidence ID</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Excel Table — rolling CSR register (freeze / filter required)</t>
+  </si>
+  <si>
+    <t>FACILITY</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>FRM-125</t>
+  </si>
+  <si>
+    <t>Final Status</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HSE</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INCIDENT_CLASS</t>
+  </si>
+  <si>
+    <t>INDEPENDENT</t>
+  </si>
+  <si>
+    <t>INSPECTION</t>
+  </si>
+  <si>
+    <t>INSURANCE</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>ISSUE</t>
+  </si>
+  <si>
+    <t>ISSUE_ACTION</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LEGAL</t>
+  </si>
+  <si>
+    <t>LIGHTING_AREA</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>M365 evidence / shared workbook</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING ROOM</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>Meaning</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
+  </si>
+  <si>
+    <t>NOTICE: Keep one row per customer-specific requirement. Record the source, class, affected process, owner, risk level, due date and current status; do not dilute customer language into vague summaries.</t>
+  </si>
+  <si>
+    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVATION</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>OJT</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>OUTDOOR</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PACKAGING</t>
+  </si>
+  <si>
+    <t>PARTY_TYPE</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PHYSICAL ACUTE</t>
+  </si>
+  <si>
+    <t>PHYSICAL CHRONIC</t>
+  </si>
+  <si>
+    <t>PLANNED</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Prepared Date</t>
+  </si>
+  <si>
+    <t>Process Owner</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QMS</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>READ-AND-UNDERSTAND</t>
+  </si>
+  <si>
+    <t>RECALL</t>
+  </si>
+  <si>
+    <t>REGULATOR</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REPLACE</t>
+  </si>
+  <si>
+    <t>REQUIREMENT_CLASS</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>RETURN</t>
+  </si>
+  <si>
+    <t>REVIEW_OUTCOME</t>
+  </si>
+  <si>
+    <t>REVISE</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
+  </si>
+  <si>
+    <t>Reference Path or Link</t>
+  </si>
+  <si>
+    <t>Register Status</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t>Requirement Summary</t>
+  </si>
+  <si>
+    <t>Response</t>
+  </si>
+  <si>
+    <t>Retention / Archive Ref</t>
+  </si>
+  <si>
+    <t>Review Date</t>
+  </si>
+  <si>
+    <t>Review Owner</t>
+  </si>
+  <si>
+    <t>Review Period</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>Risk Level</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SECURITY</t>
+  </si>
+  <si>
+    <t>SHAREHOLDER</t>
+  </si>
+  <si>
+    <t>SHOP FLOOR</t>
+  </si>
+  <si>
+    <t>SOCIAL</t>
+  </si>
+  <si>
+    <t>SOP-101 / SOP-102; ANNEX-QMS-001 / 002 / 011 / 024</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STRATEGIC</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUPPLIER</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Source System</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>TRACEABILITY</t>
+  </si>
+  <si>
+    <t>TRAINING_METHOD</t>
+  </si>
+  <si>
+    <t>TRANSITION CUSTOMER</t>
+  </si>
+  <si>
+    <t>TRANSITION MARKET</t>
+  </si>
+  <si>
+    <t>TRANSITION REGULATORY</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>UNDER REVIEW</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>WAREHOUSE</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +778,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +841,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="146">
+  <borders count="149">
     <border>
       <left/>
       <right/>
@@ -1771,11 +2419,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="371">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2727,6 +3409,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5498,67 +6189,67 @@
       <c r="BC36" s="277" t="n"/>
       <c r="BD36" s="277" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="320" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="368" t="inlineStr">
         <is>
           <t>NOTICE: Keep one row per customer-specific requirement. Record the source, class, affected process, owner, risk level, due date and current status; do not dilute customer language into vague summaries.</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="6" t="n"/>
-      <c r="S37" s="6" t="n"/>
-      <c r="T37" s="6" t="n"/>
-      <c r="U37" s="6" t="n"/>
-      <c r="V37" s="6" t="n"/>
-      <c r="W37" s="6" t="n"/>
-      <c r="X37" s="6" t="n"/>
-      <c r="Y37" s="6" t="n"/>
-      <c r="Z37" s="6" t="n"/>
-      <c r="AA37" s="6" t="n"/>
-      <c r="AB37" s="6" t="n"/>
-      <c r="AC37" s="6" t="n"/>
-      <c r="AD37" s="6" t="n"/>
-      <c r="AE37" s="6" t="n"/>
-      <c r="AF37" s="6" t="n"/>
-      <c r="AG37" s="6" t="n"/>
-      <c r="AH37" s="6" t="n"/>
-      <c r="AI37" s="6" t="n"/>
-      <c r="AJ37" s="6" t="n"/>
-      <c r="AK37" s="6" t="n"/>
-      <c r="AL37" s="6" t="n"/>
-      <c r="AM37" s="6" t="n"/>
-      <c r="AN37" s="6" t="n"/>
-      <c r="AO37" s="6" t="n"/>
-      <c r="AP37" s="6" t="n"/>
-      <c r="AQ37" s="6" t="n"/>
-      <c r="AR37" s="6" t="n"/>
-      <c r="AS37" s="6" t="n"/>
-      <c r="AT37" s="6" t="n"/>
-      <c r="AU37" s="6" t="n"/>
-      <c r="AV37" s="6" t="n"/>
-      <c r="AW37" s="6" t="n"/>
-      <c r="AX37" s="6" t="n"/>
-      <c r="AY37" s="6" t="n"/>
-      <c r="AZ37" s="6" t="n"/>
-      <c r="BA37" s="6" t="n"/>
-      <c r="BB37" s="6" t="n"/>
-      <c r="BC37" s="6" t="n"/>
-      <c r="BD37" s="7" t="n"/>
+      <c r="B37" s="369" t="n"/>
+      <c r="C37" s="369" t="n"/>
+      <c r="D37" s="369" t="n"/>
+      <c r="E37" s="369" t="n"/>
+      <c r="F37" s="369" t="n"/>
+      <c r="G37" s="369" t="n"/>
+      <c r="H37" s="369" t="n"/>
+      <c r="I37" s="369" t="n"/>
+      <c r="J37" s="369" t="n"/>
+      <c r="K37" s="369" t="n"/>
+      <c r="L37" s="369" t="n"/>
+      <c r="M37" s="369" t="n"/>
+      <c r="N37" s="369" t="n"/>
+      <c r="O37" s="369" t="n"/>
+      <c r="P37" s="369" t="n"/>
+      <c r="Q37" s="369" t="n"/>
+      <c r="R37" s="369" t="n"/>
+      <c r="S37" s="369" t="n"/>
+      <c r="T37" s="369" t="n"/>
+      <c r="U37" s="369" t="n"/>
+      <c r="V37" s="369" t="n"/>
+      <c r="W37" s="369" t="n"/>
+      <c r="X37" s="369" t="n"/>
+      <c r="Y37" s="369" t="n"/>
+      <c r="Z37" s="369" t="n"/>
+      <c r="AA37" s="369" t="n"/>
+      <c r="AB37" s="369" t="n"/>
+      <c r="AC37" s="369" t="n"/>
+      <c r="AD37" s="369" t="n"/>
+      <c r="AE37" s="369" t="n"/>
+      <c r="AF37" s="369" t="n"/>
+      <c r="AG37" s="369" t="n"/>
+      <c r="AH37" s="369" t="n"/>
+      <c r="AI37" s="369" t="n"/>
+      <c r="AJ37" s="369" t="n"/>
+      <c r="AK37" s="369" t="n"/>
+      <c r="AL37" s="369" t="n"/>
+      <c r="AM37" s="369" t="n"/>
+      <c r="AN37" s="369" t="n"/>
+      <c r="AO37" s="369" t="n"/>
+      <c r="AP37" s="369" t="n"/>
+      <c r="AQ37" s="369" t="n"/>
+      <c r="AR37" s="369" t="n"/>
+      <c r="AS37" s="369" t="n"/>
+      <c r="AT37" s="369" t="n"/>
+      <c r="AU37" s="369" t="n"/>
+      <c r="AV37" s="369" t="n"/>
+      <c r="AW37" s="369" t="n"/>
+      <c r="AX37" s="369" t="n"/>
+      <c r="AY37" s="369" t="n"/>
+      <c r="AZ37" s="369" t="n"/>
+      <c r="BA37" s="369" t="n"/>
+      <c r="BB37" s="369" t="n"/>
+      <c r="BC37" s="369" t="n"/>
+      <c r="BD37" s="370" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -847,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="149">
+  <borders count="154">
     <border>
       <left/>
       <right/>
@@ -2452,6 +2452,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -24,644 +24,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. ACTIVE LOG TABLE</t>
-  </si>
-  <si>
-    <t>  3. PERIODIC REVIEW / CLOSURE</t>
-  </si>
-  <si>
-    <t>  4. PERIODIC REVIEW SIGN-OFF</t>
-  </si>
-  <si>
-    <t>  CSR FLAG REFERENCE</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$14)+1</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCEPT</t>
-  </si>
-  <si>
-    <t>ACCEPT WITH ACTION</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>AWARE</t>
-  </si>
-  <si>
-    <t>Affected Process</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>Boundary / SoR</t>
-  </si>
-  <si>
-    <t>CERTIFICATION BODY</t>
-  </si>
-  <si>
-    <t>CERT_STATUS</t>
-  </si>
-  <si>
-    <t>CLASSROOM</t>
-  </si>
-  <si>
-    <t>CLIMATE_SCENARIO</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COACHING</t>
-  </si>
-  <si>
-    <t>COMBINED</t>
-  </si>
-  <si>
-    <t>COMMUNITY</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACTUAL</t>
-  </si>
-  <si>
-    <t>COPY_ACTION</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR Class</t>
-  </si>
-  <si>
-    <t>CSR Register ID</t>
-  </si>
-  <si>
-    <t>CSR Source</t>
-  </si>
-  <si>
-    <t>CSR_CLASS</t>
-  </si>
-  <si>
-    <t>CURRENCY</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>CUSTOMER CSR REGISTER</t>
-  </si>
-  <si>
-    <t>CUSTOMER CSR REGISTER — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>CUSTOMER CSR REGISTER — CSR CLASSIFICATION REFERENCE</t>
-  </si>
-  <si>
-    <t>CUSTOMER CSR REGISTER — EVIDENCE REFERENCE REGISTER</t>
-  </si>
-  <si>
-    <t>Closure Date</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Customer</t>
-  </si>
-  <si>
-    <t>Customer / Scope</t>
-  </si>
-  <si>
-    <t>Customer CSR register bridges Pack C governance to Pack A contract / engineering controls and Pack B quality / packaging / cleanliness obligations.</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DESTROY</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT_PRIORITY</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMPLOYEE</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ENVIRONMENT</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>EXPIRING</t>
-  </si>
-  <si>
-    <t>EXTERNAL COURSE</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Escalated CSR Items</t>
-  </si>
-  <si>
-    <t>Evidence Folder Ref</t>
-  </si>
-  <si>
-    <t>Evidence ID</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Excel Table — rolling CSR register (freeze / filter required)</t>
-  </si>
-  <si>
-    <t>FACILITY</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINANCE</t>
-  </si>
-  <si>
-    <t>FRM-125</t>
-  </si>
-  <si>
-    <t>Final Status</t>
-  </si>
-  <si>
-    <t>Flag</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>HSE</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INCIDENT_CLASS</t>
-  </si>
-  <si>
-    <t>INDEPENDENT</t>
-  </si>
-  <si>
-    <t>INSPECTION</t>
-  </si>
-  <si>
-    <t>INSURANCE</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>ISSUE</t>
-  </si>
-  <si>
-    <t>ISSUE_ACTION</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>JPY</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LEGAL</t>
-  </si>
-  <si>
-    <t>LIGHTING_AREA</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>M365 evidence / shared workbook</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING ROOM</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Meaning</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-  </si>
-  <si>
-    <t>NOTICE: Keep one row per customer-specific requirement. Record the source, class, affected process, owner, risk level, due date and current status; do not dilute customer language into vague summaries.</t>
-  </si>
-  <si>
-    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OBSERVATION</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>OFFICE</t>
-  </si>
-  <si>
-    <t>OJT</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>OUTDOOR</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PACKAGING</t>
-  </si>
-  <si>
-    <t>PARTY_TYPE</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PHYSICAL ACUTE</t>
-  </si>
-  <si>
-    <t>PHYSICAL CHRONIC</t>
-  </si>
-  <si>
-    <t>PLANNED</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Prepared Date</t>
-  </si>
-  <si>
-    <t>Process Owner</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QMS</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>READ-AND-UNDERSTAND</t>
-  </si>
-  <si>
-    <t>RECALL</t>
-  </si>
-  <si>
-    <t>REGULATOR</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>REQUIREMENT_CLASS</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>RETURN</t>
-  </si>
-  <si>
-    <t>REVIEW_OUTCOME</t>
-  </si>
-  <si>
-    <t>REVISE</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-  </si>
-  <si>
-    <t>Reference Path or Link</t>
-  </si>
-  <si>
-    <t>Register Status</t>
-  </si>
-  <si>
-    <t>Related Record</t>
-  </si>
-  <si>
-    <t>Requirement Summary</t>
-  </si>
-  <si>
-    <t>Response</t>
-  </si>
-  <si>
-    <t>Retention / Archive Ref</t>
-  </si>
-  <si>
-    <t>Review Date</t>
-  </si>
-  <si>
-    <t>Review Owner</t>
-  </si>
-  <si>
-    <t>Review Period</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewer</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>Risk Level</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SECURITY</t>
-  </si>
-  <si>
-    <t>SHAREHOLDER</t>
-  </si>
-  <si>
-    <t>SHOP FLOOR</t>
-  </si>
-  <si>
-    <t>SOCIAL</t>
-  </si>
-  <si>
-    <t>SOP-101 / SOP-102; ANNEX-QMS-001 / 002 / 011 / 024</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STRATEGIC</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUPPLIER</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source System</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>TRACEABILITY</t>
-  </si>
-  <si>
-    <t>TRAINING_METHOD</t>
-  </si>
-  <si>
-    <t>TRANSITION CUSTOMER</t>
-  </si>
-  <si>
-    <t>TRANSITION MARKET</t>
-  </si>
-  <si>
-    <t>TRANSITION REGULATORY</t>
-  </si>
-  <si>
-    <t>Trigger</t>
-  </si>
-  <si>
-    <t>UNDER REVIEW</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VALID</t>
-  </si>
-  <si>
-    <t>VND</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>WAREHOUSE</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8151,67 +7513,67 @@
       <c r="BC21" s="277" t="n"/>
       <c r="BD21" s="277" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="320" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="368" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="369" t="n"/>
+      <c r="C22" s="369" t="n"/>
+      <c r="D22" s="369" t="n"/>
+      <c r="E22" s="369" t="n"/>
+      <c r="F22" s="369" t="n"/>
+      <c r="G22" s="369" t="n"/>
+      <c r="H22" s="369" t="n"/>
+      <c r="I22" s="369" t="n"/>
+      <c r="J22" s="369" t="n"/>
+      <c r="K22" s="369" t="n"/>
+      <c r="L22" s="369" t="n"/>
+      <c r="M22" s="369" t="n"/>
+      <c r="N22" s="369" t="n"/>
+      <c r="O22" s="369" t="n"/>
+      <c r="P22" s="369" t="n"/>
+      <c r="Q22" s="369" t="n"/>
+      <c r="R22" s="369" t="n"/>
+      <c r="S22" s="369" t="n"/>
+      <c r="T22" s="369" t="n"/>
+      <c r="U22" s="369" t="n"/>
+      <c r="V22" s="369" t="n"/>
+      <c r="W22" s="369" t="n"/>
+      <c r="X22" s="369" t="n"/>
+      <c r="Y22" s="369" t="n"/>
+      <c r="Z22" s="369" t="n"/>
+      <c r="AA22" s="369" t="n"/>
+      <c r="AB22" s="369" t="n"/>
+      <c r="AC22" s="369" t="n"/>
+      <c r="AD22" s="369" t="n"/>
+      <c r="AE22" s="369" t="n"/>
+      <c r="AF22" s="369" t="n"/>
+      <c r="AG22" s="369" t="n"/>
+      <c r="AH22" s="369" t="n"/>
+      <c r="AI22" s="369" t="n"/>
+      <c r="AJ22" s="369" t="n"/>
+      <c r="AK22" s="369" t="n"/>
+      <c r="AL22" s="369" t="n"/>
+      <c r="AM22" s="369" t="n"/>
+      <c r="AN22" s="369" t="n"/>
+      <c r="AO22" s="369" t="n"/>
+      <c r="AP22" s="369" t="n"/>
+      <c r="AQ22" s="369" t="n"/>
+      <c r="AR22" s="369" t="n"/>
+      <c r="AS22" s="369" t="n"/>
+      <c r="AT22" s="369" t="n"/>
+      <c r="AU22" s="369" t="n"/>
+      <c r="AV22" s="369" t="n"/>
+      <c r="AW22" s="369" t="n"/>
+      <c r="AX22" s="369" t="n"/>
+      <c r="AY22" s="369" t="n"/>
+      <c r="AZ22" s="369" t="n"/>
+      <c r="BA22" s="369" t="n"/>
+      <c r="BB22" s="369" t="n"/>
+      <c r="BC22" s="369" t="n"/>
+      <c r="BD22" s="370" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -9702,67 +9064,67 @@
       <c r="BC20" s="277" t="n"/>
       <c r="BD20" s="277" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="320" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="368" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
-      <c r="S21" s="6" t="n"/>
-      <c r="T21" s="6" t="n"/>
-      <c r="U21" s="6" t="n"/>
-      <c r="V21" s="6" t="n"/>
-      <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
-      <c r="AB21" s="6" t="n"/>
-      <c r="AC21" s="6" t="n"/>
-      <c r="AD21" s="6" t="n"/>
-      <c r="AE21" s="6" t="n"/>
-      <c r="AF21" s="6" t="n"/>
-      <c r="AG21" s="6" t="n"/>
-      <c r="AH21" s="6" t="n"/>
-      <c r="AI21" s="6" t="n"/>
-      <c r="AJ21" s="6" t="n"/>
-      <c r="AK21" s="6" t="n"/>
-      <c r="AL21" s="6" t="n"/>
-      <c r="AM21" s="6" t="n"/>
-      <c r="AN21" s="6" t="n"/>
-      <c r="AO21" s="6" t="n"/>
-      <c r="AP21" s="6" t="n"/>
-      <c r="AQ21" s="6" t="n"/>
-      <c r="AR21" s="6" t="n"/>
-      <c r="AS21" s="6" t="n"/>
-      <c r="AT21" s="6" t="n"/>
-      <c r="AU21" s="6" t="n"/>
-      <c r="AV21" s="6" t="n"/>
-      <c r="AW21" s="6" t="n"/>
-      <c r="AX21" s="6" t="n"/>
-      <c r="AY21" s="6" t="n"/>
-      <c r="AZ21" s="6" t="n"/>
-      <c r="BA21" s="6" t="n"/>
-      <c r="BB21" s="6" t="n"/>
-      <c r="BC21" s="6" t="n"/>
-      <c r="BD21" s="7" t="n"/>
+      <c r="B21" s="369" t="n"/>
+      <c r="C21" s="369" t="n"/>
+      <c r="D21" s="369" t="n"/>
+      <c r="E21" s="369" t="n"/>
+      <c r="F21" s="369" t="n"/>
+      <c r="G21" s="369" t="n"/>
+      <c r="H21" s="369" t="n"/>
+      <c r="I21" s="369" t="n"/>
+      <c r="J21" s="369" t="n"/>
+      <c r="K21" s="369" t="n"/>
+      <c r="L21" s="369" t="n"/>
+      <c r="M21" s="369" t="n"/>
+      <c r="N21" s="369" t="n"/>
+      <c r="O21" s="369" t="n"/>
+      <c r="P21" s="369" t="n"/>
+      <c r="Q21" s="369" t="n"/>
+      <c r="R21" s="369" t="n"/>
+      <c r="S21" s="369" t="n"/>
+      <c r="T21" s="369" t="n"/>
+      <c r="U21" s="369" t="n"/>
+      <c r="V21" s="369" t="n"/>
+      <c r="W21" s="369" t="n"/>
+      <c r="X21" s="369" t="n"/>
+      <c r="Y21" s="369" t="n"/>
+      <c r="Z21" s="369" t="n"/>
+      <c r="AA21" s="369" t="n"/>
+      <c r="AB21" s="369" t="n"/>
+      <c r="AC21" s="369" t="n"/>
+      <c r="AD21" s="369" t="n"/>
+      <c r="AE21" s="369" t="n"/>
+      <c r="AF21" s="369" t="n"/>
+      <c r="AG21" s="369" t="n"/>
+      <c r="AH21" s="369" t="n"/>
+      <c r="AI21" s="369" t="n"/>
+      <c r="AJ21" s="369" t="n"/>
+      <c r="AK21" s="369" t="n"/>
+      <c r="AL21" s="369" t="n"/>
+      <c r="AM21" s="369" t="n"/>
+      <c r="AN21" s="369" t="n"/>
+      <c r="AO21" s="369" t="n"/>
+      <c r="AP21" s="369" t="n"/>
+      <c r="AQ21" s="369" t="n"/>
+      <c r="AR21" s="369" t="n"/>
+      <c r="AS21" s="369" t="n"/>
+      <c r="AT21" s="369" t="n"/>
+      <c r="AU21" s="369" t="n"/>
+      <c r="AV21" s="369" t="n"/>
+      <c r="AW21" s="369" t="n"/>
+      <c r="AX21" s="369" t="n"/>
+      <c r="AY21" s="369" t="n"/>
+      <c r="AZ21" s="369" t="n"/>
+      <c r="BA21" s="369" t="n"/>
+      <c r="BB21" s="369" t="n"/>
+      <c r="BC21" s="369" t="n"/>
+      <c r="BD21" s="370" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -10404,67 +9766,67 @@
       <c r="BC7" s="6" t="n"/>
       <c r="BD7" s="7" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="368" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="6" t="n"/>
-      <c r="AC8" s="6" t="n"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="6" t="n"/>
-      <c r="AI8" s="6" t="n"/>
-      <c r="AJ8" s="6" t="n"/>
-      <c r="AK8" s="6" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="6" t="n"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="6" t="n"/>
-      <c r="AQ8" s="6" t="n"/>
-      <c r="AR8" s="6" t="n"/>
-      <c r="AS8" s="6" t="n"/>
-      <c r="AT8" s="6" t="n"/>
-      <c r="AU8" s="6" t="n"/>
-      <c r="AV8" s="6" t="n"/>
-      <c r="AW8" s="6" t="n"/>
-      <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="6" t="n"/>
-      <c r="BB8" s="6" t="n"/>
-      <c r="BC8" s="6" t="n"/>
-      <c r="BD8" s="7" t="n"/>
+      <c r="B8" s="369" t="n"/>
+      <c r="C8" s="369" t="n"/>
+      <c r="D8" s="369" t="n"/>
+      <c r="E8" s="369" t="n"/>
+      <c r="F8" s="369" t="n"/>
+      <c r="G8" s="369" t="n"/>
+      <c r="H8" s="369" t="n"/>
+      <c r="I8" s="369" t="n"/>
+      <c r="J8" s="369" t="n"/>
+      <c r="K8" s="369" t="n"/>
+      <c r="L8" s="369" t="n"/>
+      <c r="M8" s="369" t="n"/>
+      <c r="N8" s="369" t="n"/>
+      <c r="O8" s="369" t="n"/>
+      <c r="P8" s="369" t="n"/>
+      <c r="Q8" s="369" t="n"/>
+      <c r="R8" s="369" t="n"/>
+      <c r="S8" s="369" t="n"/>
+      <c r="T8" s="369" t="n"/>
+      <c r="U8" s="369" t="n"/>
+      <c r="V8" s="369" t="n"/>
+      <c r="W8" s="369" t="n"/>
+      <c r="X8" s="369" t="n"/>
+      <c r="Y8" s="369" t="n"/>
+      <c r="Z8" s="369" t="n"/>
+      <c r="AA8" s="369" t="n"/>
+      <c r="AB8" s="369" t="n"/>
+      <c r="AC8" s="369" t="n"/>
+      <c r="AD8" s="369" t="n"/>
+      <c r="AE8" s="369" t="n"/>
+      <c r="AF8" s="369" t="n"/>
+      <c r="AG8" s="369" t="n"/>
+      <c r="AH8" s="369" t="n"/>
+      <c r="AI8" s="369" t="n"/>
+      <c r="AJ8" s="369" t="n"/>
+      <c r="AK8" s="369" t="n"/>
+      <c r="AL8" s="369" t="n"/>
+      <c r="AM8" s="369" t="n"/>
+      <c r="AN8" s="369" t="n"/>
+      <c r="AO8" s="369" t="n"/>
+      <c r="AP8" s="369" t="n"/>
+      <c r="AQ8" s="369" t="n"/>
+      <c r="AR8" s="369" t="n"/>
+      <c r="AS8" s="369" t="n"/>
+      <c r="AT8" s="369" t="n"/>
+      <c r="AU8" s="369" t="n"/>
+      <c r="AV8" s="369" t="n"/>
+      <c r="AW8" s="369" t="n"/>
+      <c r="AX8" s="369" t="n"/>
+      <c r="AY8" s="369" t="n"/>
+      <c r="AZ8" s="369" t="n"/>
+      <c r="BA8" s="369" t="n"/>
+      <c r="BB8" s="369" t="n"/>
+      <c r="BC8" s="369" t="n"/>
+      <c r="BD8" s="370" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="267" t="inlineStr">
@@ -11836,67 +11198,67 @@
       <c r="BC21" s="304" t="n"/>
       <c r="BD21" s="305" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="368" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="369" t="n"/>
+      <c r="C22" s="369" t="n"/>
+      <c r="D22" s="369" t="n"/>
+      <c r="E22" s="369" t="n"/>
+      <c r="F22" s="369" t="n"/>
+      <c r="G22" s="369" t="n"/>
+      <c r="H22" s="369" t="n"/>
+      <c r="I22" s="369" t="n"/>
+      <c r="J22" s="369" t="n"/>
+      <c r="K22" s="369" t="n"/>
+      <c r="L22" s="369" t="n"/>
+      <c r="M22" s="369" t="n"/>
+      <c r="N22" s="369" t="n"/>
+      <c r="O22" s="369" t="n"/>
+      <c r="P22" s="369" t="n"/>
+      <c r="Q22" s="369" t="n"/>
+      <c r="R22" s="369" t="n"/>
+      <c r="S22" s="369" t="n"/>
+      <c r="T22" s="369" t="n"/>
+      <c r="U22" s="369" t="n"/>
+      <c r="V22" s="369" t="n"/>
+      <c r="W22" s="369" t="n"/>
+      <c r="X22" s="369" t="n"/>
+      <c r="Y22" s="369" t="n"/>
+      <c r="Z22" s="369" t="n"/>
+      <c r="AA22" s="369" t="n"/>
+      <c r="AB22" s="369" t="n"/>
+      <c r="AC22" s="369" t="n"/>
+      <c r="AD22" s="369" t="n"/>
+      <c r="AE22" s="369" t="n"/>
+      <c r="AF22" s="369" t="n"/>
+      <c r="AG22" s="369" t="n"/>
+      <c r="AH22" s="369" t="n"/>
+      <c r="AI22" s="369" t="n"/>
+      <c r="AJ22" s="369" t="n"/>
+      <c r="AK22" s="369" t="n"/>
+      <c r="AL22" s="369" t="n"/>
+      <c r="AM22" s="369" t="n"/>
+      <c r="AN22" s="369" t="n"/>
+      <c r="AO22" s="369" t="n"/>
+      <c r="AP22" s="369" t="n"/>
+      <c r="AQ22" s="369" t="n"/>
+      <c r="AR22" s="369" t="n"/>
+      <c r="AS22" s="369" t="n"/>
+      <c r="AT22" s="369" t="n"/>
+      <c r="AU22" s="369" t="n"/>
+      <c r="AV22" s="369" t="n"/>
+      <c r="AW22" s="369" t="n"/>
+      <c r="AX22" s="369" t="n"/>
+      <c r="AY22" s="369" t="n"/>
+      <c r="AZ22" s="369" t="n"/>
+      <c r="BA22" s="369" t="n"/>
+      <c r="BB22" s="369" t="n"/>
+      <c r="BC22" s="369" t="n"/>
+      <c r="BD22" s="370" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -209,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="154">
+  <borders count="156">
     <border>
       <left/>
       <right/>
@@ -1873,11 +1873,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="371">
+  <cellXfs count="408">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2838,6 +2862,97 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="148" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="118" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="132" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="120" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="125" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="136" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="125" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="154" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2920,11 +3035,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2938,9 +3053,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2953,11 +3065,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2971,9 +3083,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -2986,11 +3095,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3004,9 +3113,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3019,11 +3125,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3037,9 +3143,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3397,7 +3500,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="306" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -3409,7 +3512,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="219" t="inlineStr">
+      <c r="L1" s="406" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER</t>
         </is>
@@ -3443,7 +3546,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -3468,279 +3571,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="310" t="inlineStr">
+      <c r="A2" s="371" t="n"/>
+      <c r="B2" s="372" t="n"/>
+      <c r="C2" s="372" t="n"/>
+      <c r="D2" s="372" t="n"/>
+      <c r="E2" s="372" t="n"/>
+      <c r="F2" s="372" t="n"/>
+      <c r="G2" s="372" t="n"/>
+      <c r="H2" s="372" t="n"/>
+      <c r="I2" s="372" t="n"/>
+      <c r="J2" s="372" t="n"/>
+      <c r="K2" s="373" t="n"/>
+      <c r="L2" s="372" t="n"/>
+      <c r="M2" s="372" t="n"/>
+      <c r="N2" s="372" t="n"/>
+      <c r="O2" s="372" t="n"/>
+      <c r="P2" s="372" t="n"/>
+      <c r="Q2" s="372" t="n"/>
+      <c r="R2" s="372" t="n"/>
+      <c r="S2" s="372" t="n"/>
+      <c r="T2" s="372" t="n"/>
+      <c r="U2" s="372" t="n"/>
+      <c r="V2" s="372" t="n"/>
+      <c r="W2" s="372" t="n"/>
+      <c r="X2" s="372" t="n"/>
+      <c r="Y2" s="372" t="n"/>
+      <c r="Z2" s="372" t="n"/>
+      <c r="AA2" s="372" t="n"/>
+      <c r="AB2" s="372" t="n"/>
+      <c r="AC2" s="372" t="n"/>
+      <c r="AD2" s="372" t="n"/>
+      <c r="AE2" s="372" t="n"/>
+      <c r="AF2" s="372" t="n"/>
+      <c r="AG2" s="372" t="n"/>
+      <c r="AH2" s="372" t="n"/>
+      <c r="AI2" s="372" t="n"/>
+      <c r="AJ2" s="372" t="n"/>
+      <c r="AK2" s="372" t="n"/>
+      <c r="AL2" s="372" t="n"/>
+      <c r="AM2" s="372" t="n"/>
+      <c r="AN2" s="372" t="n"/>
+      <c r="AO2" s="372" t="n"/>
+      <c r="AP2" s="373" t="n"/>
+      <c r="AQ2" s="374" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="311" t="n"/>
-      <c r="AS2" s="311" t="n"/>
-      <c r="AT2" s="311" t="n"/>
-      <c r="AU2" s="311" t="n"/>
-      <c r="AV2" s="312" t="n"/>
-      <c r="AW2" s="313" t="inlineStr">
+      <c r="AR2" s="375" t="n"/>
+      <c r="AS2" s="375" t="n"/>
+      <c r="AT2" s="375" t="n"/>
+      <c r="AU2" s="375" t="n"/>
+      <c r="AV2" s="376" t="n"/>
+      <c r="AW2" s="377" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="311" t="n"/>
-      <c r="AY2" s="311" t="n"/>
-      <c r="AZ2" s="311" t="n"/>
-      <c r="BA2" s="311" t="n"/>
-      <c r="BB2" s="311" t="n"/>
-      <c r="BC2" s="311" t="n"/>
-      <c r="BD2" s="314" t="n"/>
+      <c r="AX2" s="378" t="n"/>
+      <c r="AY2" s="378" t="n"/>
+      <c r="AZ2" s="378" t="n"/>
+      <c r="BA2" s="378" t="n"/>
+      <c r="BB2" s="378" t="n"/>
+      <c r="BC2" s="378" t="n"/>
+      <c r="BD2" s="379" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="310" t="inlineStr">
+      <c r="A3" s="380" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="381" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="381" t="n"/>
+      <c r="AQ3" s="382" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="311" t="n"/>
-      <c r="AS3" s="311" t="n"/>
-      <c r="AT3" s="311" t="n"/>
-      <c r="AU3" s="311" t="n"/>
-      <c r="AV3" s="312" t="n"/>
-      <c r="AW3" s="313" t="inlineStr">
+      <c r="AR3" s="383" t="n"/>
+      <c r="AS3" s="383" t="n"/>
+      <c r="AT3" s="383" t="n"/>
+      <c r="AU3" s="383" t="n"/>
+      <c r="AV3" s="384" t="n"/>
+      <c r="AW3" s="279" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="311" t="n"/>
-      <c r="AY3" s="311" t="n"/>
-      <c r="AZ3" s="311" t="n"/>
-      <c r="BA3" s="311" t="n"/>
-      <c r="BB3" s="311" t="n"/>
-      <c r="BC3" s="311" t="n"/>
-      <c r="BD3" s="314" t="n"/>
+      <c r="AX3" s="385" t="n"/>
+      <c r="AY3" s="385" t="n"/>
+      <c r="AZ3" s="385" t="n"/>
+      <c r="BA3" s="385" t="n"/>
+      <c r="BB3" s="385" t="n"/>
+      <c r="BC3" s="385" t="n"/>
+      <c r="BD3" s="386" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="231" t="inlineStr">
+      <c r="A4" s="380" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="381" t="n"/>
+      <c r="L4" s="387" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="310" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="381" t="n"/>
+      <c r="AQ4" s="382" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="311" t="n"/>
-      <c r="AS4" s="311" t="n"/>
-      <c r="AT4" s="311" t="n"/>
-      <c r="AU4" s="311" t="n"/>
-      <c r="AV4" s="312" t="n"/>
-      <c r="AW4" s="313" t="inlineStr">
+      <c r="AR4" s="383" t="n"/>
+      <c r="AS4" s="383" t="n"/>
+      <c r="AT4" s="383" t="n"/>
+      <c r="AU4" s="383" t="n"/>
+      <c r="AV4" s="384" t="n"/>
+      <c r="AW4" s="279" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="311" t="n"/>
-      <c r="AY4" s="311" t="n"/>
-      <c r="AZ4" s="311" t="n"/>
-      <c r="BA4" s="311" t="n"/>
-      <c r="BB4" s="311" t="n"/>
-      <c r="BC4" s="311" t="n"/>
-      <c r="BD4" s="314" t="n"/>
+      <c r="AX4" s="385" t="n"/>
+      <c r="AY4" s="385" t="n"/>
+      <c r="AZ4" s="385" t="n"/>
+      <c r="BA4" s="385" t="n"/>
+      <c r="BB4" s="385" t="n"/>
+      <c r="BC4" s="385" t="n"/>
+      <c r="BD4" s="386" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="380" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="381" t="n"/>
+      <c r="L5" s="388" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="315" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="381" t="n"/>
+      <c r="AQ5" s="382" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="316" t="n"/>
-      <c r="AS5" s="316" t="n"/>
-      <c r="AT5" s="316" t="n"/>
-      <c r="AU5" s="316" t="n"/>
-      <c r="AV5" s="317" t="n"/>
-      <c r="AW5" s="318" t="inlineStr">
+      <c r="AR5" s="383" t="n"/>
+      <c r="AS5" s="383" t="n"/>
+      <c r="AT5" s="383" t="n"/>
+      <c r="AU5" s="383" t="n"/>
+      <c r="AV5" s="384" t="n"/>
+      <c r="AW5" s="279" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="316" t="n"/>
-      <c r="AY5" s="316" t="n"/>
-      <c r="AZ5" s="316" t="n"/>
-      <c r="BA5" s="316" t="n"/>
-      <c r="BB5" s="316" t="n"/>
-      <c r="BC5" s="316" t="n"/>
-      <c r="BD5" s="319" t="n"/>
+      <c r="AX5" s="385" t="n"/>
+      <c r="AY5" s="385" t="n"/>
+      <c r="AZ5" s="385" t="n"/>
+      <c r="BA5" s="385" t="n"/>
+      <c r="BB5" s="385" t="n"/>
+      <c r="BC5" s="385" t="n"/>
+      <c r="BD5" s="386" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="240" t="n"/>
-      <c r="B6" s="240" t="n"/>
-      <c r="C6" s="240" t="n"/>
-      <c r="D6" s="240" t="n"/>
-      <c r="E6" s="240" t="n"/>
-      <c r="F6" s="240" t="n"/>
-      <c r="G6" s="240" t="n"/>
-      <c r="H6" s="240" t="n"/>
-      <c r="I6" s="240" t="n"/>
-      <c r="J6" s="240" t="n"/>
-      <c r="K6" s="240" t="n"/>
-      <c r="L6" s="240" t="n"/>
-      <c r="M6" s="240" t="n"/>
-      <c r="N6" s="240" t="n"/>
-      <c r="O6" s="240" t="n"/>
-      <c r="P6" s="240" t="n"/>
-      <c r="Q6" s="240" t="n"/>
-      <c r="R6" s="240" t="n"/>
-      <c r="S6" s="240" t="n"/>
-      <c r="T6" s="240" t="n"/>
-      <c r="U6" s="240" t="n"/>
-      <c r="V6" s="240" t="n"/>
-      <c r="W6" s="240" t="n"/>
-      <c r="X6" s="240" t="n"/>
-      <c r="Y6" s="240" t="n"/>
-      <c r="Z6" s="240" t="n"/>
-      <c r="AA6" s="240" t="n"/>
-      <c r="AB6" s="240" t="n"/>
-      <c r="AC6" s="240" t="n"/>
-      <c r="AD6" s="240" t="n"/>
-      <c r="AE6" s="240" t="n"/>
-      <c r="AF6" s="240" t="n"/>
-      <c r="AG6" s="240" t="n"/>
-      <c r="AH6" s="240" t="n"/>
-      <c r="AI6" s="240" t="n"/>
-      <c r="AJ6" s="240" t="n"/>
-      <c r="AK6" s="240" t="n"/>
-      <c r="AL6" s="240" t="n"/>
-      <c r="AM6" s="240" t="n"/>
-      <c r="AN6" s="240" t="n"/>
-      <c r="AO6" s="240" t="n"/>
-      <c r="AP6" s="240" t="n"/>
-      <c r="AQ6" s="240" t="n"/>
-      <c r="AR6" s="240" t="n"/>
-      <c r="AS6" s="240" t="n"/>
-      <c r="AT6" s="240" t="n"/>
-      <c r="AU6" s="240" t="n"/>
-      <c r="AV6" s="240" t="n"/>
-      <c r="AW6" s="240" t="n"/>
-      <c r="AX6" s="240" t="n"/>
-      <c r="AY6" s="240" t="n"/>
-      <c r="AZ6" s="240" t="n"/>
-      <c r="BA6" s="240" t="n"/>
-      <c r="BB6" s="240" t="n"/>
-      <c r="BC6" s="240" t="n"/>
-      <c r="BD6" s="240" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="389" t="n"/>
+      <c r="B6" s="390" t="n"/>
+      <c r="C6" s="390" t="n"/>
+      <c r="D6" s="390" t="n"/>
+      <c r="E6" s="390" t="n"/>
+      <c r="F6" s="390" t="n"/>
+      <c r="G6" s="390" t="n"/>
+      <c r="H6" s="390" t="n"/>
+      <c r="I6" s="390" t="n"/>
+      <c r="J6" s="390" t="n"/>
+      <c r="K6" s="391" t="n"/>
+      <c r="L6" s="390" t="n"/>
+      <c r="M6" s="390" t="n"/>
+      <c r="N6" s="390" t="n"/>
+      <c r="O6" s="390" t="n"/>
+      <c r="P6" s="390" t="n"/>
+      <c r="Q6" s="390" t="n"/>
+      <c r="R6" s="390" t="n"/>
+      <c r="S6" s="390" t="n"/>
+      <c r="T6" s="390" t="n"/>
+      <c r="U6" s="390" t="n"/>
+      <c r="V6" s="390" t="n"/>
+      <c r="W6" s="390" t="n"/>
+      <c r="X6" s="390" t="n"/>
+      <c r="Y6" s="390" t="n"/>
+      <c r="Z6" s="390" t="n"/>
+      <c r="AA6" s="390" t="n"/>
+      <c r="AB6" s="390" t="n"/>
+      <c r="AC6" s="390" t="n"/>
+      <c r="AD6" s="390" t="n"/>
+      <c r="AE6" s="390" t="n"/>
+      <c r="AF6" s="390" t="n"/>
+      <c r="AG6" s="390" t="n"/>
+      <c r="AH6" s="390" t="n"/>
+      <c r="AI6" s="390" t="n"/>
+      <c r="AJ6" s="390" t="n"/>
+      <c r="AK6" s="390" t="n"/>
+      <c r="AL6" s="390" t="n"/>
+      <c r="AM6" s="390" t="n"/>
+      <c r="AN6" s="390" t="n"/>
+      <c r="AO6" s="390" t="n"/>
+      <c r="AP6" s="391" t="n"/>
+      <c r="AQ6" s="392" t="n"/>
+      <c r="AR6" s="392" t="n"/>
+      <c r="AS6" s="392" t="n"/>
+      <c r="AT6" s="392" t="n"/>
+      <c r="AU6" s="392" t="n"/>
+      <c r="AV6" s="393" t="n"/>
+      <c r="AW6" s="394" t="n"/>
+      <c r="AX6" s="394" t="n"/>
+      <c r="AY6" s="394" t="n"/>
+      <c r="AZ6" s="394" t="n"/>
+      <c r="BA6" s="394" t="n"/>
+      <c r="BB6" s="394" t="n"/>
+      <c r="BC6" s="394" t="n"/>
+      <c r="BD6" s="395" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="396" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="321" t="inlineStr">
@@ -5610,66 +5826,66 @@
       <c r="BD36" s="277" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="368" t="inlineStr">
+      <c r="A37" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Keep one row per customer-specific requirement. Record the source, class, affected process, owner, risk level, due date and current status; do not dilute customer language into vague summaries.</t>
         </is>
       </c>
-      <c r="B37" s="369" t="n"/>
-      <c r="C37" s="369" t="n"/>
-      <c r="D37" s="369" t="n"/>
-      <c r="E37" s="369" t="n"/>
-      <c r="F37" s="369" t="n"/>
-      <c r="G37" s="369" t="n"/>
-      <c r="H37" s="369" t="n"/>
-      <c r="I37" s="369" t="n"/>
-      <c r="J37" s="369" t="n"/>
-      <c r="K37" s="369" t="n"/>
-      <c r="L37" s="369" t="n"/>
-      <c r="M37" s="369" t="n"/>
-      <c r="N37" s="369" t="n"/>
-      <c r="O37" s="369" t="n"/>
-      <c r="P37" s="369" t="n"/>
-      <c r="Q37" s="369" t="n"/>
-      <c r="R37" s="369" t="n"/>
-      <c r="S37" s="369" t="n"/>
-      <c r="T37" s="369" t="n"/>
-      <c r="U37" s="369" t="n"/>
-      <c r="V37" s="369" t="n"/>
-      <c r="W37" s="369" t="n"/>
-      <c r="X37" s="369" t="n"/>
-      <c r="Y37" s="369" t="n"/>
-      <c r="Z37" s="369" t="n"/>
-      <c r="AA37" s="369" t="n"/>
-      <c r="AB37" s="369" t="n"/>
-      <c r="AC37" s="369" t="n"/>
-      <c r="AD37" s="369" t="n"/>
-      <c r="AE37" s="369" t="n"/>
-      <c r="AF37" s="369" t="n"/>
-      <c r="AG37" s="369" t="n"/>
-      <c r="AH37" s="369" t="n"/>
-      <c r="AI37" s="369" t="n"/>
-      <c r="AJ37" s="369" t="n"/>
-      <c r="AK37" s="369" t="n"/>
-      <c r="AL37" s="369" t="n"/>
-      <c r="AM37" s="369" t="n"/>
-      <c r="AN37" s="369" t="n"/>
-      <c r="AO37" s="369" t="n"/>
-      <c r="AP37" s="369" t="n"/>
-      <c r="AQ37" s="369" t="n"/>
-      <c r="AR37" s="369" t="n"/>
-      <c r="AS37" s="369" t="n"/>
-      <c r="AT37" s="369" t="n"/>
-      <c r="AU37" s="369" t="n"/>
-      <c r="AV37" s="369" t="n"/>
-      <c r="AW37" s="369" t="n"/>
-      <c r="AX37" s="369" t="n"/>
-      <c r="AY37" s="369" t="n"/>
-      <c r="AZ37" s="369" t="n"/>
-      <c r="BA37" s="369" t="n"/>
-      <c r="BB37" s="369" t="n"/>
-      <c r="BC37" s="369" t="n"/>
-      <c r="BD37" s="370" t="n"/>
+      <c r="B37" s="397" t="n"/>
+      <c r="C37" s="397" t="n"/>
+      <c r="D37" s="397" t="n"/>
+      <c r="E37" s="397" t="n"/>
+      <c r="F37" s="397" t="n"/>
+      <c r="G37" s="397" t="n"/>
+      <c r="H37" s="397" t="n"/>
+      <c r="I37" s="397" t="n"/>
+      <c r="J37" s="397" t="n"/>
+      <c r="K37" s="397" t="n"/>
+      <c r="L37" s="397" t="n"/>
+      <c r="M37" s="397" t="n"/>
+      <c r="N37" s="397" t="n"/>
+      <c r="O37" s="397" t="n"/>
+      <c r="P37" s="397" t="n"/>
+      <c r="Q37" s="397" t="n"/>
+      <c r="R37" s="397" t="n"/>
+      <c r="S37" s="397" t="n"/>
+      <c r="T37" s="397" t="n"/>
+      <c r="U37" s="397" t="n"/>
+      <c r="V37" s="397" t="n"/>
+      <c r="W37" s="397" t="n"/>
+      <c r="X37" s="397" t="n"/>
+      <c r="Y37" s="397" t="n"/>
+      <c r="Z37" s="397" t="n"/>
+      <c r="AA37" s="397" t="n"/>
+      <c r="AB37" s="397" t="n"/>
+      <c r="AC37" s="397" t="n"/>
+      <c r="AD37" s="397" t="n"/>
+      <c r="AE37" s="397" t="n"/>
+      <c r="AF37" s="397" t="n"/>
+      <c r="AG37" s="397" t="n"/>
+      <c r="AH37" s="397" t="n"/>
+      <c r="AI37" s="397" t="n"/>
+      <c r="AJ37" s="397" t="n"/>
+      <c r="AK37" s="397" t="n"/>
+      <c r="AL37" s="397" t="n"/>
+      <c r="AM37" s="397" t="n"/>
+      <c r="AN37" s="397" t="n"/>
+      <c r="AO37" s="397" t="n"/>
+      <c r="AP37" s="397" t="n"/>
+      <c r="AQ37" s="397" t="n"/>
+      <c r="AR37" s="397" t="n"/>
+      <c r="AS37" s="397" t="n"/>
+      <c r="AT37" s="397" t="n"/>
+      <c r="AU37" s="397" t="n"/>
+      <c r="AV37" s="397" t="n"/>
+      <c r="AW37" s="397" t="n"/>
+      <c r="AX37" s="397" t="n"/>
+      <c r="AY37" s="397" t="n"/>
+      <c r="AZ37" s="397" t="n"/>
+      <c r="BA37" s="397" t="n"/>
+      <c r="BB37" s="397" t="n"/>
+      <c r="BC37" s="397" t="n"/>
+      <c r="BD37" s="398" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -6308,7 +6524,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="306" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -6320,7 +6536,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="219" t="inlineStr">
+      <c r="L1" s="406" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — CSR CLASSIFICATION REFERENCE</t>
         </is>
@@ -6354,7 +6570,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6379,279 +6595,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="310" t="inlineStr">
+      <c r="A2" s="371" t="n"/>
+      <c r="B2" s="372" t="n"/>
+      <c r="C2" s="372" t="n"/>
+      <c r="D2" s="372" t="n"/>
+      <c r="E2" s="372" t="n"/>
+      <c r="F2" s="372" t="n"/>
+      <c r="G2" s="372" t="n"/>
+      <c r="H2" s="372" t="n"/>
+      <c r="I2" s="372" t="n"/>
+      <c r="J2" s="372" t="n"/>
+      <c r="K2" s="373" t="n"/>
+      <c r="L2" s="372" t="n"/>
+      <c r="M2" s="372" t="n"/>
+      <c r="N2" s="372" t="n"/>
+      <c r="O2" s="372" t="n"/>
+      <c r="P2" s="372" t="n"/>
+      <c r="Q2" s="372" t="n"/>
+      <c r="R2" s="372" t="n"/>
+      <c r="S2" s="372" t="n"/>
+      <c r="T2" s="372" t="n"/>
+      <c r="U2" s="372" t="n"/>
+      <c r="V2" s="372" t="n"/>
+      <c r="W2" s="372" t="n"/>
+      <c r="X2" s="372" t="n"/>
+      <c r="Y2" s="372" t="n"/>
+      <c r="Z2" s="372" t="n"/>
+      <c r="AA2" s="372" t="n"/>
+      <c r="AB2" s="372" t="n"/>
+      <c r="AC2" s="372" t="n"/>
+      <c r="AD2" s="372" t="n"/>
+      <c r="AE2" s="372" t="n"/>
+      <c r="AF2" s="372" t="n"/>
+      <c r="AG2" s="372" t="n"/>
+      <c r="AH2" s="372" t="n"/>
+      <c r="AI2" s="372" t="n"/>
+      <c r="AJ2" s="372" t="n"/>
+      <c r="AK2" s="372" t="n"/>
+      <c r="AL2" s="372" t="n"/>
+      <c r="AM2" s="372" t="n"/>
+      <c r="AN2" s="372" t="n"/>
+      <c r="AO2" s="372" t="n"/>
+      <c r="AP2" s="373" t="n"/>
+      <c r="AQ2" s="374" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="311" t="n"/>
-      <c r="AS2" s="311" t="n"/>
-      <c r="AT2" s="311" t="n"/>
-      <c r="AU2" s="311" t="n"/>
-      <c r="AV2" s="312" t="n"/>
-      <c r="AW2" s="313" t="inlineStr">
+      <c r="AR2" s="375" t="n"/>
+      <c r="AS2" s="375" t="n"/>
+      <c r="AT2" s="375" t="n"/>
+      <c r="AU2" s="375" t="n"/>
+      <c r="AV2" s="376" t="n"/>
+      <c r="AW2" s="377" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="311" t="n"/>
-      <c r="AY2" s="311" t="n"/>
-      <c r="AZ2" s="311" t="n"/>
-      <c r="BA2" s="311" t="n"/>
-      <c r="BB2" s="311" t="n"/>
-      <c r="BC2" s="311" t="n"/>
-      <c r="BD2" s="314" t="n"/>
+      <c r="AX2" s="378" t="n"/>
+      <c r="AY2" s="378" t="n"/>
+      <c r="AZ2" s="378" t="n"/>
+      <c r="BA2" s="378" t="n"/>
+      <c r="BB2" s="378" t="n"/>
+      <c r="BC2" s="378" t="n"/>
+      <c r="BD2" s="379" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="310" t="inlineStr">
+      <c r="A3" s="380" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="381" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="381" t="n"/>
+      <c r="AQ3" s="382" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="311" t="n"/>
-      <c r="AS3" s="311" t="n"/>
-      <c r="AT3" s="311" t="n"/>
-      <c r="AU3" s="311" t="n"/>
-      <c r="AV3" s="312" t="n"/>
-      <c r="AW3" s="313" t="inlineStr">
+      <c r="AR3" s="383" t="n"/>
+      <c r="AS3" s="383" t="n"/>
+      <c r="AT3" s="383" t="n"/>
+      <c r="AU3" s="383" t="n"/>
+      <c r="AV3" s="384" t="n"/>
+      <c r="AW3" s="279" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="311" t="n"/>
-      <c r="AY3" s="311" t="n"/>
-      <c r="AZ3" s="311" t="n"/>
-      <c r="BA3" s="311" t="n"/>
-      <c r="BB3" s="311" t="n"/>
-      <c r="BC3" s="311" t="n"/>
-      <c r="BD3" s="314" t="n"/>
+      <c r="AX3" s="385" t="n"/>
+      <c r="AY3" s="385" t="n"/>
+      <c r="AZ3" s="385" t="n"/>
+      <c r="BA3" s="385" t="n"/>
+      <c r="BB3" s="385" t="n"/>
+      <c r="BC3" s="385" t="n"/>
+      <c r="BD3" s="386" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="231" t="inlineStr">
+      <c r="A4" s="380" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="381" t="n"/>
+      <c r="L4" s="387" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="310" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="381" t="n"/>
+      <c r="AQ4" s="382" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="311" t="n"/>
-      <c r="AS4" s="311" t="n"/>
-      <c r="AT4" s="311" t="n"/>
-      <c r="AU4" s="311" t="n"/>
-      <c r="AV4" s="312" t="n"/>
-      <c r="AW4" s="313" t="inlineStr">
+      <c r="AR4" s="383" t="n"/>
+      <c r="AS4" s="383" t="n"/>
+      <c r="AT4" s="383" t="n"/>
+      <c r="AU4" s="383" t="n"/>
+      <c r="AV4" s="384" t="n"/>
+      <c r="AW4" s="279" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="311" t="n"/>
-      <c r="AY4" s="311" t="n"/>
-      <c r="AZ4" s="311" t="n"/>
-      <c r="BA4" s="311" t="n"/>
-      <c r="BB4" s="311" t="n"/>
-      <c r="BC4" s="311" t="n"/>
-      <c r="BD4" s="314" t="n"/>
+      <c r="AX4" s="385" t="n"/>
+      <c r="AY4" s="385" t="n"/>
+      <c r="AZ4" s="385" t="n"/>
+      <c r="BA4" s="385" t="n"/>
+      <c r="BB4" s="385" t="n"/>
+      <c r="BC4" s="385" t="n"/>
+      <c r="BD4" s="386" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="380" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="381" t="n"/>
+      <c r="L5" s="388" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="315" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="381" t="n"/>
+      <c r="AQ5" s="382" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="316" t="n"/>
-      <c r="AS5" s="316" t="n"/>
-      <c r="AT5" s="316" t="n"/>
-      <c r="AU5" s="316" t="n"/>
-      <c r="AV5" s="317" t="n"/>
-      <c r="AW5" s="318" t="inlineStr">
+      <c r="AR5" s="383" t="n"/>
+      <c r="AS5" s="383" t="n"/>
+      <c r="AT5" s="383" t="n"/>
+      <c r="AU5" s="383" t="n"/>
+      <c r="AV5" s="384" t="n"/>
+      <c r="AW5" s="279" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="316" t="n"/>
-      <c r="AY5" s="316" t="n"/>
-      <c r="AZ5" s="316" t="n"/>
-      <c r="BA5" s="316" t="n"/>
-      <c r="BB5" s="316" t="n"/>
-      <c r="BC5" s="316" t="n"/>
-      <c r="BD5" s="319" t="n"/>
+      <c r="AX5" s="385" t="n"/>
+      <c r="AY5" s="385" t="n"/>
+      <c r="AZ5" s="385" t="n"/>
+      <c r="BA5" s="385" t="n"/>
+      <c r="BB5" s="385" t="n"/>
+      <c r="BC5" s="385" t="n"/>
+      <c r="BD5" s="386" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="240" t="n"/>
-      <c r="B6" s="240" t="n"/>
-      <c r="C6" s="240" t="n"/>
-      <c r="D6" s="240" t="n"/>
-      <c r="E6" s="240" t="n"/>
-      <c r="F6" s="240" t="n"/>
-      <c r="G6" s="240" t="n"/>
-      <c r="H6" s="240" t="n"/>
-      <c r="I6" s="240" t="n"/>
-      <c r="J6" s="240" t="n"/>
-      <c r="K6" s="240" t="n"/>
-      <c r="L6" s="240" t="n"/>
-      <c r="M6" s="240" t="n"/>
-      <c r="N6" s="240" t="n"/>
-      <c r="O6" s="240" t="n"/>
-      <c r="P6" s="240" t="n"/>
-      <c r="Q6" s="240" t="n"/>
-      <c r="R6" s="240" t="n"/>
-      <c r="S6" s="240" t="n"/>
-      <c r="T6" s="240" t="n"/>
-      <c r="U6" s="240" t="n"/>
-      <c r="V6" s="240" t="n"/>
-      <c r="W6" s="240" t="n"/>
-      <c r="X6" s="240" t="n"/>
-      <c r="Y6" s="240" t="n"/>
-      <c r="Z6" s="240" t="n"/>
-      <c r="AA6" s="240" t="n"/>
-      <c r="AB6" s="240" t="n"/>
-      <c r="AC6" s="240" t="n"/>
-      <c r="AD6" s="240" t="n"/>
-      <c r="AE6" s="240" t="n"/>
-      <c r="AF6" s="240" t="n"/>
-      <c r="AG6" s="240" t="n"/>
-      <c r="AH6" s="240" t="n"/>
-      <c r="AI6" s="240" t="n"/>
-      <c r="AJ6" s="240" t="n"/>
-      <c r="AK6" s="240" t="n"/>
-      <c r="AL6" s="240" t="n"/>
-      <c r="AM6" s="240" t="n"/>
-      <c r="AN6" s="240" t="n"/>
-      <c r="AO6" s="240" t="n"/>
-      <c r="AP6" s="240" t="n"/>
-      <c r="AQ6" s="240" t="n"/>
-      <c r="AR6" s="240" t="n"/>
-      <c r="AS6" s="240" t="n"/>
-      <c r="AT6" s="240" t="n"/>
-      <c r="AU6" s="240" t="n"/>
-      <c r="AV6" s="240" t="n"/>
-      <c r="AW6" s="240" t="n"/>
-      <c r="AX6" s="240" t="n"/>
-      <c r="AY6" s="240" t="n"/>
-      <c r="AZ6" s="240" t="n"/>
-      <c r="BA6" s="240" t="n"/>
-      <c r="BB6" s="240" t="n"/>
-      <c r="BC6" s="240" t="n"/>
-      <c r="BD6" s="240" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="389" t="n"/>
+      <c r="B6" s="390" t="n"/>
+      <c r="C6" s="390" t="n"/>
+      <c r="D6" s="390" t="n"/>
+      <c r="E6" s="390" t="n"/>
+      <c r="F6" s="390" t="n"/>
+      <c r="G6" s="390" t="n"/>
+      <c r="H6" s="390" t="n"/>
+      <c r="I6" s="390" t="n"/>
+      <c r="J6" s="390" t="n"/>
+      <c r="K6" s="391" t="n"/>
+      <c r="L6" s="390" t="n"/>
+      <c r="M6" s="390" t="n"/>
+      <c r="N6" s="390" t="n"/>
+      <c r="O6" s="390" t="n"/>
+      <c r="P6" s="390" t="n"/>
+      <c r="Q6" s="390" t="n"/>
+      <c r="R6" s="390" t="n"/>
+      <c r="S6" s="390" t="n"/>
+      <c r="T6" s="390" t="n"/>
+      <c r="U6" s="390" t="n"/>
+      <c r="V6" s="390" t="n"/>
+      <c r="W6" s="390" t="n"/>
+      <c r="X6" s="390" t="n"/>
+      <c r="Y6" s="390" t="n"/>
+      <c r="Z6" s="390" t="n"/>
+      <c r="AA6" s="390" t="n"/>
+      <c r="AB6" s="390" t="n"/>
+      <c r="AC6" s="390" t="n"/>
+      <c r="AD6" s="390" t="n"/>
+      <c r="AE6" s="390" t="n"/>
+      <c r="AF6" s="390" t="n"/>
+      <c r="AG6" s="390" t="n"/>
+      <c r="AH6" s="390" t="n"/>
+      <c r="AI6" s="390" t="n"/>
+      <c r="AJ6" s="390" t="n"/>
+      <c r="AK6" s="390" t="n"/>
+      <c r="AL6" s="390" t="n"/>
+      <c r="AM6" s="390" t="n"/>
+      <c r="AN6" s="390" t="n"/>
+      <c r="AO6" s="390" t="n"/>
+      <c r="AP6" s="391" t="n"/>
+      <c r="AQ6" s="392" t="n"/>
+      <c r="AR6" s="392" t="n"/>
+      <c r="AS6" s="392" t="n"/>
+      <c r="AT6" s="392" t="n"/>
+      <c r="AU6" s="392" t="n"/>
+      <c r="AV6" s="393" t="n"/>
+      <c r="AW6" s="394" t="n"/>
+      <c r="AX6" s="394" t="n"/>
+      <c r="AY6" s="394" t="n"/>
+      <c r="AZ6" s="394" t="n"/>
+      <c r="BA6" s="394" t="n"/>
+      <c r="BB6" s="394" t="n"/>
+      <c r="BC6" s="394" t="n"/>
+      <c r="BD6" s="395" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="396" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="321" t="inlineStr">
@@ -7514,66 +7843,66 @@
       <c r="BD21" s="277" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="368" t="inlineStr">
+      <c r="A22" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="369" t="n"/>
-      <c r="C22" s="369" t="n"/>
-      <c r="D22" s="369" t="n"/>
-      <c r="E22" s="369" t="n"/>
-      <c r="F22" s="369" t="n"/>
-      <c r="G22" s="369" t="n"/>
-      <c r="H22" s="369" t="n"/>
-      <c r="I22" s="369" t="n"/>
-      <c r="J22" s="369" t="n"/>
-      <c r="K22" s="369" t="n"/>
-      <c r="L22" s="369" t="n"/>
-      <c r="M22" s="369" t="n"/>
-      <c r="N22" s="369" t="n"/>
-      <c r="O22" s="369" t="n"/>
-      <c r="P22" s="369" t="n"/>
-      <c r="Q22" s="369" t="n"/>
-      <c r="R22" s="369" t="n"/>
-      <c r="S22" s="369" t="n"/>
-      <c r="T22" s="369" t="n"/>
-      <c r="U22" s="369" t="n"/>
-      <c r="V22" s="369" t="n"/>
-      <c r="W22" s="369" t="n"/>
-      <c r="X22" s="369" t="n"/>
-      <c r="Y22" s="369" t="n"/>
-      <c r="Z22" s="369" t="n"/>
-      <c r="AA22" s="369" t="n"/>
-      <c r="AB22" s="369" t="n"/>
-      <c r="AC22" s="369" t="n"/>
-      <c r="AD22" s="369" t="n"/>
-      <c r="AE22" s="369" t="n"/>
-      <c r="AF22" s="369" t="n"/>
-      <c r="AG22" s="369" t="n"/>
-      <c r="AH22" s="369" t="n"/>
-      <c r="AI22" s="369" t="n"/>
-      <c r="AJ22" s="369" t="n"/>
-      <c r="AK22" s="369" t="n"/>
-      <c r="AL22" s="369" t="n"/>
-      <c r="AM22" s="369" t="n"/>
-      <c r="AN22" s="369" t="n"/>
-      <c r="AO22" s="369" t="n"/>
-      <c r="AP22" s="369" t="n"/>
-      <c r="AQ22" s="369" t="n"/>
-      <c r="AR22" s="369" t="n"/>
-      <c r="AS22" s="369" t="n"/>
-      <c r="AT22" s="369" t="n"/>
-      <c r="AU22" s="369" t="n"/>
-      <c r="AV22" s="369" t="n"/>
-      <c r="AW22" s="369" t="n"/>
-      <c r="AX22" s="369" t="n"/>
-      <c r="AY22" s="369" t="n"/>
-      <c r="AZ22" s="369" t="n"/>
-      <c r="BA22" s="369" t="n"/>
-      <c r="BB22" s="369" t="n"/>
-      <c r="BC22" s="369" t="n"/>
-      <c r="BD22" s="370" t="n"/>
+      <c r="B22" s="397" t="n"/>
+      <c r="C22" s="397" t="n"/>
+      <c r="D22" s="397" t="n"/>
+      <c r="E22" s="397" t="n"/>
+      <c r="F22" s="397" t="n"/>
+      <c r="G22" s="397" t="n"/>
+      <c r="H22" s="397" t="n"/>
+      <c r="I22" s="397" t="n"/>
+      <c r="J22" s="397" t="n"/>
+      <c r="K22" s="397" t="n"/>
+      <c r="L22" s="397" t="n"/>
+      <c r="M22" s="397" t="n"/>
+      <c r="N22" s="397" t="n"/>
+      <c r="O22" s="397" t="n"/>
+      <c r="P22" s="397" t="n"/>
+      <c r="Q22" s="397" t="n"/>
+      <c r="R22" s="397" t="n"/>
+      <c r="S22" s="397" t="n"/>
+      <c r="T22" s="397" t="n"/>
+      <c r="U22" s="397" t="n"/>
+      <c r="V22" s="397" t="n"/>
+      <c r="W22" s="397" t="n"/>
+      <c r="X22" s="397" t="n"/>
+      <c r="Y22" s="397" t="n"/>
+      <c r="Z22" s="397" t="n"/>
+      <c r="AA22" s="397" t="n"/>
+      <c r="AB22" s="397" t="n"/>
+      <c r="AC22" s="397" t="n"/>
+      <c r="AD22" s="397" t="n"/>
+      <c r="AE22" s="397" t="n"/>
+      <c r="AF22" s="397" t="n"/>
+      <c r="AG22" s="397" t="n"/>
+      <c r="AH22" s="397" t="n"/>
+      <c r="AI22" s="397" t="n"/>
+      <c r="AJ22" s="397" t="n"/>
+      <c r="AK22" s="397" t="n"/>
+      <c r="AL22" s="397" t="n"/>
+      <c r="AM22" s="397" t="n"/>
+      <c r="AN22" s="397" t="n"/>
+      <c r="AO22" s="397" t="n"/>
+      <c r="AP22" s="397" t="n"/>
+      <c r="AQ22" s="397" t="n"/>
+      <c r="AR22" s="397" t="n"/>
+      <c r="AS22" s="397" t="n"/>
+      <c r="AT22" s="397" t="n"/>
+      <c r="AU22" s="397" t="n"/>
+      <c r="AV22" s="397" t="n"/>
+      <c r="AW22" s="397" t="n"/>
+      <c r="AX22" s="397" t="n"/>
+      <c r="AY22" s="397" t="n"/>
+      <c r="AZ22" s="397" t="n"/>
+      <c r="BA22" s="397" t="n"/>
+      <c r="BB22" s="397" t="n"/>
+      <c r="BC22" s="397" t="n"/>
+      <c r="BD22" s="398" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -7905,7 +8234,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="306" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -7917,7 +8246,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="219" t="inlineStr">
+      <c r="L1" s="406" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — EVIDENCE REFERENCE REGISTER</t>
         </is>
@@ -7951,7 +8280,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="307" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7976,279 +8305,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="310" t="inlineStr">
+      <c r="A2" s="371" t="n"/>
+      <c r="B2" s="372" t="n"/>
+      <c r="C2" s="372" t="n"/>
+      <c r="D2" s="372" t="n"/>
+      <c r="E2" s="372" t="n"/>
+      <c r="F2" s="372" t="n"/>
+      <c r="G2" s="372" t="n"/>
+      <c r="H2" s="372" t="n"/>
+      <c r="I2" s="372" t="n"/>
+      <c r="J2" s="372" t="n"/>
+      <c r="K2" s="373" t="n"/>
+      <c r="L2" s="372" t="n"/>
+      <c r="M2" s="372" t="n"/>
+      <c r="N2" s="372" t="n"/>
+      <c r="O2" s="372" t="n"/>
+      <c r="P2" s="372" t="n"/>
+      <c r="Q2" s="372" t="n"/>
+      <c r="R2" s="372" t="n"/>
+      <c r="S2" s="372" t="n"/>
+      <c r="T2" s="372" t="n"/>
+      <c r="U2" s="372" t="n"/>
+      <c r="V2" s="372" t="n"/>
+      <c r="W2" s="372" t="n"/>
+      <c r="X2" s="372" t="n"/>
+      <c r="Y2" s="372" t="n"/>
+      <c r="Z2" s="372" t="n"/>
+      <c r="AA2" s="372" t="n"/>
+      <c r="AB2" s="372" t="n"/>
+      <c r="AC2" s="372" t="n"/>
+      <c r="AD2" s="372" t="n"/>
+      <c r="AE2" s="372" t="n"/>
+      <c r="AF2" s="372" t="n"/>
+      <c r="AG2" s="372" t="n"/>
+      <c r="AH2" s="372" t="n"/>
+      <c r="AI2" s="372" t="n"/>
+      <c r="AJ2" s="372" t="n"/>
+      <c r="AK2" s="372" t="n"/>
+      <c r="AL2" s="372" t="n"/>
+      <c r="AM2" s="372" t="n"/>
+      <c r="AN2" s="372" t="n"/>
+      <c r="AO2" s="372" t="n"/>
+      <c r="AP2" s="373" t="n"/>
+      <c r="AQ2" s="374" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="311" t="n"/>
-      <c r="AS2" s="311" t="n"/>
-      <c r="AT2" s="311" t="n"/>
-      <c r="AU2" s="311" t="n"/>
-      <c r="AV2" s="312" t="n"/>
-      <c r="AW2" s="313" t="inlineStr">
+      <c r="AR2" s="375" t="n"/>
+      <c r="AS2" s="375" t="n"/>
+      <c r="AT2" s="375" t="n"/>
+      <c r="AU2" s="375" t="n"/>
+      <c r="AV2" s="376" t="n"/>
+      <c r="AW2" s="377" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="311" t="n"/>
-      <c r="AY2" s="311" t="n"/>
-      <c r="AZ2" s="311" t="n"/>
-      <c r="BA2" s="311" t="n"/>
-      <c r="BB2" s="311" t="n"/>
-      <c r="BC2" s="311" t="n"/>
-      <c r="BD2" s="314" t="n"/>
+      <c r="AX2" s="378" t="n"/>
+      <c r="AY2" s="378" t="n"/>
+      <c r="AZ2" s="378" t="n"/>
+      <c r="BA2" s="378" t="n"/>
+      <c r="BB2" s="378" t="n"/>
+      <c r="BC2" s="378" t="n"/>
+      <c r="BD2" s="379" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="310" t="inlineStr">
+      <c r="A3" s="380" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="381" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="381" t="n"/>
+      <c r="AQ3" s="382" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="311" t="n"/>
-      <c r="AS3" s="311" t="n"/>
-      <c r="AT3" s="311" t="n"/>
-      <c r="AU3" s="311" t="n"/>
-      <c r="AV3" s="312" t="n"/>
-      <c r="AW3" s="313" t="inlineStr">
+      <c r="AR3" s="383" t="n"/>
+      <c r="AS3" s="383" t="n"/>
+      <c r="AT3" s="383" t="n"/>
+      <c r="AU3" s="383" t="n"/>
+      <c r="AV3" s="384" t="n"/>
+      <c r="AW3" s="279" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="311" t="n"/>
-      <c r="AY3" s="311" t="n"/>
-      <c r="AZ3" s="311" t="n"/>
-      <c r="BA3" s="311" t="n"/>
-      <c r="BB3" s="311" t="n"/>
-      <c r="BC3" s="311" t="n"/>
-      <c r="BD3" s="314" t="n"/>
+      <c r="AX3" s="385" t="n"/>
+      <c r="AY3" s="385" t="n"/>
+      <c r="AZ3" s="385" t="n"/>
+      <c r="BA3" s="385" t="n"/>
+      <c r="BB3" s="385" t="n"/>
+      <c r="BC3" s="385" t="n"/>
+      <c r="BD3" s="386" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="231" t="inlineStr">
+      <c r="A4" s="380" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="381" t="n"/>
+      <c r="L4" s="387" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="310" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="381" t="n"/>
+      <c r="AQ4" s="382" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="311" t="n"/>
-      <c r="AS4" s="311" t="n"/>
-      <c r="AT4" s="311" t="n"/>
-      <c r="AU4" s="311" t="n"/>
-      <c r="AV4" s="312" t="n"/>
-      <c r="AW4" s="313" t="inlineStr">
+      <c r="AR4" s="383" t="n"/>
+      <c r="AS4" s="383" t="n"/>
+      <c r="AT4" s="383" t="n"/>
+      <c r="AU4" s="383" t="n"/>
+      <c r="AV4" s="384" t="n"/>
+      <c r="AW4" s="279" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="311" t="n"/>
-      <c r="AY4" s="311" t="n"/>
-      <c r="AZ4" s="311" t="n"/>
-      <c r="BA4" s="311" t="n"/>
-      <c r="BB4" s="311" t="n"/>
-      <c r="BC4" s="311" t="n"/>
-      <c r="BD4" s="314" t="n"/>
+      <c r="AX4" s="385" t="n"/>
+      <c r="AY4" s="385" t="n"/>
+      <c r="AZ4" s="385" t="n"/>
+      <c r="BA4" s="385" t="n"/>
+      <c r="BB4" s="385" t="n"/>
+      <c r="BC4" s="385" t="n"/>
+      <c r="BD4" s="386" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="380" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="381" t="n"/>
+      <c r="L5" s="388" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="315" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="381" t="n"/>
+      <c r="AQ5" s="382" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="316" t="n"/>
-      <c r="AS5" s="316" t="n"/>
-      <c r="AT5" s="316" t="n"/>
-      <c r="AU5" s="316" t="n"/>
-      <c r="AV5" s="317" t="n"/>
-      <c r="AW5" s="318" t="inlineStr">
+      <c r="AR5" s="383" t="n"/>
+      <c r="AS5" s="383" t="n"/>
+      <c r="AT5" s="383" t="n"/>
+      <c r="AU5" s="383" t="n"/>
+      <c r="AV5" s="384" t="n"/>
+      <c r="AW5" s="279" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="316" t="n"/>
-      <c r="AY5" s="316" t="n"/>
-      <c r="AZ5" s="316" t="n"/>
-      <c r="BA5" s="316" t="n"/>
-      <c r="BB5" s="316" t="n"/>
-      <c r="BC5" s="316" t="n"/>
-      <c r="BD5" s="319" t="n"/>
+      <c r="AX5" s="385" t="n"/>
+      <c r="AY5" s="385" t="n"/>
+      <c r="AZ5" s="385" t="n"/>
+      <c r="BA5" s="385" t="n"/>
+      <c r="BB5" s="385" t="n"/>
+      <c r="BC5" s="385" t="n"/>
+      <c r="BD5" s="386" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="240" t="n"/>
-      <c r="B6" s="240" t="n"/>
-      <c r="C6" s="240" t="n"/>
-      <c r="D6" s="240" t="n"/>
-      <c r="E6" s="240" t="n"/>
-      <c r="F6" s="240" t="n"/>
-      <c r="G6" s="240" t="n"/>
-      <c r="H6" s="240" t="n"/>
-      <c r="I6" s="240" t="n"/>
-      <c r="J6" s="240" t="n"/>
-      <c r="K6" s="240" t="n"/>
-      <c r="L6" s="240" t="n"/>
-      <c r="M6" s="240" t="n"/>
-      <c r="N6" s="240" t="n"/>
-      <c r="O6" s="240" t="n"/>
-      <c r="P6" s="240" t="n"/>
-      <c r="Q6" s="240" t="n"/>
-      <c r="R6" s="240" t="n"/>
-      <c r="S6" s="240" t="n"/>
-      <c r="T6" s="240" t="n"/>
-      <c r="U6" s="240" t="n"/>
-      <c r="V6" s="240" t="n"/>
-      <c r="W6" s="240" t="n"/>
-      <c r="X6" s="240" t="n"/>
-      <c r="Y6" s="240" t="n"/>
-      <c r="Z6" s="240" t="n"/>
-      <c r="AA6" s="240" t="n"/>
-      <c r="AB6" s="240" t="n"/>
-      <c r="AC6" s="240" t="n"/>
-      <c r="AD6" s="240" t="n"/>
-      <c r="AE6" s="240" t="n"/>
-      <c r="AF6" s="240" t="n"/>
-      <c r="AG6" s="240" t="n"/>
-      <c r="AH6" s="240" t="n"/>
-      <c r="AI6" s="240" t="n"/>
-      <c r="AJ6" s="240" t="n"/>
-      <c r="AK6" s="240" t="n"/>
-      <c r="AL6" s="240" t="n"/>
-      <c r="AM6" s="240" t="n"/>
-      <c r="AN6" s="240" t="n"/>
-      <c r="AO6" s="240" t="n"/>
-      <c r="AP6" s="240" t="n"/>
-      <c r="AQ6" s="240" t="n"/>
-      <c r="AR6" s="240" t="n"/>
-      <c r="AS6" s="240" t="n"/>
-      <c r="AT6" s="240" t="n"/>
-      <c r="AU6" s="240" t="n"/>
-      <c r="AV6" s="240" t="n"/>
-      <c r="AW6" s="240" t="n"/>
-      <c r="AX6" s="240" t="n"/>
-      <c r="AY6" s="240" t="n"/>
-      <c r="AZ6" s="240" t="n"/>
-      <c r="BA6" s="240" t="n"/>
-      <c r="BB6" s="240" t="n"/>
-      <c r="BC6" s="240" t="n"/>
-      <c r="BD6" s="240" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="389" t="n"/>
+      <c r="B6" s="390" t="n"/>
+      <c r="C6" s="390" t="n"/>
+      <c r="D6" s="390" t="n"/>
+      <c r="E6" s="390" t="n"/>
+      <c r="F6" s="390" t="n"/>
+      <c r="G6" s="390" t="n"/>
+      <c r="H6" s="390" t="n"/>
+      <c r="I6" s="390" t="n"/>
+      <c r="J6" s="390" t="n"/>
+      <c r="K6" s="391" t="n"/>
+      <c r="L6" s="390" t="n"/>
+      <c r="M6" s="390" t="n"/>
+      <c r="N6" s="390" t="n"/>
+      <c r="O6" s="390" t="n"/>
+      <c r="P6" s="390" t="n"/>
+      <c r="Q6" s="390" t="n"/>
+      <c r="R6" s="390" t="n"/>
+      <c r="S6" s="390" t="n"/>
+      <c r="T6" s="390" t="n"/>
+      <c r="U6" s="390" t="n"/>
+      <c r="V6" s="390" t="n"/>
+      <c r="W6" s="390" t="n"/>
+      <c r="X6" s="390" t="n"/>
+      <c r="Y6" s="390" t="n"/>
+      <c r="Z6" s="390" t="n"/>
+      <c r="AA6" s="390" t="n"/>
+      <c r="AB6" s="390" t="n"/>
+      <c r="AC6" s="390" t="n"/>
+      <c r="AD6" s="390" t="n"/>
+      <c r="AE6" s="390" t="n"/>
+      <c r="AF6" s="390" t="n"/>
+      <c r="AG6" s="390" t="n"/>
+      <c r="AH6" s="390" t="n"/>
+      <c r="AI6" s="390" t="n"/>
+      <c r="AJ6" s="390" t="n"/>
+      <c r="AK6" s="390" t="n"/>
+      <c r="AL6" s="390" t="n"/>
+      <c r="AM6" s="390" t="n"/>
+      <c r="AN6" s="390" t="n"/>
+      <c r="AO6" s="390" t="n"/>
+      <c r="AP6" s="391" t="n"/>
+      <c r="AQ6" s="392" t="n"/>
+      <c r="AR6" s="392" t="n"/>
+      <c r="AS6" s="392" t="n"/>
+      <c r="AT6" s="392" t="n"/>
+      <c r="AU6" s="392" t="n"/>
+      <c r="AV6" s="393" t="n"/>
+      <c r="AW6" s="394" t="n"/>
+      <c r="AX6" s="394" t="n"/>
+      <c r="AY6" s="394" t="n"/>
+      <c r="AZ6" s="394" t="n"/>
+      <c r="BA6" s="394" t="n"/>
+      <c r="BB6" s="394" t="n"/>
+      <c r="BC6" s="394" t="n"/>
+      <c r="BD6" s="395" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="320" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="396" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="321" t="inlineStr">
@@ -9065,66 +9507,66 @@
       <c r="BD20" s="277" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="368" t="inlineStr">
+      <c r="A21" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="369" t="n"/>
-      <c r="C21" s="369" t="n"/>
-      <c r="D21" s="369" t="n"/>
-      <c r="E21" s="369" t="n"/>
-      <c r="F21" s="369" t="n"/>
-      <c r="G21" s="369" t="n"/>
-      <c r="H21" s="369" t="n"/>
-      <c r="I21" s="369" t="n"/>
-      <c r="J21" s="369" t="n"/>
-      <c r="K21" s="369" t="n"/>
-      <c r="L21" s="369" t="n"/>
-      <c r="M21" s="369" t="n"/>
-      <c r="N21" s="369" t="n"/>
-      <c r="O21" s="369" t="n"/>
-      <c r="P21" s="369" t="n"/>
-      <c r="Q21" s="369" t="n"/>
-      <c r="R21" s="369" t="n"/>
-      <c r="S21" s="369" t="n"/>
-      <c r="T21" s="369" t="n"/>
-      <c r="U21" s="369" t="n"/>
-      <c r="V21" s="369" t="n"/>
-      <c r="W21" s="369" t="n"/>
-      <c r="X21" s="369" t="n"/>
-      <c r="Y21" s="369" t="n"/>
-      <c r="Z21" s="369" t="n"/>
-      <c r="AA21" s="369" t="n"/>
-      <c r="AB21" s="369" t="n"/>
-      <c r="AC21" s="369" t="n"/>
-      <c r="AD21" s="369" t="n"/>
-      <c r="AE21" s="369" t="n"/>
-      <c r="AF21" s="369" t="n"/>
-      <c r="AG21" s="369" t="n"/>
-      <c r="AH21" s="369" t="n"/>
-      <c r="AI21" s="369" t="n"/>
-      <c r="AJ21" s="369" t="n"/>
-      <c r="AK21" s="369" t="n"/>
-      <c r="AL21" s="369" t="n"/>
-      <c r="AM21" s="369" t="n"/>
-      <c r="AN21" s="369" t="n"/>
-      <c r="AO21" s="369" t="n"/>
-      <c r="AP21" s="369" t="n"/>
-      <c r="AQ21" s="369" t="n"/>
-      <c r="AR21" s="369" t="n"/>
-      <c r="AS21" s="369" t="n"/>
-      <c r="AT21" s="369" t="n"/>
-      <c r="AU21" s="369" t="n"/>
-      <c r="AV21" s="369" t="n"/>
-      <c r="AW21" s="369" t="n"/>
-      <c r="AX21" s="369" t="n"/>
-      <c r="AY21" s="369" t="n"/>
-      <c r="AZ21" s="369" t="n"/>
-      <c r="BA21" s="369" t="n"/>
-      <c r="BB21" s="369" t="n"/>
-      <c r="BC21" s="369" t="n"/>
-      <c r="BD21" s="370" t="n"/>
+      <c r="B21" s="397" t="n"/>
+      <c r="C21" s="397" t="n"/>
+      <c r="D21" s="397" t="n"/>
+      <c r="E21" s="397" t="n"/>
+      <c r="F21" s="397" t="n"/>
+      <c r="G21" s="397" t="n"/>
+      <c r="H21" s="397" t="n"/>
+      <c r="I21" s="397" t="n"/>
+      <c r="J21" s="397" t="n"/>
+      <c r="K21" s="397" t="n"/>
+      <c r="L21" s="397" t="n"/>
+      <c r="M21" s="397" t="n"/>
+      <c r="N21" s="397" t="n"/>
+      <c r="O21" s="397" t="n"/>
+      <c r="P21" s="397" t="n"/>
+      <c r="Q21" s="397" t="n"/>
+      <c r="R21" s="397" t="n"/>
+      <c r="S21" s="397" t="n"/>
+      <c r="T21" s="397" t="n"/>
+      <c r="U21" s="397" t="n"/>
+      <c r="V21" s="397" t="n"/>
+      <c r="W21" s="397" t="n"/>
+      <c r="X21" s="397" t="n"/>
+      <c r="Y21" s="397" t="n"/>
+      <c r="Z21" s="397" t="n"/>
+      <c r="AA21" s="397" t="n"/>
+      <c r="AB21" s="397" t="n"/>
+      <c r="AC21" s="397" t="n"/>
+      <c r="AD21" s="397" t="n"/>
+      <c r="AE21" s="397" t="n"/>
+      <c r="AF21" s="397" t="n"/>
+      <c r="AG21" s="397" t="n"/>
+      <c r="AH21" s="397" t="n"/>
+      <c r="AI21" s="397" t="n"/>
+      <c r="AJ21" s="397" t="n"/>
+      <c r="AK21" s="397" t="n"/>
+      <c r="AL21" s="397" t="n"/>
+      <c r="AM21" s="397" t="n"/>
+      <c r="AN21" s="397" t="n"/>
+      <c r="AO21" s="397" t="n"/>
+      <c r="AP21" s="397" t="n"/>
+      <c r="AQ21" s="397" t="n"/>
+      <c r="AR21" s="397" t="n"/>
+      <c r="AS21" s="397" t="n"/>
+      <c r="AT21" s="397" t="n"/>
+      <c r="AU21" s="397" t="n"/>
+      <c r="AV21" s="397" t="n"/>
+      <c r="AW21" s="397" t="n"/>
+      <c r="AX21" s="397" t="n"/>
+      <c r="AY21" s="397" t="n"/>
+      <c r="AZ21" s="397" t="n"/>
+      <c r="BA21" s="397" t="n"/>
+      <c r="BB21" s="397" t="n"/>
+      <c r="BC21" s="397" t="n"/>
+      <c r="BD21" s="398" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -9476,7 +9918,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="306" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -9488,7 +9930,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="288" t="inlineStr">
+      <c r="L1" s="407" t="inlineStr">
         <is>
           <t>CUSTOMER CSR REGISTER — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -9522,7 +9964,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="362" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -9547,286 +9989,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="364" t="inlineStr">
+      <c r="A2" s="371" t="n"/>
+      <c r="B2" s="372" t="n"/>
+      <c r="C2" s="372" t="n"/>
+      <c r="D2" s="372" t="n"/>
+      <c r="E2" s="372" t="n"/>
+      <c r="F2" s="372" t="n"/>
+      <c r="G2" s="372" t="n"/>
+      <c r="H2" s="372" t="n"/>
+      <c r="I2" s="372" t="n"/>
+      <c r="J2" s="372" t="n"/>
+      <c r="K2" s="373" t="n"/>
+      <c r="L2" s="372" t="n"/>
+      <c r="M2" s="372" t="n"/>
+      <c r="N2" s="372" t="n"/>
+      <c r="O2" s="372" t="n"/>
+      <c r="P2" s="372" t="n"/>
+      <c r="Q2" s="372" t="n"/>
+      <c r="R2" s="372" t="n"/>
+      <c r="S2" s="372" t="n"/>
+      <c r="T2" s="372" t="n"/>
+      <c r="U2" s="372" t="n"/>
+      <c r="V2" s="372" t="n"/>
+      <c r="W2" s="372" t="n"/>
+      <c r="X2" s="372" t="n"/>
+      <c r="Y2" s="372" t="n"/>
+      <c r="Z2" s="372" t="n"/>
+      <c r="AA2" s="372" t="n"/>
+      <c r="AB2" s="372" t="n"/>
+      <c r="AC2" s="372" t="n"/>
+      <c r="AD2" s="372" t="n"/>
+      <c r="AE2" s="372" t="n"/>
+      <c r="AF2" s="372" t="n"/>
+      <c r="AG2" s="372" t="n"/>
+      <c r="AH2" s="372" t="n"/>
+      <c r="AI2" s="372" t="n"/>
+      <c r="AJ2" s="372" t="n"/>
+      <c r="AK2" s="372" t="n"/>
+      <c r="AL2" s="372" t="n"/>
+      <c r="AM2" s="372" t="n"/>
+      <c r="AN2" s="372" t="n"/>
+      <c r="AO2" s="372" t="n"/>
+      <c r="AP2" s="373" t="n"/>
+      <c r="AQ2" s="374" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="311" t="n"/>
-      <c r="AS2" s="311" t="n"/>
-      <c r="AT2" s="311" t="n"/>
-      <c r="AU2" s="311" t="n"/>
-      <c r="AV2" s="312" t="n"/>
-      <c r="AW2" s="365" t="inlineStr">
+      <c r="AR2" s="375" t="n"/>
+      <c r="AS2" s="375" t="n"/>
+      <c r="AT2" s="375" t="n"/>
+      <c r="AU2" s="375" t="n"/>
+      <c r="AV2" s="376" t="n"/>
+      <c r="AW2" s="377" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="311" t="n"/>
-      <c r="AY2" s="311" t="n"/>
-      <c r="AZ2" s="311" t="n"/>
-      <c r="BA2" s="311" t="n"/>
-      <c r="BB2" s="311" t="n"/>
-      <c r="BC2" s="311" t="n"/>
-      <c r="BD2" s="314" t="n"/>
+      <c r="AX2" s="378" t="n"/>
+      <c r="AY2" s="378" t="n"/>
+      <c r="AZ2" s="378" t="n"/>
+      <c r="BA2" s="378" t="n"/>
+      <c r="BB2" s="378" t="n"/>
+      <c r="BC2" s="378" t="n"/>
+      <c r="BD2" s="379" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="364" t="inlineStr">
+      <c r="A3" s="380" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="381" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="381" t="n"/>
+      <c r="AQ3" s="382" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="311" t="n"/>
-      <c r="AS3" s="311" t="n"/>
-      <c r="AT3" s="311" t="n"/>
-      <c r="AU3" s="311" t="n"/>
-      <c r="AV3" s="312" t="n"/>
-      <c r="AW3" s="365" t="inlineStr">
+      <c r="AR3" s="383" t="n"/>
+      <c r="AS3" s="383" t="n"/>
+      <c r="AT3" s="383" t="n"/>
+      <c r="AU3" s="383" t="n"/>
+      <c r="AV3" s="384" t="n"/>
+      <c r="AW3" s="279" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="311" t="n"/>
-      <c r="AY3" s="311" t="n"/>
-      <c r="AZ3" s="311" t="n"/>
-      <c r="BA3" s="311" t="n"/>
-      <c r="BB3" s="311" t="n"/>
-      <c r="BC3" s="311" t="n"/>
-      <c r="BD3" s="314" t="n"/>
+      <c r="AX3" s="385" t="n"/>
+      <c r="AY3" s="385" t="n"/>
+      <c r="AZ3" s="385" t="n"/>
+      <c r="BA3" s="385" t="n"/>
+      <c r="BB3" s="385" t="n"/>
+      <c r="BC3" s="385" t="n"/>
+      <c r="BD3" s="386" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="41" t="inlineStr">
+      <c r="A4" s="380" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="381" t="n"/>
+      <c r="L4" s="387" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="364" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="381" t="n"/>
+      <c r="AQ4" s="382" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="311" t="n"/>
-      <c r="AS4" s="311" t="n"/>
-      <c r="AT4" s="311" t="n"/>
-      <c r="AU4" s="311" t="n"/>
-      <c r="AV4" s="312" t="n"/>
-      <c r="AW4" s="365" t="inlineStr">
+      <c r="AR4" s="383" t="n"/>
+      <c r="AS4" s="383" t="n"/>
+      <c r="AT4" s="383" t="n"/>
+      <c r="AU4" s="383" t="n"/>
+      <c r="AV4" s="384" t="n"/>
+      <c r="AW4" s="279" t="inlineStr">
         <is>
           <t>QMS</t>
         </is>
       </c>
-      <c r="AX4" s="311" t="n"/>
-      <c r="AY4" s="311" t="n"/>
-      <c r="AZ4" s="311" t="n"/>
-      <c r="BA4" s="311" t="n"/>
-      <c r="BB4" s="311" t="n"/>
-      <c r="BC4" s="311" t="n"/>
-      <c r="BD4" s="314" t="n"/>
+      <c r="AX4" s="385" t="n"/>
+      <c r="AY4" s="385" t="n"/>
+      <c r="AZ4" s="385" t="n"/>
+      <c r="BA4" s="385" t="n"/>
+      <c r="BB4" s="385" t="n"/>
+      <c r="BC4" s="385" t="n"/>
+      <c r="BD4" s="386" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="380" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="381" t="n"/>
+      <c r="L5" s="388" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="366" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="381" t="n"/>
+      <c r="AQ5" s="382" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="316" t="n"/>
-      <c r="AS5" s="316" t="n"/>
-      <c r="AT5" s="316" t="n"/>
-      <c r="AU5" s="316" t="n"/>
-      <c r="AV5" s="317" t="n"/>
-      <c r="AW5" s="367" t="inlineStr">
+      <c r="AR5" s="383" t="n"/>
+      <c r="AS5" s="383" t="n"/>
+      <c r="AT5" s="383" t="n"/>
+      <c r="AU5" s="383" t="n"/>
+      <c r="AV5" s="384" t="n"/>
+      <c r="AW5" s="279" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="316" t="n"/>
-      <c r="AY5" s="316" t="n"/>
-      <c r="AZ5" s="316" t="n"/>
-      <c r="BA5" s="316" t="n"/>
-      <c r="BB5" s="316" t="n"/>
-      <c r="BC5" s="316" t="n"/>
-      <c r="BD5" s="319" t="n"/>
+      <c r="AX5" s="385" t="n"/>
+      <c r="AY5" s="385" t="n"/>
+      <c r="AZ5" s="385" t="n"/>
+      <c r="BA5" s="385" t="n"/>
+      <c r="BB5" s="385" t="n"/>
+      <c r="BC5" s="385" t="n"/>
+      <c r="BD5" s="386" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="277" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="389" t="n"/>
+      <c r="B6" s="399" t="n"/>
+      <c r="C6" s="399" t="n"/>
+      <c r="D6" s="399" t="n"/>
+      <c r="E6" s="399" t="n"/>
+      <c r="F6" s="399" t="n"/>
+      <c r="G6" s="399" t="n"/>
+      <c r="H6" s="399" t="n"/>
+      <c r="I6" s="399" t="n"/>
+      <c r="J6" s="399" t="n"/>
+      <c r="K6" s="400" t="n"/>
+      <c r="L6" s="399" t="n"/>
+      <c r="M6" s="399" t="n"/>
+      <c r="N6" s="399" t="n"/>
+      <c r="O6" s="399" t="n"/>
+      <c r="P6" s="399" t="n"/>
+      <c r="Q6" s="399" t="n"/>
+      <c r="R6" s="399" t="n"/>
+      <c r="S6" s="399" t="n"/>
+      <c r="T6" s="399" t="n"/>
+      <c r="U6" s="399" t="n"/>
+      <c r="V6" s="399" t="n"/>
+      <c r="W6" s="399" t="n"/>
+      <c r="X6" s="399" t="n"/>
+      <c r="Y6" s="399" t="n"/>
+      <c r="Z6" s="399" t="n"/>
+      <c r="AA6" s="399" t="n"/>
+      <c r="AB6" s="399" t="n"/>
+      <c r="AC6" s="399" t="n"/>
+      <c r="AD6" s="399" t="n"/>
+      <c r="AE6" s="399" t="n"/>
+      <c r="AF6" s="399" t="n"/>
+      <c r="AG6" s="399" t="n"/>
+      <c r="AH6" s="399" t="n"/>
+      <c r="AI6" s="399" t="n"/>
+      <c r="AJ6" s="399" t="n"/>
+      <c r="AK6" s="399" t="n"/>
+      <c r="AL6" s="399" t="n"/>
+      <c r="AM6" s="399" t="n"/>
+      <c r="AN6" s="399" t="n"/>
+      <c r="AO6" s="399" t="n"/>
+      <c r="AP6" s="400" t="n"/>
+      <c r="AQ6" s="401" t="n"/>
+      <c r="AR6" s="401" t="n"/>
+      <c r="AS6" s="401" t="n"/>
+      <c r="AT6" s="401" t="n"/>
+      <c r="AU6" s="401" t="n"/>
+      <c r="AV6" s="402" t="n"/>
+      <c r="AW6" s="403" t="n"/>
+      <c r="AX6" s="403" t="n"/>
+      <c r="AY6" s="403" t="n"/>
+      <c r="AZ6" s="403" t="n"/>
+      <c r="BA6" s="403" t="n"/>
+      <c r="BB6" s="403" t="n"/>
+      <c r="BC6" s="403" t="n"/>
+      <c r="BD6" s="404" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="405" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="368" t="inlineStr">
+      <c r="A8" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="369" t="n"/>
-      <c r="C8" s="369" t="n"/>
-      <c r="D8" s="369" t="n"/>
-      <c r="E8" s="369" t="n"/>
-      <c r="F8" s="369" t="n"/>
-      <c r="G8" s="369" t="n"/>
-      <c r="H8" s="369" t="n"/>
-      <c r="I8" s="369" t="n"/>
-      <c r="J8" s="369" t="n"/>
-      <c r="K8" s="369" t="n"/>
-      <c r="L8" s="369" t="n"/>
-      <c r="M8" s="369" t="n"/>
-      <c r="N8" s="369" t="n"/>
-      <c r="O8" s="369" t="n"/>
-      <c r="P8" s="369" t="n"/>
-      <c r="Q8" s="369" t="n"/>
-      <c r="R8" s="369" t="n"/>
-      <c r="S8" s="369" t="n"/>
-      <c r="T8" s="369" t="n"/>
-      <c r="U8" s="369" t="n"/>
-      <c r="V8" s="369" t="n"/>
-      <c r="W8" s="369" t="n"/>
-      <c r="X8" s="369" t="n"/>
-      <c r="Y8" s="369" t="n"/>
-      <c r="Z8" s="369" t="n"/>
-      <c r="AA8" s="369" t="n"/>
-      <c r="AB8" s="369" t="n"/>
-      <c r="AC8" s="369" t="n"/>
-      <c r="AD8" s="369" t="n"/>
-      <c r="AE8" s="369" t="n"/>
-      <c r="AF8" s="369" t="n"/>
-      <c r="AG8" s="369" t="n"/>
-      <c r="AH8" s="369" t="n"/>
-      <c r="AI8" s="369" t="n"/>
-      <c r="AJ8" s="369" t="n"/>
-      <c r="AK8" s="369" t="n"/>
-      <c r="AL8" s="369" t="n"/>
-      <c r="AM8" s="369" t="n"/>
-      <c r="AN8" s="369" t="n"/>
-      <c r="AO8" s="369" t="n"/>
-      <c r="AP8" s="369" t="n"/>
-      <c r="AQ8" s="369" t="n"/>
-      <c r="AR8" s="369" t="n"/>
-      <c r="AS8" s="369" t="n"/>
-      <c r="AT8" s="369" t="n"/>
-      <c r="AU8" s="369" t="n"/>
-      <c r="AV8" s="369" t="n"/>
-      <c r="AW8" s="369" t="n"/>
-      <c r="AX8" s="369" t="n"/>
-      <c r="AY8" s="369" t="n"/>
-      <c r="AZ8" s="369" t="n"/>
-      <c r="BA8" s="369" t="n"/>
-      <c r="BB8" s="369" t="n"/>
-      <c r="BC8" s="369" t="n"/>
-      <c r="BD8" s="370" t="n"/>
+      <c r="B8" s="397" t="n"/>
+      <c r="C8" s="397" t="n"/>
+      <c r="D8" s="397" t="n"/>
+      <c r="E8" s="397" t="n"/>
+      <c r="F8" s="397" t="n"/>
+      <c r="G8" s="397" t="n"/>
+      <c r="H8" s="397" t="n"/>
+      <c r="I8" s="397" t="n"/>
+      <c r="J8" s="397" t="n"/>
+      <c r="K8" s="397" t="n"/>
+      <c r="L8" s="397" t="n"/>
+      <c r="M8" s="397" t="n"/>
+      <c r="N8" s="397" t="n"/>
+      <c r="O8" s="397" t="n"/>
+      <c r="P8" s="397" t="n"/>
+      <c r="Q8" s="397" t="n"/>
+      <c r="R8" s="397" t="n"/>
+      <c r="S8" s="397" t="n"/>
+      <c r="T8" s="397" t="n"/>
+      <c r="U8" s="397" t="n"/>
+      <c r="V8" s="397" t="n"/>
+      <c r="W8" s="397" t="n"/>
+      <c r="X8" s="397" t="n"/>
+      <c r="Y8" s="397" t="n"/>
+      <c r="Z8" s="397" t="n"/>
+      <c r="AA8" s="397" t="n"/>
+      <c r="AB8" s="397" t="n"/>
+      <c r="AC8" s="397" t="n"/>
+      <c r="AD8" s="397" t="n"/>
+      <c r="AE8" s="397" t="n"/>
+      <c r="AF8" s="397" t="n"/>
+      <c r="AG8" s="397" t="n"/>
+      <c r="AH8" s="397" t="n"/>
+      <c r="AI8" s="397" t="n"/>
+      <c r="AJ8" s="397" t="n"/>
+      <c r="AK8" s="397" t="n"/>
+      <c r="AL8" s="397" t="n"/>
+      <c r="AM8" s="397" t="n"/>
+      <c r="AN8" s="397" t="n"/>
+      <c r="AO8" s="397" t="n"/>
+      <c r="AP8" s="397" t="n"/>
+      <c r="AQ8" s="397" t="n"/>
+      <c r="AR8" s="397" t="n"/>
+      <c r="AS8" s="397" t="n"/>
+      <c r="AT8" s="397" t="n"/>
+      <c r="AU8" s="397" t="n"/>
+      <c r="AV8" s="397" t="n"/>
+      <c r="AW8" s="397" t="n"/>
+      <c r="AX8" s="397" t="n"/>
+      <c r="AY8" s="397" t="n"/>
+      <c r="AZ8" s="397" t="n"/>
+      <c r="BA8" s="397" t="n"/>
+      <c r="BB8" s="397" t="n"/>
+      <c r="BC8" s="397" t="n"/>
+      <c r="BD8" s="398" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="267" t="inlineStr">
@@ -11199,66 +11809,66 @@
       <c r="BD21" s="305" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="368" t="inlineStr">
+      <c r="A22" s="296" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="369" t="n"/>
-      <c r="C22" s="369" t="n"/>
-      <c r="D22" s="369" t="n"/>
-      <c r="E22" s="369" t="n"/>
-      <c r="F22" s="369" t="n"/>
-      <c r="G22" s="369" t="n"/>
-      <c r="H22" s="369" t="n"/>
-      <c r="I22" s="369" t="n"/>
-      <c r="J22" s="369" t="n"/>
-      <c r="K22" s="369" t="n"/>
-      <c r="L22" s="369" t="n"/>
-      <c r="M22" s="369" t="n"/>
-      <c r="N22" s="369" t="n"/>
-      <c r="O22" s="369" t="n"/>
-      <c r="P22" s="369" t="n"/>
-      <c r="Q22" s="369" t="n"/>
-      <c r="R22" s="369" t="n"/>
-      <c r="S22" s="369" t="n"/>
-      <c r="T22" s="369" t="n"/>
-      <c r="U22" s="369" t="n"/>
-      <c r="V22" s="369" t="n"/>
-      <c r="W22" s="369" t="n"/>
-      <c r="X22" s="369" t="n"/>
-      <c r="Y22" s="369" t="n"/>
-      <c r="Z22" s="369" t="n"/>
-      <c r="AA22" s="369" t="n"/>
-      <c r="AB22" s="369" t="n"/>
-      <c r="AC22" s="369" t="n"/>
-      <c r="AD22" s="369" t="n"/>
-      <c r="AE22" s="369" t="n"/>
-      <c r="AF22" s="369" t="n"/>
-      <c r="AG22" s="369" t="n"/>
-      <c r="AH22" s="369" t="n"/>
-      <c r="AI22" s="369" t="n"/>
-      <c r="AJ22" s="369" t="n"/>
-      <c r="AK22" s="369" t="n"/>
-      <c r="AL22" s="369" t="n"/>
-      <c r="AM22" s="369" t="n"/>
-      <c r="AN22" s="369" t="n"/>
-      <c r="AO22" s="369" t="n"/>
-      <c r="AP22" s="369" t="n"/>
-      <c r="AQ22" s="369" t="n"/>
-      <c r="AR22" s="369" t="n"/>
-      <c r="AS22" s="369" t="n"/>
-      <c r="AT22" s="369" t="n"/>
-      <c r="AU22" s="369" t="n"/>
-      <c r="AV22" s="369" t="n"/>
-      <c r="AW22" s="369" t="n"/>
-      <c r="AX22" s="369" t="n"/>
-      <c r="AY22" s="369" t="n"/>
-      <c r="AZ22" s="369" t="n"/>
-      <c r="BA22" s="369" t="n"/>
-      <c r="BB22" s="369" t="n"/>
-      <c r="BC22" s="369" t="n"/>
-      <c r="BD22" s="370" t="n"/>
+      <c r="B22" s="397" t="n"/>
+      <c r="C22" s="397" t="n"/>
+      <c r="D22" s="397" t="n"/>
+      <c r="E22" s="397" t="n"/>
+      <c r="F22" s="397" t="n"/>
+      <c r="G22" s="397" t="n"/>
+      <c r="H22" s="397" t="n"/>
+      <c r="I22" s="397" t="n"/>
+      <c r="J22" s="397" t="n"/>
+      <c r="K22" s="397" t="n"/>
+      <c r="L22" s="397" t="n"/>
+      <c r="M22" s="397" t="n"/>
+      <c r="N22" s="397" t="n"/>
+      <c r="O22" s="397" t="n"/>
+      <c r="P22" s="397" t="n"/>
+      <c r="Q22" s="397" t="n"/>
+      <c r="R22" s="397" t="n"/>
+      <c r="S22" s="397" t="n"/>
+      <c r="T22" s="397" t="n"/>
+      <c r="U22" s="397" t="n"/>
+      <c r="V22" s="397" t="n"/>
+      <c r="W22" s="397" t="n"/>
+      <c r="X22" s="397" t="n"/>
+      <c r="Y22" s="397" t="n"/>
+      <c r="Z22" s="397" t="n"/>
+      <c r="AA22" s="397" t="n"/>
+      <c r="AB22" s="397" t="n"/>
+      <c r="AC22" s="397" t="n"/>
+      <c r="AD22" s="397" t="n"/>
+      <c r="AE22" s="397" t="n"/>
+      <c r="AF22" s="397" t="n"/>
+      <c r="AG22" s="397" t="n"/>
+      <c r="AH22" s="397" t="n"/>
+      <c r="AI22" s="397" t="n"/>
+      <c r="AJ22" s="397" t="n"/>
+      <c r="AK22" s="397" t="n"/>
+      <c r="AL22" s="397" t="n"/>
+      <c r="AM22" s="397" t="n"/>
+      <c r="AN22" s="397" t="n"/>
+      <c r="AO22" s="397" t="n"/>
+      <c r="AP22" s="397" t="n"/>
+      <c r="AQ22" s="397" t="n"/>
+      <c r="AR22" s="397" t="n"/>
+      <c r="AS22" s="397" t="n"/>
+      <c r="AT22" s="397" t="n"/>
+      <c r="AU22" s="397" t="n"/>
+      <c r="AV22" s="397" t="n"/>
+      <c r="AW22" s="397" t="n"/>
+      <c r="AX22" s="397" t="n"/>
+      <c r="AY22" s="397" t="n"/>
+      <c r="AZ22" s="397" t="n"/>
+      <c r="BA22" s="397" t="n"/>
+      <c r="BB22" s="397" t="n"/>
+      <c r="BC22" s="397" t="n"/>
+      <c r="BD22" s="398" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -826,6 +826,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3592,7 +3595,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="246">
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="Z23:AF23"/>
@@ -5484,7 +5486,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="69">
     <mergeCell ref="AJ15:AS15"/>
     <mergeCell ref="L4:AP4"/>
@@ -7009,7 +7010,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -1357,7 +1357,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>QA / QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1427,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -4240,7 +4240,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>QA / QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -4310,7 +4310,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -5809,7 +5809,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>QA / QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5879,7 +5879,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -7352,7 +7352,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>QA / QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -7422,7 +7422,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>

--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRReg" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRFlags" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_CSRFlags" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM125_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM125_CSRReg'!$1:$13</definedName>
@@ -812,7 +814,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1271,7 +1273,7 @@
       <c r="AV2" s="37" t="n"/>
       <c r="AW2" s="38" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="36" t="n"/>
@@ -1327,7 +1329,7 @@
       <c r="AV3" s="37" t="n"/>
       <c r="AW3" s="38" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="36" t="n"/>
@@ -1357,7 +1359,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QA / QMS</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1429,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -1638,7 +1640,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Review Period</t>
+          <t>Linked FRM-122</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1670,7 +1672,7 @@
       <c r="AB10" s="27" t="n"/>
       <c r="AC10" s="19" t="inlineStr">
         <is>
-          <t>Prepared Date</t>
+          <t>Ref: SOP-101</t>
         </is>
       </c>
       <c r="AD10" s="6" t="n"/>
@@ -1682,7 +1684,11 @@
       <c r="AJ10" s="6" t="n"/>
       <c r="AK10" s="6" t="n"/>
       <c r="AL10" s="7" t="n"/>
-      <c r="AM10" s="22" t="n"/>
+      <c r="AM10" s="22" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN10" s="26" t="n"/>
       <c r="AO10" s="26" t="n"/>
       <c r="AP10" s="26" t="n"/>
@@ -3595,6 +3601,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="246">
     <mergeCell ref="C25:H25"/>
     <mergeCell ref="Z23:AF23"/>
@@ -4240,7 +4247,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QA / QMS</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -4310,7 +4317,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -5486,6 +5493,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="69">
     <mergeCell ref="AJ15:AS15"/>
     <mergeCell ref="L4:AP4"/>
@@ -5809,7 +5817,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QA / QMS</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5879,7 +5887,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -7010,6 +7018,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>
@@ -7352,7 +7361,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>QA / QMS</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -7422,7 +7431,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -8726,4 +8735,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-122; Parent ref: SOP-101</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
+++ b/04-Bieu-Mau/01-FRM-100/FRM-125_Customer_CSR_Register.xlsx
@@ -757,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="245">
+  <borders count="246">
     <border>
       <left/>
       <right/>
@@ -3511,12 +3511,16 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="494">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4707,6 +4711,7 @@
     <xf numFmtId="0" fontId="82" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4783,6 +4788,43 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Khách hàng
+Tên khách hàng có yêu cầu đặc biệt (CSR).</t>
+      </text>
+    </comment>
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <t>Yêu cầu đặc biệt của khách hàng
+Customer-Specific Requirements: yêu cầu riêng ngoài tiêu chuẩn.
+Ví dụ: ASML yêu cầu cleanliness Class 5, Applied Materials yêu cầu passivation.</t>
+      </text>
+    </comment>
+    <comment ref="AG9" authorId="0" shapeId="0">
+      <text>
+        <t>Trạng thái
+ACTIVE = đang áp dụng.
+CLOSED = không còn hiệu lực.
+PENDING = đang đánh giá.</t>
+      </text>
+    </comment>
+    <comment ref="AQ9" authorId="0" shapeId="0">
+      <text>
+        <t>Bằng chứng / Hành động
+Ghi tham chiếu đến bằng chứng tuân thủ hoặc hành động cần thực hiện.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4806,6 +4848,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5417,7 +5462,7 @@
       <c r="BD6" s="30" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="494" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -6515,7 +6560,7 @@
       <c r="BD24" s="492" t="n"/>
     </row>
     <row r="25" ht="4" customHeight="1" s="264">
-      <c r="A25" s="469" t="n"/>
+      <c r="A25" s="494" t="n"/>
       <c r="B25" s="26" t="n"/>
       <c r="C25" s="26" t="n"/>
       <c r="D25" s="26" t="n"/>
@@ -6575,7 +6620,7 @@
     <row r="26" ht="24" customHeight="1" s="264">
       <c r="A26" s="493" t="inlineStr">
         <is>
-          <t>NOTICE — Ref: SOP-101. Retain: 5 years.</t>
+          <t>NOTICE — Update when receiving new customer requirements. Ref: SOP-101. Retain: 5 years.</t>
         </is>
       </c>
       <c r="B26" s="471" t="n"/>
@@ -6738,6 +6783,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
